--- a/data/consistency-check-datasets/screening/annotated_screening_dataset.xlsx
+++ b/data/consistency-check-datasets/screening/annotated_screening_dataset.xlsx
@@ -8,7 +8,7 @@
     <sheet state="visible" name="search-sample" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'train-sample'!$A$1:$H$101</definedName>
+    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'train-sample'!$A$1:$I$101</definedName>
     <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'search-sample'!$A$1:$G$401</definedName>
   </definedNames>
   <calcPr/>
@@ -87,7 +87,7 @@
         <rFont val="Arial"/>
         <color theme="1"/>
       </rPr>
-      <t xml:space="preserve">A sample of </t>
+      <t xml:space="preserve">A random sample of </t>
     </r>
     <r>
       <rPr>
@@ -119,7 +119,7 @@
       </rPr>
       <t xml:space="preserve"> of the screening dataset was drawn and manually coded after reading titles and abstracts. 
 In their original source, each of these records was adopted from a previously published review, where it had been read in full and marked "Eligible" by the review authors. Here, we re-read the titles and abstracts of these records in line with our eligibility criteria and relabelled them to measure consistency.
-["ELIGIBLE"] = 79 ; ["NOT_ELIGIBLE"] = 21</t>
+</t>
     </r>
   </si>
   <si>
@@ -149,8 +149,7 @@
         <rFont val="Arial"/>
         <color theme="1"/>
       </rPr>
-      <t xml:space="preserve"> was manually coded after reading titles and abstracts.
-["ELIGIBLE"]= 121, ["NOT_ELIGIBLE"]= 279</t>
+      <t xml:space="preserve"> was manually coded after reading titles and abstracts.</t>
     </r>
   </si>
   <si>
@@ -187,783 +186,49 @@
     <t>eligibility</t>
   </si>
   <si>
-    <t>WOS:000399848100008</t>
-  </si>
-  <si>
-    <t>Combined effects of climate and land management on watershed vegetation dynamics in an arid environment</t>
-  </si>
-  <si>
-    <t>Leaf area index (LAI) is a key parameter to characterize vegetation dynamics and ecosystem structure that determines the ecosystem functions and services such as clean water supply and carbon sequestration in a watershed. However, linking LAI dynamics and environmental controls (i.e., coupling biosphere, atmosphere, and anthroposphere) remains challenging and such type of studies have rarely been done at a watershed scale due to data availability. The present study examined the spatial and temporal variations of LAI for five ecosystem types within a watershed with a complex topography in the Upper Heihe River Basin, a major inland river in the arid and semi-arid western China. We integrated remote sensing-based GLASS (Global Land Surface Satellite) LAI products, interpolated climate data, watershed characteristics, and land management records for the period of 2001-2012. We determined the relationships among LAI, topography, air temperature and precipitation, and grazing history by five ecosystem types using several advanced statistical methods. We show that long-term mean LAI distribution had an obvious vertical pattern as controlled by precipitation and temperature in a hilly watershed. Overall, watershed-wide mean LAI had an increasing trend overtime for all ecosystem types during 2001-2012, presumably as a result of global warming and a wetting climate. However, the fluctuations of observed LAI at a pixel scale (1 km) varied greatly across the watershed. We classified the vegetation changes within the watershed as 'Improved', 'Stabilized', and 'Degraded' according their respective LAI changes. We found that climate was not the only driver for temporal vegetation changes for all land cover types. Grazing partially contributed to the decline of LAI in some areas and masked the positive climate warming effects in other areas. Extreme weathers such as cold spells and droughts could substantially affect inter-annual variability of LAI dynamics. We concluded that temporal and spatial LAI dynamics were rather complex and were affected by both climate variations and human disturbances in the study basin. Future monitoring studies should focus on the functional interactions among vegetation dynamics, climate variations, land management, and human disturbances. Published by Elsevier B.V.</t>
-  </si>
-  <si>
-    <t>10.1016/j.scitotenv.2017.02.210</t>
-  </si>
-  <si>
-    <t>Jaureguiberry et al</t>
-  </si>
-  <si>
-    <t xml:space="preserve">vegetation dynamics linked to effects from cc and land mgt </t>
+    <t>Assessing risks to marine ecosystems with indicators, ecosystem models and experts</t>
+  </si>
+  <si>
+    <t>Assessing risks to marine ecosystems is critical due to their biological and economic importance, and because many have recently undergone regime shifts due to overfishing and environmental change. Yet defining collapsed ecosystem states, selecting informative indicators and reconstructing long-term marine ecosystem changes remains challenging. The IUCN Red List of Ecosystems constitutes the global standard for quantifying risks to ecosystems and we conducted the first Red List assessment of an offshore marine ecosystem, focusing on the southern Benguela in South Africa. We used an analogous but collapsed ecosystem – the northern Benguela – to help define collapse in the southern Benguela and derived collapse thresholds with structured expert elicitation (i.e. repeatable estimation by expert judgment). To capture complex ecosystem dynamics and reconstruct historical ecosystem states, we used environmental indicators as well as survey-, catch- and model-based indicators. We listed the ecosystem in 1960 and 2015 as Endangered, with assessment outcomes robust to alternative model parametrizations. While many indicators improved between 1960 and 2015, seabird populations have suffered large declines since 1900 and remain at risk, pointing towards ongoing management priorities. Catch-based indicators often over-estimated risks compared to survey- and model-based indicators, warning against listing ecosystems as threatened solely based on indicators of pressure. We show that risk assessments provide a framework for interpreting data from indicators, ecosystem models and experts to inform the management of marine ecosystems. This work highlights the feasibility of conducting Red List of Ecosystems assessments for marine ecosystems.</t>
+  </si>
+  <si>
+    <t>na</t>
+  </si>
+  <si>
+    <t>RLE Database</t>
+  </si>
+  <si>
+    <t>risk assessment of marine ecosystem with overfishing and environmental change</t>
   </si>
   <si>
     <t>["ELIGIBLE"]</t>
   </si>
   <si>
-    <t>WOS:000391956900011</t>
-  </si>
-  <si>
-    <t>Realized climatic niches are conserved along maximum temperatures among herpetofaunal invaders</t>
-  </si>
-  <si>
-    <t>AimThe conservatism of the realized climatic niche is a pivotal assumption for predicting invasion risk under present and future climates. To date, however, no studies have identified the particular dimensions of realized climatic niches that are spatially and temporally conserved for a whole taxonomic group on a global scale. Understanding realized niche dynamics along each individual climatic variable separately is a key consideration for improving forecasts of invasive species distributions and anticipating future range expansions. LocationGlobal. MethodsUsing 181 successful invasion events for 128 alien herpetofaunal species across the globe, we applied a robust niche dynamics framework and analysed the conservatism of the realized climatic niche and its influencing factors along 19 temperature and precipitation variables. ResultsWe found that the magnitude of the niche expansion along the maximum temperature of the warmest month (or warmest quarter) was, on average, the lowest compared with the niche expansion magnitude along the minimum, average, range and seasonal temperature characteristics and all precipitation variables. Furthermore, the niche shift along the maximum temperature was only negatively correlated with native range size and was unrelated to residence time, species traits, introduction propagule pressure, topographic heterogeneity or equatorwards and polewards range expansion. Main conclusionsWe provide the first evidence that the realized climatic niche of alien herpetofaunal species is generally most conserved along maximum temperatures. This finding highlights the importance of preferentially choosing conserved climatic niche parameters to develop robust predictions of biological invasions or shifts in species ranges in response to climate change.</t>
-  </si>
-  <si>
-    <t>10.1111/jbi.12808</t>
-  </si>
-  <si>
-    <t>realized climatic niche (the set env and climate condiions a spiece occupies in nature); herpetofauna (Invasive) realized climatic nich is conserved along max temp;</t>
-  </si>
-  <si>
-    <t>WOS:000331673800014</t>
-  </si>
-  <si>
-    <t>Was overfishing of predatory fish responsible for a lobster-induced regime shift in the Benguela?</t>
-  </si>
-  <si>
-    <t>The top-down effects of predators have been demonstrated for terrestrial, freshwater and marine systems and their removal can cause a shift in ecosystem state. In many cases, the depletion of top-predators occurred long before humans began monitoring these systems, but models can elucidate likely ecosystem changes. In this paper we use a multispecies model to demonstrate that the abundance of predators can induce different ecosystem states, emphasising the importance of sustainable harvesting. Our model is founded on empirical data documenting a regime-shift that took place in the kelp-forest ecosystem along the south-west coast of South Africa following an 'invasion' by the West Coast rock lobster Jasus lalandii in the early 1990s. Formerly dominated by herbivores and encrusting corallines, the ecosystem became dominated by lobsters and macroalgae. A combination of illegal fishing of abalone Haliotis midae and the lobster-induced extermination of the urchin Parechinus angulosus (which shelters juvenile abalone) depleted abalone stocks severely. In this currently over-fished ecosystem where predators of lobsters are scarce, the regime-shift appears irreversible. Using an intermediate complexity model of lobster, urchin and abalone relationships, we simulated the effects of predatory fish at various population levels on the course of development of the currently lobster-dominated system. Our results indicate that current levels of fish biomass (&lt;10% of the pristine population) would have been too small to significantly affect the lobster population. However, at pristine levels of fish abundance (or even 50% less), the invasion of lobsters would have been controlled by linefish, and urchin and abalone populations would not have collapsed. The effect of the lobster invasion had a greater influence on abalone abundance than illegal fishing, but together they severely depleted the abalone. Ecosystem effects of historical exploitation of top predators are of central concern, and our ecosystem model indicates that depletion of linefish had severe consequences for lobsters, urchins and abalone, illustrating how overfishing of top predators may precipitate regime shifts, with profound socio-economic consequences. (C) 2013 Elsevier B.V. All rights reserved.</t>
-  </si>
-  <si>
-    <t>10.1016/j.ecolmodel.2013.11.004</t>
-  </si>
-  <si>
-    <t>Over fishing as driver causing ecosystem shift</t>
-  </si>
-  <si>
-    <t>WOS:000244692700016</t>
-  </si>
-  <si>
-    <t>Impacts of global changes and extreme hydroclimatic events on macroinvertebrate community structures in the French Rhone River</t>
-  </si>
-  <si>
-    <t>We assessed the temporal changes in and the relationships between the structures of the macroinvertebrate communities and the environmental conditions of the French Rhone River (the river from Lake Geneva to the Mediterranean Sea) over the last 20 years (1985-2004). Multisite environmental and biological datasets were analysed using multiple CO-inertia analysis (MCOA) and Procrustean analysis. Changes in environmental conditions were mainly marked by an improvement in water quality between 1985 and 1991 and by an increase in water temperature from 1985 onwards due to climate change. Improvement in water quality seemed to delay changes in community structures under global warming. We then observed trends in community structures coupled with high temperatures and a decrease in oxygen content. Interestingly, we observed both gradual changes and rapid switches in community states. These shifts seemed coupled to extreme hydroclimatic events (i.e. pulse disturbances). Floods and the 2003 heatwave enhanced the development of eurytolerant and invasive taxa which were probably able to take advantage of gradual warming environmental conditions. Despite various site-specific press constraints (e.g. hydropower schemes, nuclear power plants), similar changes in community structures were observed along the French Rhone River. Such consistency in temporal processes at large geographical scales underlined the strength of hydroclimatic constraints on community dynamics compared to specific local disturbances. Finally, community structures did not show any sign of recovery, and their relative sensitivities to extreme hydroclimatic events seemed to increase with time. Thus, our results suggest that global changes may reduce the resilience of current community states.</t>
-  </si>
-  <si>
-    <t>10.1007/s00442-006-0655-1</t>
-  </si>
-  <si>
-    <t>Climate warming and water quality improved linked to macroinvertebrate community changes</t>
-  </si>
-  <si>
-    <t>WOS:000367110300012</t>
-  </si>
-  <si>
-    <t>The temporal dynamics of a regional flora-The effects of global and local impacts</t>
-  </si>
-  <si>
-    <t>The main trends in changes in the global vascular plant biodiversity are generally considered to be a decrease in rare indigenous species and a spread of invasive plants. In the present paper, the impact of these changes on the flora of the state of Baden-Wurttemberg (Southwest-Germany) is examined. The data come from a regional floristic mapping project, which consists of two consecutive surveys, dating from 1970 to 1998 and from 2005 to present. In contrast to many other studies, not only a part of the flora or of an ecosystem was studied but the entire vascular plant flora of a region. As the recent survey is not yet completed, samples of 46 out of 1100 grid cells are analysed as a preliminary study on the trends in entire Baden-Wurttemberg. In the present paper we address the issues (1) whether changes in biodiversity observed in other studies, e.g. decrease of rare native species and increase of invasives, affect the flora of Baden-Wurttemberg, (2) which abiotic factors, i.e. climatic or soil conditions, cause these changes of species diversity. The analysis of the two consecutive surveys revealed a continuing decrease of rare native species and a constant increase of neophytes, thus reflecting the global trends. Many extinction events happened before 1970, some already in the 19th century. Changes in land use and urbanisation of former rural regions are two important factors for these changes. A statistic analysis using Ellenberg indicator values revealed the nitrogen input from agriculture and the effects of global warming as further potential causes for these trends. (C) 2015 Elsevier GmbH. All rights reserved.</t>
-  </si>
-  <si>
-    <t>10.1016/j.flora.2015.09.013</t>
-  </si>
-  <si>
-    <t>regional vascular plant biodiversity: deceases in rare species and spread of IAS due to anthropogenic impacts</t>
-  </si>
-  <si>
-    <t>WOS:000339385100016</t>
-  </si>
-  <si>
-    <t>Sensitivity and responses of diatoms to climate warming in lakes heavily influenced by humans</t>
-  </si>
-  <si>
-    <t>1. Diatom communities have been shown to respond strongly to current climate warming in remote lakes, while evidence remains equivocal for lakes under strong local human pressures. 2. Temporal dynamics of planktonic diatoms in three subalpine lakes (Geneva, Annecy and Bourget) reconstructed from palaeolimnological approaches were used to assess the relative effects of phosphorus concentrations, fisheries management practices and climate warming in structuring communities over the last century. 3. Changes in total phosphorous concentration (TP), air temperature and fish predation pressure could explain the temporal dynamics of most diatom species in the sediment records. TP was found to be not only the main driver of changes in community composition but also an important factor modulating diatom sensitivity and responses to climate warming. 4. The diatom community of Lake Bourget showed the highest vulnerability and direct responses to climate warming, favouring spring species that can resist earlier stratification in mesotrophic lakes (such as Asterionella formosa, Aulacoseira islandica and Stephanodiscus parvus) and summer species that can make the best trade-off between decreasing nutrient concentrations and increased water column stability (Diatoma tenuis, A. islandica). In Lake Geneva, climate warming also contributed to shaping diatom communities but through an indirect pathway; fisheries management practices and climate warming interacted to reinforce top-down control, favouring large, colonial inedible species (Stephanodicus binderanus and A. formosa). For Lake Annecy, the most nutrient limited of the three lakes studied, no changes in diatom community structure were directly related to warmer air temperatures over the last 25 years. 5. All three lakes have been subjected to the same climate variability. Yet the magnitude and responses of their diatom communities to climate warming were dissimilar and strongly modulated by differences in lake trophic status and fish management practices.</t>
-  </si>
-  <si>
-    <t>10.1111/fwb.12380</t>
-  </si>
-  <si>
-    <t>impact of climate warming and fisheries mgt in subalpine lakes on diatom community.</t>
-  </si>
-  <si>
-    <t>WOS:000428400500003</t>
-  </si>
-  <si>
-    <t>Productivity and recovery of forage fish under climate change and fishing: North Sea sandeel as a case study</t>
-  </si>
-  <si>
-    <t>Forage fish occupy a central position in marine food-webs worldwide by mediating the transfer of energy and organic matter from lower to higher trophic levels. The lesser sandeel (Ammodytes marinus) is one of the ecologically and economically most important forage fish species in the North-east Atlantic, acting as a key prey for predatory fish and sea birds, as well as supporting a large commercial fishery. In this case study, we investigate the underlying factors affecting recruitment and how these in turn affect productivity of the North Sea sandeel using long-term data and modelling. Our results demonstrate how sandeel productivity in the central North Sea (Dogger Bank) depends on a combination of external and internal regulatory factors, including fishing and climate effects, as well as density dependence and food availability of the preferred zooplankton prey (Calanus finmarchicus and Temora longicornis). Furthermore, our model scenarios suggest that while fishing largely contributed to the abrupt stock decline during the late 1990s and the following period of low biomass, a complete recovery of the stock to the highly productive levels of the early 1980s would only be possible through changes in the surrounding ecosystem, involving lower temperatures and improved feeding conditions. To that end, we stress the need for ecosystem-based management accounting for multiple internal and external factors occurring within the broader context of the ecosystem in which forage fish species, such as sandeel, play an important and integral part.</t>
-  </si>
-  <si>
-    <t>10.1111/fog.12246</t>
-  </si>
-  <si>
-    <t>fishing and climate (anthro drivers) affecting forage fish biodiv</t>
-  </si>
-  <si>
-    <t>WOS:000254086900002</t>
-  </si>
-  <si>
-    <t>The link between international trade and the global distribution of invasive alien species</t>
-  </si>
-  <si>
-    <t>Invasive alien species (IAS) exact large biodiversity and economic costs and are a significant component of human-induced, global environmental change. Previous studies looking at the variation in alien species across regions have been limited geographically or taxonomically or have not considered economics. We used a global invasive species database to regress IAS per-country on a suite of socioeconomic, ecological, and biogeographical variables. We varied the countries included in the regression tree analyses, in order to explore whether certain outliers were biasing the results, and in most of the cases, merchandise imports was the most important explanatory variable. The greater the degree of international trade, the higher the number of IAS. We also found a positive relationship between species richness and the number of invasives, in accord with other investigations at large spatial scales. Island status (overall), country area, latitude, continental position (New World versus Old World) or other measures of human disturbance (e.g., GDP per capita, population density) were not found to be important determinants of a country's degree of biological invasion, contrary to previous studies. Our findings also provide support to the idea that more resources for combating IAS should be directed at the introduction stage and that novel trade instruments need to be explored to account for this environmental externality.</t>
-  </si>
-  <si>
-    <t>10.1007/s10530-007-9138-5</t>
-  </si>
-  <si>
-    <t>link b/w international trade (anthro source) and distribution of IAS, driving the biodiv change</t>
-  </si>
-  <si>
-    <t>WOS:000269675600012</t>
-  </si>
-  <si>
-    <t>Impacts of grazing, selective logging and hyper-aggressors on diurnal bird fauna in intact forest landscapes of the Brigalow Belt, Queensland</t>
-  </si>
-  <si>
-    <t>The impact of forest management on diurnal bird assemblages and abundance was investigated in contiguous tracts of eucalypt forest in the Brigalow Belt Bioregion, south central Queensland. Sites were located across three levels of livestock grazing intensity and three levels of selective logging intensity within the most extensive habitat type, Corymbia citriodora-dominant forest. We recorded a high rate of incidence and large numbers of the hyper-aggressive noisy miner Manorina melanocephala (Passeriformes: Meliphagidae) at the majority of our survey sites, a phenomenon rarely reported in non-cleared landscapes. As shown by numerous studies in fragmented landscapes, the distribution of this species in our study had a substantial negative effect upon the distribution of small passerine species. Noisy miners exerted the strongest influence upon small passerine abundance, and masked any forest management effects. However, key habitat features important for small passerines were identified, including a relatively high density of large trees and stems in the midstorey. Selective logging appeared to exert a minimal effect upon noisy miner abundance, whereas grazing intensity had a profound, positive influence. Noisy miners were most abundant in intensively grazed forest with minimal midstorey and a low volume of coarse woody debris. Higher road density in the forest landscape also corresponded with increased numbers of noisy miners. Reduction in grazing pressure in Brigalow Belt forests has the potential to benefit small passerine assemblages across large areas through moderating noisy miner abundance. The strong relationship between noisy miners and small passerines suggests that noisy miner abundance could act as an easily measured indicator of forest condition, potentially contributing to monitoring of forest management outcomes.</t>
-  </si>
-  <si>
-    <t>10.1111/j.1442-9993.2009.01979.x</t>
-  </si>
-  <si>
-    <t>imapct of grazing and selective logging (anthro sources) on diurnal bird assemblage</t>
-  </si>
-  <si>
-    <t>WOS:000209091500024</t>
-  </si>
-  <si>
-    <t>Analysing ethnobotanical and fishery-related importance of mangroves of the East-Godavari Delta (Andhra Pradesh, India) for conservation and management purposes</t>
-  </si>
-  <si>
-    <t>Mangrove forests, though essentially common and wide-spread, are highly threatened. Local societies along with their knowledge about the mangrove also are endangered, while they are still underrepresented as scientific research topics. With the present study we document local utilization patterns, and perception of ecosystem change. We illustrate how information generated by ethnobiological research can be used to strengthen the management of the ecosystem. This study was conducted in the Godavari mangrove forest located in the East-Godavari District of the state Andhra Pradesh in India, where mangroves have been degrading due to over-exploitation, extensive development of aquaculture, and pollution from rural and urbanized areas (Kakinada). One hundred interviews were carried out among the fisherfolk population present in two mangrove zones in the study area, a wildlife sanctuary with strong conservation status and an adjacent zone. Results from the interviews indicated that Avicennia marina (Forsk.) Vierh., a dominant species in the Godavari mangroves, is used most frequently as firewood and for construction. Multiple products of the mangrove included the bark of Ceriops decandra (Griff.) Ding Hou to dye the fishing nets and improve their durability, the bark of Aegiceras corniculatum (L.) Blanco to poison and catch fish, and the leaves of Avicennia spp. and Excoecaria agallocha L. as fodder for cattle. No medicinal uses of true mangrove species were reported, but there were a few traditional uses for mangrove associates. Utilization patterns varied in the two zones that we investigated, most likely due to differences in their ecology and legal status. The findings are discussed in relation with the demographic and socio-economic traits of the fisherfolk communities of the Godavari mangroves and indicate a clear dependency of their livelihood on the mangrove forest. Reported changes in the Godavari mangrove cover also differed in the two zones, with significantly less perceptions of a decrease in the protected area, as compared to the adjacent non-protected area. A posteriori comparisons between sequential satellite imagery (retrospective till 1977) and respondents that were at least 15 years back then, revealed a mangrove decrease which was however perceived to different extents depending on the area with which the fishermen were familiar. While local needs had not been incorporated in the existing policy, we created a framework on how data on ethnobotanical traditions, fishery-related activities and local people's perceptions of change can be incorporated into management strategies.</t>
-  </si>
-  <si>
-    <t>10.1186/1746-4269-2-24</t>
-  </si>
-  <si>
-    <t xml:space="preserve">anthro threats to mangrove biodiv presented.
-ethnobotanical analysis (study of interations and use of plants within specific human culture and env); </t>
-  </si>
-  <si>
-    <t>WOS:000418334200001</t>
-  </si>
-  <si>
-    <t>Long-term carbon sink in Borneo's forests halted by drought and vulnerable to edge effects</t>
-  </si>
-  <si>
-    <t>Less than half of anthropogenic carbon dioxide emissions remain in the atmosphere. While carbon balance models imply large carbon uptake in tropical forests, direct on-the-ground observations are still lacking in Southeast Asia. Here, using long-term plot monitoring records of up to half a century, we find that intact forests in Borneo gained 0.43 Mg C ha(-1) per year (95% CI 0.14-0.72, mean period 1988-2010) above-ground live biomass. These results closely match those from African and Amazonian plot networks, suggesting that the world's remaining intact tropical forests are now en masse out-of-equilibrium. Although both pantropical and long-term, the sink in remaining intact forests appears vulnerable to climate and land use changes. Across Borneo the 1997-1998 El Nino drought temporarily halted the carbon sink by increasing tree mortality, while fragmentation persistently offset the sink and turned many edge-affected forests into a carbon source to the atmosphere.</t>
-  </si>
-  <si>
-    <t>10.1038/s41467-017-01997-0</t>
-  </si>
-  <si>
-    <t>Forest loss (anthro driver) affecting forest biomas and biodiv. , i.e. long term carbon sink in borneo forests vulnerable to effects from deforestation</t>
-  </si>
-  <si>
-    <t>WOS:000401719600004</t>
-  </si>
-  <si>
-    <t>Identifying and quantifying environmental thresholds for ecological shifts in a large semi-regulated river</t>
-  </si>
-  <si>
-    <t>Ecological shifts, between a clear macrophyte-dominated state and a turbid state dominated by phytoplankton and high inorganic suspended solids, have been well described in shallow lake ecosystems. While few documented examples exist in rivers, models predict regime shifts, especially in regulated rivers with high water retention time. Here I quantified ecological shifts in a large, semi-regulated floodplain river during a transition from a turbid-to a clear-water state using water quality, aquatic vegetation and fisheries data from a rigorous, standardized long-term data set. My findings indicate that significant changes occurred in total suspended solids concentration, aquatic macrophyte abundance, native and non-native fish biomass, fish functional feeding guild patterns, fish habitat guild assemblages and fish spawning guild assemblage patterns over a nearly 20-year period in Navigation Pool 8 of the Upper Mississippi River. Transitions in physical and biological indicators were examined to identify mechanisms underlying the ecological shifts. Environmental variables driving fish assemblage changes were identified (total suspended solids and aquatic vegetation) and management-relevant thresholds are presented. Awareness of management thresholds is critical for resource managers to implement measures to prevent the river from moving to a degraded state characterized by high non-native fish abundance and low predatory fish species abundance.</t>
-  </si>
-  <si>
-    <t>10.1080/02705060.2017.1319431</t>
-  </si>
-  <si>
-    <t>river regulation (anthro source) as driver of aquatic biodiv change</t>
-  </si>
-  <si>
-    <t>WOS:000305461200004</t>
-  </si>
-  <si>
-    <t>Abiotic drivers of coastal fish community change during four decades in the Baltic Sea</t>
-  </si>
-  <si>
-    <t>Evidence for long-term change of marine ecosystems is increasing worldwide. Coastal areas harbour the socio-economically and ecologically most vital aquatic ecosystems, but are under increasing anthropogenic pressure. Little is known, however, about how environmental perturbations affect the development of coastal systems. In this paper, datasets of coastal fish communities covering almost four decades (early/mid 1970s to 2008) in three different basins of the Baltic Sea were analysed. There were clear changes in species composition over time in all but one dataset and coherence among basins in the timing of change. Changes were mainly associated with variables related to climate (water temperature, salinity, and North Atlantic Oscillation index), but less so with those reflecting nutrient status (nutrient concentrations and loading). Despite the importance of local water temperature, regional climatic variables were more important for the temporal development of communities. The results indicate that Baltic coastal fish communities have undergone large structural changes governed by processes acting on both local and regional scales. The findings suggest that ecological targets should be set accounting for long-term changes in community structure and that a common management of coastal and offshore ecosystems would be beneficial.</t>
-  </si>
-  <si>
-    <t>10.1093/icesjms/fss072</t>
-  </si>
-  <si>
-    <t>changes in coastal fish community driven by abiotic factors (non living physical and chemical compon of ecosystem)</t>
-  </si>
-  <si>
-    <t>WOS:000185371200002</t>
-  </si>
-  <si>
-    <t>Conservation of Mediterranean temporary ponds under agricultural intensification: an evaluation using amphibians</t>
-  </si>
-  <si>
-    <t>This study examined responses of amphibians breeding in Mediterranean temporary ponds to a gradient of agricultural intensification, aiming to identify land uses and management prescriptions favouring the conservation of these habitats in farmed landscapes. Larval amphibian assemblages and habitat attributes were sampled at 57 ponds, 10 of which had been converted into permanent irrigation reservoirs. Species richness increased with area and hydroperiod in temporary ponds, with the addition of rare species to ponds with long hydroperiods resulting in a tendency for the less widespread species (e.g. Triturus marmoratus and T. boscai) to occur in the most species-rich ponds, while species-poor ponds consisted predominantly of widespread species only (nested pattern). However, one species (Pelodytes punctatus) was largely restricted to the most ephemeral ponds, whereas permanent irrigation reservoirs were species-poor and lacked most species occurring in temporary waters. The strongest negative correlates of amphibian abundances were the intensification of agricultural land uses, the transformation of ponds into permanent reservoirs and the introduction of exotic predators (fish and crayfish) from the irrigation channels. The results suggest that conservation of temporary pond amphibian assemblages in Mediterranean farmland requires networks of ponds with diverse hydroperiods, where the natural hydrologic regimes, less intensive land uses and isolation from irrigation waters should be preserved. (C) 2003 Elsevier Ltd. All rights reserved.</t>
-  </si>
-  <si>
-    <t>10.1016/S0006-3207(03)00051-X</t>
-  </si>
-  <si>
-    <t>intensification gradient (range of how land use intensity increases from one point to other); response of amphibians to agri intensification gradient</t>
-  </si>
-  <si>
-    <t>WOS:000414755500014</t>
-  </si>
-  <si>
-    <t>Inter-decadal changes in fish communities of a tropical bay in southeastern Brazil</t>
-  </si>
-  <si>
-    <t>Long-term evaluations of coastal fish communities worldwide have in many cases showed a decrease in the species richness and abundance as a result of anthropogenic impacts. Fish communities in two zones (inner and outer) of a tropical bay in southeastern Brazil were sampled monthly during six years over two decades (1983-1985, 1993-1995, 1999-2001) using identical sampling methods. Over time, an increase in temperature and a decrease in water transparency were detected, while salinity remained stable. Fish assemblage was dominated by benthivorous species both migrant and resident species. The fish assemblage structure differed significantly between the two bay zones. Significant decreases in the fish richness, abundance and biomass were detected over time. The highest decreases in the species richness was recorded between 1983-1985 and 1993-1995 for the marine migrants in both bay zones and for the resident and marine straggler species in the outer zone. Dominant species such as the clupeoids Anchoa januaria, Anchoa tricolor, Harengula clupeola, the gerreid Eucinostomos argenteus, the sciaenid Micropogonias furnieri, the atherinopsid Atherinella brasiliensis and the ariid Genidens barbus decreased over time, whereas the mugilid Mugil liza increased. Persistent differences in the fish assemblage structure between the two bay zones over the three periods can be attributed at least in part to differences in environmental variables between the zones and seem to be a key ecological element to maintenance of biodiversity. This is the first study to examine long-term changes in the fish community of a tropical bay in Brazil. (C) 2015 Elsevier B.V. All rights reserved.</t>
-  </si>
-  <si>
-    <t>10.1016/j.rsma.2015.06.001</t>
-  </si>
-  <si>
-    <t>decrease in richness of fish communities from anthro impacts</t>
-  </si>
-  <si>
-    <t>WOS:000646507600009</t>
-  </si>
-  <si>
-    <t>Land use land cover dynamics and fragmentation-induced changes in woody plant community structure in a mining landscape, Ghana</t>
-  </si>
-  <si>
-    <t>The study assessed the dynamics of mining land use land cover changes and consequent fragmentation impacts on woody plant community structure in the Ahafo Region, Ghana. Landsat images were utilised to determine land use and cover changes using a supervised classification method. Plant community structure was determined within 60 (20 x 20 m) plots that were randomly laid in equal numbers in fragmented and intact forests. Our findings showed that the mining landscape experienced a substantial land use/cover change between 2003 and 2018, with considerable forest cover loss at the expense of increasing cover of plantation, settlement/bare surface, mine site, and waterbody. Woody plant species diversity was significantly lower in the fragmented forest around the mine. Likewise, fragmentation caused a shift in plant species composition in the fragmented forest, whose composition was less homogenised compared to the intact forest. Plant abundance did not differ significantly between the two forests, but it was invasive and cultivated tree species that increased the total abundance of woody plants in the fragmented forests. The mining landscape was dominated by an invasive alien species, Broussonetia papyrifera which poses an ecological threat to native species. In conclusion, our findings suggest that mining contributed to intense land use/cover dynamics and fragmentation that impaired woody plant community structure around the mine. There is the need to accord priority to management intervention that would seek to manage and conserve the remaining forest fragments and its biodiversity in the mining landscape.</t>
-  </si>
-  <si>
-    <t>10.1016/j.tfp.2021.100070</t>
-  </si>
-  <si>
-    <t>Keck et al</t>
-  </si>
-  <si>
-    <t>impact of land use change and fragmentation on woodly plants community structure</t>
-  </si>
-  <si>
-    <t>WOS:000226791700006</t>
-  </si>
-  <si>
-    <t>Are invasive species the drivers or passengers of change in degraded ecosystems?</t>
-  </si>
-  <si>
-    <t>Few invaded ecosystems are free from habitat loss and disturbance, leading to uncertainty whether dominant invasive species are driving community change or are passengers along for the environmental ride. The driver model predicts that invaded communities are highly interactive, with subordinate native species being limited or excluded by competition from the exotic dominants. The passenger model predicts that invaded communities are primarily structured by noninteractive factors (environmental change, dispersal limitation) that are less constraining on the exotics, which thus dominate. We tested these alternative hypotheses in an invaded, fragmented, and fire-suppressed oak savanna. We examined the impact of two invasive dominant perennial grasses on community structure using a reduction (mowing of aboveground biomass) and removal (weeding of above- and belowground biomass) experiment conducted at different seasons and soil depths. We examined the relative importance of competition vs. dispersal limitation with experimental seed additions. Competition by the dominants limits the abundance and reproduction of many native and exotic species based on their increased performance with removals and mowing. The treatments resulted in increased light availability and bare soil; soil moisture and N were unaffected. Although competition was limiting for some, 36 of 79 species did not respond to the treatments or declined in the absence of grass cover. Seed additions revealed that some subordinates are dispersal limited; competition alone was insufficient to explain their rarity even though it does exacerbate dispersal inefficiencies by lowering reproduction. While the net effects of the dominants were negative, their presence restricted woody plants, facilitated seedling survival with moderate disturbance (i.e., treatments applied in the fall), or was not the primary limiting factor for the occurrence of some species. Finally, the species most functionally distinct from the dominants (forbs, woody plants) responded most significantly to the treatments. This suggests that relative abundance is determined more by trade-offs relating to environmental conditions (long-term fire suppression) than to traits relating to resource capture (which should most impact functionally similar species). This points toward the passenger model as the underlying cause of exotic dominance, although their combined effects (suppressive and facilitative) on community structure are substantial.</t>
-  </si>
-  <si>
-    <t>10.1890/04-0669</t>
-  </si>
-  <si>
-    <t>habitat disturbances and IAS affecting community biodiversity</t>
-  </si>
-  <si>
-    <t>WOS:000320791000002</t>
-  </si>
-  <si>
-    <t>The introduction of Littorina littorea to British Columbia, Canada: potential impacts and the importance of biotic resistance by native predators</t>
-  </si>
-  <si>
-    <t>Although the establishment and spread of non-indigenous species depends upon survival in the face of novel environmental conditions and novel biological interactions, relatively little attention has been focused on the specific role of native predators in limiting invasion success. The European common periwinkle, Littorina littorea, was recently introduced to the Pacific coast of Canada and provides a case study of an introduction into an area with an important predator guild (sea stars) that is functionally minor in the invader's native habitat. Here, we assess the likelihood of establishment, spread, and negative ecological impact of this introduced gastropod, with an emphasis on the role of native sea stars as agents of biotic resistance. Size frequency distributions and local market availability suggest that L. littorea was most likely introduced via the live seafood trade. Non-native hitchhikers (e.g., the trematode Cryptocotyle lingua) were found on/in both market and field specimens. Laboratory studies and field observations confirmed that L. littorea can survive seasonal low salinity in Vancouver, British Columbia. Periwinkles also readily consumed native Ulva, suggesting that periwinkles could impact native communities via herbivory or resource competition. Unlike native gastropods, however, L. littorea lacked behavioural avoidance responses to Northeast Pacific predatory sea stars (Pisaster ochraceus and Pycnopodia helianthoides), and sea star predation rates on L. littorea were much higher than predation rates on native turban snails (Chlorostoma funebralis) in common garden experiments. We therefore expect periwinkle establishment in British Columbia to be limited to areas with low predator density, as is seen in its field distribution to date. We caution that this conclusion may understate the importance of the L. littorea introduction if it also serves as a vector for additional non-indigenous species such as C. lingua.</t>
-  </si>
-  <si>
-    <t>10.1007/s00227-013-2206-8</t>
-  </si>
-  <si>
-    <t>intro of Littorina littorea (invasive) and biodiversity change</t>
-  </si>
-  <si>
-    <t>WOS:000443567600013</t>
-  </si>
-  <si>
-    <t>World's Largest Mass Bathing Event Influences the Bacterial Communities of Godavari, a Holy River of India</t>
-  </si>
-  <si>
-    <t>Kumbh Mela is one of the largest religious mass gathering events (MGE) involving bathing in rivers. The exponential rise in the number of devotees, from around 0.4 million in 1903 to 120 million in 2013, bathing in small specified sites can have a dramatic impact on the river ecosystem. Here, we present the spatiotemporal profiling of bacterial communities in Godavari River, Nashik, India, comprising five sites during the Kumbh Mela, held in 2015. Assessment of environmental parameters indicated deterioration of water quality. Targeted amplicon sequencing demonstrates approximately 37.5% loss in microbial diversity because of anthropogenic activity during MGE. A significant decrease in phyla viz. Actinobacteria, Chloroflexi, Proteobacteria, and Bacteroidetes was observed, while we noted substantial increase in prevalence of the phylum Firmicutes (94.6%) during MGE. qPCR estimations suggested nearly 130-fold increase in bacterial load during the event. Bayesian mixing model accounted the source of enormous incorporation of bacterial load of human origin. Further, metagenomic imputations depicted increase in virulence and antibiotic resistance genes during the MGE. These observations suggest the striking impact of the mass bathing on river ecosystem. The subsequent increase in infectious diseases and drug-resistant microbes pose a critical public health concern.</t>
-  </si>
-  <si>
-    <t>10.1007/s00248-018-1169-1</t>
-  </si>
-  <si>
-    <t>mass bathing (anthro source) and impact of river bacterial communities</t>
-  </si>
-  <si>
-    <t>WOS:000534700300001</t>
-  </si>
-  <si>
-    <t>Urbanization alters the composition, but not the diversity and structure, of Neotropical savanna woody plant communities</t>
-  </si>
-  <si>
-    <t>Urbanization is one of the main drivers of environmental change and can result in drastic changes to the biodiversity and composition of plant communities. The objective of the present work was to investigate whether the structure, diversity and composition of Neotropical savanna woody plant communities differ among fragments immersed in urban, peri-urban and rural environments. The study was carried out in nine Neotropical savannas with distinct levels of urbanization in the municipality of Montes Claros, state of Minas Gerais, Brazil. A total of 469 woody individuals belonging to 76 species and 30 families of plants were sampled. The most specious families were the Fabaceae with seventeen species and the Vochysiaceae with eight. The most abundant species were Myracrodruon urundeuva in urban areas, Byrsonima pachyphyla in peri-urban areas and Hymenaea stigonocarpa in rural areas. The diversity (species richness, estimated species richness and Simpson diversity index) and structure (abundance, cover and height) of the plant communities under study did not vary in response to urbanization, although species composition experienced notable changes. The urban plant communities were very distinct from the rural plant communities. Furthermore, the dominant species were very different among the urban, peri-urban and rural areas. These findings demonstrate that urbanization affects Neotropical savanna species that are susceptible to anthropization. Furthermore, among the anthropogenic pressures related to urbanization, fragmentation and isolation seem to be the most influential determinants of the composition of Neotropical savanna communities.</t>
-  </si>
-  <si>
-    <t>10.1007/s12224-020-09366-4</t>
-  </si>
-  <si>
-    <t>Effect on urbanization on composition of woody plant communities</t>
-  </si>
-  <si>
-    <t>WOS:000701772800007</t>
-  </si>
-  <si>
-    <t>A survey of benthic invertebrate communities in native and non-native seagrass beds in St. John, USVI</t>
-  </si>
-  <si>
-    <t>Halophila stipulacea, a seagrass native to the Indian Ocean, spread to the Caribbean in 2002. Few studies have explored the spatiotemporal distribution of H. stipulacea throughout the Caribbean and whether native invertebrates utilize this non-native seagrass as habitat. We surveyed the shallow, nearshore subtidal zones of four bays in St. John, US Virgin Islands over a two-year period to assess the abundance of both H. stipulacea and native seagrass species. We then surveyed macroinvertebrate communities in one bay with large areas of H. stipulacea, native seagrasses, and bare substrate to assess how macroinvertebrate species composition varied in these habitats. Our survey of the benthic macroinvertebrates revealed that: (1) native invertebrate species utilize H. stipulacea beds and (2) the density and richness of invertebrates was significantly higher in H. stipulacea beds compared to both native seagrass beds and bare substrate. Our results show that H. stipulacea is a common component of nearshore communities in St. John, USVI and that native invertebrates use H. stipulacea beds as habitat - results that agree with findings from other recent studies. While these findings indicate that native macroinvertebrate species can be abundant in non-native seagrass, further investigation, including experimental manipulations, preference tests, and surveys across broad spatial scales, are required to develop a robust understanding of the ecological impacts of this non-native grass.</t>
-  </si>
-  <si>
-    <t>10.1016/j.aquabot.2021.103448</t>
-  </si>
-  <si>
-    <t>non-native seagrass invastion and its effect on benthic invertebrate communities</t>
-  </si>
-  <si>
-    <t>WOS:000287448100010</t>
-  </si>
-  <si>
-    <t>Forest fragmentation drives Atlantic forest of northeastern Brazil to biotic homogenization</t>
-  </si>
-  <si>
-    <t>Aim To examine whether the tree flora of the Atlantic forest of northeastern Brazil has experienced detectable taxonomic homogenization via the proliferation of native pioneer species in response to habitat loss and fragmentation. Location Biotic homogenization (BH) was examined across the Atlantic forest of northeast Brazil, i.e. a 56,000 km2 piece of tropical forest and a distinct centre of species endemism in South America. Methods We assessed a dataset consisting of 5122 tree records and compared the similarity of tree floras from 12 semi-natural sub-regions of the Atlantic forest between two time periods: pre-1980 (plant records between 1902 and 1980), and post-1980 (between 1981 and 2006). To understand the mechanisms leading to BH (1) tree floras were ordered (via non-metric multidimensional scaling - NMDS) by date (pre/post 1980) based on species occurrence and frequency, (2) NMDS axes were regressed against the proportion of those species that increased their occurrence post-1980 (i.e. the winner species), and (3) patterns of geographic distribution and frequency of particular life-history traits were examined across winner species and a control group. Results Tree floras across the Atlantic forest became c. 20-40% more similar to each other post-1980, but patterns of species similarity were also influenced by between-plot geographical distance. NMDS ordination clearly segregated pre- and post-1980 floras with a clear signal of floristic convergence. Furthermore, winner tree species were largely composed of short-lived and small-seeded pioneer species that exhibit wide geographic distributions. Main conclusions Our results suggest that tropical forest biotas are susceptible to taxonomic homogenization (i.e. increasing levels of similarity) in the context of severe human-disturbance via the proliferation of particular groups of native species comprised mainly by ecologically-plastic, generalist species. We are thus extending the concept of homogenization to address and highlight a pervasive biological shift in the structure of tropical forest communities currently taking place across hyper-fragmented landscapes.</t>
-  </si>
-  <si>
-    <t>10.1111/j.1472-4642.2010.00739.x</t>
-  </si>
-  <si>
-    <t>forest fragmentation and its effect on atlantic forest biotic homgenization</t>
-  </si>
-  <si>
-    <t>WOS:000376798800013</t>
-  </si>
-  <si>
-    <t>Biodiversity consequences of land-use change and forest disturbance in the Amazon: A multi-scale assessment using ant communities</t>
-  </si>
-  <si>
-    <t>Quantifying and understanding the main drivers of biodiversity responses to human disturbances at multiple scales is key to foster effective conservation plans and management systems. Here we report on a detailed regional assessment of the response of ant communities to land-use change and forest disturbance in the Brazilian Amazon. We aimed to explore the effects of land-use intensification at both site and landscape scales, examining variation in ant species richness and composition, and asking which set of environmental variables best predict observed patterns of diversity. We sampled 192 sites distributed across 18 landscapes (each 50 km(2)) in Paragominas, eastern Brazilian Amazon, covering ca. 20,000 km(2). We sampled from undisturbed primary forest through varyingly disturbed primary forests, secondary forests, pastures and mechanised agriculture, following a gradient of decreasing total aboveground biomass. Irrespective of forest disturbance class, ant species richness was almost twice as high in forests when compared to production areas. In contrast, ant species composition showed continuous variation from primary forest to intensive agriculture, following a gradient of aboveground biomass. Ant species richness at all spatial scales increased with primary forest cover in the surrounding landscapes. We highlight the limited value of species richness as an indicator of changes in habitat quality, reinforcing calls to consider species composition in assessments of forest disturbance. Taken together, our results reveal the unique biodiversity value of undisturbed primary forests, but also show that disturbed primary forests and secondary forests have high conservation value, and thus play an important role in regional conservation planning. (C) 2016 Elsevier Ltd. All rights reserved.</t>
-  </si>
-  <si>
-    <t>10.1016/j.biocon.2016.03.005</t>
-  </si>
-  <si>
-    <t>Land use change, forest disturbances, and its impact on ant communities</t>
-  </si>
-  <si>
-    <t>WOS:000704969600011</t>
-  </si>
-  <si>
-    <t>Diuron environmental levels effects on marine nematodes: Assessment of ecological indices, taxonomic diversity, and functional traits</t>
-  </si>
-  <si>
-    <t>Coastal marine systems are the most sensitive zones to emerging pollutants. The present study aims to investigate the effect of Diuron on the meiofaunal assemblages, collected from the Bizerte channel (Tunisia). Microcosm experiments were set up using four increasing Diuron concentrations [D1 (10 ng g-1 dry weight (DW)), D2 (50 ng g-1 DW), D3 (250 ng g-1 DW) and (1250 ng g-1 DW)] compared to non-contaminated sediments (controls) and all plots were incubated for 30 days. Our results show that Diuron-supplemented sediments provoked the significant decrease of meiofaunal abundance as well as a change in nematodes' diversity and structure composition. All univariate indices, as well as the cumulative k-dominance, were lower in the Diuron than the control plot. Additionally, the ordination of treatments according to the two-dimensional nMDS plots analysis showed a clear structural separation of the Diuron treated replicates from the controls based on the functional groups lists. These current data emphasize the utility of the use of biological traits in the detection of disturbances in the aquatic biotope.</t>
-  </si>
-  <si>
-    <t>10.1016/j.chemosphere.2021.132262</t>
-  </si>
-  <si>
-    <t>diuron (herbicide pollutant) effects on marine nematode communities</t>
-  </si>
-  <si>
-    <t>WOS:000369491500101</t>
-  </si>
-  <si>
-    <t>Disentangling the responses of boreal stream assemblages to low stressor levels of diffuse pollution and altered channel morphology</t>
-  </si>
-  <si>
-    <t>Non-point diffuse pollution from land use and alteration of hydromorphology are among the most detrimental stressors to stream ecosystems. We explored the independent and interactive effects of morphological channel alteration (channelization for water transport of timber) and diffuse pollution on species richness and community structure of four organism groups in boreal streams: diatoms, macrophytes, macroinvertebrates, and fish. Furthermore, the effect of these stressors on stream condition was evaluated by Ecological Quality Ratios (EQR) from the national Water Framework Directive (WFD) assessment system. We grouped 91 study sites into four groups that were impacted by either diffuse pollution or hydromorphological alteration, by both stressors, or by neither one. Macroinvertebrate richness was reduced by diffuse pollution, whereas other biological groups were unaltered. Hydromorphological modification had no effect on taxon richness of any of the assemblages. Community structure of all groups was significantly affected by diffuse pollution but not by hydromorphology. Similarly, EQRs indicated negative response by diatoms, macroinvertebrates and fish to diffuse pollution, but not to hydromorphological alteration. Agricultural diffuse pollution thus affected species identities and abundances rather than taxonomic richness. Our results suggest that channelization of boreal streams for timber transport has not altered hydromorphological conditions sufficiently to have a strong impact on stream biota, whereas even moderate nutrient enrichment may be ecologically harmful. Controlling diffuse pollution and associated land use stressors should be prioritized over restoration of in-stream habitat structure to improve the ecological condition of boreal streams. (C) 2015 Elsevier B.V. All rights reserved.</t>
-  </si>
-  <si>
-    <t>10.1016/j.scitotenv.2015.12.031</t>
-  </si>
-  <si>
-    <t>Diffuse pollution (from land to water) and channel morphology (shapes and structure of river channels) alteration effects on boreal assemblage</t>
-  </si>
-  <si>
-    <t>WOS:000438220000023</t>
-  </si>
-  <si>
-    <t>Recovery of mammal diversity in tropical forests: a functional approach to measuring restoration</t>
-  </si>
-  <si>
-    <t>Ecological restoration is increasingly applied in tropical forests to mitigate biodiversity loss and recover ecosystem functions. In restoration ecology, functional richness, rather than species richness, often determines community assembly, and measures of functional diversity provide a mechanistic link between diversity and ecological functioning of restored habitat. Vertebrate animals are important for ecosystem functioning. Here, we examine the functional diversity of small-to-medium sized mammals to evaluate the diversity and functional recovery of tropical rainforest. We assess how mammal species diversity and composition and functional diversity and composition, vary along a restoration chronosequence from degraded pasture to old-growth tropical rainforest in the Wet Tropics of Australia. Species richness, diversity, evenness, and abundance did not vary, but total mammal biomass and mean species body mass increased with restoration age. Species composition in restoration forests converged on the composition of old-growth rainforest and diverged from pasture with increasing restoration age. Functional metrics provided a clearer pattern of recovery than traditional species metrics, with most functional metrics significantly increasing with restoration age when taxonomic-based metrics did not. Functional evenness and dispersion increased significantly with restoration age, suggesting that niche complementarity enhances species' abundances in restored sites. The change in community composition represented a functional shift from invasive, herbivorous, terrestrial habitat generalists and open environment specialists in pasture and young restoration sites, to predominantly endemic, folivorous, arboreal, and fossorial forest species in older restoration sites. This shift has positive implications for conservation and demonstrates the potential of tropical forest restoration to recover rainforest-like, diverse faunal communities.</t>
-  </si>
-  <si>
-    <t>10.1111/rec.12582</t>
-  </si>
-  <si>
-    <t>recovery of mamal functional diversity in tropical forests; 
-" a functional shift from invasive, herbivorous, terrestrial habitat generalists and open environment specialists in pasture and young restoration sites"</t>
-  </si>
-  <si>
-    <t>WOS:000246343500015</t>
-  </si>
-  <si>
-    <t>Community and species responses by birds to group retention in a coastal temperate forest on Vancouver Island, British Columbia</t>
-  </si>
-  <si>
-    <t>Group retention is a forest harvesting technique designed to sustain biodiversity and mitigate concerns regarding clearcut logging. It is characterized by retained forest patches that vary in number, size, spatial arrangement, and habitat attributes. We used birds to compare community composition and species abundance among clearcut, group retention, and uncut control forest treatments, and evaluated species' responses to percentage retention. The bird community in group retention was more similar to that in control forests than it was to the community in clearcuts. The probability of occurrence for many bird species typical of uncut control forests was related positively to percentage retention. A preliminary analysis of plot-level effects (i.e., amount of forest sampled) suggests that patch size may be more important than total amount of retention. (c) 2007 Elsevier B.V. All rights reserved.</t>
-  </si>
-  <si>
-    <t>10.1016/j.foreco.2007.03.002</t>
-  </si>
-  <si>
-    <t>bird community response to harvesting and logging</t>
-  </si>
-  <si>
-    <t>WOS:000351016900004</t>
-  </si>
-  <si>
-    <t>Effects of proximity to offshore fish farms over soft-bottom macrofauna</t>
-  </si>
-  <si>
-    <t>Sea-cage fish farms impact the seabed within their immediate vicinity, potentially affecting recipient communities. We assessed whether proximity to three sea-cage fish farms at the Canary Islands altered patterns in the abundance, assemblage structure and richness of soft-bottom macrofauna. We related among-farm variability in dissimilarities in macrofaunal assemblage structure between seabeds beneath cages and controls to differences in hydrodynamics, production and seabed topography. Contrasting patterns of species abundances with varying proximity to fish farms were observed: some species decreased while other species increased their abundances with increasing distance at some farms. Although faunal assemblages at 0 m (i.e. beneath the cages) were different, in terms of assemblage structure, from those found at controls, pairwise differences in assemblage structure among distances away varied among the studied fish farms. Species richness showed inconsistent patterns with proximity to cages among fish farms. In summary, inconsistent patterns of macrofaunal assemblages with varying proximity to aquaculture facilities preclude confident predictions on the way offshore aquaculture alters macrofauna in the study region.</t>
-  </si>
-  <si>
-    <t>10.1017/S0025315414001386</t>
-  </si>
-  <si>
-    <t>impact of fish farms (commercial controlled env) on soft-bottom macrofauna communitie</t>
-  </si>
-  <si>
-    <t>WOS:000268196000007</t>
-  </si>
-  <si>
-    <t>Biodiversity recovery during rainforest reforestation as indicated by rapid assessment of epigaeic ants in tropical and subtropical Australia</t>
-  </si>
-  <si>
-    <t>There is growing interest in the potential for reforestation to assist the recovery of rainforest biodiversity. There is also a need to identify taxonomically tractable groups for use as cost-effective indicators when monitoring the status of biodiversity within reforested sites. Insects are an important component of terrestrial biodiversity but often require considerable resources to sample at species level. Ant genera and generic-based functional groups have been suggested as possible indicators of environmental disturbance. Here we ask to what extent the development of biodiversity is indicated by epigacic ant genera and functional groups, across different types of reforestation in tropical and subtropical Australia. In each region, we used pitfall traps to sample the ants in replicate sites of: unmanaged regrowth, monoculture and mixed species plantations and 'ecological restoration' plantings, together with reference sites in pasture and rainforest. We recorded 35 epigaeic ant genera (and 4623 individuals) from 50 tropical sites, and 39 genera (and 9904 individuals) from 54 subtropical sites, with 47 genera overall. Community composition of both genera and functional groups differed between pasture and rainforest, although many genera were widespread in both. Reforested sites were intermediate between pasture and rainforest in both regions, and showed a gradient associated with decreasing grass and increasing tree and litter cover. Older monoculture plantations and ecological restoration plantings had the most rainforest-like ant assemblages, and mixed-species cabinet timber plots the least, of the reforested sites. We conclude that ground-active ant genera and functional groups sampled in rapid surveys by pitfall-trapping showed only a modest ability to discriminate among different types of reforestation. Species-level identification, perhaps together with expanded sampling effort, could be more informative, but would require resourcing beyond the scope of rapid assessments.</t>
-  </si>
-  <si>
-    <t>10.1111/j.1442-9993.2009.01943.x</t>
-  </si>
-  <si>
-    <t>biodiversity recovery during rainforest reforestation (replanting trees and allowing natural regeneration)</t>
-  </si>
-  <si>
-    <t>WOS:000668739900006</t>
-  </si>
-  <si>
-    <t>Human encroachment into wildlife gut microbiomes</t>
-  </si>
-  <si>
-    <t>In the Anthropocene, humans, domesticated animals, wildlife, and their environments are interconnected, especially as humans advance further into wildlife habitats. Wildlife gut microbiomes play a vital role in host health. Changes to wildlife gut microbiomes due to anthropogenic disturbances, such as habitat fragmentation, can disrupt natural gut microbiota homeostasis and make animals vulnerable to infections that may become zoonotic. However, it remains unclear whether the disruption to wildlife gut microbiomes is caused by habitat fragmentation per se or the combination of habitat fragmentation with additional anthropogenic disturbances, such as contact with humans, domesticated animals, invasive species, and their pathogens. Here, we show that habitat fragmentation per se does not impact the gut microbiome of a generalist rodent species native to Central America, Tome's spiny rat Proechimys semispinosus, but additional anthropogenic disturbances do. Indeed, compared to protected continuous and fragmented forest landscapes that are largely untouched by other human activities, the gut microbiomes of spiny rats inhabiting human-disturbed fragmented landscapes revealed a reduced alpha diversity and a shifted and more dispersed beta diversity. Their microbiomes contained more taxa associated with domesticated animals and their potential pathogens, suggesting a shift in potential metagenome functions. On the one hand, the compositional shift could indicate a degree of gut microbial adaption known as metagenomic plasticity. On the other hand, the greater variation in community structure and reduced alpha diversity may signal a decline in beneficial microbial functions and illustrate that gut adaption may not catch up with anthropogenic disturbances, even in a generalist species with large phenotypic plasticity, with potentially harmful consequences to both wildlife and human health. Fackelmann et al. study the gut microbial composition of spiny rats across tropical forests in Panama with varying levels of protection and fragmentation in order to disentangle the relative influences of habitat fragmentation and anthropogenic disturbance on wildlife gut microbiomes. They find that habitat fragmentation on its own did not affect the gut microbiome, but the microbiomes of individuals inhabiting forest fragments affected by anthropogenic disturbance displayed a shift in community composition and structure, and were more likely to have microbiota associated with domesticated animals and their pathogens.</t>
-  </si>
-  <si>
-    <t>10.1038/s42003-021-02315-7</t>
-  </si>
-  <si>
-    <t>human encroachment via habitat fragmentation into wildlife gut microbiomes</t>
-  </si>
-  <si>
-    <t>WOS:000070978100008</t>
-  </si>
-  <si>
-    <t>Field assessment of numerical impacts of coastal sewage disposal on fish larvae relative to natural variability</t>
-  </si>
-  <si>
-    <t>Sewage disposal in aquatic environments can have significant impacts on assemblages of organisms. There have been few field investigations on effects of sewage disposal on fish larvae. Data on abundances of larvae, current velocities and the size and shape of sewage plumes from point-source shoreline outfalls off Sydney (Australia) indicated that alongshore currents could transport large numbers of fish larvae into plumes, potentially affecting their health. Assemblages of fish larvae in surface sewage plumes differed to those in distant shelf (control) waters, but no such impacts were detected for assemblages in subsurface (20 m depth) waters beneath plumes. No predictable negative or positive numerical responses of fish larvae to sewage disposal were detected. Abundances of fish larvae fluctuated greatly in space and throughout time, and responses appeared to vary between taxa, outfalls and sampling periods. However, the large inherent level of natural spatial and temporal variability in abundances of larvae confounded the detection of possible impacts. Future field investigations need to focus on effects of sewage disposal on the health and condition of fish larvae. Designs for future field-based studies are discussed.</t>
-  </si>
-  <si>
-    <t>10.1023/A:1007365232465</t>
-  </si>
-  <si>
-    <t>coastal sewage (pollution) disposal impacts on fish larvae assemblages</t>
-  </si>
-  <si>
-    <t>WOS:000236382600013</t>
-  </si>
-  <si>
-    <t>Response of meiofauna and nematode communities to increased levels of contaminants in a laboratory microcosm experiment</t>
-  </si>
-  <si>
-    <t>This study was undertaken to assess the response of meiofauna and nematode (multispecies) associations in terms of density, diversity, and composition to different environmental contaminants and also to evaluate the use of meiofauna and nematodes as indicators in pollution monitoring. Sediment was collected from the mouth of the Swartkops River estuary and defaunated by successive freezing and thwarting. The sediment was then subdivided into flasks and treated with different contaminants (organic carbon, Zn, Cu, Ph, Fe) at different concentrations, before meiofauna-rich sediment was added to each of them. The setup was allowed to mature for 32 days. Various biological indices were used to assess the biological status of the nematode communities in the laboratory experiment. Nematode identification was done to the genus level. The results indicate that higher concentrations of heavy metals and organic carbon had an impact on the nematode density, diversity, and community structure. Nematode genera such as Axonolaimus, Theristus, and Paramonohystera were found to be tolerant to metal pollution. This study also observed that nematode communities react differently to metal and organic pollution. (c) 2005 Elsevier Inc. All rights reserved.</t>
-  </si>
-  <si>
-    <t>10.1016/j.ecoenv.2005.01.010</t>
-  </si>
-  <si>
-    <t>neiofauna and nematode responses (density, diversity, and composition) to environmental contaminants (pollution)</t>
-  </si>
-  <si>
-    <t>WOS:000302926400020</t>
-  </si>
-  <si>
-    <t>From forests to cattail: how does the riparian zone influence stream fish?</t>
-  </si>
-  <si>
-    <t>The aim of this study was to verify whether taxonomic and functional composition of stream fishes vary under three different preservation conditions of riparian zone: preserved (PRE), intermediate condition (INT), and degraded (DEG). Five stream stretches representing each condition were selected. Samples were taken from each stream in three occasions during the dry seasons from 2004 to 2007. Electro fishing (PRE and INT), sieves, dip nets, and hand seines (DEG) were used according to the characteristics of each sampled site. Overall, 46 species were registered. Differences in the taxonomic and functional species composition among groups were found, following the condition of riparian zones. The ichthyofauna :;recorded in the PRE was typical to pristine environments, consisting of species with specialized habits, notably benthic insectivores, intolerant, and rheophilics. In the INT group, replacement of riparian forest with shrubs and/or grasses created environmental conditions which favor the occurrence of tolerant species but also harbor a residual fauna of sensitive species. DEG streams presented mostly detritivores, tolerant, small sized fishes which occupy the surface and preferred slow water flux. Changes in the species composition were represented by the occurrence and dominance of tolerant species in detriment of the more, sensitive and specialist species, following the gradient of degradation in the riparian zone. Forested streams act as unique habitats to many specialized species and it can be presumable that the degradation of riparian vegetation can generate biotic homogenization which may reduce species diversity and ecosystem services.</t>
-  </si>
-  <si>
-    <t>10.1590/S1679-62252012000100020</t>
-  </si>
-  <si>
-    <t xml:space="preserve">riparian degradation (destruction or loss of vegetation and habitats along water bodies) and effect no fish composition </t>
-  </si>
-  <si>
-    <t>WOS:000296894900012</t>
-  </si>
-  <si>
-    <t>Effects of anthropogenic activities on lizard communities in northern Madagascar</t>
-  </si>
-  <si>
-    <t>Madagascar is a biodiversity hotspot threatened by habitat loss, which is detrimental to the future survival of forest-dwelling herpetofauna. For conservation purposes, it is essential to determine how species respond to different types of anthropogenic habitat alteration. We conducted standardized field surveys (a variation of visual encounter survey) to assess species richness, abundance and diversity among forest, clear-cut and orchard habitat types in Montagne des Francais, north Madagascar. Forest sites proved to be very different from clear-cut and orchard sites with regards to habitat structure. Lizard species richness, abundance and diversity were significantly lower in clear-cut sites, with only 11% of the observed forest diversity recorded. This shift in species occurrence suggests that lizards are particularly sensitive to this type of habitat alteration. Orchard cultivation did not affect lizard species richness to the same extent, as 56% of the observed forest diversity was recorded in this habitat type. Furthermore lizard abundance was significantly higher in orchard habitat. These observations indicate that although anthropogenic activity can have an adverse effect on the lizard fauna of a given site, it will seldom lead to a total loss of diversity as species typical of pristine forest (specialists) are replaced by species adapted to secondary habitats (often generalists). Our results support the contention that anthropogenic habitat alteration can have a strong negative influence on lizard communities. Researchers should continue to identify which species may be lost or become more vulnerable in future (as a result of population decline) in response to anthropogenic habitat alteration.</t>
-  </si>
-  <si>
-    <t>10.1111/j.1469-1795.2011.00459.x</t>
-  </si>
-  <si>
-    <t>murphy et al</t>
-  </si>
-  <si>
-    <t>effect of habitat loss on lizard communities</t>
-  </si>
-  <si>
-    <t>WOS:000188294900011</t>
-  </si>
-  <si>
-    <t>Effects of long-term nutrient fertilisation and irrigation on the microarthropod community in a boreal Norway spruce stand</t>
-  </si>
-  <si>
-    <t>Intensive nutrient fertilisation of forests has been suggested as a method to increase production of biofuels as a replacement for fossil fuels. We used a field experiment in a Norway spruce, Picea abies (L.) Karst., stand in northern Sweden to examine possible long-term effects of forest fertilisation on soil fauna (Oribatida, Mesostigmata, Collembola, predatory macroarthropods). Fertilisers had been applied annually for a period of 13 years, both in solid and liquid form, and N was added as ammonium nitrate (75-100 kg N ha(-1) per year). For comparison, control plots and plots receiving only irrigation were included. An autumn sampling showed soil fauna decreases in Plots receiving fertiliser in solid form, but increases in plots receiving liquid fertiliser. Clear shifts in community composition following both fertilisation methods were seen in Oribatida and Collembola, but species number and diversity were not significantly affected. This was probably due to increases in tolerant species that balanced decreases in other species. Liquid fertilisation had less negative effects on many species than fertilisation in solid form. Irrigation alone did not affect faunal abundances and had no effect on community composition of Oribatida and Collembola. The study indicates that intensive forest fertilisation will cause large shifts in soil microarthropod communities, but that species richness may remain unaffected. The risk of species loss will probably depend upon the size of the areas used for this purpose. (C) 2003 Elsevier B.V. All rights reserved.</t>
-  </si>
-  <si>
-    <t>10.1016/j.foreco.2003.07.012</t>
-  </si>
-  <si>
-    <t>nutrient fertilisation effects on microarthropod community in boreal forest</t>
-  </si>
-  <si>
-    <t>WOS:000281833700003</t>
-  </si>
-  <si>
-    <t>Experimental plant invasion reduces arthropod abundance and richness across multiple trophic levels</t>
-  </si>
-  <si>
-    <t>Plant invasions are known to have negative impacts on native plant communities, yet their influence on higher trophic levels has not been well documented. Past studies investigating the effects of invasive plants on herbivores and carnivores have been largely observational in nature and thus lack the ability to tease apart whether differences are a cause or consequence of the invasion. In addition, understanding how plant traits and plant species compositions change in invaded habitats may increase our ability to predict when and where invasive plants will have effects that cascade to animals. To assess effects on arthropods, we experimentally introduced a non-native plant (Microstegium vimineum, Japanese stiltgrass) in a community re-assembly experiment. We also investigated possible mechanisms through which the invader could affect associated arthropods, including changes in native plant species richness, above-ground plant biomass, light availability and vegetation height. In experimentally invaded plots, arthropod abundance was reduced by 39%, and species richness declined by 19%. Carnivores experienced greater reductions in abundance than herbivores (61% vs 31% reduction). Arthropod composition significantly diverged between experimentally invaded and control plots, and particular species belonging to the abundant families Aphididae (aphids), Formicidae (ants) and Phalacridae (shining flower beetles) contributed the most to compositional differences. Among the mechanisms we investigated, only the reduction in native plant species richness caused by invasion was strongly correlated with total arthropod abundance and richness. In sum, our results demonstrate negative impacts of M. vimineum invasion on higher trophic levels and suggest that these effects occur, in part, indirectly through invader-mediated reductions in the richness of the native plant community. The particularly strong response of carnivores suggests that plant invasion could reduce top-down control of herbivorous species for native plants.</t>
-  </si>
-  <si>
-    <t>10.1111/j.1600-0706.2010.18382.x</t>
-  </si>
-  <si>
-    <t>IAS invasion (experimental plant invasion) and its impact on arthropod abundance and richness across trophic levels</t>
-  </si>
-  <si>
-    <t>WOS:000294460300002</t>
-  </si>
-  <si>
-    <t>The effects of land-use change on arthropod richness and abundance on Santa Maria Island (Azores): unmanaged plantations favour endemic beetles</t>
-  </si>
-  <si>
-    <t>We study how endemic, native and introduced arthropod species richness, abundance, diversity and community composition vary between four different habitat types (native forest, exotic forest of Cryptomeria japonica, semi-natural pasture and intensive pasture) and how arthropod richness and abundance change with increasing distance from the native forest in adjacent habitat types in Santa Maria Island, the Azores. Arthropods were sampled in four 150 m long transects in each habitat type. Arthropods were identified to species level and classified as Azorean endemic, single-island endemic (SIE), native, or introduced. The native forest had the highest values for species richness of Azorean endemics, SIEs and natives; and also had highest values of Azorean endemic diversity (Fisher's alpha). In contrast, the intensive pasture had the lowest values for endemic and native species richness and diversity, but the highest values of total arthropod abundance and introduced species richness and diversity. Arthropod community composition was significantly different between the four habitat types. In the semi-natural pasture, the number of SIE species decreased with increasing distance from the native forest, and in the exotic forest the abundance of both Azorean endemics and SIEs decreased with increasing distance from the native forest. There is a gradient of decreasing arthropod richness and abundance from the native forest to the intensive pasture. Although this study demonstrates the important role of the native forest in arthropod conservation in the Azores, it also shows that unmanaged exotic forests have provided alternative habitat suitable for some native species of forest specialist arthropods, particularly saproxylic beetles.</t>
-  </si>
-  <si>
-    <t>10.1007/s10841-010-9330-2</t>
-  </si>
-  <si>
-    <t>land use change effects on arthropod richness in azores</t>
-  </si>
-  <si>
-    <t>WOS:000257412900003</t>
-  </si>
-  <si>
-    <t>The impact of land-use change on larval insect communities: Testing the role of habitat elements in conservation</t>
-  </si>
-  <si>
-    <t>Conservationists have proposed that maintaining key elements of the original land-cover type in modified landscapes may mitigate the detrimental effects of land-cover change on residual species. We tested this hypothesis for aquatic insect communities in tank-forming bromeliads in forested and non-forested habitats in Costa Rica. Bromeliad tanks hold much of the standing water in this region and therefore provide an important resource for insects with aquatic larval stages. We quantified the relative importance of land-use type and the bromeliad-specific local environment on the insect community, and also the effect of land-use type on this local environment. Insect species responded to both land-use type and the local environment, with these variables explaining a total of 36% of species densities. The local environment independently explained 19% of insect densities, while land-use type explained 17%, mainly through its modification of the local environment. Local environmental conditions were strongly correlated to land-use type (r(2) = 0.64), with non-forest habitat having a higher average temperature, a greater variation in temperature, and a lower density of bromeliads. Our results indicate that the land-use type in which bromeliads occur influences the relative densities of insects by altering the local environment of bromeliads. Therefore, maintaining bromeliads under land-use conversion will not necessarily maintain the bromeliad insect community of the original forested habitat.</t>
-  </si>
-  <si>
-    <t>10.2980/15-2-3098</t>
-  </si>
-  <si>
-    <t>land use change impact on larval insect communities</t>
-  </si>
-  <si>
-    <t>WOS:000208663500002</t>
-  </si>
-  <si>
-    <t>Reduction of riparian arthropod abundance and diversity as a consequence of giant reed (Arundo donax) invasion</t>
-  </si>
-  <si>
-    <t>The non-indigenous perennial grass, Arundo donax, is an aggressive invader of riparian areas throughout California and many sub-tropical regions of the world, and is hypothesized to provide poorer quality habitat for native wildlife in riparian systems. We sampled aerial and ground-dwelling insects and other terrestrial arthropods associated with Arundo, native willow vegetation (Salix spp.), and mixtures of the two vegetation types during two seasons to determine how Arundo influences invertebrate composition in a low gradient stream in central California. The total number of organisms, total biomass and taxonomic richness of aerial invertebrates associated with native vegetation was approximately twice that associated with Arundo vegetation, while mixed vegetation supported intermediate arthropod levels. Shannon-Weaver (Weiner) diversity associated with native vegetation stands was also higher than that of Arundo vegetation. Ground-dwelling assemblages did not show differences as great as aerial assemblages which are more critical to foraging avian species. These results indicate that vegetation type is a significant factor reducing the abundance and diversity of invertebrates in this, and presumably in many other riparian ecosystems where this invasive species has become a dominant component. Arundo invasion changes the vegetation structure of riparian zones and in turn, may increasingly jeopardize its habitat value for birds and other wildlife whose diets are largely composed of insects found in native riparian vegetation.</t>
-  </si>
-  <si>
-    <t>10.1023/A:1026190115521</t>
-  </si>
-  <si>
-    <t>giant reed (IAS) invasion is reducing riparian arthropod abundance and diversity</t>
-  </si>
-  <si>
-    <t>WOS:000276509400029</t>
-  </si>
-  <si>
-    <t>Non-native grass invasion alters native plant composition in experimental communities</t>
-  </si>
-  <si>
-    <t>Invasions of non-native species are considered to have significant impacts on native species, but few studies have quantified the direct effects of invasions on native community structure and composition. Many studies on the effects of invasions fail to distinguish between (1) differential responses of native and non-native species to environmental conditions, and (2) direct impacts of invasions on native communities. In particular, invasions may alter community assembly following disturbance and prevent recolonization of native species. To determine if invasions directly impact native communities, we established 32 experimental plots (27.5 m(2)) and seeded them with 12 native species. Then, we added seed of a non-native invasive grass (Microstegium vimineum) to half of the plots and compared native plant community responses between control and invaded plots. Invasion reduced native biomass by 46, 64, and 58%, respectively, over three growing seasons. After the second year of the experiment, invaded plots had 43% lower species richness and 38% lower diversity as calculated from the Shannon index. Nonmetric multidimensional scaling ordination showed a significant divergence in composition between invaded and control plots. Further, there was a strong negative relationship between invader and native plant biomass, signifying that native plants are more strongly suppressed in densely invaded areas. Our results show that a non-native invasive plant inhibits native species establishment and growth following disturbance and that native species do not gain competitive dominance after multiple growing seasons. Thus, plant invaders can alter the structure of native plant communities and reduce the success of restoration efforts.</t>
-  </si>
-  <si>
-    <t>10.1007/s10530-009-9546-9</t>
-  </si>
-  <si>
-    <t>non native grass invasion is altering native plant composition</t>
-  </si>
-  <si>
-    <t>WOS:000243104300011</t>
-  </si>
-  <si>
-    <t>Seagrass habitat disturbance:: how loss and fragmentation of eelgrass Zostera marina influences epifaunal abundance and diversity</t>
-  </si>
-  <si>
-    <t>Seagrass habitats commonly display evidence of anthropogenic disturbances such as propeller scars, mooring and anchor damage, trampling, and plant harvesting. These physical disturbances may lead to habitat loss and fragmentation, yet effects of this habitat removal on seagrass epifaunal communities are not well understood. We investigated how the degree of eelgrass Zostera marina L. loss influenced the abundance, diversity, and community composition of epifauna within experimental seagrass plots in San Diego Bay, California, USA. We established replicate small (4 m(2)) and large (16 m(2)) plots within existing eelgrass habitat, and removed all aboveground and belowground plant material within randomly chosen cells to establish 4 to 6 levels of eelgrass clearing. We then sampled for epifauna up to 8 wk after eelgrass harvesting. We found no correlations between seagrass loss and epifaunal species richness, total epifaunal density or epifaunal diversity in small plots. In large plots, however, plots with 90% habitat removal had significantly lower epifaunal species richness and total epifaunal density than plots with 0, 10 or 50% habitat removal, suggesting that beyond a threshold level of eelgrass disturbance, species richness and abundance rapidly decline. Multivariate ordinations revealed that the 90% removal plots also had significantly different species composition than plots with less habitat loss. Our results support previous theoretical models predicting threshold levels of habitat loss for faunal communities and broaden our understanding of the response of marine epifauna to seagrass habitat degradation.</t>
-  </si>
-  <si>
-    <t>10.3354/meps326133</t>
-  </si>
-  <si>
-    <t>sea grass habitat disturbance affecting epifaunal abundance and diversity</t>
-  </si>
-  <si>
-    <t>WOS:000178213200007</t>
-  </si>
-  <si>
-    <t>Fertilization with nitrogen and phosphorus increases abundance of non-native species in Hawaiian montane forests</t>
-  </si>
-  <si>
-    <t>We examined the effects of fertilization on the diversity, abundance, and cover of the understory plant community of two montane wet forests in Hawaii. One site occupies a young substrate, where aboveground tree growth is limited by nitrogen (N), while the other site is on an older substrate, where aboveground tree growth is limited by phosphorus (P). Both sites contained an on-going, long-term factorial fertilization experiment in which plots were fertilized semi-annually with N, P, or N and P in combination. In each fertilization treatment, we measured density of species greater than or equal to0.5 m tall and percent cover of species &lt;0.5 m tall. Fertilization with N reduced species richness at the young, N-limited site, but none of the nutrient additions altered species richness at the older, P-limited site. Species diversity and evenness were not affected by fertilization at either site. At the site with low N availability, plots fertilized with NP had higher densities of the non-native ginger Hedychium gardnerianum, and at the site with low P-availability, densities of the exotic shrub Rubus argutus were higher in P- and NP-fertilized plots. Other effects included declines in moss cover with fertilization at both sites, and reduced abundance of native seedlings in response to N and NP addition at the N-limited site. Continued long-term fertilization could lead to greater dominance of non-native species by encouraging their growth at the expense of native species, which may suffer decreased recruitment as fertilization and increased abundance of the non-native species may reduce suitable substrates for seedling establishment.</t>
-  </si>
-  <si>
-    <t>10.1023/A:1020332824836</t>
-  </si>
-  <si>
-    <t>fertilization increases abundance of non-native species in forests</t>
-  </si>
-  <si>
-    <t>WOS:000182948500002</t>
-  </si>
-  <si>
-    <t>Effects of the exotic macrophyte, para grass (Urochloa mutica), on benthic and epiphytic macroinvertebrates of a tropical floodplain</t>
-  </si>
-  <si>
-    <t>1. We examined the effect of the exotic macrophyte, para grass (Urochloa mutica ), on benthic and epiphytic macroinvertebrates of a tropical floodplain in northern Australia. Macroinvertebrates were sampled from four grass communities: (1) para grass, (2) hymenachne (Hymenachne acutigluma ), a native perennial; (3) rice (Oryza meridionalis ), a native annual, and (4) areas where para grass had been sprayed with herbicide. 2. Macroinvertebrate richness, abundance and community similarity showed very few differences among the grass communities, particularly in the epiphytic habitat. Benthic invertebrates showed some differences among grasses, with lower richness and abundance and different community structure associated with hymenachne. Herbicide control of para grass had no apparent effect on benthic invertebrates but reduced the abundance of epiphytic invertebrates in the short term. 3. The results of this study indicate that para grass has very little impact on macroinvertebrate communities, despite the changes to macrophyte communities. This is probably because para grass has similar physical structure to the native grasses and because none of these grasses contribute directly to aquatic food webs. Control of para grass using herbicide has little impact on aquatic invertebrates. This suggests that predicting the impact of weed invasion in wetlands requires an understanding of both the functional properties of macrophytes and the habitat preferences of the macroinvertebrates.</t>
-  </si>
-  <si>
-    <t>10.1046/j.1365-2427.2003.01072.x</t>
-  </si>
-  <si>
-    <t>exotic macrophyte para grass (IAS) effects on benthic communities</t>
-  </si>
-  <si>
-    <t>WOS:000247228800011</t>
-  </si>
-  <si>
-    <t>Species groups occupying different trophic levels respond differently to the invasion of semi-natural vegetation by Solidago canadensis</t>
-  </si>
-  <si>
-    <t>We studied the impact of the invasive plant species Solidago canadensis on the species richness of vascular plants and the abundance, species richness and diversity of butterflies, hoverflies and carabid beetles in herbaceous semi-natural habitats near Ljubljana, Slovenia. The species groups were sampled in sites dominated by S. canadensis and paired nearby sites covered by semi-natural vegetation. Plant species richness and species richness, abundance and diversity of butterfly species were lower in plots dominated by S. canadensis. Hoverfly abundance, diversity and species richness were negatively affected only in July just before the onset of flowering of S. canadensis, but tended to be positively affected in August during the height of flowering of S. canadensis. Only the abundance of carabid beetles was reduced in plots dominated by S. canadensis. The responses of the insect groups seem largely driven by the effects of Solidago on the availability of essential resources like food or larval host plants. Our results suggest that insect species that are closely related to plant species composition are more vulnerable to the effects of invasive plant species than those that are loosely or only indirectly related to plant species composition. (c) 2007 Elsevier Ltd. All rights reserved.</t>
-  </si>
-  <si>
-    <t>10.1016/j.biocon.2007.01.005</t>
-  </si>
-  <si>
-    <t>solidago canadensis (IAS) impact on plant, butterfly, hoverfly, carabid beetle diversity</t>
-  </si>
-  <si>
-    <t>WOS:000225858000003</t>
-  </si>
-  <si>
-    <t>Influence of habitat fragmentation and crop system on Columbia Basin shrubsteppe communities</t>
-  </si>
-  <si>
-    <t>Crop production in much of the western United States has caused extensive fragmentation of shrubsteppe and other grasslands and has increased regional levels of disturbance through repeated tillage of crop fields and applications of agrochemicals. Although there have been numerous studies of the effects of fragmentation on arthropods in forests, old fields, and cropland, there have been very few studies of fragmentation effects on grassland arthropods. I conducted a two-year study in the Columbia Basin region of the U.S. Pacific Northwest to determine the effects of fragmentation and regional disturbance on shrubsteppe communities. I sampled plants and arthropods in 20 shrubsteppe fragments associated with annual crops, 20 fragments associated with perennial crops, and 20 large sections of shrubsteppe distant from crop fields. Fragments were corners of crop irrigation circles, and only sites that were undisturbed, with an apparent high coverage of shrubs, were included in the study. Results indicated no significant differences in coverages of shrubs, perennial grasses, total perennial forbs, total annual/biennial forbs, and species richness of grasses and shrubs between fragments and large sections of shrubsteppe. Mean percent coverage of the annual grass Bromus tectorum was 18.6% greater in small fragments than in large sections of shrubsteppe distant from crop fields, and mean coverage of bare ground was 22.9% higher and coverage of biological soil crusts was 41.5% lower in the fragments than in large shrubsteppe sections. Shrubsteppe fragments had significantly lower abundances of obligate herbivores, omnivores, total herbivores, obligate predators, total predators, plant detritivores, total detritivores, and butterflies, as well as fewer individuals of numerous other taxa within these trophic groups. Fragmentation had very little effect on species richness within trophic groups, probably because fragments were not that isolated from each other and large sections of shrubsteppe. Shrubsteppe communities that were next to highly disturbed annual crops had greater coverages of total annual/biennial forbs, and lower coverages of total perennial forbs and biological soil crusts when compared to shrubsteppe near perennial crops. Abundances of obligate herbivores, omnivores, total predators, plant detritivores, vertebrate-detritus feeders, and bees were similar in shrubsteppe near annual crops and near perennial crops. However, within these trophic groups, shrubsteppe near annual crops supported fewer obligate shrub-feeding grasshoppers, herbivorous ground beetles, harvestmen, antlions, darkling beetles, and butterflies than did shrubsteppe near perennial crops. The results suggest that a reduction in resources within fragments and regional disturbances caused by the production of annual crops were responsible for changes in arthropod trophic structure in fragments. Changes in trophic structure were probably not due to reductions in habitat heterogeneity or habitat isolation because plant community structure was similar in fragmented and unfragmented shrubsteppe, and fragments were not isolated from large sections of shrubsteppe.</t>
-  </si>
-  <si>
-    <t>10.1890/03-5249</t>
-  </si>
-  <si>
-    <t>habitat fragmentation and crop system effects on arthropod communities</t>
-  </si>
-  <si>
-    <t>WOS:000310464500014</t>
-  </si>
-  <si>
-    <t>Plant invasion impacts on arthropod abundance, diversity and feeding consistent across environmental and geographic gradients</t>
-  </si>
-  <si>
-    <t>Exotic plant invasion not only changes native plant communities, it also alters associated arthropod community diversity and structure. These impacts often are contradictory and context-specific by study location. M. vimineum is an Asian grass currently invading the eastern United States that generally escapes herbivory. The invasion impacts on arthropod communities are mixed, and the effects on arthropod food webs are largely unknown. Because M. vimineum has a unique delta C-13 value, its carbon flow can be resolved from native plants in recipient food webs. We investigate arthropod communities at M. vimineum-invaded sites along a 100-km geographic and environmental gradient in the southeastern U.S. We investigate M. vimineum impacts on arthropod abundance and diversity, how M. vimineum-derived carbon contributes to arthropod biomass and how environmental variation modifies invasion effects on arthropod communities. We find that M. vimineum invasion corresponds with increased arthropod diversity and abundance, but reduced evenness. Herbivore damage to leaves is equivalent between native species and M. vimineum, but the type of herbivore damage is not the same between the native and invader plants. We also find that herbivores derive 37 % of their biomass-carbon from the exotic plant but predators almost none (4 %). Detritivores derive exotic carbon (9 %) proportional to M. vimineum in the litter layer. Whereas exotic plant impacts on arthropod communities often seem idiosyncratic by site, we find no context-dependent invasion effects of M. vimineum by study location. The consistency suggests that the impacts may be broadly generalizable, at least within well-established parts of the invasion range.</t>
-  </si>
-  <si>
-    <t>10.1007/s10530-012-0258-1</t>
-  </si>
-  <si>
-    <t>plant invasion impacts on arthropod community diversity and food webs</t>
-  </si>
-  <si>
-    <t>WOS:000280973100010</t>
-  </si>
-  <si>
-    <t>Experimental introduction of the alien plant Hieracium lepidulum reveals no significant impact on montane plant communities in New Zealand</t>
-  </si>
-  <si>
-    <t>Aim There is debate over whether alien plants necessarily alter the communities they invade or can coexist with native species without discernable impacts. We followed the fate of montane plant communities in response to the experimental sowing of the alien weed Hieracium lepidulum, looking for changes in plant community composition and structure over 6 years. Location Craigieburn Range, New Zealand. Methods We used a replicated randomised block design, with 30 x 30 cm plots (n = 756) subdivided into 5 x 5 cm cells to examine and compare the effects of H. lepidulum at 0.09 m2 (plot) and 0.0025 m2 (cell) scales. Plots were sown with between 0 and 15,625 H. lepidulum seeds in 2003, forming gradients of invader density and cover. Measurements comprised community richness, evenness and diversity along with H. lepidulum density and cover at both scales. The relationships between the invader and local community attributes were modelled using hierarchical mixed-effect models. Results Plant communities differed in the extent to which they became invaded, with H. lepidulum cover in the plots ranging from 0% to 52%, with a mean of only 1.89%. Plot species richness increased from 2003 to 2009, with a component of this increase (+0.002 species per year) associated with increasing H. lepidulum density. Other relationships between the plant community and H. lepidulum were generally non-significant. Main conclusions In these montane plant communities, it appears H. lepidulum coexists with the native community with no measurable negative effects after 6 years on species richness, evenness or diversity, even where density and cover of the invader are highest. We suggest H. lepidulum has persisted preferentially at those sites with abiotic conditions sufficient to support a species-rich assemblage.</t>
-  </si>
-  <si>
-    <t>10.1111/j.1472-4642.2010.00684.x</t>
-  </si>
-  <si>
-    <t>experimental introduction of alien plant with no significant impact on montane communities</t>
-  </si>
-  <si>
-    <t>WOS:000276425400006</t>
-  </si>
-  <si>
-    <t>Invasive alien goldenrods negatively affect grassland bird communities in Eastern Europe</t>
-  </si>
-  <si>
-    <t>Invasive alien plants constitute a major threat to local biodiversity. Moreover, their appearance often coincides with land use change. Many endangered groups of organisms suffer from habitat loss, which is often a consequence of the invasion of alien plants This paper examines how invasive alien goldenrods Solidago spp affect the richness of endangered grassland bird species and numbers of breeding pairs in abandoned meadows in southern Poland. Meadows invaded by goldenrods (n = 15) had lower bird spedes richness and a lower number of breeding pairs than meadows in which goldenrods were absent (n = 15) Two important factors positively influencing bird species richness were meadow area and shrub density (the latter only in meadows without goldenrods). Moreover, both the index of potential food density (number of butterflies) and plant species richness were much lower in meadows invaded by goldenrods than in meadows without these plants Urgent action aimed at preventing the invasion of alien goldenrods in abandoned meadows is needed and such measures should involve regular mowing Our results also highlight the fact that land abandonment in Central and Eastern Europe is not necessarily as beneficial for biodiversity as it is commonly believed and it may even lead to a decrease in the populations of several bird species in the agricultural landscape. (C) 2009 Elsevier Ltd. All rights reserved.</t>
-  </si>
-  <si>
-    <t>10.1016/j.biocon.2009.12.030</t>
-  </si>
-  <si>
-    <t>goldenrods (IAS) negatively affecting grassland bird communities</t>
-  </si>
-  <si>
-    <t>WOS:000258413600018</t>
-  </si>
-  <si>
-    <t>Compositional and functional stability of arthropod communities in the face of ant invasions</t>
-  </si>
-  <si>
-    <t>There is a general consensus that the diversity of a biotic community can have an influence on its stability, but the strength, ubiquity, and relative importance of this effect is less clear. In the context of biological invasions, diversity has usually been studied in terms of its effect on a community's invasibility, but diversity may also influence stability by affecting the magnitude of compositional or functional changes experienced by a community upon invasion. We examined the impacts of invasive ants on arthropod communities at five natural area sites in the Hawaiian Islands, and assessed whether differences among sites in community diversity and density variables were related to measures of stability. Ant invasion was usually associated with significant changes in overall community composition, as measured by Bray-Curtis distances, particularly among endemic subsets of the communities. Changes in mean species richness were also strong at three of the five sites. Among sites, diversity was negatively related to stability as measured by resistance to overall compositional change, but this effect could not be separated from the strong negative effect of invasive ant density on compositional stability. When compositional stability was measured as proportional change in richness, the best predictor of stability among endemic community subsets was endemic richness, with richer communities losing proportionately more species than species-poor communities. This effect was highly significant even after controlling for differences in invasive ant density and suggested that communities that had already lost many endemic species were resistant to further species loss upon ant invasion, while more intact communities remained vulnerable to species loss. Communities underwent strong but idiosyncratic functional shifts in association with ant invasion, both in terms of trophic structure and total arthropod biomass. There were no apparent relationships, however, between functional stability and community diversity or density measures. Instead, invasive ant density was the best among-site predictor of the magnitude of functional change. Overall, diversity appeared to be a poor predictor of stability in the face of ant invasion in these communities, possibly because any actual diversity effects were overshadowed by community-specific factors and variation in the magnitude of the ant-mediated perturbation.</t>
-  </si>
-  <si>
-    <t>10.1890/07-1293.1</t>
-  </si>
-  <si>
-    <t>ant invasions impact on arthropod community</t>
-  </si>
-  <si>
-    <t>WOS:000275033500012</t>
-  </si>
-  <si>
-    <t>Assessing impacts of introduced aquaculture species on native fish communities: Nile tilapia and major carps in SE Asian freshwaters</t>
-  </si>
-  <si>
-    <t>Herbivorous or omnivorous tilapia and carp species form the backbone of tropical inland aquaculture and fisheries enhancement and have been introduced widely outside their natural ranges. Perceptions of their impact on native fish faunas vary widely, but there have been few rigorous assessments. To quantify the impact of tilapia and carp stocking on native fish communities in freshwater wetlands of the Mekong region, we conducted observational and experimental impact-control studies replicated at the wetland level, at a total of 46 sites in Lao PDR. The studies were designed as paired comparisons of wetlands where the nonnative species (Nile tilapia Oreochromis niloticus, mrigal Cirrhinus cirrhosus, rohu Labeo rohita and bighead carp Hypophthalmichthys nobilis) were stocked in substantial numbers with similar wetlands where the species were absent. Stocking of these non-native species was associated with significant increases in total fish biomass, by 180% in the observational study and by 49% in the experiment. Native fish biomass was not affected by stocking of the non-native species. No significant impacts on native fish species richness, diversity indices, species composition or feeding guild composition were detected, except for moderately negative effects on Simpson diversity and equitability in the observational study. In the experiment, no effect had a point estimate exceeding -14%, or a 95% confidence limit exceeding -35% of the non-impacted value. Use of these non-native tilapia and carp species in fisheries enhancement in mainland SE Asia supported substantial increases in harvestable biomass while having only mild impacts on native fish communities. Escapes of the same species from pond and cage aquaculture facilities are likely to result in lower biomass in the wild and have lower impacts than enhancement stocking. We encourage building on our results through a systematic and stakeholder-participatory evaluation of the significance and acceptability of benefits and risks associated with the use of these non-native species. This evaluation should be extended to the relative benefits and risks of replacing non-native species with native ones in aquaculture and enhancement, considering that risks associated with using the current set of non-native species are increasingly well known and appear mild-to-moderate, whilst ecological and genetic risks of releasing domesticated types of native species are poorly known. (C) 2009 Elsevier B.V. All rights reserved.</t>
-  </si>
-  <si>
-    <t>10.1016/j.aquaculture.2009.11.022</t>
-  </si>
-  <si>
-    <t>tilapia, carps (IAS) impact on native fish communities</t>
-  </si>
-  <si>
-    <t>WOS:000224463400005</t>
-  </si>
-  <si>
-    <t>Refugia and local controls: Benthic invertebrate dynamics in Lower Green Bay, Lake Michigan following zebra mussel invasion</t>
-  </si>
-  <si>
-    <t>In many aquatic ecosystems benthic invertebrate abundance has increased following zebra mussel (Dreissena polymorpha) invasion. We examine the impact of zebra mussel density on the abundance and distribution of benthic invertebrates and postulate refuge from predation as a mechanism for the increases we found in some taxa. Benthic invertebrates in zebra mussel druses and in adjacent sediment samples were surveyed at sites in six locations representing various trophic conditions in lower Green Bay. Mean invertebrate density and taxa richness were significantly higher in the druses than in the adjacent sediment. Species diversity in the druses was inversely correlated to turbidity over the study area. Sediment samples were dominated by oligochaetes and chironomids. Amphipods were the most abundant taxa in most, but not all, of the druse samples. Other taxa present included leeches, hydra, mayflies, and caddisflies. The effectiveness of druses as refuge from predation for amphipods was investigated under laboratory conditions with various predators (perch, round goby, and rusty crayfish). In mesocosms, predation losses averaged 75% lower where zebra mussels were present. In the absence of mussels, predation loss to perch and round goby was 100% and 66% to crayfish. We conclude that the increased abundance of other invertebrates in druses in lower Green Bay may be due to increased refugia, however the assemblage composition at any given site varies with local conditions.</t>
-  </si>
-  <si>
-    <t>10.1016/S0380-1330(04)70356-1</t>
-  </si>
-  <si>
-    <t>Zebra mussel (IAS) impact on benthic invertebrate abundance and distribution</t>
+    <t>Mangroves of the Western Coral Triangle</t>
+  </si>
+  <si>
+    <t>The 'Mangroves of the Western Coral Triangle' is a regional ecosystem subgroup (level 4 unit of the IUCN Global Ecosystem Typology. It includes intertidal forests and shrublands of the following marine ecoregions in the Western Coral  Triangle  province:  Banda  Sea,  Eastern  Philippines,  Halmahera,  Lesser  Sunda,  Northeast  Sulawesi, Palawan/North Borneo, Papua, and Sulawesi Sea/Makassar Strait. The diverse biota of this provinceincludes 48 species of true mangroves, plus many mangrove-associated taxa. Mangroveshad a mapped extent of 19,821 km2in 2020, representing 13.4% of the global mangrove resource by area.  Although only 4.7 % of the province’s mangroves occur on carbonate sediments, they include fragile patches of vegetation on many of the thousands of islands in the Western Coral Triangle, Mangroves are threatened by illegal logging,  conversion  for  agriculture  or  aquaculture,  and  industrial,  urban  and  tourism  development,  including coastal land reclamation and mining. They are also threatened by climate change, especially sea-level rise, and by increasingly frequent typhoons and tropical storms.Today the Western Coral Triangle mangroves cover ≈32% less than our estimate for 1970 based on national studies. The rate of loss declined to -6.6% from 1996 to 2020 and has slowed further since 2015. The Western Coral Triangle mangroves are estimated to decrease by -18% over the next 50 years. They are also threatened by future sea-level rise (SLR). Under a mid-high to extreme SLR scenario, more than 30% of the mangroves would be submerged by 2070. Moreover, we estimate that 4% of the mangroves are undergoing degradation and this could rise to 10.7% over a 50-year period based on analysis of the decay of vegetation indexes. These estimates are very conservative; however, no other data sources were available to measure environmental degradation at the provincelevel. Overall, the Western Coral Triangle mangrove ecosystem is assessed as Vulnerable (VU).VU</t>
+  </si>
+  <si>
+    <t>mangroves of western coral triangle ecosystem assessment; with anthropogenic threats (logging, agri/aqua conversion, industral dev, urban dev, mining, etc) to biodiversity</t>
+  </si>
+  <si>
+    <t>Mangroves of The Bay of Bengal</t>
+  </si>
+  <si>
+    <t>Mangroves of the Bay of Bengal is a regional ecosystem subgroup (level 4 unit of the IUCN Global Ecosystem Typology) spanning parts of South and Southeast Asia. It includes coastal areas of eastern India, Bangladesh, and northern and central Myanmar, and contains one of the largest single mangrove ecosystems in the world: the Sundarbans.Mangroves dominate along the extensive coastal waterways of the Ganges-Brahmaputra and Ayeyarwady deltas in  India-Bangladesh  and  Myanmar,respectively.  They  occur  on  mainly  coastal  alluvial  sediments  deposited  by these  and  other  river  systems.  Their  mapped  extent  in  2020  was  10,250  km2,  representing  7%  of  the  global mangrove area. The Bay of Bengal provincemangroves are threatened by highpopulation pressure and intense natural resources use, including mangrove-associated fisheries and conversion to agriculture or aquaculture. Mangrove degradation and  conversion  have  caused  serious  coastal  erosion.  Destructive  cyclones  exacerbated  by  climate  change  also cause  coastal  erosion  and  damage  to  mangroves,  while  reduced  freshwater  flows  and  salinity  intrusion  in  the Sundarbans are threatening salt-sensitive mangrove tree species like Heritiera formes. This species is classified as Endangered (EN) by IUCN, whileBruguiera hainesiiand Sonneratia griffithiiare Critically Endangered (CR).Today the Bay of Bengal mangroves cover ≈8% less than our broad estimation for 1970. The rate of decline has slowed since 2015 and, if the present rate persists, an overall decrease of -12% is projected over the next 50 years. However, they are expected to be resilient to even extreme sea-level rise scenarios, due to high sediment supply and vertical accretion. We estimate that 5% of the Bay of Bengal mangroves are undergoing degradation. This value could rise to 15% over a 50-year period based on decay of vegetation indexes. Overall, the Bay of Bengal mangrove ecosystem is assessed as Least Concern (LC).</t>
+  </si>
+  <si>
+    <t>mangroves of bay of bengal ecosystem under anthropogenic threats</t>
+  </si>
+  <si>
+    <t>Mangroves of the South China Sea</t>
+  </si>
+  <si>
+    <t>The 'Mangroves of South China Sea' is a regional ecosystem subgroup (level 4 unit of the IUCN Global Ecosystem Typology in the South China Sea province. It includes intertidal forests and shrublands of the marine ecoregions of the Gulf of Tonkin, South China Sea Oceanic Islands and Southern China. The diverse biota of this ecoregion is characterised by 42 species of true mangroves, plus many associated taxa. There is a significant decline in species diversity with increasing latitude towards the northern limit of mangroves in Fujian Province. Two species: Avicennia rumphianaand Camptostemon philippinensisare in the IUCN Red List of threatened species.  The South China Sea ecoregion mangroves are mainly scattered open coast and estuarine formations, except in the Red River Delta. Their mapped extent in 2020 was 543 km2representing only 0.4% of the global mangrove resource. The current threats to mangroves are mainly from coastal urbanisation and industrialisation, sea dyke construction, pollution,  and  climate-related  impacts,  especially  from  typhoons,  which  occur  frequently  in  thisprovince.Today, the South China Sea mangroves cover ≈36% less than in 1970 based on national studies. The South China Sea mangroves are also threatened by sea-level rise(SLR). Under a mid-high SLR scenario, and considering the limited coastal sediment supply, 50% of the mangrove area will be submerged by 2070. Moreover, we estimate that ≈3.5% of the mangroves are undergoing degradation. Based on analysis of the decay of vegetation indexes, this could rise to 10.2% over a 50-year period. These estimates are very conservative; however, no other data sources were available to measure environmental degradation at the ecoregion level. Considering the significant effect of future SLR, the South China Sea mangroves are assessed as Endangered (EN).EN</t>
+  </si>
+  <si>
+    <t>mangroves of south china Sea with significant decline in species diversity due to anthro threats (Industrialisation, pollution, urbanization, etc)</t>
   </si>
   <si>
     <t>Mangroves of the Sunda Shelf</t>
@@ -972,31 +237,16 @@
     <t>The 'Mangroves of the Sunda Shelf' is a regional ecosystem subgroup (level 4 unit of the IUCN Global Ecosystem Typology in the Sunda Shelf province. It includes intertidal forests and shrublands of the marine regions of the Malacca Straits, Gulf of Thailand, southern Viet Nam and the Sunda Shelf/Java Sea. This provincehas a tropical climate with protracted rainfall that provides very favourable conditions for mangroves. The rich mangrove biota includes 49 species of true mangrove plants and many mangrove-associated taxa. Five mangrove species are in the IUCN Red List of threatened species.Mangroves in the Sunda Shelf provincehad a mapped extent in 2020 of 12,350 km2, representing 8.4% of the global mangrove resource by area. The main threats to mangroves are conversion for agricultural and aquaculture use, or for coastal infrastructure development. These practices impact on the remaining mangroves through coastal erosion,  land  subsidence  and  pollution.  Climate  change  (especially  sea-level  rise)  is  an  additional  and  serious threat.Today the Sunda Shelf mangroves cover ≈ 35% less than our broad estimations for 1970, based on country level studies;  however,  the  rate  of  area  loss  slowed to -4.8%  from  1996  to  2020 and  has  decelerated  further  since 2010. The Sunda Shelf mangrove area is estimated to decrease by 13.7% over the next 50 years. Moreover, we estimate  that  3.4%  of  the  mangroves  are  undergoing  degradation,  and  this  could  rise  to  10%  over  a  50-year period, based on an analysis of the decay of vegetation indexes. These estimates are very conservative; however, no other data sources were available to measure environmental degradation at the provincelevel. More than 30% of the Sunda Shelf mangrove extent could be submerged by 2070 due to sea-level rise. Overall, the Sunda Shelf mangrove ecosystem is assessed as Vulnerable (VU) under subcriteria A1 and C2.VU</t>
   </si>
   <si>
-    <t>na</t>
-  </si>
-  <si>
-    <t>RLE Database</t>
-  </si>
-  <si>
     <t>anthro threats (land conversion, aquaculture, pollution) to mangrove biodiversity documented</t>
   </si>
   <si>
-    <t>Mangroves of The Bay of Bengal</t>
-  </si>
-  <si>
-    <t>Mangroves of the Bay of Bengal is a regional ecosystem subgroup (level 4 unit of the IUCN Global Ecosystem Typology) spanning parts of South and Southeast Asia. It includes coastal areas of eastern India, Bangladesh, and northern and central Myanmar, and contains one of the largest single mangrove ecosystems in the world: the Sundarbans.Mangroves dominate along the extensive coastal waterways of the Ganges-Brahmaputra and Ayeyarwady deltas in  India-Bangladesh  and  Myanmar,respectively.  They  occur  on  mainly  coastal  alluvial  sediments  deposited  by these  and  other  river  systems.  Their  mapped  extent  in  2020  was  10,250  km2,  representing  7%  of  the  global mangrove area. The Bay of Bengal provincemangroves are threatened by highpopulation pressure and intense natural resources use, including mangrove-associated fisheries and conversion to agriculture or aquaculture. Mangrove degradation and  conversion  have  caused  serious  coastal  erosion.  Destructive  cyclones  exacerbated  by  climate  change  also cause  coastal  erosion  and  damage  to  mangroves,  while  reduced  freshwater  flows  and  salinity  intrusion  in  the Sundarbans are threatening salt-sensitive mangrove tree species like Heritiera formes. This species is classified as Endangered (EN) by IUCN, whileBruguiera hainesiiand Sonneratia griffithiiare Critically Endangered (CR).Today the Bay of Bengal mangroves cover ≈8% less than our broad estimation for 1970. The rate of decline has slowed since 2015 and, if the present rate persists, an overall decrease of -12% is projected over the next 50 years. However, they are expected to be resilient to even extreme sea-level rise scenarios, due to high sediment supply and vertical accretion. We estimate that 5% of the Bay of Bengal mangroves are undergoing degradation. This value could rise to 15% over a 50-year period based on decay of vegetation indexes. Overall, the Bay of Bengal mangrove ecosystem is assessed as Least Concern (LC).</t>
-  </si>
-  <si>
-    <t>mangroves of bay of bengal ecosystem under anthropogenic threats</t>
-  </si>
-  <si>
-    <t>Assessing ecosystem collapse risk in ecosystems dominated by foundation species: The case of fringe mangroves</t>
-  </si>
-  <si>
-    <t>Ecosystem collapse, i.e. the endpoint of ecosystem decline, is a central concept of IUCN Red List of Ecosystems (RLE) assessments and the identification of ecosystems most vulnerable to global environmental change. Estimating collapse risk can be challenging for ecosystems reliant on a few dominant species to perform most of their functions because the range of suitable and feasible indicators is small. This study investigates the robustness and adequacy of the current RLE approach for risk assessments in such ecosystems, using a fringe mangrove ecosystem as a case study. Following the RLE protocol, we constructed a conceptual model of the key ecosystem processes for the Philippines’ fringe mangrove forests. Satellite remote sensing data and existing maps of mangrove forests were then combined to assess the spatial distribution of the ecosystem considered (Criteria A and B), while the Normalized Difference Vegetation Index was used to assess biotic degradation (Criterion D). Insufficient data were available to assess Criteria C (environmental degradation) and E (quantitative analysis). Overall, the ecosystem was assessed as ‘Least Concern’ based on extensive geographic distribution and only weak support for declines in extent. Criterion D was classed as ‘Data Deficient’ since there was no clear relationship between the vegetation index and fringe mangrove degradation. Our results demonstrate how gaps in our appreciation and understanding of the structure and functioning of ecosystems are more likely to impede risk assessments of ecosystems characterised by a small number of foundation species, due to the low level of redundancy between candidate indicators available for their assessments. Satellite remote sensing combined with derivation of explicit conceptual ecosystem models provides a way to structure efforts to identify suitable indicators as well as opportunities to overcome many of these challenges, even for relatively data-poor ecosystems.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ecosystem collapse risk assessment for fringe mangroves; although anthro aren't listed explicity I assume it eligible still </t>
+    <t>Threatened ecosystems of Myanmar: An IUCN Red List of Ecosystems Assessment.</t>
+  </si>
+  <si>
+    <t>The Myanmar National Ecosystem Assessment contributes to the GEF funded Strengthening Sustainability of Protected Area Management in Myanmar project. To support the Myanmar National Ecosystem Assessment, Myanmar’s terrestrial ecosystems were assessed under the International Union for the Conservation of Nature (IUCN) Red List of Ecosystems Categories and Criteria. This report summarises the methods and findings of the assessment, including detailed ecological descriptions of the 64 ecosystem types assessed. A total of 64 ecosystem types were identified and evaluated under the IUCN Red List of Ecosystems categories and criteria. Twenty-nine (45.3%) ecosystems were assigned a threatened status, consisting of 8 (12.5%) Critically Endangered ecosystem types, 9 (14.1%) Endangered and 12 (18.8%) Vulnerable ecosystem types. One ecosystem type, Central Ayeyarwady Palm Savanna ecosystem types was confirmed as Collapsed. A further two ecosystem types, Ayeyarwady kanazo swamp forest and Southern Rakhine hills evergreen rainforest, were assessed with an upper plausible status outcome of Collapsed, although their final assessment was Critically Endangered. Twenty-eight ecosystem types were assessed as Near Threatened or Least Concern. However, a post-assessment expert review by experts suggested that 11 of the 25 Least Concern ecosystems could qualify for a different assessment outcome if more data was available. These 11 ecosystems were reclassified to Data Deficient. Thus, 17 of Myanmar’s ecosystem types were classified as Data Deficient. Data deficient ecosystem types were primarily ecosystems for which there were historical records, but with insufficient published information to assess the criteria (e.g. Rocky Tanintharyi karst). Alternatively, there were insufficient distribution records to incorporate into our mapping workflow to allow assessments of Criterion A and B (e.g. Grassy saltmarsh). Data deficient ecosystems also tended to occur in regions that were inaccessible to field researchers due to travel restrictions (e.g. Shan limestone grasslands). Urgent further work to confirm the distribution and assess the status of these data deficient ecosystems is recommended. This IUCN Red List of Ecosystems assessment has shown a dire situation for Myanmar’s ecosystems. Of the area assessed, nearly two-thirds (64%, 426,628 km2) is mapped as a natural ecosystem type, but of this over half (57.8%, 24,750 km2) of remaining area contains a threatened ecosystem type (CR, EN or VU). This means over one third of Myanmar’s land area contains threatened ecosystems. There needs to be an increase in conservation efforts to reverse this situation and slow the trajectory towards collapse for ecosystems that are not currently threatened. Conservation planning will be key to identify what are the best conservation actions and where to apply them to reduce the risk of collapse for Myanmar’s natural ecosystems.</t>
+  </si>
+  <si>
+    <t>threatened ecosystems assessment of myanmar; drivers of ecosystem decline assessed</t>
   </si>
   <si>
     <t>Ecosystem assessment of mountain ash forest in the Central Highlands of Victoria, south-eastern Australia</t>
@@ -1008,22 +258,22 @@
     <t>mountain ash forest ecosystem risk assessment, decline from logging and fire</t>
   </si>
   <si>
-    <t>Threatened Status Assessment of Multiple Grassland Ecosystems and Conservation Strategies in the Xilin River Basin, NE China</t>
-  </si>
-  <si>
-    <t>The Red List of Ecosystems, proposed by the International Union for Conservation of Nature can determine the status of ecosystems for biodiversity conservation. In this study, we applied the Red List of Ecosystems Categories and Criteria 2.0 with its four major criteria (A, B, C, and D) to assess twelve dominant ecosystems in the Xilin River Basin, a representative grassland-dominating area in China. We employed Geographical Information Systems and remote sensing to process the obtained satellite products from the years 2000 to 2015, and generated indicators for biological processes and degradation of environment with boreal ecosystem productivity simulator. The results show that all twelve ecosystems in the Xilin River Basin confront varying threats: Artemisia frigida grassland and Festuca ovina grassland face the highest risk of collapse, sharing an endangered status; Filifolium sibiricum meadow grassland and Leymus chinensis grassland have a least concern status, while the remaining eight ecosystems display a vulnerable status. This study overcomes the limits of data deficiency by introducing the boreal ecosystem productivity simulator to simulate biological processes and the plant–environment interaction. It sheds light on further application of the Red List of Ecosystems, and bridges the research gap and promote local ecosystems conservation in China.</t>
-  </si>
-  <si>
-    <t>threatened status assessment of grassland ecosystems</t>
-  </si>
-  <si>
-    <t>Mangroves of the South China Sea</t>
-  </si>
-  <si>
-    <t>The 'Mangroves of South China Sea' is a regional ecosystem subgroup (level 4 unit of the IUCN Global Ecosystem Typology in the South China Sea province. It includes intertidal forests and shrublands of the marine ecoregions of the Gulf of Tonkin, South China Sea Oceanic Islands and Southern China. The diverse biota of this ecoregion is characterised by 42 species of true mangroves, plus many associated taxa. There is a significant decline in species diversity with increasing latitude towards the northern limit of mangroves in Fujian Province. Two species: Avicennia rumphianaand Camptostemon philippinensisare in the IUCN Red List of threatened species.  The South China Sea ecoregion mangroves are mainly scattered open coast and estuarine formations, except in the Red River Delta. Their mapped extent in 2020 was 543 km2representing only 0.4% of the global mangrove resource. The current threats to mangroves are mainly from coastal urbanisation and industrialisation, sea dyke construction, pollution,  and  climate-related  impacts,  especially  from  typhoons,  which  occur  frequently  in  thisprovince.Today, the South China Sea mangroves cover ≈36% less than in 1970 based on national studies. The South China Sea mangroves are also threatened by sea-level rise(SLR). Under a mid-high SLR scenario, and considering the limited coastal sediment supply, 50% of the mangrove area will be submerged by 2070. Moreover, we estimate that ≈3.5% of the mangroves are undergoing degradation. Based on analysis of the decay of vegetation indexes, this could rise to 10.2% over a 50-year period. These estimates are very conservative; however, no other data sources were available to measure environmental degradation at the ecoregion level. Considering the significant effect of future SLR, the South China Sea mangroves are assessed as Endangered (EN).EN</t>
-  </si>
-  <si>
-    <t>mangroves of south china Sea with significant decline in species diversity due to anthro threats (Industrialisation, pollution, urbanization, etc)</t>
+    <t>Status of connected wetlands of the Lake Eyre Basin, Australia</t>
+  </si>
+  <si>
+    <t>The Lake Eyre Basin, one of the world's last unregulated wild river basins, covers almost one sixth of the Australian continent, with large areas of connected wetlands (73 903 km2), including floodplains, lakes, waterholes and river channels. Few data existed and so we used literature and government biotic and abiotic data and anthropogenic impacts to assess the conservation risk of the ecosystem as Least Concern (IUCN Red List criteria for ecosystems, version 2.0). This was based on limited distributional change and low levels of degradation or anthropogenic threatening processes. The approach could be applied to ecosystem assessments of other large river basins around the world, given the Lake Eyre Basin occupies one extreme (unmodified) while the Aral Sea (collapsed), previously assessed, occupies the other extreme (highly modified). River flow analysis with available biotic data is critical for risk assessment as well as identification and tracking of long-term threats. Assessment was possible at this large basin scale and appropriate, given the critical importance of connectivity but could also occur at finer spatial scale. Increased diversions for irrigation, mining impacts on floodplains and projected increased temperatures threaten the current status (Least Concern) of the connected wetlands of the Lake Eyre Basin ecosystem.</t>
+  </si>
+  <si>
+    <t>risk of future ecosystem degradation with anthro impacts analyzed (irrgiation, mining impacts, increased temp)</t>
+  </si>
+  <si>
+    <t>Vulnerability of Antarctic shallow invertebrate-dominated ecosystems</t>
+  </si>
+  <si>
+    <t>Human impacts threaten not only species, but also entire ecosystems. Ecosystems under stress can collapse or transition into different states, potentially reducing biodiversity at a variety of scales. Here we examine the vulnerability of Antarctic shallow invertebrate-dominated ecosystems, which may be threatened for several reasons. These unique shallow-water communities mostly consist of dark-adapted invertebrates, and rely on sea ice to create low-light marine environments. Climate change is likely to cause early breakout of seasonal sea ice in parts of Antarctica, which will dramatically increase the amount of light reaching shallow seabed. This is predicted to result in ecological regime shifts, in which invertebrate-dominated communities are replaced by macroalgal beds. Habitat for these endemic Antarctic ecosystems is globally rare, and the fragmented nature of their distribution along Antarctic coast increases their sensitivity to change. Concurrently, human activities in Antarctica are concentrated in areas where these habitats occur, compounding potential impacts. While there are clear mechanisms of threat to these ecosystems, lack of knowledge about their spatial distribution obscures predictions of potential ecosystem loss, and the likelihood of recovery. In this paper we describe these ecosystems, their association with the environment and the reasons for their vulnerability. We estimate their spatial distribution around Antarctica using sea ice and bathymetric data, and apply the International Union for Conservation of Nature Red List of Ecosystems criteria to assess their vulnerability. Best available data suggest that shallow ice-covered ecosystems are likely Near Threatened to Vulnerable in places, although the magnitude of risk is spatially variable and requires additional data to strengthen the assessment.</t>
+  </si>
+  <si>
+    <t>vulnerability of antarctic shallow invertebrate ecosystems to climate change</t>
   </si>
   <si>
     <t>An International Union for Conservation of Nature risk assessment of coastal lowland rainforests of the Wet Tropics Bioregion, Queensland, Australia</t>
@@ -1033,42 +283,6 @@
   </si>
   <si>
     <t>iucn risk assessment of coastal lowland rainforests; agri and land clearing as anthropogenic drivers of loss</t>
-  </si>
-  <si>
-    <t>Using multiple lines of evidence to assess the risk of ecosystem collapse</t>
-  </si>
-  <si>
-    <t>Effective ecosystem risk assessment relies on a conceptual understanding of ecosystem dynamics and the synthesis of multiple lines of evidence. Risk assessment protocols and ecosystem models integrate limited observational data with threat scenarios, making them valuable tools for monitoring ecosystem status and diagnosing key mechanisms of decline to be addressed by management. We applied the IUCN Red List of Ecosystems criteria to quantify the risk of collapse of the Meso-American Reef, a unique ecosystem containing the second longest barrier reef in the world. We collated a wide array of empirical data (field and remotely sensed), and used a stochastic ecosystem model to backcast past ecosystem dynamics, as well as forecast future ecosystem dynamics under 11 scenarios of threat. The ecosystem is at high risk from mass bleaching in the coming decades, with compounding effects of ocean acidification, hurricanes, pollution and fishing. The overall status of the ecosystem is Critically Endangered (plausibly Vulnerable to Critically Endangered), with notable differences among Red List criteria and data types in detecting the most severe symptoms of risk. Our case study provides a template for assessing risks to coral reefs and for further application of ecosystem models in risk assessment.</t>
-  </si>
-  <si>
-    <t>ecosystem collapse risk assessment of meso american Reef using multiple evidences; Anthropogenic threats and biodiversity change</t>
-  </si>
-  <si>
-    <t>Assessing risk of estuarine ecosystem collapse</t>
-  </si>
-  <si>
-    <t>Estuarine ecosystems are increasingly threatened by coastal development and climate change. The large number of estuaries globally necessitates risk assessment to prioritise conservation efforts. Schemes for assessing risk of ecosystem collapse have been designed around terrestrial ecosystems, often defined by a single characteristic vegetation type, with their applicability to estuaries unclear. Here we consider the causes and symptoms of estuarine ecosystem collapse and assess, using a case study of the Chesapeake Bay, the applicability of ecosystem-level risk assessments to estuarine ecosystems, typified by mosaics of habitats. Functional estuaries are characterised by habitat heterogeneity and connectivity, maintenance of constituent habitats through recruitment, and a complex trophic structure including apex predators. Additionally, primary production and biomass are dominated by benthic, as opposed to pelagic, species. Hence, homogenisation of habitat types, decreased connectivity, recruitment failure, loss of apex predators and a decreased ratio of benthic to pelagic biomass may be symptoms of a trajectory towards collapse. In terrestrial ecosystems, criteria used for assessing risk of ecosystem collapse include declining or restricted distribution of ecosystems, degradation of the abiotic environment, changes in species composition and declining ecological function. As the boundaries of estuaries are typically defined by topography, rarely do significant changes in the area of the ecosystem occur. Furthermore, because the extent of estuaries is typically small, assessments based on area of occupancy may over-inflate risk. Instead, criteria based on abiotic and biotic changes, many of which are documented through monitoring programs, may be most useful for risk assessments of estuarine ecosystems.</t>
-  </si>
-  <si>
-    <t>estuarine ecosystem collapse risk from coastal development and climate ch.</t>
-  </si>
-  <si>
-    <t>Mangroves of the Western Coral Triangle</t>
-  </si>
-  <si>
-    <t>The 'Mangroves of the Western Coral Triangle' is a regional ecosystem subgroup (level 4 unit of the IUCN Global Ecosystem Typology. It includes intertidal forests and shrublands of the following marine ecoregions in the Western Coral  Triangle  province:  Banda  Sea,  Eastern  Philippines,  Halmahera,  Lesser  Sunda,  Northeast  Sulawesi, Palawan/North Borneo, Papua, and Sulawesi Sea/Makassar Strait. The diverse biota of this provinceincludes 48 species of true mangroves, plus many mangrove-associated taxa. Mangroveshad a mapped extent of 19,821 km2in 2020, representing 13.4% of the global mangrove resource by area.  Although only 4.7 % of the province’s mangroves occur on carbonate sediments, they include fragile patches of vegetation on many of the thousands of islands in the Western Coral Triangle, Mangroves are threatened by illegal logging,  conversion  for  agriculture  or  aquaculture,  and  industrial,  urban  and  tourism  development,  including coastal land reclamation and mining. They are also threatened by climate change, especially sea-level rise, and by increasingly frequent typhoons and tropical storms.Today the Western Coral Triangle mangroves cover ≈32% less than our estimate for 1970 based on national studies. The rate of loss declined to -6.6% from 1996 to 2020 and has slowed further since 2015. The Western Coral Triangle mangroves are estimated to decrease by -18% over the next 50 years. They are also threatened by future sea-level rise (SLR). Under a mid-high to extreme SLR scenario, more than 30% of the mangroves would be submerged by 2070. Moreover, we estimate that 4% of the mangroves are undergoing degradation and this could rise to 10.7% over a 50-year period based on analysis of the decay of vegetation indexes. These estimates are very conservative; however, no other data sources were available to measure environmental degradation at the provincelevel. Overall, the Western Coral Triangle mangrove ecosystem is assessed as Vulnerable (VU).VU</t>
-  </si>
-  <si>
-    <t>mangroves of western coral triangle ecosystem assessment; with anthropogenic threats (logging, agri/aqua conversion, industral dev, urban dev, mining, etc) to biodiversity</t>
-  </si>
-  <si>
-    <t>Threatened ecosystems of Myanmar: An IUCN Red List of Ecosystems Assessment.</t>
-  </si>
-  <si>
-    <t>The Myanmar National Ecosystem Assessment contributes to the GEF funded Strengthening Sustainability of Protected Area Management in Myanmar project. To support the Myanmar National Ecosystem Assessment, Myanmar’s terrestrial ecosystems were assessed under the International Union for the Conservation of Nature (IUCN) Red List of Ecosystems Categories and Criteria. This report summarises the methods and findings of the assessment, including detailed ecological descriptions of the 64 ecosystem types assessed. A total of 64 ecosystem types were identified and evaluated under the IUCN Red List of Ecosystems categories and criteria. Twenty-nine (45.3%) ecosystems were assigned a threatened status, consisting of 8 (12.5%) Critically Endangered ecosystem types, 9 (14.1%) Endangered and 12 (18.8%) Vulnerable ecosystem types. One ecosystem type, Central Ayeyarwady Palm Savanna ecosystem types was confirmed as Collapsed. A further two ecosystem types, Ayeyarwady kanazo swamp forest and Southern Rakhine hills evergreen rainforest, were assessed with an upper plausible status outcome of Collapsed, although their final assessment was Critically Endangered. Twenty-eight ecosystem types were assessed as Near Threatened or Least Concern. However, a post-assessment expert review by experts suggested that 11 of the 25 Least Concern ecosystems could qualify for a different assessment outcome if more data was available. These 11 ecosystems were reclassified to Data Deficient. Thus, 17 of Myanmar’s ecosystem types were classified as Data Deficient. Data deficient ecosystem types were primarily ecosystems for which there were historical records, but with insufficient published information to assess the criteria (e.g. Rocky Tanintharyi karst). Alternatively, there were insufficient distribution records to incorporate into our mapping workflow to allow assessments of Criterion A and B (e.g. Grassy saltmarsh). Data deficient ecosystems also tended to occur in regions that were inaccessible to field researchers due to travel restrictions (e.g. Shan limestone grasslands). Urgent further work to confirm the distribution and assess the status of these data deficient ecosystems is recommended. This IUCN Red List of Ecosystems assessment has shown a dire situation for Myanmar’s ecosystems. Of the area assessed, nearly two-thirds (64%, 426,628 km2) is mapped as a natural ecosystem type, but of this over half (57.8%, 24,750 km2) of remaining area contains a threatened ecosystem type (CR, EN or VU). This means over one third of Myanmar’s land area contains threatened ecosystems. There needs to be an increase in conservation efforts to reverse this situation and slow the trajectory towards collapse for ecosystems that are not currently threatened. Conservation planning will be key to identify what are the best conservation actions and where to apply them to reduce the risk of collapse for Myanmar’s natural ecosystems.</t>
-  </si>
-  <si>
-    <t>threatened ecosystems assessment of myanmar; drivers of ecosystem decline assessed</t>
   </si>
   <si>
     <t>Mayotte's mangroves are declining, according to the Red List of Ecosystems</t>
@@ -1088,22 +302,49 @@
     <t>mayotte mangroves declining from land clearing, urbanization and pollution</t>
   </si>
   <si>
-    <t>Assessing risks to marine ecosystems with indicators, ecosystem models and experts</t>
-  </si>
-  <si>
-    <t>Assessing risks to marine ecosystems is critical due to their biological and economic importance, and because many have recently undergone regime shifts due to overfishing and environmental change. Yet defining collapsed ecosystem states, selecting informative indicators and reconstructing long-term marine ecosystem changes remains challenging. The IUCN Red List of Ecosystems constitutes the global standard for quantifying risks to ecosystems and we conducted the first Red List assessment of an offshore marine ecosystem, focusing on the southern Benguela in South Africa. We used an analogous but collapsed ecosystem – the northern Benguela – to help define collapse in the southern Benguela and derived collapse thresholds with structured expert elicitation (i.e. repeatable estimation by expert judgment). To capture complex ecosystem dynamics and reconstruct historical ecosystem states, we used environmental indicators as well as survey-, catch- and model-based indicators. We listed the ecosystem in 1960 and 2015 as Endangered, with assessment outcomes robust to alternative model parametrizations. While many indicators improved between 1960 and 2015, seabird populations have suffered large declines since 1900 and remain at risk, pointing towards ongoing management priorities. Catch-based indicators often over-estimated risks compared to survey- and model-based indicators, warning against listing ecosystems as threatened solely based on indicators of pressure. We show that risk assessments provide a framework for interpreting data from indicators, ecosystem models and experts to inform the management of marine ecosystems. This work highlights the feasibility of conducting Red List of Ecosystems assessments for marine ecosystems.</t>
-  </si>
-  <si>
-    <t>risk assessment of marine ecosystem with overfishing and environmental change</t>
-  </si>
-  <si>
-    <t>Vulnerability of Antarctic shallow invertebrate-dominated ecosystems</t>
-  </si>
-  <si>
-    <t>Human impacts threaten not only species, but also entire ecosystems. Ecosystems under stress can collapse or transition into different states, potentially reducing biodiversity at a variety of scales. Here we examine the vulnerability of Antarctic shallow invertebrate-dominated ecosystems, which may be threatened for several reasons. These unique shallow-water communities mostly consist of dark-adapted invertebrates, and rely on sea ice to create low-light marine environments. Climate change is likely to cause early breakout of seasonal sea ice in parts of Antarctica, which will dramatically increase the amount of light reaching shallow seabed. This is predicted to result in ecological regime shifts, in which invertebrate-dominated communities are replaced by macroalgal beds. Habitat for these endemic Antarctic ecosystems is globally rare, and the fragmented nature of their distribution along Antarctic coast increases their sensitivity to change. Concurrently, human activities in Antarctica are concentrated in areas where these habitats occur, compounding potential impacts. While there are clear mechanisms of threat to these ecosystems, lack of knowledge about their spatial distribution obscures predictions of potential ecosystem loss, and the likelihood of recovery. In this paper we describe these ecosystems, their association with the environment and the reasons for their vulnerability. We estimate their spatial distribution around Antarctica using sea ice and bathymetric data, and apply the International Union for Conservation of Nature Red List of Ecosystems criteria to assess their vulnerability. Best available data suggest that shallow ice-covered ecosystems are likely Near Threatened to Vulnerable in places, although the magnitude of risk is spatially variable and requires additional data to strengthen the assessment.</t>
-  </si>
-  <si>
-    <t>vulnerability of antarctic shallow invertebrate ecosystems to climate change</t>
+    <t>Threatened Status Assessment of Multiple Grassland Ecosystems and Conservation Strategies in the Xilin River Basin, NE China</t>
+  </si>
+  <si>
+    <t>The Red List of Ecosystems, proposed by the International Union for Conservation of Nature can determine the status of ecosystems for biodiversity conservation. In this study, we applied the Red List of Ecosystems Categories and Criteria 2.0 with its four major criteria (A, B, C, and D) to assess twelve dominant ecosystems in the Xilin River Basin, a representative grassland-dominating area in China. We employed Geographical Information Systems and remote sensing to process the obtained satellite products from the years 2000 to 2015, and generated indicators for biological processes and degradation of environment with boreal ecosystem productivity simulator. The results show that all twelve ecosystems in the Xilin River Basin confront varying threats: Artemisia frigida grassland and Festuca ovina grassland face the highest risk of collapse, sharing an endangered status; Filifolium sibiricum meadow grassland and Leymus chinensis grassland have a least concern status, while the remaining eight ecosystems display a vulnerable status. This study overcomes the limits of data deficiency by introducing the boreal ecosystem productivity simulator to simulate biological processes and the plant–environment interaction. It sheds light on further application of the Red List of Ecosystems, and bridges the research gap and promote local ecosystems conservation in China.</t>
+  </si>
+  <si>
+    <t>threatened status assessment of grassland ecosystems</t>
+  </si>
+  <si>
+    <t>Using multiple lines of evidence to assess the risk of ecosystem collapse</t>
+  </si>
+  <si>
+    <t>Effective ecosystem risk assessment relies on a conceptual understanding of ecosystem dynamics and the synthesis of multiple lines of evidence. Risk assessment protocols and ecosystem models integrate limited observational data with threat scenarios, making them valuable tools for monitoring ecosystem status and diagnosing key mechanisms of decline to be addressed by management. We applied the IUCN Red List of Ecosystems criteria to quantify the risk of collapse of the Meso-American Reef, a unique ecosystem containing the second longest barrier reef in the world. We collated a wide array of empirical data (field and remotely sensed), and used a stochastic ecosystem model to backcast past ecosystem dynamics, as well as forecast future ecosystem dynamics under 11 scenarios of threat. The ecosystem is at high risk from mass bleaching in the coming decades, with compounding effects of ocean acidification, hurricanes, pollution and fishing. The overall status of the ecosystem is Critically Endangered (plausibly Vulnerable to Critically Endangered), with notable differences among Red List criteria and data types in detecting the most severe symptoms of risk. Our case study provides a template for assessing risks to coral reefs and for further application of ecosystem models in risk assessment.</t>
+  </si>
+  <si>
+    <t>ecosystem collapse risk assessment of meso american Reef using multiple evidences; Anthropogenic threats and biodiversity change</t>
+  </si>
+  <si>
+    <t>Assessing ecosystem collapse risk in ecosystems dominated by foundation species: The case of fringe mangroves</t>
+  </si>
+  <si>
+    <t>Ecosystem collapse, i.e. the endpoint of ecosystem decline, is a central concept of IUCN Red List of Ecosystems (RLE) assessments and the identification of ecosystems most vulnerable to global environmental change. Estimating collapse risk can be challenging for ecosystems reliant on a few dominant species to perform most of their functions because the range of suitable and feasible indicators is small. This study investigates the robustness and adequacy of the current RLE approach for risk assessments in such ecosystems, using a fringe mangrove ecosystem as a case study. Following the RLE protocol, we constructed a conceptual model of the key ecosystem processes for the Philippines’ fringe mangrove forests. Satellite remote sensing data and existing maps of mangrove forests were then combined to assess the spatial distribution of the ecosystem considered (Criteria A and B), while the Normalized Difference Vegetation Index was used to assess biotic degradation (Criterion D). Insufficient data were available to assess Criteria C (environmental degradation) and E (quantitative analysis). Overall, the ecosystem was assessed as ‘Least Concern’ based on extensive geographic distribution and only weak support for declines in extent. Criterion D was classed as ‘Data Deficient’ since there was no clear relationship between the vegetation index and fringe mangrove degradation. Our results demonstrate how gaps in our appreciation and understanding of the structure and functioning of ecosystems are more likely to impede risk assessments of ecosystems characterised by a small number of foundation species, due to the low level of redundancy between candidate indicators available for their assessments. Satellite remote sensing combined with derivation of explicit conceptual ecosystem models provides a way to structure efforts to identify suitable indicators as well as opportunities to overcome many of these challenges, even for relatively data-poor ecosystems.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ecosystem collapse risk assessment for fringe mangroves; although anthro aren't listed explicity I assume it eligible still </t>
+  </si>
+  <si>
+    <t>Red list of China's forest ecosystems: A conservation assessment and protected area gap analysis</t>
+  </si>
+  <si>
+    <t>Current biodiversity loss is far greater than at any time in human history. As complementary tool to prioritize biodiversity for conservation, the IUCN Red List of Ecosystems (RLE) is well justified as a conservation tool. Although China's biodiversity is among the world's richest, a significant part of this diversity is under threat. Based on the distribution of 229 forest formations, we assessed the risk status according to the IUCN RLE criteria, and evaluated the conservation status of threatened forests by comparing ecosystem distribution with terrestrial national and provincial nature reserves (NNRs and PNRs, respectively). We found that 90 threatened forest formations accounted for 16% of the area, but for 39.3% of the number of assessed formations. Threatened forest formations were mainly located in western Sichuan, Yunnan, southeastern Xizang, southwestern Guangxi, Hainan Island, northeastern China, and the mountains of Taiwan. Tropical rain forests and evergreen broad-leaved forests together accounted for the highest number of threatened formations. Northern Xinjiang (with the Tianshan and Altai Mountains) proved to be a unique area that has rarely been identified as hotspot of plant conservation. On average, NNRs covered 13.2%, and NNRs and PNRs together covered 22.7%, of the threatened forest distribution areas. However, 15 threatened forest formations were not covered by NNRs or PNRs. We suggest that the red list of ecosystems will contribute towards providing a more informative picture of the status of biodiversity. Our work highlights the need to use the red list of ecosystems as additional tool in plant conservation.</t>
+  </si>
+  <si>
+    <t>red List assessment of china forest ecosystems; showing threatened status from anthropogenic impacts</t>
+  </si>
+  <si>
+    <t>Assessing risk of estuarine ecosystem collapse</t>
+  </si>
+  <si>
+    <t>Estuarine ecosystems are increasingly threatened by coastal development and climate change. The large number of estuaries globally necessitates risk assessment to prioritise conservation efforts. Schemes for assessing risk of ecosystem collapse have been designed around terrestrial ecosystems, often defined by a single characteristic vegetation type, with their applicability to estuaries unclear. Here we consider the causes and symptoms of estuarine ecosystem collapse and assess, using a case study of the Chesapeake Bay, the applicability of ecosystem-level risk assessments to estuarine ecosystems, typified by mosaics of habitats. Functional estuaries are characterised by habitat heterogeneity and connectivity, maintenance of constituent habitats through recruitment, and a complex trophic structure including apex predators. Additionally, primary production and biomass are dominated by benthic, as opposed to pelagic, species. Hence, homogenisation of habitat types, decreased connectivity, recruitment failure, loss of apex predators and a decreased ratio of benthic to pelagic biomass may be symptoms of a trajectory towards collapse. In terrestrial ecosystems, criteria used for assessing risk of ecosystem collapse include declining or restricted distribution of ecosystems, degradation of the abiotic environment, changes in species composition and declining ecological function. As the boundaries of estuaries are typically defined by topography, rarely do significant changes in the area of the ecosystem occur. Furthermore, because the extent of estuaries is typically small, assessments based on area of occupancy may over-inflate risk. Instead, criteria based on abiotic and biotic changes, many of which are documented through monitoring programs, may be most useful for risk assessments of estuarine ecosystems.</t>
+  </si>
+  <si>
+    <t>estuarine ecosystem collapse risk from coastal development and climate ch.</t>
   </si>
   <si>
     <t>Integrating outcomes of IUCN red list of ecosystems assessments for connected coastal wetlands</t>
@@ -1115,46 +356,106 @@
     <t>coastal wetlands global declines from habitat clearing and pollution</t>
   </si>
   <si>
-    <t>Red list of China's forest ecosystems: A conservation assessment and protected area gap analysis</t>
-  </si>
-  <si>
-    <t>Current biodiversity loss is far greater than at any time in human history. As complementary tool to prioritize biodiversity for conservation, the IUCN Red List of Ecosystems (RLE) is well justified as a conservation tool. Although China's biodiversity is among the world's richest, a significant part of this diversity is under threat. Based on the distribution of 229 forest formations, we assessed the risk status according to the IUCN RLE criteria, and evaluated the conservation status of threatened forests by comparing ecosystem distribution with terrestrial national and provincial nature reserves (NNRs and PNRs, respectively). We found that 90 threatened forest formations accounted for 16% of the area, but for 39.3% of the number of assessed formations. Threatened forest formations were mainly located in western Sichuan, Yunnan, southeastern Xizang, southwestern Guangxi, Hainan Island, northeastern China, and the mountains of Taiwan. Tropical rain forests and evergreen broad-leaved forests together accounted for the highest number of threatened formations. Northern Xinjiang (with the Tianshan and Altai Mountains) proved to be a unique area that has rarely been identified as hotspot of plant conservation. On average, NNRs covered 13.2%, and NNRs and PNRs together covered 22.7%, of the threatened forest distribution areas. However, 15 threatened forest formations were not covered by NNRs or PNRs. We suggest that the red list of ecosystems will contribute towards providing a more informative picture of the status of biodiversity. Our work highlights the need to use the red list of ecosystems as additional tool in plant conservation.</t>
-  </si>
-  <si>
-    <t>red List assessment of china forest ecosystems; showing threatened status from anthropogenic impacts</t>
-  </si>
-  <si>
-    <t>WOS:000360940400006</t>
-  </si>
-  <si>
-    <t>Fauna crime: elucidating the potential source and introduction history of European smelt (Osmerus eperlanus L.) into Lake Storsjoen, Norway</t>
-  </si>
-  <si>
-    <t>The ability to accurately determine the original source of invading species offers several powerful applications in invasive species ecology and management and may enable important information on the invading species in its native habitat. Lake Storsjoen in South-Central Norway was recently found to have been subjected to an illegal translocation of the European smelt (Osmerus eperlanus). The main aim of this study was to infer the most likely source (s) of the invading smelt by using microsatellite markers, and subsequently to infer its introduction history. The results indicated that the smelt is most likely a result of introduction from the large Lake Mjosa, and that the translocated smelt comprise a large number of individuals. The smelt in Lake Storsjoen showed no significant genetic bottleneck effect. However, a corresponding significant test for a recent population expansion indicates that the smelt has had a high reproductive success and population growth in its new environment. The results from this study illustrate the usefulness of applying multilocus genetic markers for inferring origin of translocated populations, demographic events and introduction histories comprising an effective tool for assessment of invasive species.</t>
-  </si>
-  <si>
-    <t>10.1007/s10592-015-0724-2</t>
+    <t>WOS:000070978100008</t>
+  </si>
+  <si>
+    <t>Field assessment of numerical impacts of coastal sewage disposal on fish larvae relative to natural variability</t>
+  </si>
+  <si>
+    <t>Sewage disposal in aquatic environments can have significant impacts on assemblages of organisms. There have been few field investigations on effects of sewage disposal on fish larvae. Data on abundances of larvae, current velocities and the size and shape of sewage plumes from point-source shoreline outfalls off Sydney (Australia) indicated that alongshore currents could transport large numbers of fish larvae into plumes, potentially affecting their health. Assemblages of fish larvae in surface sewage plumes differed to those in distant shelf (control) waters, but no such impacts were detected for assemblages in subsurface (20 m depth) waters beneath plumes. No predictable negative or positive numerical responses of fish larvae to sewage disposal were detected. Abundances of fish larvae fluctuated greatly in space and throughout time, and responses appeared to vary between taxa, outfalls and sampling periods. However, the large inherent level of natural spatial and temporal variability in abundances of larvae confounded the detection of possible impacts. Future field investigations need to focus on effects of sewage disposal on the health and condition of fish larvae. Designs for future field-based studies are discussed.</t>
+  </si>
+  <si>
+    <t>10.1023/A:1007365232465</t>
+  </si>
+  <si>
+    <t>Keck et al</t>
+  </si>
+  <si>
+    <t>coastal sewage (pollution) disposal impacts on fish larvae assemblages</t>
+  </si>
+  <si>
+    <t>WOS:000076782200006</t>
+  </si>
+  <si>
+    <t>Effects of nitrogen addition on successional dynamics and species diversity in Michigan old-fields</t>
+  </si>
+  <si>
+    <t>1 We examined the impact of nitrogen addition on early successional dynamics and plant species diversity in replicate plots of an old-field succession treatment in south-western Michigan, USA, for 7 years following abandonment from agriculture. 2 Nitrogen addition significantly increased above-ground plant biomass, but had no effect on the displacement or persistence of different life-history groups. Annual species made up a similar proportion of community biomass and decreased at equivalent rates in control and nitrogen-addition microplots. Perennial species biomass increased at similar rates in the control and nitrogen-addition microplots. 3 Annual species dominated initially, but declined in abundance over the first 4 years and were replaced by biennials and then herbaceous perennials. The resulting high numbers of species losses and gains were not affected by nitrogen addition. 4 Nitrogen addition did not affect mean species density or the Shannon index of diversity. There was also no temporal change in the similarity of species composition between control and nitrogen-addition microplots, indicating that nitrogen addition did not cause divergence over time in community composition. In year 7, similar species dominated the nitrogen-addition and control microplots, but there were differences in species composition and abundance of the subordinate species in each community. 5 Only in year 6 of this study was there a significant negative relationship between community biomass and the Shannon diversity index. There was no significant relationship between community biomass and species density in any of the first 7 years following abandonment. Thus, the community response to increased biomass due to nitrogen addition was expressed primarily through changes in community structure, not richness. 6 The effects of nitrogen addition on the early successional dynamics, species composition and consequently diversity of a plant community may depend on initial site conditions. The response to nitrogen enrichment may be slower in sites such as ours with fertile soils that become dominated by herbaceous perennial dicots.</t>
+  </si>
+  <si>
+    <t>10.1046/j.1365-2745.1998.8650794.x</t>
+  </si>
+  <si>
+    <t>murphy et al</t>
+  </si>
+  <si>
+    <t xml:space="preserve">effects on nitrogen addition on plant diversity </t>
+  </si>
+  <si>
+    <t>WOS:000175841000005</t>
+  </si>
+  <si>
+    <t>Estimating the long-term effects of stocking domesticated trout into wild brown trout (Salmo trutta) populations: an approach using microsatellite DNA analysis of historical and contemporary samples</t>
+  </si>
+  <si>
+    <t>Indigenous salmonid fish gene pools are affected by domesticated conspecifics, derived from aquaculture escapes and deliberate releases. Variability was examined at nine microsatellite loci in order to assess the long-term impact of stocking domesticated trout in two brown trout populations. The study was based on analysis of two historical samples (194556), represented by old scale collections, and seven contemporary samples (1986-2000). In one population historical and contemporary samples were remarkably genetically similar despite more than a decade of intense stocking. Estimation of admixture proportions showed a small genetic contribution from domesticated trout (approximately 6%), and individual admixture analysis demonstrated a majority of nonadmixed individuals. The expected genetic contribution by domesticated trout was 64%, assessed from the number of stocked trout and assuming equal survival and reproductive performance of wild and domesticated trout. This demonstrates poor performance and low fitness of domesticated trout in the wild. In another population there was a strong genetic contribution from domesticated trout (between 57% and 88% in different samples), both in samples from a broodstock thought to represent the indigenous population and in a sample of wild spawners. Survival of domesticated trout and admixture with indigenous fish in the broodstock and subsequent stocking into the river, combined with a low population size of native trout relative to the number of stocked trout, could explain the observed introgression. Few nonadmixed individuals remained in the introgressed population, and I discuss how individual admixture analysis can be used to identify and conserve nonintrogressed remains of the population.</t>
+  </si>
+  <si>
+    <t>10.1046/j.1365-294X.2002.01495.x</t>
   </si>
   <si>
     <t>shaw et al</t>
   </si>
   <si>
-    <t>Illegal translocation of European smelt into Norwegian lake; anthro introduction of invasive species affecting biodiversity</t>
-  </si>
-  <si>
-    <t>WOS:000369456300023</t>
-  </si>
-  <si>
-    <t>Genetic consequences of human forest exploitation in two colobus monkeys in Guinea Bissau</t>
-  </si>
-  <si>
-    <t>The ability of forest-dwelling species to adapt to changes in their habitat is being increasingly challenged by the rapid pace of human-induced forest degradation. Understanding the effect of such environmental changes on biodiversity requires comparative analyses across species living within the same habitats. We investigated the effect of forest exploitation on the genetic structure and demography of two sympatric arboreal primates showing differences in their socioecology: the Western black-and-white colobus (Colobus polykomos) and Temminck's red colobus (Procolobus badius temminckii). We conducted the study in a fragmented and human-impacted forest in Guinea Bissau. Using microsatellite data from six C. polykomos and eight P. b. temminckii social groups, we found that in C polykomos the distribution of genetic diversity followed an isolation-by-distance pattern whereas for P. b. temminckii, the results suggested restriction in female dispersal. We detected a strong, recent bottleneck for both primates, which we inferred to have resulted from the anthropogenic exploitation of forest resources in the last centuries. The bottleneck signal was stronger for P. b. temminckii as a likely consequence of its larger estimated ancestral population size. Finally, we discussed the different analytical approaches used. Our results confirm that P. b. temminckii is more affected by habitat changes than C polykomos, despite being phylogenetically close. Nonetheless, the low estimated effective population sizes and the known demographic changes indicate that both species are severely threatened by human forest exploitation, requiring urgent conservation action. (C) 2015 Elsevier Ltd. All rights reserved.</t>
-  </si>
-  <si>
-    <t>10.1016/j.biocon.2015.12.019</t>
-  </si>
-  <si>
-    <t>result of human forest exploitation on colobus monkeys</t>
+    <t>effects of stocking domesticated trout on wild brown trout populations</t>
+  </si>
+  <si>
+    <t>WOS:000178213200007</t>
+  </si>
+  <si>
+    <t>Fertilization with nitrogen and phosphorus increases abundance of non-native species in Hawaiian montane forests</t>
+  </si>
+  <si>
+    <t>We examined the effects of fertilization on the diversity, abundance, and cover of the understory plant community of two montane wet forests in Hawaii. One site occupies a young substrate, where aboveground tree growth is limited by nitrogen (N), while the other site is on an older substrate, where aboveground tree growth is limited by phosphorus (P). Both sites contained an on-going, long-term factorial fertilization experiment in which plots were fertilized semi-annually with N, P, or N and P in combination. In each fertilization treatment, we measured density of species greater than or equal to0.5 m tall and percent cover of species &lt;0.5 m tall. Fertilization with N reduced species richness at the young, N-limited site, but none of the nutrient additions altered species richness at the older, P-limited site. Species diversity and evenness were not affected by fertilization at either site. At the site with low N availability, plots fertilized with NP had higher densities of the non-native ginger Hedychium gardnerianum, and at the site with low P-availability, densities of the exotic shrub Rubus argutus were higher in P- and NP-fertilized plots. Other effects included declines in moss cover with fertilization at both sites, and reduced abundance of native seedlings in response to N and NP addition at the N-limited site. Continued long-term fertilization could lead to greater dominance of non-native species by encouraging their growth at the expense of native species, which may suffer decreased recruitment as fertilization and increased abundance of the non-native species may reduce suitable substrates for seedling establishment.</t>
+  </si>
+  <si>
+    <t>10.1023/A:1020332824836</t>
+  </si>
+  <si>
+    <t>fertilization increases abundance of non-native species in forests</t>
+  </si>
+  <si>
+    <t>WOS:000182948500002</t>
+  </si>
+  <si>
+    <t>Effects of the exotic macrophyte, para grass (Urochloa mutica), on benthic and epiphytic macroinvertebrates of a tropical floodplain</t>
+  </si>
+  <si>
+    <t>1. We examined the effect of the exotic macrophyte, para grass (Urochloa mutica ), on benthic and epiphytic macroinvertebrates of a tropical floodplain in northern Australia. Macroinvertebrates were sampled from four grass communities: (1) para grass, (2) hymenachne (Hymenachne acutigluma ), a native perennial; (3) rice (Oryza meridionalis ), a native annual, and (4) areas where para grass had been sprayed with herbicide. 2. Macroinvertebrate richness, abundance and community similarity showed very few differences among the grass communities, particularly in the epiphytic habitat. Benthic invertebrates showed some differences among grasses, with lower richness and abundance and different community structure associated with hymenachne. Herbicide control of para grass had no apparent effect on benthic invertebrates but reduced the abundance of epiphytic invertebrates in the short term. 3. The results of this study indicate that para grass has very little impact on macroinvertebrate communities, despite the changes to macrophyte communities. This is probably because para grass has similar physical structure to the native grasses and because none of these grasses contribute directly to aquatic food webs. Control of para grass using herbicide has little impact on aquatic invertebrates. This suggests that predicting the impact of weed invasion in wetlands requires an understanding of both the functional properties of macrophytes and the habitat preferences of the macroinvertebrates.</t>
+  </si>
+  <si>
+    <t>10.1046/j.1365-2427.2003.01072.x</t>
+  </si>
+  <si>
+    <t>exotic macrophyte para grass (IAS) effects on benthic communities</t>
+  </si>
+  <si>
+    <t>WOS:000185371200002</t>
+  </si>
+  <si>
+    <t>Conservation of Mediterranean temporary ponds under agricultural intensification: an evaluation using amphibians</t>
+  </si>
+  <si>
+    <t>This study examined responses of amphibians breeding in Mediterranean temporary ponds to a gradient of agricultural intensification, aiming to identify land uses and management prescriptions favouring the conservation of these habitats in farmed landscapes. Larval amphibian assemblages and habitat attributes were sampled at 57 ponds, 10 of which had been converted into permanent irrigation reservoirs. Species richness increased with area and hydroperiod in temporary ponds, with the addition of rare species to ponds with long hydroperiods resulting in a tendency for the less widespread species (e.g. Triturus marmoratus and T. boscai) to occur in the most species-rich ponds, while species-poor ponds consisted predominantly of widespread species only (nested pattern). However, one species (Pelodytes punctatus) was largely restricted to the most ephemeral ponds, whereas permanent irrigation reservoirs were species-poor and lacked most species occurring in temporary waters. The strongest negative correlates of amphibian abundances were the intensification of agricultural land uses, the transformation of ponds into permanent reservoirs and the introduction of exotic predators (fish and crayfish) from the irrigation channels. The results suggest that conservation of temporary pond amphibian assemblages in Mediterranean farmland requires networks of ponds with diverse hydroperiods, where the natural hydrologic regimes, less intensive land uses and isolation from irrigation waters should be preserved. (C) 2003 Elsevier Ltd. All rights reserved.</t>
+  </si>
+  <si>
+    <t>10.1016/S0006-3207(03)00051-X</t>
+  </si>
+  <si>
+    <t>Jaureguiberry et al</t>
+  </si>
+  <si>
+    <t>intensification gradient (range of how land use intensity increases from one point to other); response of amphibians to agri intensification gradient</t>
   </si>
   <si>
     <t>WOS:000186895000002</t>
@@ -1172,79 +473,335 @@
     <t>chinese sturgeon population decline after dam construction blocked migratory route</t>
   </si>
   <si>
-    <t>WOS:000362824300001</t>
-  </si>
-  <si>
-    <t>Short-term genetic consequences of habitat loss and fragmentation for the neotropical palm Oenocarpus bataua</t>
-  </si>
-  <si>
-    <t>Habitat loss and fragmentation may impact animal-mediated dispersal of seed and pollen, and a key question is how the genetic attributes of plant populations respond to these changes. Theory predicts that genetic diversity may be less sensitive to such disruptions in the short term, whereas inbreeding and genetic structure may respond more strongly. However, results from studies to date vary in relation to species, context and the parameter being assessed, triggering calls for more empirical studies, especially from the tropics, where plant-animal dispersal mutualisms are both disproportionately common and at risk. We compared the genetic characteristics of adults and recruits in a long-lived palm Oenocarpus bataua in a recently fragmented landscape (&lt;2 generations) in northwest Ecuador using a suite of 10 polymorphic microsatellite markers. We sampled individuals from six forest fragments and one nearby continuous forest. Our goal was to assess short-term consequences of fragmentation, with a focus on how well empirical data from this system follow theoretical expectations. Mostly congruent with predictions, we found stronger genetic differentiation and fine-scale spatial genetic structure among recruits in fragments compared with recruits in continuous forest, but we did not record differences in genetic diversity or inbreeding, nor did we record any differences between adults in fragments and adults in continuous forest. Our findings suggest that genetic characteristics of populations vary in their sensitivity to change in response to habitat loss and fragmentation, and that fine-scale spatial genetic structure may be a particularly useful indicator of genetic change in recently fragmented landscapes.</t>
-  </si>
-  <si>
-    <t>10.1038/hdy.2015.35</t>
-  </si>
-  <si>
-    <t>result of habitat loss and fragmentation for neotropical palm</t>
-  </si>
-  <si>
-    <t>WOS:000175841000005</t>
-  </si>
-  <si>
-    <t>Estimating the long-term effects of stocking domesticated trout into wild brown trout (Salmo trutta) populations: an approach using microsatellite DNA analysis of historical and contemporary samples</t>
-  </si>
-  <si>
-    <t>Indigenous salmonid fish gene pools are affected by domesticated conspecifics, derived from aquaculture escapes and deliberate releases. Variability was examined at nine microsatellite loci in order to assess the long-term impact of stocking domesticated trout in two brown trout populations. The study was based on analysis of two historical samples (194556), represented by old scale collections, and seven contemporary samples (1986-2000). In one population historical and contemporary samples were remarkably genetically similar despite more than a decade of intense stocking. Estimation of admixture proportions showed a small genetic contribution from domesticated trout (approximately 6%), and individual admixture analysis demonstrated a majority of nonadmixed individuals. The expected genetic contribution by domesticated trout was 64%, assessed from the number of stocked trout and assuming equal survival and reproductive performance of wild and domesticated trout. This demonstrates poor performance and low fitness of domesticated trout in the wild. In another population there was a strong genetic contribution from domesticated trout (between 57% and 88% in different samples), both in samples from a broodstock thought to represent the indigenous population and in a sample of wild spawners. Survival of domesticated trout and admixture with indigenous fish in the broodstock and subsequent stocking into the river, combined with a low population size of native trout relative to the number of stocked trout, could explain the observed introgression. Few nonadmixed individuals remained in the introgressed population, and I discuss how individual admixture analysis can be used to identify and conserve nonintrogressed remains of the population.</t>
-  </si>
-  <si>
-    <t>10.1046/j.1365-294X.2002.01495.x</t>
-  </si>
-  <si>
-    <t>effects of stocking domesticated trout on wild brown trout populations</t>
-  </si>
-  <si>
-    <t>WOS:000432992100019</t>
-  </si>
-  <si>
-    <t>Genetic diversity through time and space: diversity and demographic history from natural history specimens and serially sampled contemporary populations of the threatened Gouldian finch (Erythrura gouldiae)</t>
-  </si>
-  <si>
-    <t>Declines in population size can compromise the viability of populations by reducing the effective population size (N-e), which may result in loss of genetic diversity and inbreeding. Temporal population genetic data can be a powerful tool for testing the presence and severity of reductions in N-e. The Gouldian finch (Erythrura gouldiae) is a flagship for conservation of Australian monsoonal savanna species. This species underwent severe population declines in the twentieth century due to land use changes associated with European colonization. Microsatellite and mitochondrial genetic data from Gouldian finch samples sourced from natural history collections prior to land use changes were compared with contemporary samples to estimate the severity of decline in effective population size and to detect changes in gene flow. These data show that Gouldian finch decline was not as severe as some sources suggest, and that population genetic connectivity has not changed following land use changes in the twentieth century. Multiple estimators of current N-e using genetic data from consecutive years suggest the Gouldian finch N-e is likely between a few hundred and a few thousand individuals, with some estimates within the range considered of conservation concern. This work has identified the need to genetically characterize populations in Queensland, and to understand critical demographic parameters (e.g. lifespan) in the Gouldian finch. Understanding these factors is vital to further improve genetic estimates of population size, key to the formation of appropriate conservation management of this species.</t>
-  </si>
-  <si>
-    <t>10.1007/s10592-018-1051-1</t>
-  </si>
-  <si>
-    <t>Gouldian finch population decline due to land use change and fire</t>
-  </si>
-  <si>
-    <t>WOS:000328626100023</t>
-  </si>
-  <si>
-    <t>Assessment Impacts of Weather and Land Use/Land Cover (LULC) Change on Urban Vegetation Net Primary Productivity (NPP): A Case Study in Guangzhou, China</t>
-  </si>
-  <si>
-    <t>Net primary productivity (NPP) can indicate vegetation ecosystem services ability and reflect variation response to climate change and human activities. This study applied MODIS-1 km NPP products to investigate the NPP variation from 2001 to 2006, a fast urban expansion and adjustment period in Guangzhou, China, and quantify the impacts of weather and land use/land cover (LULC) changes, respectively. The results showed that the NPP mean value increased at a rate of 11.6 gCm(-2)yr(-1) during the initial three years and decreased at an accelerated rate of 31.0 gCm(-2)yr(-1) during the final three years, resulting in a total NPP loss of approximately 167 x 10(6) gC. The spatiotemporal of NPP varied obviously in the central area, suburb and exurb of Guangzhou driven by three patterns of weather and LULC changes. By the interactive effects and the weather variation dominated effects, NPP of most areas changed slightly with dynamic index less than 5% of NPP mean value in the central area and the suburb. The LULC change dominated effects caused obvious NPP reduction, by more than 15% of the NPP mean value, which occurred in some areas of the suburb and extended to the exurb with the outward urban sprawl. Importantly, conversion from wood grassland, shrublands and even forests to croplands occupied by urban landscapes proved to be a main process in the conversion from high-NPP coverage to low-NPP coverage, thereby leading to the rapid degradation of urban carbon stock capacity in urban fringe areas. It is helpful for government to monitor urban ecological health and safety and make relevant policies.</t>
-  </si>
-  <si>
-    <t>10.3390/rs5084125</t>
-  </si>
-  <si>
-    <t>NPP (which in turn supports more species and richness) and its changes due to land use change</t>
-  </si>
-  <si>
-    <t>WOS:000321558700006</t>
-  </si>
-  <si>
-    <t>Desertification dynamic and the relative roles of climate change and human activities in desertification in the Heihe River Basin based on NPP</t>
-  </si>
-  <si>
-    <t>Relative roles of climate change and human activities in desertification are the hotspot of research on desertification dynamic and its driving mechanism. To overcome the shortcomings of existing studies, this paper selected net primary productivity (NPP) as an indicator to analyze desertification dynamic and its impact factors. In addition, the change trends of actual NPP, potential NPP and HNPP (human appropriation of NPP, the difference between potential NPP and actual NPP) were used to analyze the desertification dynamic and calculate the relative roles of climate change, human activities and a combination of the two factors in desertification. In this study, the Moderate Resolution Imaging Spectroradiometer (MODIS)-Normalised Difference Vegetation Index (NDVI) and meteorological data were utilized to drive the Carnegie-Ames-Stanford Approach (CASA) model to calculate the actual NPP from 2001 to 2010 in the Heihe River Basin. Potential NPP was estimated using the Thornthwaite Memorial model. Results showed that 61% of the whole basin area underwent land degradation, of which 90.5% was caused by human activities, 8.6% by climate change, and 0.9% by a combination of the two factors. On the contrary, 1.5% of desertification reversion area was caused by human activities and 90.7% by climate change, the rest 7.8% by a combination of the two factors. Moreover, it was demonstrated that 95.9% of the total actual NPP decrease was induced by human activities, while 69.3% of the total actual NPP increase was caused by climate change. The results revealed that climate change dominated desertification reversion, while human activities dominated desertification expansion. Moreover, the relative roles of both climate change and human activities in desertification possessed great spatial heterogeneity. Additionally, ecological protection policies should be enhanced in the Heihe River Basin to prevent desertification expansion under the condition of climate change.</t>
-  </si>
-  <si>
-    <t>10.1007/s40333-013-0181-z</t>
-  </si>
-  <si>
-    <t>Desertification (degradation of ecosytems) due t human activities and CC</t>
+    <t>WOS:000188294900011</t>
+  </si>
+  <si>
+    <t>Effects of long-term nutrient fertilisation and irrigation on the microarthropod community in a boreal Norway spruce stand</t>
+  </si>
+  <si>
+    <t>Intensive nutrient fertilisation of forests has been suggested as a method to increase production of biofuels as a replacement for fossil fuels. We used a field experiment in a Norway spruce, Picea abies (L.) Karst., stand in northern Sweden to examine possible long-term effects of forest fertilisation on soil fauna (Oribatida, Mesostigmata, Collembola, predatory macroarthropods). Fertilisers had been applied annually for a period of 13 years, both in solid and liquid form, and N was added as ammonium nitrate (75-100 kg N ha(-1) per year). For comparison, control plots and plots receiving only irrigation were included. An autumn sampling showed soil fauna decreases in Plots receiving fertiliser in solid form, but increases in plots receiving liquid fertiliser. Clear shifts in community composition following both fertilisation methods were seen in Oribatida and Collembola, but species number and diversity were not significantly affected. This was probably due to increases in tolerant species that balanced decreases in other species. Liquid fertilisation had less negative effects on many species than fertilisation in solid form. Irrigation alone did not affect faunal abundances and had no effect on community composition of Oribatida and Collembola. The study indicates that intensive forest fertilisation will cause large shifts in soil microarthropod communities, but that species richness may remain unaffected. The risk of species loss will probably depend upon the size of the areas used for this purpose. (C) 2003 Elsevier B.V. All rights reserved.</t>
+  </si>
+  <si>
+    <t>10.1016/j.foreco.2003.07.012</t>
+  </si>
+  <si>
+    <t>nutrient fertilisation effects on microarthropod community in boreal forest</t>
+  </si>
+  <si>
+    <t>WOS:000208663500002</t>
+  </si>
+  <si>
+    <t>Reduction of riparian arthropod abundance and diversity as a consequence of giant reed (Arundo donax) invasion</t>
+  </si>
+  <si>
+    <t>The non-indigenous perennial grass, Arundo donax, is an aggressive invader of riparian areas throughout California and many sub-tropical regions of the world, and is hypothesized to provide poorer quality habitat for native wildlife in riparian systems. We sampled aerial and ground-dwelling insects and other terrestrial arthropods associated with Arundo, native willow vegetation (Salix spp.), and mixtures of the two vegetation types during two seasons to determine how Arundo influences invertebrate composition in a low gradient stream in central California. The total number of organisms, total biomass and taxonomic richness of aerial invertebrates associated with native vegetation was approximately twice that associated with Arundo vegetation, while mixed vegetation supported intermediate arthropod levels. Shannon-Weaver (Weiner) diversity associated with native vegetation stands was also higher than that of Arundo vegetation. Ground-dwelling assemblages did not show differences as great as aerial assemblages which are more critical to foraging avian species. These results indicate that vegetation type is a significant factor reducing the abundance and diversity of invertebrates in this, and presumably in many other riparian ecosystems where this invasive species has become a dominant component. Arundo invasion changes the vegetation structure of riparian zones and in turn, may increasingly jeopardize its habitat value for birds and other wildlife whose diets are largely composed of insects found in native riparian vegetation.</t>
+  </si>
+  <si>
+    <t>10.1023/A:1026190115521</t>
+  </si>
+  <si>
+    <t>giant reed (IAS) invasion is reducing riparian arthropod abundance and diversity</t>
+  </si>
+  <si>
+    <t>WOS:000209091500024</t>
+  </si>
+  <si>
+    <t>Analysing ethnobotanical and fishery-related importance of mangroves of the East-Godavari Delta (Andhra Pradesh, India) for conservation and management purposes</t>
+  </si>
+  <si>
+    <t>Mangrove forests, though essentially common and wide-spread, are highly threatened. Local societies along with their knowledge about the mangrove also are endangered, while they are still underrepresented as scientific research topics. With the present study we document local utilization patterns, and perception of ecosystem change. We illustrate how information generated by ethnobiological research can be used to strengthen the management of the ecosystem. This study was conducted in the Godavari mangrove forest located in the East-Godavari District of the state Andhra Pradesh in India, where mangroves have been degrading due to over-exploitation, extensive development of aquaculture, and pollution from rural and urbanized areas (Kakinada). One hundred interviews were carried out among the fisherfolk population present in two mangrove zones in the study area, a wildlife sanctuary with strong conservation status and an adjacent zone. Results from the interviews indicated that Avicennia marina (Forsk.) Vierh., a dominant species in the Godavari mangroves, is used most frequently as firewood and for construction. Multiple products of the mangrove included the bark of Ceriops decandra (Griff.) Ding Hou to dye the fishing nets and improve their durability, the bark of Aegiceras corniculatum (L.) Blanco to poison and catch fish, and the leaves of Avicennia spp. and Excoecaria agallocha L. as fodder for cattle. No medicinal uses of true mangrove species were reported, but there were a few traditional uses for mangrove associates. Utilization patterns varied in the two zones that we investigated, most likely due to differences in their ecology and legal status. The findings are discussed in relation with the demographic and socio-economic traits of the fisherfolk communities of the Godavari mangroves and indicate a clear dependency of their livelihood on the mangrove forest. Reported changes in the Godavari mangrove cover also differed in the two zones, with significantly less perceptions of a decrease in the protected area, as compared to the adjacent non-protected area. A posteriori comparisons between sequential satellite imagery (retrospective till 1977) and respondents that were at least 15 years back then, revealed a mangrove decrease which was however perceived to different extents depending on the area with which the fishermen were familiar. While local needs had not been incorporated in the existing policy, we created a framework on how data on ethnobotanical traditions, fishery-related activities and local people's perceptions of change can be incorporated into management strategies.</t>
+  </si>
+  <si>
+    <t>10.1186/1746-4269-2-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">anthro threats to mangrove biodiv presented.
+ethnobotanical analysis (study of interations and use of plants within specific human culture and env); </t>
+  </si>
+  <si>
+    <t>WOS:000224463400005</t>
+  </si>
+  <si>
+    <t>Refugia and local controls: Benthic invertebrate dynamics in Lower Green Bay, Lake Michigan following zebra mussel invasion</t>
+  </si>
+  <si>
+    <t>In many aquatic ecosystems benthic invertebrate abundance has increased following zebra mussel (Dreissena polymorpha) invasion. We examine the impact of zebra mussel density on the abundance and distribution of benthic invertebrates and postulate refuge from predation as a mechanism for the increases we found in some taxa. Benthic invertebrates in zebra mussel druses and in adjacent sediment samples were surveyed at sites in six locations representing various trophic conditions in lower Green Bay. Mean invertebrate density and taxa richness were significantly higher in the druses than in the adjacent sediment. Species diversity in the druses was inversely correlated to turbidity over the study area. Sediment samples were dominated by oligochaetes and chironomids. Amphipods were the most abundant taxa in most, but not all, of the druse samples. Other taxa present included leeches, hydra, mayflies, and caddisflies. The effectiveness of druses as refuge from predation for amphipods was investigated under laboratory conditions with various predators (perch, round goby, and rusty crayfish). In mesocosms, predation losses averaged 75% lower where zebra mussels were present. In the absence of mussels, predation loss to perch and round goby was 100% and 66% to crayfish. We conclude that the increased abundance of other invertebrates in druses in lower Green Bay may be due to increased refugia, however the assemblage composition at any given site varies with local conditions.</t>
+  </si>
+  <si>
+    <t>10.1016/S0380-1330(04)70356-1</t>
+  </si>
+  <si>
+    <t>Zebra mussel (IAS) impact on benthic invertebrate abundance and distribution</t>
+  </si>
+  <si>
+    <t>WOS:000225858000003</t>
+  </si>
+  <si>
+    <t>Influence of habitat fragmentation and crop system on Columbia Basin shrubsteppe communities</t>
+  </si>
+  <si>
+    <t>Crop production in much of the western United States has caused extensive fragmentation of shrubsteppe and other grasslands and has increased regional levels of disturbance through repeated tillage of crop fields and applications of agrochemicals. Although there have been numerous studies of the effects of fragmentation on arthropods in forests, old fields, and cropland, there have been very few studies of fragmentation effects on grassland arthropods. I conducted a two-year study in the Columbia Basin region of the U.S. Pacific Northwest to determine the effects of fragmentation and regional disturbance on shrubsteppe communities. I sampled plants and arthropods in 20 shrubsteppe fragments associated with annual crops, 20 fragments associated with perennial crops, and 20 large sections of shrubsteppe distant from crop fields. Fragments were corners of crop irrigation circles, and only sites that were undisturbed, with an apparent high coverage of shrubs, were included in the study. Results indicated no significant differences in coverages of shrubs, perennial grasses, total perennial forbs, total annual/biennial forbs, and species richness of grasses and shrubs between fragments and large sections of shrubsteppe. Mean percent coverage of the annual grass Bromus tectorum was 18.6% greater in small fragments than in large sections of shrubsteppe distant from crop fields, and mean coverage of bare ground was 22.9% higher and coverage of biological soil crusts was 41.5% lower in the fragments than in large shrubsteppe sections. Shrubsteppe fragments had significantly lower abundances of obligate herbivores, omnivores, total herbivores, obligate predators, total predators, plant detritivores, total detritivores, and butterflies, as well as fewer individuals of numerous other taxa within these trophic groups. Fragmentation had very little effect on species richness within trophic groups, probably because fragments were not that isolated from each other and large sections of shrubsteppe. Shrubsteppe communities that were next to highly disturbed annual crops had greater coverages of total annual/biennial forbs, and lower coverages of total perennial forbs and biological soil crusts when compared to shrubsteppe near perennial crops. Abundances of obligate herbivores, omnivores, total predators, plant detritivores, vertebrate-detritus feeders, and bees were similar in shrubsteppe near annual crops and near perennial crops. However, within these trophic groups, shrubsteppe near annual crops supported fewer obligate shrub-feeding grasshoppers, herbivorous ground beetles, harvestmen, antlions, darkling beetles, and butterflies than did shrubsteppe near perennial crops. The results suggest that a reduction in resources within fragments and regional disturbances caused by the production of annual crops were responsible for changes in arthropod trophic structure in fragments. Changes in trophic structure were probably not due to reductions in habitat heterogeneity or habitat isolation because plant community structure was similar in fragmented and unfragmented shrubsteppe, and fragments were not isolated from large sections of shrubsteppe.</t>
+  </si>
+  <si>
+    <t>10.1890/03-5249</t>
+  </si>
+  <si>
+    <t>habitat fragmentation and crop system effects on arthropod communities</t>
+  </si>
+  <si>
+    <t>WOS:000226791700006</t>
+  </si>
+  <si>
+    <t>Are invasive species the drivers or passengers of change in degraded ecosystems?</t>
+  </si>
+  <si>
+    <t>Few invaded ecosystems are free from habitat loss and disturbance, leading to uncertainty whether dominant invasive species are driving community change or are passengers along for the environmental ride. The driver model predicts that invaded communities are highly interactive, with subordinate native species being limited or excluded by competition from the exotic dominants. The passenger model predicts that invaded communities are primarily structured by noninteractive factors (environmental change, dispersal limitation) that are less constraining on the exotics, which thus dominate. We tested these alternative hypotheses in an invaded, fragmented, and fire-suppressed oak savanna. We examined the impact of two invasive dominant perennial grasses on community structure using a reduction (mowing of aboveground biomass) and removal (weeding of above- and belowground biomass) experiment conducted at different seasons and soil depths. We examined the relative importance of competition vs. dispersal limitation with experimental seed additions. Competition by the dominants limits the abundance and reproduction of many native and exotic species based on their increased performance with removals and mowing. The treatments resulted in increased light availability and bare soil; soil moisture and N were unaffected. Although competition was limiting for some, 36 of 79 species did not respond to the treatments or declined in the absence of grass cover. Seed additions revealed that some subordinates are dispersal limited; competition alone was insufficient to explain their rarity even though it does exacerbate dispersal inefficiencies by lowering reproduction. While the net effects of the dominants were negative, their presence restricted woody plants, facilitated seedling survival with moderate disturbance (i.e., treatments applied in the fall), or was not the primary limiting factor for the occurrence of some species. Finally, the species most functionally distinct from the dominants (forbs, woody plants) responded most significantly to the treatments. This suggests that relative abundance is determined more by trade-offs relating to environmental conditions (long-term fire suppression) than to traits relating to resource capture (which should most impact functionally similar species). This points toward the passenger model as the underlying cause of exotic dominance, although their combined effects (suppressive and facilitative) on community structure are substantial.</t>
+  </si>
+  <si>
+    <t>10.1890/04-0669</t>
+  </si>
+  <si>
+    <t>habitat disturbances and IAS affecting community biodiversity</t>
+  </si>
+  <si>
+    <t>WOS:000236382600013</t>
+  </si>
+  <si>
+    <t>Response of meiofauna and nematode communities to increased levels of contaminants in a laboratory microcosm experiment</t>
+  </si>
+  <si>
+    <t>This study was undertaken to assess the response of meiofauna and nematode (multispecies) associations in terms of density, diversity, and composition to different environmental contaminants and also to evaluate the use of meiofauna and nematodes as indicators in pollution monitoring. Sediment was collected from the mouth of the Swartkops River estuary and defaunated by successive freezing and thwarting. The sediment was then subdivided into flasks and treated with different contaminants (organic carbon, Zn, Cu, Ph, Fe) at different concentrations, before meiofauna-rich sediment was added to each of them. The setup was allowed to mature for 32 days. Various biological indices were used to assess the biological status of the nematode communities in the laboratory experiment. Nematode identification was done to the genus level. The results indicate that higher concentrations of heavy metals and organic carbon had an impact on the nematode density, diversity, and community structure. Nematode genera such as Axonolaimus, Theristus, and Paramonohystera were found to be tolerant to metal pollution. This study also observed that nematode communities react differently to metal and organic pollution. (c) 2005 Elsevier Inc. All rights reserved.</t>
+  </si>
+  <si>
+    <t>10.1016/j.ecoenv.2005.01.010</t>
+  </si>
+  <si>
+    <t>neiofauna and nematode responses (density, diversity, and composition) to environmental contaminants (pollution)</t>
+  </si>
+  <si>
+    <t>WOS:000243104300011</t>
+  </si>
+  <si>
+    <t>Seagrass habitat disturbance:: how loss and fragmentation of eelgrass Zostera marina influences epifaunal abundance and diversity</t>
+  </si>
+  <si>
+    <t>Seagrass habitats commonly display evidence of anthropogenic disturbances such as propeller scars, mooring and anchor damage, trampling, and plant harvesting. These physical disturbances may lead to habitat loss and fragmentation, yet effects of this habitat removal on seagrass epifaunal communities are not well understood. We investigated how the degree of eelgrass Zostera marina L. loss influenced the abundance, diversity, and community composition of epifauna within experimental seagrass plots in San Diego Bay, California, USA. We established replicate small (4 m(2)) and large (16 m(2)) plots within existing eelgrass habitat, and removed all aboveground and belowground plant material within randomly chosen cells to establish 4 to 6 levels of eelgrass clearing. We then sampled for epifauna up to 8 wk after eelgrass harvesting. We found no correlations between seagrass loss and epifaunal species richness, total epifaunal density or epifaunal diversity in small plots. In large plots, however, plots with 90% habitat removal had significantly lower epifaunal species richness and total epifaunal density than plots with 0, 10 or 50% habitat removal, suggesting that beyond a threshold level of eelgrass disturbance, species richness and abundance rapidly decline. Multivariate ordinations revealed that the 90% removal plots also had significantly different species composition than plots with less habitat loss. Our results support previous theoretical models predicting threshold levels of habitat loss for faunal communities and broaden our understanding of the response of marine epifauna to seagrass habitat degradation.</t>
+  </si>
+  <si>
+    <t>10.3354/meps326133</t>
+  </si>
+  <si>
+    <t>sea grass habitat disturbance affecting epifaunal abundance and diversity</t>
+  </si>
+  <si>
+    <t>WOS:000244692700016</t>
+  </si>
+  <si>
+    <t>Impacts of global changes and extreme hydroclimatic events on macroinvertebrate community structures in the French Rhone River</t>
+  </si>
+  <si>
+    <t>We assessed the temporal changes in and the relationships between the structures of the macroinvertebrate communities and the environmental conditions of the French Rhone River (the river from Lake Geneva to the Mediterranean Sea) over the last 20 years (1985-2004). Multisite environmental and biological datasets were analysed using multiple CO-inertia analysis (MCOA) and Procrustean analysis. Changes in environmental conditions were mainly marked by an improvement in water quality between 1985 and 1991 and by an increase in water temperature from 1985 onwards due to climate change. Improvement in water quality seemed to delay changes in community structures under global warming. We then observed trends in community structures coupled with high temperatures and a decrease in oxygen content. Interestingly, we observed both gradual changes and rapid switches in community states. These shifts seemed coupled to extreme hydroclimatic events (i.e. pulse disturbances). Floods and the 2003 heatwave enhanced the development of eurytolerant and invasive taxa which were probably able to take advantage of gradual warming environmental conditions. Despite various site-specific press constraints (e.g. hydropower schemes, nuclear power plants), similar changes in community structures were observed along the French Rhone River. Such consistency in temporal processes at large geographical scales underlined the strength of hydroclimatic constraints on community dynamics compared to specific local disturbances. Finally, community structures did not show any sign of recovery, and their relative sensitivities to extreme hydroclimatic events seemed to increase with time. Thus, our results suggest that global changes may reduce the resilience of current community states.</t>
+  </si>
+  <si>
+    <t>10.1007/s00442-006-0655-1</t>
+  </si>
+  <si>
+    <t>Climate warming and water quality improved linked to macroinvertebrate community changes</t>
+  </si>
+  <si>
+    <t>WOS:000246343500015</t>
+  </si>
+  <si>
+    <t>Community and species responses by birds to group retention in a coastal temperate forest on Vancouver Island, British Columbia</t>
+  </si>
+  <si>
+    <t>Group retention is a forest harvesting technique designed to sustain biodiversity and mitigate concerns regarding clearcut logging. It is characterized by retained forest patches that vary in number, size, spatial arrangement, and habitat attributes. We used birds to compare community composition and species abundance among clearcut, group retention, and uncut control forest treatments, and evaluated species' responses to percentage retention. The bird community in group retention was more similar to that in control forests than it was to the community in clearcuts. The probability of occurrence for many bird species typical of uncut control forests was related positively to percentage retention. A preliminary analysis of plot-level effects (i.e., amount of forest sampled) suggests that patch size may be more important than total amount of retention. (c) 2007 Elsevier B.V. All rights reserved.</t>
+  </si>
+  <si>
+    <t>10.1016/j.foreco.2007.03.002</t>
+  </si>
+  <si>
+    <t>bird community response to harvesting and logging</t>
+  </si>
+  <si>
+    <t>WOS:000247228800011</t>
+  </si>
+  <si>
+    <t>Species groups occupying different trophic levels respond differently to the invasion of semi-natural vegetation by Solidago canadensis</t>
+  </si>
+  <si>
+    <t>We studied the impact of the invasive plant species Solidago canadensis on the species richness of vascular plants and the abundance, species richness and diversity of butterflies, hoverflies and carabid beetles in herbaceous semi-natural habitats near Ljubljana, Slovenia. The species groups were sampled in sites dominated by S. canadensis and paired nearby sites covered by semi-natural vegetation. Plant species richness and species richness, abundance and diversity of butterfly species were lower in plots dominated by S. canadensis. Hoverfly abundance, diversity and species richness were negatively affected only in July just before the onset of flowering of S. canadensis, but tended to be positively affected in August during the height of flowering of S. canadensis. Only the abundance of carabid beetles was reduced in plots dominated by S. canadensis. The responses of the insect groups seem largely driven by the effects of Solidago on the availability of essential resources like food or larval host plants. Our results suggest that insect species that are closely related to plant species composition are more vulnerable to the effects of invasive plant species than those that are loosely or only indirectly related to plant species composition. (c) 2007 Elsevier Ltd. All rights reserved.</t>
+  </si>
+  <si>
+    <t>10.1016/j.biocon.2007.01.005</t>
+  </si>
+  <si>
+    <t>solidago canadensis (IAS) impact on plant, butterfly, hoverfly, carabid beetle diversity</t>
+  </si>
+  <si>
+    <t>WOS:000254086900002</t>
+  </si>
+  <si>
+    <t>The link between international trade and the global distribution of invasive alien species</t>
+  </si>
+  <si>
+    <t>Invasive alien species (IAS) exact large biodiversity and economic costs and are a significant component of human-induced, global environmental change. Previous studies looking at the variation in alien species across regions have been limited geographically or taxonomically or have not considered economics. We used a global invasive species database to regress IAS per-country on a suite of socioeconomic, ecological, and biogeographical variables. We varied the countries included in the regression tree analyses, in order to explore whether certain outliers were biasing the results, and in most of the cases, merchandise imports was the most important explanatory variable. The greater the degree of international trade, the higher the number of IAS. We also found a positive relationship between species richness and the number of invasives, in accord with other investigations at large spatial scales. Island status (overall), country area, latitude, continental position (New World versus Old World) or other measures of human disturbance (e.g., GDP per capita, population density) were not found to be important determinants of a country's degree of biological invasion, contrary to previous studies. Our findings also provide support to the idea that more resources for combating IAS should be directed at the introduction stage and that novel trade instruments need to be explored to account for this environmental externality.</t>
+  </si>
+  <si>
+    <t>10.1007/s10530-007-9138-5</t>
+  </si>
+  <si>
+    <t>link b/w international trade (anthro source) and distribution of IAS, driving the biodiv change</t>
+  </si>
+  <si>
+    <t>WOS:000257412900003</t>
+  </si>
+  <si>
+    <t>The impact of land-use change on larval insect communities: Testing the role of habitat elements in conservation</t>
+  </si>
+  <si>
+    <t>Conservationists have proposed that maintaining key elements of the original land-cover type in modified landscapes may mitigate the detrimental effects of land-cover change on residual species. We tested this hypothesis for aquatic insect communities in tank-forming bromeliads in forested and non-forested habitats in Costa Rica. Bromeliad tanks hold much of the standing water in this region and therefore provide an important resource for insects with aquatic larval stages. We quantified the relative importance of land-use type and the bromeliad-specific local environment on the insect community, and also the effect of land-use type on this local environment. Insect species responded to both land-use type and the local environment, with these variables explaining a total of 36% of species densities. The local environment independently explained 19% of insect densities, while land-use type explained 17%, mainly through its modification of the local environment. Local environmental conditions were strongly correlated to land-use type (r(2) = 0.64), with non-forest habitat having a higher average temperature, a greater variation in temperature, and a lower density of bromeliads. Our results indicate that the land-use type in which bromeliads occur influences the relative densities of insects by altering the local environment of bromeliads. Therefore, maintaining bromeliads under land-use conversion will not necessarily maintain the bromeliad insect community of the original forested habitat.</t>
+  </si>
+  <si>
+    <t>10.2980/15-2-3098</t>
+  </si>
+  <si>
+    <t>land use change impact on larval insect communities</t>
+  </si>
+  <si>
+    <t>WOS:000258413600018</t>
+  </si>
+  <si>
+    <t>Compositional and functional stability of arthropod communities in the face of ant invasions</t>
+  </si>
+  <si>
+    <t>There is a general consensus that the diversity of a biotic community can have an influence on its stability, but the strength, ubiquity, and relative importance of this effect is less clear. In the context of biological invasions, diversity has usually been studied in terms of its effect on a community's invasibility, but diversity may also influence stability by affecting the magnitude of compositional or functional changes experienced by a community upon invasion. We examined the impacts of invasive ants on arthropod communities at five natural area sites in the Hawaiian Islands, and assessed whether differences among sites in community diversity and density variables were related to measures of stability. Ant invasion was usually associated with significant changes in overall community composition, as measured by Bray-Curtis distances, particularly among endemic subsets of the communities. Changes in mean species richness were also strong at three of the five sites. Among sites, diversity was negatively related to stability as measured by resistance to overall compositional change, but this effect could not be separated from the strong negative effect of invasive ant density on compositional stability. When compositional stability was measured as proportional change in richness, the best predictor of stability among endemic community subsets was endemic richness, with richer communities losing proportionately more species than species-poor communities. This effect was highly significant even after controlling for differences in invasive ant density and suggested that communities that had already lost many endemic species were resistant to further species loss upon ant invasion, while more intact communities remained vulnerable to species loss. Communities underwent strong but idiosyncratic functional shifts in association with ant invasion, both in terms of trophic structure and total arthropod biomass. There were no apparent relationships, however, between functional stability and community diversity or density measures. Instead, invasive ant density was the best among-site predictor of the magnitude of functional change. Overall, diversity appeared to be a poor predictor of stability in the face of ant invasion in these communities, possibly because any actual diversity effects were overshadowed by community-specific factors and variation in the magnitude of the ant-mediated perturbation.</t>
+  </si>
+  <si>
+    <t>10.1890/07-1293.1</t>
+  </si>
+  <si>
+    <t>ant invasions impact on arthropod community</t>
+  </si>
+  <si>
+    <t>WOS:000268196000007</t>
+  </si>
+  <si>
+    <t>Biodiversity recovery during rainforest reforestation as indicated by rapid assessment of epigaeic ants in tropical and subtropical Australia</t>
+  </si>
+  <si>
+    <t>There is growing interest in the potential for reforestation to assist the recovery of rainforest biodiversity. There is also a need to identify taxonomically tractable groups for use as cost-effective indicators when monitoring the status of biodiversity within reforested sites. Insects are an important component of terrestrial biodiversity but often require considerable resources to sample at species level. Ant genera and generic-based functional groups have been suggested as possible indicators of environmental disturbance. Here we ask to what extent the development of biodiversity is indicated by epigacic ant genera and functional groups, across different types of reforestation in tropical and subtropical Australia. In each region, we used pitfall traps to sample the ants in replicate sites of: unmanaged regrowth, monoculture and mixed species plantations and 'ecological restoration' plantings, together with reference sites in pasture and rainforest. We recorded 35 epigaeic ant genera (and 4623 individuals) from 50 tropical sites, and 39 genera (and 9904 individuals) from 54 subtropical sites, with 47 genera overall. Community composition of both genera and functional groups differed between pasture and rainforest, although many genera were widespread in both. Reforested sites were intermediate between pasture and rainforest in both regions, and showed a gradient associated with decreasing grass and increasing tree and litter cover. Older monoculture plantations and ecological restoration plantings had the most rainforest-like ant assemblages, and mixed-species cabinet timber plots the least, of the reforested sites. We conclude that ground-active ant genera and functional groups sampled in rapid surveys by pitfall-trapping showed only a modest ability to discriminate among different types of reforestation. Species-level identification, perhaps together with expanded sampling effort, could be more informative, but would require resourcing beyond the scope of rapid assessments.</t>
+  </si>
+  <si>
+    <t>10.1111/j.1442-9993.2009.01943.x</t>
+  </si>
+  <si>
+    <t>biodiversity recovery during rainforest reforestation (replanting trees and allowing natural regeneration)</t>
+  </si>
+  <si>
+    <t>WOS:000269675600012</t>
+  </si>
+  <si>
+    <t>Impacts of grazing, selective logging and hyper-aggressors on diurnal bird fauna in intact forest landscapes of the Brigalow Belt, Queensland</t>
+  </si>
+  <si>
+    <t>The impact of forest management on diurnal bird assemblages and abundance was investigated in contiguous tracts of eucalypt forest in the Brigalow Belt Bioregion, south central Queensland. Sites were located across three levels of livestock grazing intensity and three levels of selective logging intensity within the most extensive habitat type, Corymbia citriodora-dominant forest. We recorded a high rate of incidence and large numbers of the hyper-aggressive noisy miner Manorina melanocephala (Passeriformes: Meliphagidae) at the majority of our survey sites, a phenomenon rarely reported in non-cleared landscapes. As shown by numerous studies in fragmented landscapes, the distribution of this species in our study had a substantial negative effect upon the distribution of small passerine species. Noisy miners exerted the strongest influence upon small passerine abundance, and masked any forest management effects. However, key habitat features important for small passerines were identified, including a relatively high density of large trees and stems in the midstorey. Selective logging appeared to exert a minimal effect upon noisy miner abundance, whereas grazing intensity had a profound, positive influence. Noisy miners were most abundant in intensively grazed forest with minimal midstorey and a low volume of coarse woody debris. Higher road density in the forest landscape also corresponded with increased numbers of noisy miners. Reduction in grazing pressure in Brigalow Belt forests has the potential to benefit small passerine assemblages across large areas through moderating noisy miner abundance. The strong relationship between noisy miners and small passerines suggests that noisy miner abundance could act as an easily measured indicator of forest condition, potentially contributing to monitoring of forest management outcomes.</t>
+  </si>
+  <si>
+    <t>10.1111/j.1442-9993.2009.01979.x</t>
+  </si>
+  <si>
+    <t>imapct of grazing and selective logging (anthro sources) on diurnal bird assemblage</t>
+  </si>
+  <si>
+    <t>WOS:000275033500012</t>
+  </si>
+  <si>
+    <t>Assessing impacts of introduced aquaculture species on native fish communities: Nile tilapia and major carps in SE Asian freshwaters</t>
+  </si>
+  <si>
+    <t>Herbivorous or omnivorous tilapia and carp species form the backbone of tropical inland aquaculture and fisheries enhancement and have been introduced widely outside their natural ranges. Perceptions of their impact on native fish faunas vary widely, but there have been few rigorous assessments. To quantify the impact of tilapia and carp stocking on native fish communities in freshwater wetlands of the Mekong region, we conducted observational and experimental impact-control studies replicated at the wetland level, at a total of 46 sites in Lao PDR. The studies were designed as paired comparisons of wetlands where the nonnative species (Nile tilapia Oreochromis niloticus, mrigal Cirrhinus cirrhosus, rohu Labeo rohita and bighead carp Hypophthalmichthys nobilis) were stocked in substantial numbers with similar wetlands where the species were absent. Stocking of these non-native species was associated with significant increases in total fish biomass, by 180% in the observational study and by 49% in the experiment. Native fish biomass was not affected by stocking of the non-native species. No significant impacts on native fish species richness, diversity indices, species composition or feeding guild composition were detected, except for moderately negative effects on Simpson diversity and equitability in the observational study. In the experiment, no effect had a point estimate exceeding -14%, or a 95% confidence limit exceeding -35% of the non-impacted value. Use of these non-native tilapia and carp species in fisheries enhancement in mainland SE Asia supported substantial increases in harvestable biomass while having only mild impacts on native fish communities. Escapes of the same species from pond and cage aquaculture facilities are likely to result in lower biomass in the wild and have lower impacts than enhancement stocking. We encourage building on our results through a systematic and stakeholder-participatory evaluation of the significance and acceptability of benefits and risks associated with the use of these non-native species. This evaluation should be extended to the relative benefits and risks of replacing non-native species with native ones in aquaculture and enhancement, considering that risks associated with using the current set of non-native species are increasingly well known and appear mild-to-moderate, whilst ecological and genetic risks of releasing domesticated types of native species are poorly known. (C) 2009 Elsevier B.V. All rights reserved.</t>
+  </si>
+  <si>
+    <t>10.1016/j.aquaculture.2009.11.022</t>
+  </si>
+  <si>
+    <t>tilapia, carps (IAS) impact on native fish communities</t>
+  </si>
+  <si>
+    <t>WOS:000276425400006</t>
+  </si>
+  <si>
+    <t>Invasive alien goldenrods negatively affect grassland bird communities in Eastern Europe</t>
+  </si>
+  <si>
+    <t>Invasive alien plants constitute a major threat to local biodiversity. Moreover, their appearance often coincides with land use change. Many endangered groups of organisms suffer from habitat loss, which is often a consequence of the invasion of alien plants This paper examines how invasive alien goldenrods Solidago spp affect the richness of endangered grassland bird species and numbers of breeding pairs in abandoned meadows in southern Poland. Meadows invaded by goldenrods (n = 15) had lower bird spedes richness and a lower number of breeding pairs than meadows in which goldenrods were absent (n = 15) Two important factors positively influencing bird species richness were meadow area and shrub density (the latter only in meadows without goldenrods). Moreover, both the index of potential food density (number of butterflies) and plant species richness were much lower in meadows invaded by goldenrods than in meadows without these plants Urgent action aimed at preventing the invasion of alien goldenrods in abandoned meadows is needed and such measures should involve regular mowing Our results also highlight the fact that land abandonment in Central and Eastern Europe is not necessarily as beneficial for biodiversity as it is commonly believed and it may even lead to a decrease in the populations of several bird species in the agricultural landscape. (C) 2009 Elsevier Ltd. All rights reserved.</t>
+  </si>
+  <si>
+    <t>10.1016/j.biocon.2009.12.030</t>
+  </si>
+  <si>
+    <t>goldenrods (IAS) negatively affecting grassland bird communities</t>
+  </si>
+  <si>
+    <t>WOS:000276509400029</t>
+  </si>
+  <si>
+    <t>Non-native grass invasion alters native plant composition in experimental communities</t>
+  </si>
+  <si>
+    <t>Invasions of non-native species are considered to have significant impacts on native species, but few studies have quantified the direct effects of invasions on native community structure and composition. Many studies on the effects of invasions fail to distinguish between (1) differential responses of native and non-native species to environmental conditions, and (2) direct impacts of invasions on native communities. In particular, invasions may alter community assembly following disturbance and prevent recolonization of native species. To determine if invasions directly impact native communities, we established 32 experimental plots (27.5 m(2)) and seeded them with 12 native species. Then, we added seed of a non-native invasive grass (Microstegium vimineum) to half of the plots and compared native plant community responses between control and invaded plots. Invasion reduced native biomass by 46, 64, and 58%, respectively, over three growing seasons. After the second year of the experiment, invaded plots had 43% lower species richness and 38% lower diversity as calculated from the Shannon index. Nonmetric multidimensional scaling ordination showed a significant divergence in composition between invaded and control plots. Further, there was a strong negative relationship between invader and native plant biomass, signifying that native plants are more strongly suppressed in densely invaded areas. Our results show that a non-native invasive plant inhibits native species establishment and growth following disturbance and that native species do not gain competitive dominance after multiple growing seasons. Thus, plant invaders can alter the structure of native plant communities and reduce the success of restoration efforts.</t>
+  </si>
+  <si>
+    <t>10.1007/s10530-009-9546-9</t>
+  </si>
+  <si>
+    <t>non native grass invasion is altering native plant composition</t>
+  </si>
+  <si>
+    <t>WOS:000280973100010</t>
+  </si>
+  <si>
+    <t>Experimental introduction of the alien plant Hieracium lepidulum reveals no significant impact on montane plant communities in New Zealand</t>
+  </si>
+  <si>
+    <t>Aim There is debate over whether alien plants necessarily alter the communities they invade or can coexist with native species without discernable impacts. We followed the fate of montane plant communities in response to the experimental sowing of the alien weed Hieracium lepidulum, looking for changes in plant community composition and structure over 6 years. Location Craigieburn Range, New Zealand. Methods We used a replicated randomised block design, with 30 x 30 cm plots (n = 756) subdivided into 5 x 5 cm cells to examine and compare the effects of H. lepidulum at 0.09 m2 (plot) and 0.0025 m2 (cell) scales. Plots were sown with between 0 and 15,625 H. lepidulum seeds in 2003, forming gradients of invader density and cover. Measurements comprised community richness, evenness and diversity along with H. lepidulum density and cover at both scales. The relationships between the invader and local community attributes were modelled using hierarchical mixed-effect models. Results Plant communities differed in the extent to which they became invaded, with H. lepidulum cover in the plots ranging from 0% to 52%, with a mean of only 1.89%. Plot species richness increased from 2003 to 2009, with a component of this increase (+0.002 species per year) associated with increasing H. lepidulum density. Other relationships between the plant community and H. lepidulum were generally non-significant. Main conclusions In these montane plant communities, it appears H. lepidulum coexists with the native community with no measurable negative effects after 6 years on species richness, evenness or diversity, even where density and cover of the invader are highest. We suggest H. lepidulum has persisted preferentially at those sites with abiotic conditions sufficient to support a species-rich assemblage.</t>
+  </si>
+  <si>
+    <t>10.1111/j.1472-4642.2010.00684.x</t>
+  </si>
+  <si>
+    <t>experimental introduction of alien plant with no significant impact on montane communities</t>
+  </si>
+  <si>
+    <t>WOS:000281833700003</t>
+  </si>
+  <si>
+    <t>Experimental plant invasion reduces arthropod abundance and richness across multiple trophic levels</t>
+  </si>
+  <si>
+    <t>Plant invasions are known to have negative impacts on native plant communities, yet their influence on higher trophic levels has not been well documented. Past studies investigating the effects of invasive plants on herbivores and carnivores have been largely observational in nature and thus lack the ability to tease apart whether differences are a cause or consequence of the invasion. In addition, understanding how plant traits and plant species compositions change in invaded habitats may increase our ability to predict when and where invasive plants will have effects that cascade to animals. To assess effects on arthropods, we experimentally introduced a non-native plant (Microstegium vimineum, Japanese stiltgrass) in a community re-assembly experiment. We also investigated possible mechanisms through which the invader could affect associated arthropods, including changes in native plant species richness, above-ground plant biomass, light availability and vegetation height. In experimentally invaded plots, arthropod abundance was reduced by 39%, and species richness declined by 19%. Carnivores experienced greater reductions in abundance than herbivores (61% vs 31% reduction). Arthropod composition significantly diverged between experimentally invaded and control plots, and particular species belonging to the abundant families Aphididae (aphids), Formicidae (ants) and Phalacridae (shining flower beetles) contributed the most to compositional differences. Among the mechanisms we investigated, only the reduction in native plant species richness caused by invasion was strongly correlated with total arthropod abundance and richness. In sum, our results demonstrate negative impacts of M. vimineum invasion on higher trophic levels and suggest that these effects occur, in part, indirectly through invader-mediated reductions in the richness of the native plant community. The particularly strong response of carnivores suggests that plant invasion could reduce top-down control of herbivorous species for native plants.</t>
+  </si>
+  <si>
+    <t>10.1111/j.1600-0706.2010.18382.x</t>
+  </si>
+  <si>
+    <t>IAS invasion (experimental plant invasion) and its impact on arthropod abundance and richness across trophic levels</t>
+  </si>
+  <si>
+    <t>WOS:000287448100010</t>
+  </si>
+  <si>
+    <t>Forest fragmentation drives Atlantic forest of northeastern Brazil to biotic homogenization</t>
+  </si>
+  <si>
+    <t>Aim To examine whether the tree flora of the Atlantic forest of northeastern Brazil has experienced detectable taxonomic homogenization via the proliferation of native pioneer species in response to habitat loss and fragmentation. Location Biotic homogenization (BH) was examined across the Atlantic forest of northeast Brazil, i.e. a 56,000 km2 piece of tropical forest and a distinct centre of species endemism in South America. Methods We assessed a dataset consisting of 5122 tree records and compared the similarity of tree floras from 12 semi-natural sub-regions of the Atlantic forest between two time periods: pre-1980 (plant records between 1902 and 1980), and post-1980 (between 1981 and 2006). To understand the mechanisms leading to BH (1) tree floras were ordered (via non-metric multidimensional scaling - NMDS) by date (pre/post 1980) based on species occurrence and frequency, (2) NMDS axes were regressed against the proportion of those species that increased their occurrence post-1980 (i.e. the winner species), and (3) patterns of geographic distribution and frequency of particular life-history traits were examined across winner species and a control group. Results Tree floras across the Atlantic forest became c. 20-40% more similar to each other post-1980, but patterns of species similarity were also influenced by between-plot geographical distance. NMDS ordination clearly segregated pre- and post-1980 floras with a clear signal of floristic convergence. Furthermore, winner tree species were largely composed of short-lived and small-seeded pioneer species that exhibit wide geographic distributions. Main conclusions Our results suggest that tropical forest biotas are susceptible to taxonomic homogenization (i.e. increasing levels of similarity) in the context of severe human-disturbance via the proliferation of particular groups of native species comprised mainly by ecologically-plastic, generalist species. We are thus extending the concept of homogenization to address and highlight a pervasive biological shift in the structure of tropical forest communities currently taking place across hyper-fragmented landscapes.</t>
+  </si>
+  <si>
+    <t>10.1111/j.1472-4642.2010.00739.x</t>
+  </si>
+  <si>
+    <t>forest fragmentation and its effect on atlantic forest biotic homgenization</t>
   </si>
   <si>
     <t>WOS:000293038700014</t>
@@ -1262,49 +819,64 @@
     <t>changes in carbon stock level due to cc, land use chang, logging, fires</t>
   </si>
   <si>
-    <t>WOS:000608979000001</t>
-  </si>
-  <si>
-    <t>Sea-ice microbial communities in the Central Arctic Ocean: Limited responses to short-term pCO2 perturbations</t>
-  </si>
-  <si>
-    <t>The Arctic Ocean is more susceptible to ocean acidification than other marine environments due to its weaker buffering capacity, while its cold surface water with relatively low salinity promotes atmospheric CO2 uptake. We studied how sea-ice microbial communities in the central Arctic Ocean may be affected by changes in the carbonate system expected as a consequence of ocean acidification. In a series of four experiments during late summer 2018 aboard the icebreaker Oden, we addressed microbial growth, production of dissolved organic carbon (DOC) and extracellular polymeric substances (EPS), photosynthetic activity, and bacterial assemblage structure as sea-ice microbial communities were exposed to elevated partial pressures of CO2 (pCO(2)). We incubated intact, bottom ice-core sections and dislodged, under-ice algal aggregates (dominated by Melosira arctica) in separate experiments under approximately 400, 650, 1000, and 2000 mu atm pCO(2) for 10 d under different nutrient regimes. The results indicate that the growth of sea-ice algae and bacteria was unaffected by these higher pCO(2) levels, and concentrations of DOC and EPS were unaffected by a shifted inorganic C/N balance, resulting from the CO2 enrichment. These central Arctic sea-ice microbial communities thus appear to be largely insensitive to short-term pCO(2) perturbations. Given the natural, seasonally driven fluctuations in the carbonate system of sea ice, its resident microorganisms may be sufficiently tolerant of large variations in pCO(2) and thus less vulnerable than pelagic communities to the impacts of ocean acidification, increasing the ecological importance of sea-ice microorganisms even as the loss of Arctic sea ice continues.</t>
-  </si>
-  <si>
-    <t>10.1002/lno.11690</t>
-  </si>
-  <si>
-    <t>pCO2 perturbations (sustained changes in pressure of CO2 in surface oceans);  microbial community changes due to pCO2 pertub.</t>
-  </si>
-  <si>
-    <t>WOS:000076782200006</t>
-  </si>
-  <si>
-    <t>Effects of nitrogen addition on successional dynamics and species diversity in Michigan old-fields</t>
-  </si>
-  <si>
-    <t>1 We examined the impact of nitrogen addition on early successional dynamics and plant species diversity in replicate plots of an old-field succession treatment in south-western Michigan, USA, for 7 years following abandonment from agriculture. 2 Nitrogen addition significantly increased above-ground plant biomass, but had no effect on the displacement or persistence of different life-history groups. Annual species made up a similar proportion of community biomass and decreased at equivalent rates in control and nitrogen-addition microplots. Perennial species biomass increased at similar rates in the control and nitrogen-addition microplots. 3 Annual species dominated initially, but declined in abundance over the first 4 years and were replaced by biennials and then herbaceous perennials. The resulting high numbers of species losses and gains were not affected by nitrogen addition. 4 Nitrogen addition did not affect mean species density or the Shannon index of diversity. There was also no temporal change in the similarity of species composition between control and nitrogen-addition microplots, indicating that nitrogen addition did not cause divergence over time in community composition. In year 7, similar species dominated the nitrogen-addition and control microplots, but there were differences in species composition and abundance of the subordinate species in each community. 5 Only in year 6 of this study was there a significant negative relationship between community biomass and the Shannon diversity index. There was no significant relationship between community biomass and species density in any of the first 7 years following abandonment. Thus, the community response to increased biomass due to nitrogen addition was expressed primarily through changes in community structure, not richness. 6 The effects of nitrogen addition on the early successional dynamics, species composition and consequently diversity of a plant community may depend on initial site conditions. The response to nitrogen enrichment may be slower in sites such as ours with fertile soils that become dominated by herbaceous perennial dicots.</t>
-  </si>
-  <si>
-    <t>10.1046/j.1365-2745.1998.8650794.x</t>
-  </si>
-  <si>
-    <t xml:space="preserve">effects on nitrogen addition on plant diversity </t>
-  </si>
-  <si>
-    <t>WOS:000435480900008</t>
-  </si>
-  <si>
-    <t>Demographic and Density Response of Northern Bobwhites to Pyric Herbivory of Non-Native Grasslands</t>
-  </si>
-  <si>
-    <t>Usable space for northern bobwhites (Colinus virginianus) has declined significantly over the past 3 decades in Texas because non-native grasses have replaced native vegetation. We hypothesized that burning patches in pastures dominated by buffelgrass (Pennisetum ciliare) and OldWorld bluestems (Bothriochloa spp. and Dichanthium spp.) followed by livestock grazing would increase limiting habitat attributes, thereby increasing usable space and bobwhite demographic parameters and population densities. Our study was conducted during 2009-2011 in LaSalle County, Texas on a ranch dominated by non-native grasses. Our experimental design was composed of 2 blocks with two 240-ha pastures, one control (graze only), and one treatment (patch-burn and graze) in each. We estimated grass standing crop in grazing exclosures (June-September) and habitat attributes along transects (October) 2009-2011. Bobwhites were captured and monitored via radiotelemetry 2-3 times/wk during March-November. Means of vegetation metrics important to bobwhites such as bare ground, traversibility, and forb and subshrub cover were similar between control and treatment units in post-treatment years. However, grass standing crop tended to be lower in treatment (June and August 2010 and September 2011-110.5 +/- 26.2 g/m(2)) compared with control units (June and August 2010 and September 2011-145.5 +/- 58.6 g/m(2)). Plant species richness was also greater (21%) in treatment (4.6 +/- 0.4/0.1 m(2)) compared with control units (3.8 +/- 0.4/0.1 m(2)) during the last year of the study (P = 0.057). Patch heterogeneity was increased in treatment units. There was an increase in bobwhite densities in treatment units, although demographicmetrics remained similar between treatment and controls. Patch burning and grazing is a viable tool for managing monotypic non-native grasslands for bobwhites in semiarid environments. (C) 2018 Published by Elsevier Inc. on behalf of The Society for Range Management.</t>
-  </si>
-  <si>
-    <t>10.1016/j.rama.2018.02.008</t>
-  </si>
-  <si>
-    <t>Ias and habitat modification affecting Northern Bobwhites</t>
+    <t>WOS:000294460300002</t>
+  </si>
+  <si>
+    <t>The effects of land-use change on arthropod richness and abundance on Santa Maria Island (Azores): unmanaged plantations favour endemic beetles</t>
+  </si>
+  <si>
+    <t>We study how endemic, native and introduced arthropod species richness, abundance, diversity and community composition vary between four different habitat types (native forest, exotic forest of Cryptomeria japonica, semi-natural pasture and intensive pasture) and how arthropod richness and abundance change with increasing distance from the native forest in adjacent habitat types in Santa Maria Island, the Azores. Arthropods were sampled in four 150 m long transects in each habitat type. Arthropods were identified to species level and classified as Azorean endemic, single-island endemic (SIE), native, or introduced. The native forest had the highest values for species richness of Azorean endemics, SIEs and natives; and also had highest values of Azorean endemic diversity (Fisher's alpha). In contrast, the intensive pasture had the lowest values for endemic and native species richness and diversity, but the highest values of total arthropod abundance and introduced species richness and diversity. Arthropod community composition was significantly different between the four habitat types. In the semi-natural pasture, the number of SIE species decreased with increasing distance from the native forest, and in the exotic forest the abundance of both Azorean endemics and SIEs decreased with increasing distance from the native forest. There is a gradient of decreasing arthropod richness and abundance from the native forest to the intensive pasture. Although this study demonstrates the important role of the native forest in arthropod conservation in the Azores, it also shows that unmanaged exotic forests have provided alternative habitat suitable for some native species of forest specialist arthropods, particularly saproxylic beetles.</t>
+  </si>
+  <si>
+    <t>10.1007/s10841-010-9330-2</t>
+  </si>
+  <si>
+    <t>land use change effects on arthropod richness in azores</t>
+  </si>
+  <si>
+    <t>WOS:000296894900012</t>
+  </si>
+  <si>
+    <t>Effects of anthropogenic activities on lizard communities in northern Madagascar</t>
+  </si>
+  <si>
+    <t>Madagascar is a biodiversity hotspot threatened by habitat loss, which is detrimental to the future survival of forest-dwelling herpetofauna. For conservation purposes, it is essential to determine how species respond to different types of anthropogenic habitat alteration. We conducted standardized field surveys (a variation of visual encounter survey) to assess species richness, abundance and diversity among forest, clear-cut and orchard habitat types in Montagne des Francais, north Madagascar. Forest sites proved to be very different from clear-cut and orchard sites with regards to habitat structure. Lizard species richness, abundance and diversity were significantly lower in clear-cut sites, with only 11% of the observed forest diversity recorded. This shift in species occurrence suggests that lizards are particularly sensitive to this type of habitat alteration. Orchard cultivation did not affect lizard species richness to the same extent, as 56% of the observed forest diversity was recorded in this habitat type. Furthermore lizard abundance was significantly higher in orchard habitat. These observations indicate that although anthropogenic activity can have an adverse effect on the lizard fauna of a given site, it will seldom lead to a total loss of diversity as species typical of pristine forest (specialists) are replaced by species adapted to secondary habitats (often generalists). Our results support the contention that anthropogenic habitat alteration can have a strong negative influence on lizard communities. Researchers should continue to identify which species may be lost or become more vulnerable in future (as a result of population decline) in response to anthropogenic habitat alteration.</t>
+  </si>
+  <si>
+    <t>10.1111/j.1469-1795.2011.00459.x</t>
+  </si>
+  <si>
+    <t>effect of habitat loss on lizard communities</t>
+  </si>
+  <si>
+    <t>WOS:000302926400020</t>
+  </si>
+  <si>
+    <t>From forests to cattail: how does the riparian zone influence stream fish?</t>
+  </si>
+  <si>
+    <t>The aim of this study was to verify whether taxonomic and functional composition of stream fishes vary under three different preservation conditions of riparian zone: preserved (PRE), intermediate condition (INT), and degraded (DEG). Five stream stretches representing each condition were selected. Samples were taken from each stream in three occasions during the dry seasons from 2004 to 2007. Electro fishing (PRE and INT), sieves, dip nets, and hand seines (DEG) were used according to the characteristics of each sampled site. Overall, 46 species were registered. Differences in the taxonomic and functional species composition among groups were found, following the condition of riparian zones. The ichthyofauna :;recorded in the PRE was typical to pristine environments, consisting of species with specialized habits, notably benthic insectivores, intolerant, and rheophilics. In the INT group, replacement of riparian forest with shrubs and/or grasses created environmental conditions which favor the occurrence of tolerant species but also harbor a residual fauna of sensitive species. DEG streams presented mostly detritivores, tolerant, small sized fishes which occupy the surface and preferred slow water flux. Changes in the species composition were represented by the occurrence and dominance of tolerant species in detriment of the more, sensitive and specialist species, following the gradient of degradation in the riparian zone. Forested streams act as unique habitats to many specialized species and it can be presumable that the degradation of riparian vegetation can generate biotic homogenization which may reduce species diversity and ecosystem services.</t>
+  </si>
+  <si>
+    <t>10.1590/S1679-62252012000100020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">riparian degradation (destruction or loss of vegetation and habitats along water bodies) and effect no fish composition </t>
+  </si>
+  <si>
+    <t>WOS:000305461200004</t>
+  </si>
+  <si>
+    <t>Abiotic drivers of coastal fish community change during four decades in the Baltic Sea</t>
+  </si>
+  <si>
+    <t>Evidence for long-term change of marine ecosystems is increasing worldwide. Coastal areas harbour the socio-economically and ecologically most vital aquatic ecosystems, but are under increasing anthropogenic pressure. Little is known, however, about how environmental perturbations affect the development of coastal systems. In this paper, datasets of coastal fish communities covering almost four decades (early/mid 1970s to 2008) in three different basins of the Baltic Sea were analysed. There were clear changes in species composition over time in all but one dataset and coherence among basins in the timing of change. Changes were mainly associated with variables related to climate (water temperature, salinity, and North Atlantic Oscillation index), but less so with those reflecting nutrient status (nutrient concentrations and loading). Despite the importance of local water temperature, regional climatic variables were more important for the temporal development of communities. The results indicate that Baltic coastal fish communities have undergone large structural changes governed by processes acting on both local and regional scales. The findings suggest that ecological targets should be set accounting for long-term changes in community structure and that a common management of coastal and offshore ecosystems would be beneficial.</t>
+  </si>
+  <si>
+    <t>10.1093/icesjms/fss072</t>
+  </si>
+  <si>
+    <t>changes in coastal fish community driven by abiotic factors (non living physical and chemical compon of ecosystem)</t>
   </si>
   <si>
     <t>WOS:000307687500011</t>
@@ -1323,13 +895,199 @@
 with anthro drivers test and referred in text</t>
   </si>
   <si>
-    <t>Status of connected wetlands of the Lake Eyre Basin, Australia</t>
-  </si>
-  <si>
-    <t>The Lake Eyre Basin, one of the world's last unregulated wild river basins, covers almost one sixth of the Australian continent, with large areas of connected wetlands (73 903 km2), including floodplains, lakes, waterholes and river channels. Few data existed and so we used literature and government biotic and abiotic data and anthropogenic impacts to assess the conservation risk of the ecosystem as Least Concern (IUCN Red List criteria for ecosystems, version 2.0). This was based on limited distributional change and low levels of degradation or anthropogenic threatening processes. The approach could be applied to ecosystem assessments of other large river basins around the world, given the Lake Eyre Basin occupies one extreme (unmodified) while the Aral Sea (collapsed), previously assessed, occupies the other extreme (highly modified). River flow analysis with available biotic data is critical for risk assessment as well as identification and tracking of long-term threats. Assessment was possible at this large basin scale and appropriate, given the critical importance of connectivity but could also occur at finer spatial scale. Increased diversions for irrigation, mining impacts on floodplains and projected increased temperatures threaten the current status (Least Concern) of the connected wetlands of the Lake Eyre Basin ecosystem.</t>
-  </si>
-  <si>
-    <t>risk of future ecosystem degradation with anthro impacts analyzed (irrgiation, mining impacts, increased temp)</t>
+    <t>WOS:000310464500014</t>
+  </si>
+  <si>
+    <t>Plant invasion impacts on arthropod abundance, diversity and feeding consistent across environmental and geographic gradients</t>
+  </si>
+  <si>
+    <t>Exotic plant invasion not only changes native plant communities, it also alters associated arthropod community diversity and structure. These impacts often are contradictory and context-specific by study location. M. vimineum is an Asian grass currently invading the eastern United States that generally escapes herbivory. The invasion impacts on arthropod communities are mixed, and the effects on arthropod food webs are largely unknown. Because M. vimineum has a unique delta C-13 value, its carbon flow can be resolved from native plants in recipient food webs. We investigate arthropod communities at M. vimineum-invaded sites along a 100-km geographic and environmental gradient in the southeastern U.S. We investigate M. vimineum impacts on arthropod abundance and diversity, how M. vimineum-derived carbon contributes to arthropod biomass and how environmental variation modifies invasion effects on arthropod communities. We find that M. vimineum invasion corresponds with increased arthropod diversity and abundance, but reduced evenness. Herbivore damage to leaves is equivalent between native species and M. vimineum, but the type of herbivore damage is not the same between the native and invader plants. We also find that herbivores derive 37 % of their biomass-carbon from the exotic plant but predators almost none (4 %). Detritivores derive exotic carbon (9 %) proportional to M. vimineum in the litter layer. Whereas exotic plant impacts on arthropod communities often seem idiosyncratic by site, we find no context-dependent invasion effects of M. vimineum by study location. The consistency suggests that the impacts may be broadly generalizable, at least within well-established parts of the invasion range.</t>
+  </si>
+  <si>
+    <t>10.1007/s10530-012-0258-1</t>
+  </si>
+  <si>
+    <t>plant invasion impacts on arthropod community diversity and food webs</t>
+  </si>
+  <si>
+    <t>WOS:000320791000002</t>
+  </si>
+  <si>
+    <t>The introduction of Littorina littorea to British Columbia, Canada: potential impacts and the importance of biotic resistance by native predators</t>
+  </si>
+  <si>
+    <t>Although the establishment and spread of non-indigenous species depends upon survival in the face of novel environmental conditions and novel biological interactions, relatively little attention has been focused on the specific role of native predators in limiting invasion success. The European common periwinkle, Littorina littorea, was recently introduced to the Pacific coast of Canada and provides a case study of an introduction into an area with an important predator guild (sea stars) that is functionally minor in the invader's native habitat. Here, we assess the likelihood of establishment, spread, and negative ecological impact of this introduced gastropod, with an emphasis on the role of native sea stars as agents of biotic resistance. Size frequency distributions and local market availability suggest that L. littorea was most likely introduced via the live seafood trade. Non-native hitchhikers (e.g., the trematode Cryptocotyle lingua) were found on/in both market and field specimens. Laboratory studies and field observations confirmed that L. littorea can survive seasonal low salinity in Vancouver, British Columbia. Periwinkles also readily consumed native Ulva, suggesting that periwinkles could impact native communities via herbivory or resource competition. Unlike native gastropods, however, L. littorea lacked behavioural avoidance responses to Northeast Pacific predatory sea stars (Pisaster ochraceus and Pycnopodia helianthoides), and sea star predation rates on L. littorea were much higher than predation rates on native turban snails (Chlorostoma funebralis) in common garden experiments. We therefore expect periwinkle establishment in British Columbia to be limited to areas with low predator density, as is seen in its field distribution to date. We caution that this conclusion may understate the importance of the L. littorea introduction if it also serves as a vector for additional non-indigenous species such as C. lingua.</t>
+  </si>
+  <si>
+    <t>10.1007/s00227-013-2206-8</t>
+  </si>
+  <si>
+    <t>intro of Littorina littorea (invasive) and biodiversity change</t>
+  </si>
+  <si>
+    <t>WOS:000321558700006</t>
+  </si>
+  <si>
+    <t>Desertification dynamic and the relative roles of climate change and human activities in desertification in the Heihe River Basin based on NPP</t>
+  </si>
+  <si>
+    <t>Relative roles of climate change and human activities in desertification are the hotspot of research on desertification dynamic and its driving mechanism. To overcome the shortcomings of existing studies, this paper selected net primary productivity (NPP) as an indicator to analyze desertification dynamic and its impact factors. In addition, the change trends of actual NPP, potential NPP and HNPP (human appropriation of NPP, the difference between potential NPP and actual NPP) were used to analyze the desertification dynamic and calculate the relative roles of climate change, human activities and a combination of the two factors in desertification. In this study, the Moderate Resolution Imaging Spectroradiometer (MODIS)-Normalised Difference Vegetation Index (NDVI) and meteorological data were utilized to drive the Carnegie-Ames-Stanford Approach (CASA) model to calculate the actual NPP from 2001 to 2010 in the Heihe River Basin. Potential NPP was estimated using the Thornthwaite Memorial model. Results showed that 61% of the whole basin area underwent land degradation, of which 90.5% was caused by human activities, 8.6% by climate change, and 0.9% by a combination of the two factors. On the contrary, 1.5% of desertification reversion area was caused by human activities and 90.7% by climate change, the rest 7.8% by a combination of the two factors. Moreover, it was demonstrated that 95.9% of the total actual NPP decrease was induced by human activities, while 69.3% of the total actual NPP increase was caused by climate change. The results revealed that climate change dominated desertification reversion, while human activities dominated desertification expansion. Moreover, the relative roles of both climate change and human activities in desertification possessed great spatial heterogeneity. Additionally, ecological protection policies should be enhanced in the Heihe River Basin to prevent desertification expansion under the condition of climate change.</t>
+  </si>
+  <si>
+    <t>10.1007/s40333-013-0181-z</t>
+  </si>
+  <si>
+    <t>Desertification (degradation of ecosytems) due t human activities and CC</t>
+  </si>
+  <si>
+    <t>WOS:000328626100023</t>
+  </si>
+  <si>
+    <t>Assessment Impacts of Weather and Land Use/Land Cover (LULC) Change on Urban Vegetation Net Primary Productivity (NPP): A Case Study in Guangzhou, China</t>
+  </si>
+  <si>
+    <t>Net primary productivity (NPP) can indicate vegetation ecosystem services ability and reflect variation response to climate change and human activities. This study applied MODIS-1 km NPP products to investigate the NPP variation from 2001 to 2006, a fast urban expansion and adjustment period in Guangzhou, China, and quantify the impacts of weather and land use/land cover (LULC) changes, respectively. The results showed that the NPP mean value increased at a rate of 11.6 gCm(-2)yr(-1) during the initial three years and decreased at an accelerated rate of 31.0 gCm(-2)yr(-1) during the final three years, resulting in a total NPP loss of approximately 167 x 10(6) gC. The spatiotemporal of NPP varied obviously in the central area, suburb and exurb of Guangzhou driven by three patterns of weather and LULC changes. By the interactive effects and the weather variation dominated effects, NPP of most areas changed slightly with dynamic index less than 5% of NPP mean value in the central area and the suburb. The LULC change dominated effects caused obvious NPP reduction, by more than 15% of the NPP mean value, which occurred in some areas of the suburb and extended to the exurb with the outward urban sprawl. Importantly, conversion from wood grassland, shrublands and even forests to croplands occupied by urban landscapes proved to be a main process in the conversion from high-NPP coverage to low-NPP coverage, thereby leading to the rapid degradation of urban carbon stock capacity in urban fringe areas. It is helpful for government to monitor urban ecological health and safety and make relevant policies.</t>
+  </si>
+  <si>
+    <t>10.3390/rs5084125</t>
+  </si>
+  <si>
+    <t>NPP (which in turn supports more species and richness) and its changes due to land use change</t>
+  </si>
+  <si>
+    <t>WOS:000331673800014</t>
+  </si>
+  <si>
+    <t>Was overfishing of predatory fish responsible for a lobster-induced regime shift in the Benguela?</t>
+  </si>
+  <si>
+    <t>The top-down effects of predators have been demonstrated for terrestrial, freshwater and marine systems and their removal can cause a shift in ecosystem state. In many cases, the depletion of top-predators occurred long before humans began monitoring these systems, but models can elucidate likely ecosystem changes. In this paper we use a multispecies model to demonstrate that the abundance of predators can induce different ecosystem states, emphasising the importance of sustainable harvesting. Our model is founded on empirical data documenting a regime-shift that took place in the kelp-forest ecosystem along the south-west coast of South Africa following an 'invasion' by the West Coast rock lobster Jasus lalandii in the early 1990s. Formerly dominated by herbivores and encrusting corallines, the ecosystem became dominated by lobsters and macroalgae. A combination of illegal fishing of abalone Haliotis midae and the lobster-induced extermination of the urchin Parechinus angulosus (which shelters juvenile abalone) depleted abalone stocks severely. In this currently over-fished ecosystem where predators of lobsters are scarce, the regime-shift appears irreversible. Using an intermediate complexity model of lobster, urchin and abalone relationships, we simulated the effects of predatory fish at various population levels on the course of development of the currently lobster-dominated system. Our results indicate that current levels of fish biomass (&lt;10% of the pristine population) would have been too small to significantly affect the lobster population. However, at pristine levels of fish abundance (or even 50% less), the invasion of lobsters would have been controlled by linefish, and urchin and abalone populations would not have collapsed. The effect of the lobster invasion had a greater influence on abalone abundance than illegal fishing, but together they severely depleted the abalone. Ecosystem effects of historical exploitation of top predators are of central concern, and our ecosystem model indicates that depletion of linefish had severe consequences for lobsters, urchins and abalone, illustrating how overfishing of top predators may precipitate regime shifts, with profound socio-economic consequences. (C) 2013 Elsevier B.V. All rights reserved.</t>
+  </si>
+  <si>
+    <t>10.1016/j.ecolmodel.2013.11.004</t>
+  </si>
+  <si>
+    <t>Over fishing as driver causing ecosystem shift</t>
+  </si>
+  <si>
+    <t>WOS:000339385100016</t>
+  </si>
+  <si>
+    <t>Sensitivity and responses of diatoms to climate warming in lakes heavily influenced by humans</t>
+  </si>
+  <si>
+    <t>1. Diatom communities have been shown to respond strongly to current climate warming in remote lakes, while evidence remains equivocal for lakes under strong local human pressures. 2. Temporal dynamics of planktonic diatoms in three subalpine lakes (Geneva, Annecy and Bourget) reconstructed from palaeolimnological approaches were used to assess the relative effects of phosphorus concentrations, fisheries management practices and climate warming in structuring communities over the last century. 3. Changes in total phosphorous concentration (TP), air temperature and fish predation pressure could explain the temporal dynamics of most diatom species in the sediment records. TP was found to be not only the main driver of changes in community composition but also an important factor modulating diatom sensitivity and responses to climate warming. 4. The diatom community of Lake Bourget showed the highest vulnerability and direct responses to climate warming, favouring spring species that can resist earlier stratification in mesotrophic lakes (such as Asterionella formosa, Aulacoseira islandica and Stephanodiscus parvus) and summer species that can make the best trade-off between decreasing nutrient concentrations and increased water column stability (Diatoma tenuis, A. islandica). In Lake Geneva, climate warming also contributed to shaping diatom communities but through an indirect pathway; fisheries management practices and climate warming interacted to reinforce top-down control, favouring large, colonial inedible species (Stephanodicus binderanus and A. formosa). For Lake Annecy, the most nutrient limited of the three lakes studied, no changes in diatom community structure were directly related to warmer air temperatures over the last 25 years. 5. All three lakes have been subjected to the same climate variability. Yet the magnitude and responses of their diatom communities to climate warming were dissimilar and strongly modulated by differences in lake trophic status and fish management practices.</t>
+  </si>
+  <si>
+    <t>10.1111/fwb.12380</t>
+  </si>
+  <si>
+    <t>impact of climate warming and fisheries mgt in subalpine lakes on diatom community.</t>
+  </si>
+  <si>
+    <t>WOS:000351016900004</t>
+  </si>
+  <si>
+    <t>Effects of proximity to offshore fish farms over soft-bottom macrofauna</t>
+  </si>
+  <si>
+    <t>Sea-cage fish farms impact the seabed within their immediate vicinity, potentially affecting recipient communities. We assessed whether proximity to three sea-cage fish farms at the Canary Islands altered patterns in the abundance, assemblage structure and richness of soft-bottom macrofauna. We related among-farm variability in dissimilarities in macrofaunal assemblage structure between seabeds beneath cages and controls to differences in hydrodynamics, production and seabed topography. Contrasting patterns of species abundances with varying proximity to fish farms were observed: some species decreased while other species increased their abundances with increasing distance at some farms. Although faunal assemblages at 0 m (i.e. beneath the cages) were different, in terms of assemblage structure, from those found at controls, pairwise differences in assemblage structure among distances away varied among the studied fish farms. Species richness showed inconsistent patterns with proximity to cages among fish farms. In summary, inconsistent patterns of macrofaunal assemblages with varying proximity to aquaculture facilities preclude confident predictions on the way offshore aquaculture alters macrofauna in the study region.</t>
+  </si>
+  <si>
+    <t>10.1017/S0025315414001386</t>
+  </si>
+  <si>
+    <t>impact of fish farms (commercial controlled env) on soft-bottom macrofauna communitie</t>
+  </si>
+  <si>
+    <t>WOS:000360940400006</t>
+  </si>
+  <si>
+    <t>Fauna crime: elucidating the potential source and introduction history of European smelt (Osmerus eperlanus L.) into Lake Storsjoen, Norway</t>
+  </si>
+  <si>
+    <t>The ability to accurately determine the original source of invading species offers several powerful applications in invasive species ecology and management and may enable important information on the invading species in its native habitat. Lake Storsjoen in South-Central Norway was recently found to have been subjected to an illegal translocation of the European smelt (Osmerus eperlanus). The main aim of this study was to infer the most likely source (s) of the invading smelt by using microsatellite markers, and subsequently to infer its introduction history. The results indicated that the smelt is most likely a result of introduction from the large Lake Mjosa, and that the translocated smelt comprise a large number of individuals. The smelt in Lake Storsjoen showed no significant genetic bottleneck effect. However, a corresponding significant test for a recent population expansion indicates that the smelt has had a high reproductive success and population growth in its new environment. The results from this study illustrate the usefulness of applying multilocus genetic markers for inferring origin of translocated populations, demographic events and introduction histories comprising an effective tool for assessment of invasive species.</t>
+  </si>
+  <si>
+    <t>10.1007/s10592-015-0724-2</t>
+  </si>
+  <si>
+    <t>Illegal translocation of European smelt into Norwegian lake; anthro introduction of invasive species affecting biodiversity</t>
+  </si>
+  <si>
+    <t>WOS:000362824300001</t>
+  </si>
+  <si>
+    <t>Short-term genetic consequences of habitat loss and fragmentation for the neotropical palm Oenocarpus bataua</t>
+  </si>
+  <si>
+    <t>Habitat loss and fragmentation may impact animal-mediated dispersal of seed and pollen, and a key question is how the genetic attributes of plant populations respond to these changes. Theory predicts that genetic diversity may be less sensitive to such disruptions in the short term, whereas inbreeding and genetic structure may respond more strongly. However, results from studies to date vary in relation to species, context and the parameter being assessed, triggering calls for more empirical studies, especially from the tropics, where plant-animal dispersal mutualisms are both disproportionately common and at risk. We compared the genetic characteristics of adults and recruits in a long-lived palm Oenocarpus bataua in a recently fragmented landscape (&lt;2 generations) in northwest Ecuador using a suite of 10 polymorphic microsatellite markers. We sampled individuals from six forest fragments and one nearby continuous forest. Our goal was to assess short-term consequences of fragmentation, with a focus on how well empirical data from this system follow theoretical expectations. Mostly congruent with predictions, we found stronger genetic differentiation and fine-scale spatial genetic structure among recruits in fragments compared with recruits in continuous forest, but we did not record differences in genetic diversity or inbreeding, nor did we record any differences between adults in fragments and adults in continuous forest. Our findings suggest that genetic characteristics of populations vary in their sensitivity to change in response to habitat loss and fragmentation, and that fine-scale spatial genetic structure may be a particularly useful indicator of genetic change in recently fragmented landscapes.</t>
+  </si>
+  <si>
+    <t>10.1038/hdy.2015.35</t>
+  </si>
+  <si>
+    <t>result of habitat loss and fragmentation for neotropical palm</t>
+  </si>
+  <si>
+    <t>WOS:000363957700011</t>
+  </si>
+  <si>
+    <t>Microspatial sampling reveals cryptic influences on gene flow in a threatened mammal</t>
+  </si>
+  <si>
+    <t>We studied the population structure and historical demography of the last remaining core population of the threatened southeastern beach mouse (SEBM; Peromyscus polionotus niveiventris) located on a federally protected barrier island complex at the Kennedy Space Center (KSC), Merritt Island National Wildlife Refuge (MINWR) and Cape Canaveral Air Force Station (CCAFS) in Florida, USA. Beach mice (N = 171) were collected from 33 trapping locations along 30 km of coastline on KSC/MINWR/CCAFS and were genotyped using 10 microsatellite loci. We found four genetic clusters of mice that likely form a metapopulation. Gene flow among clusters, assessed using assignment tests, was limited suggesting that human development can serve to inhibit dispersal of beach mice. However, when the presence of roads were examined as possible barriers to movement, gene flow appeared to be facilitated suggesting that removal of thick vegetation along roadsides increases movement. We used approximate Bayesian computation (ABC) to estimate divergence time among clusters and effective population sizes for each cluster and for the pre-divergence population. Results of ABC analyses suggest that barriers to movement likely formed following the construction of the John F. Kennedy Space Center beginning in the 1960s but that this has not heavily impacted the effective size of populations. Pre-divergence and contemporary effective sizes are similar, thus, population sizes likely remained relatively large over the last 50-100 years. The population of SEBM on KSC/MINWR/CCAFS appears to be a genetically diverse core population and individuals from this population will most likely be good candidates for any future reintroduction and translocation programs.</t>
+  </si>
+  <si>
+    <t>10.1007/s10592-015-0749-6</t>
+  </si>
+  <si>
+    <t>human dev, infra, road networks influenced dispersal of gene flow in mouse</t>
+  </si>
+  <si>
+    <t>WOS:000367110300012</t>
+  </si>
+  <si>
+    <t>The temporal dynamics of a regional flora-The effects of global and local impacts</t>
+  </si>
+  <si>
+    <t>The main trends in changes in the global vascular plant biodiversity are generally considered to be a decrease in rare indigenous species and a spread of invasive plants. In the present paper, the impact of these changes on the flora of the state of Baden-Wurttemberg (Southwest-Germany) is examined. The data come from a regional floristic mapping project, which consists of two consecutive surveys, dating from 1970 to 1998 and from 2005 to present. In contrast to many other studies, not only a part of the flora or of an ecosystem was studied but the entire vascular plant flora of a region. As the recent survey is not yet completed, samples of 46 out of 1100 grid cells are analysed as a preliminary study on the trends in entire Baden-Wurttemberg. In the present paper we address the issues (1) whether changes in biodiversity observed in other studies, e.g. decrease of rare native species and increase of invasives, affect the flora of Baden-Wurttemberg, (2) which abiotic factors, i.e. climatic or soil conditions, cause these changes of species diversity. The analysis of the two consecutive surveys revealed a continuing decrease of rare native species and a constant increase of neophytes, thus reflecting the global trends. Many extinction events happened before 1970, some already in the 19th century. Changes in land use and urbanisation of former rural regions are two important factors for these changes. A statistic analysis using Ellenberg indicator values revealed the nitrogen input from agriculture and the effects of global warming as further potential causes for these trends. (C) 2015 Elsevier GmbH. All rights reserved.</t>
+  </si>
+  <si>
+    <t>10.1016/j.flora.2015.09.013</t>
+  </si>
+  <si>
+    <t>regional vascular plant biodiversity: deceases in rare species and spread of IAS due to anthropogenic impacts</t>
+  </si>
+  <si>
+    <t>WOS:000369456300023</t>
+  </si>
+  <si>
+    <t>Genetic consequences of human forest exploitation in two colobus monkeys in Guinea Bissau</t>
+  </si>
+  <si>
+    <t>The ability of forest-dwelling species to adapt to changes in their habitat is being increasingly challenged by the rapid pace of human-induced forest degradation. Understanding the effect of such environmental changes on biodiversity requires comparative analyses across species living within the same habitats. We investigated the effect of forest exploitation on the genetic structure and demography of two sympatric arboreal primates showing differences in their socioecology: the Western black-and-white colobus (Colobus polykomos) and Temminck's red colobus (Procolobus badius temminckii). We conducted the study in a fragmented and human-impacted forest in Guinea Bissau. Using microsatellite data from six C. polykomos and eight P. b. temminckii social groups, we found that in C polykomos the distribution of genetic diversity followed an isolation-by-distance pattern whereas for P. b. temminckii, the results suggested restriction in female dispersal. We detected a strong, recent bottleneck for both primates, which we inferred to have resulted from the anthropogenic exploitation of forest resources in the last centuries. The bottleneck signal was stronger for P. b. temminckii as a likely consequence of its larger estimated ancestral population size. Finally, we discussed the different analytical approaches used. Our results confirm that P. b. temminckii is more affected by habitat changes than C polykomos, despite being phylogenetically close. Nonetheless, the low estimated effective population sizes and the known demographic changes indicate that both species are severely threatened by human forest exploitation, requiring urgent conservation action. (C) 2015 Elsevier Ltd. All rights reserved.</t>
+  </si>
+  <si>
+    <t>10.1016/j.biocon.2015.12.019</t>
+  </si>
+  <si>
+    <t>result of human forest exploitation on colobus monkeys</t>
+  </si>
+  <si>
+    <t>WOS:000369491500101</t>
+  </si>
+  <si>
+    <t>Disentangling the responses of boreal stream assemblages to low stressor levels of diffuse pollution and altered channel morphology</t>
+  </si>
+  <si>
+    <t>Non-point diffuse pollution from land use and alteration of hydromorphology are among the most detrimental stressors to stream ecosystems. We explored the independent and interactive effects of morphological channel alteration (channelization for water transport of timber) and diffuse pollution on species richness and community structure of four organism groups in boreal streams: diatoms, macrophytes, macroinvertebrates, and fish. Furthermore, the effect of these stressors on stream condition was evaluated by Ecological Quality Ratios (EQR) from the national Water Framework Directive (WFD) assessment system. We grouped 91 study sites into four groups that were impacted by either diffuse pollution or hydromorphological alteration, by both stressors, or by neither one. Macroinvertebrate richness was reduced by diffuse pollution, whereas other biological groups were unaltered. Hydromorphological modification had no effect on taxon richness of any of the assemblages. Community structure of all groups was significantly affected by diffuse pollution but not by hydromorphology. Similarly, EQRs indicated negative response by diatoms, macroinvertebrates and fish to diffuse pollution, but not to hydromorphological alteration. Agricultural diffuse pollution thus affected species identities and abundances rather than taxonomic richness. Our results suggest that channelization of boreal streams for timber transport has not altered hydromorphological conditions sufficiently to have a strong impact on stream biota, whereas even moderate nutrient enrichment may be ecologically harmful. Controlling diffuse pollution and associated land use stressors should be prioritized over restoration of in-stream habitat structure to improve the ecological condition of boreal streams. (C) 2015 Elsevier B.V. All rights reserved.</t>
+  </si>
+  <si>
+    <t>10.1016/j.scitotenv.2015.12.031</t>
+  </si>
+  <si>
+    <t>Diffuse pollution (from land to water) and channel morphology (shapes and structure of river channels) alteration effects on boreal assemblage</t>
   </si>
   <si>
     <t>WOS:000373722700008</t>
@@ -1347,19 +1105,428 @@
     <t>genetics diversity as change due to habitat fragmentation</t>
   </si>
   <si>
-    <t>WOS:000363957700011</t>
-  </si>
-  <si>
-    <t>Microspatial sampling reveals cryptic influences on gene flow in a threatened mammal</t>
-  </si>
-  <si>
-    <t>We studied the population structure and historical demography of the last remaining core population of the threatened southeastern beach mouse (SEBM; Peromyscus polionotus niveiventris) located on a federally protected barrier island complex at the Kennedy Space Center (KSC), Merritt Island National Wildlife Refuge (MINWR) and Cape Canaveral Air Force Station (CCAFS) in Florida, USA. Beach mice (N = 171) were collected from 33 trapping locations along 30 km of coastline on KSC/MINWR/CCAFS and were genotyped using 10 microsatellite loci. We found four genetic clusters of mice that likely form a metapopulation. Gene flow among clusters, assessed using assignment tests, was limited suggesting that human development can serve to inhibit dispersal of beach mice. However, when the presence of roads were examined as possible barriers to movement, gene flow appeared to be facilitated suggesting that removal of thick vegetation along roadsides increases movement. We used approximate Bayesian computation (ABC) to estimate divergence time among clusters and effective population sizes for each cluster and for the pre-divergence population. Results of ABC analyses suggest that barriers to movement likely formed following the construction of the John F. Kennedy Space Center beginning in the 1960s but that this has not heavily impacted the effective size of populations. Pre-divergence and contemporary effective sizes are similar, thus, population sizes likely remained relatively large over the last 50-100 years. The population of SEBM on KSC/MINWR/CCAFS appears to be a genetically diverse core population and individuals from this population will most likely be good candidates for any future reintroduction and translocation programs.</t>
-  </si>
-  <si>
-    <t>10.1007/s10592-015-0749-6</t>
-  </si>
-  <si>
-    <t>human dev, infra, road networks influenced dispersal of gene flow in mouse</t>
+    <t>WOS:000376798800013</t>
+  </si>
+  <si>
+    <t>Biodiversity consequences of land-use change and forest disturbance in the Amazon: A multi-scale assessment using ant communities</t>
+  </si>
+  <si>
+    <t>Quantifying and understanding the main drivers of biodiversity responses to human disturbances at multiple scales is key to foster effective conservation plans and management systems. Here we report on a detailed regional assessment of the response of ant communities to land-use change and forest disturbance in the Brazilian Amazon. We aimed to explore the effects of land-use intensification at both site and landscape scales, examining variation in ant species richness and composition, and asking which set of environmental variables best predict observed patterns of diversity. We sampled 192 sites distributed across 18 landscapes (each 50 km(2)) in Paragominas, eastern Brazilian Amazon, covering ca. 20,000 km(2). We sampled from undisturbed primary forest through varyingly disturbed primary forests, secondary forests, pastures and mechanised agriculture, following a gradient of decreasing total aboveground biomass. Irrespective of forest disturbance class, ant species richness was almost twice as high in forests when compared to production areas. In contrast, ant species composition showed continuous variation from primary forest to intensive agriculture, following a gradient of aboveground biomass. Ant species richness at all spatial scales increased with primary forest cover in the surrounding landscapes. We highlight the limited value of species richness as an indicator of changes in habitat quality, reinforcing calls to consider species composition in assessments of forest disturbance. Taken together, our results reveal the unique biodiversity value of undisturbed primary forests, but also show that disturbed primary forests and secondary forests have high conservation value, and thus play an important role in regional conservation planning. (C) 2016 Elsevier Ltd. All rights reserved.</t>
+  </si>
+  <si>
+    <t>10.1016/j.biocon.2016.03.005</t>
+  </si>
+  <si>
+    <t>Land use change, forest disturbances, and its impact on ant communities</t>
+  </si>
+  <si>
+    <t>WOS:000391956900011</t>
+  </si>
+  <si>
+    <t>Realized climatic niches are conserved along maximum temperatures among herpetofaunal invaders</t>
+  </si>
+  <si>
+    <t>AimThe conservatism of the realized climatic niche is a pivotal assumption for predicting invasion risk under present and future climates. To date, however, no studies have identified the particular dimensions of realized climatic niches that are spatially and temporally conserved for a whole taxonomic group on a global scale. Understanding realized niche dynamics along each individual climatic variable separately is a key consideration for improving forecasts of invasive species distributions and anticipating future range expansions. LocationGlobal. MethodsUsing 181 successful invasion events for 128 alien herpetofaunal species across the globe, we applied a robust niche dynamics framework and analysed the conservatism of the realized climatic niche and its influencing factors along 19 temperature and precipitation variables. ResultsWe found that the magnitude of the niche expansion along the maximum temperature of the warmest month (or warmest quarter) was, on average, the lowest compared with the niche expansion magnitude along the minimum, average, range and seasonal temperature characteristics and all precipitation variables. Furthermore, the niche shift along the maximum temperature was only negatively correlated with native range size and was unrelated to residence time, species traits, introduction propagule pressure, topographic heterogeneity or equatorwards and polewards range expansion. Main conclusionsWe provide the first evidence that the realized climatic niche of alien herpetofaunal species is generally most conserved along maximum temperatures. This finding highlights the importance of preferentially choosing conserved climatic niche parameters to develop robust predictions of biological invasions or shifts in species ranges in response to climate change.</t>
+  </si>
+  <si>
+    <t>10.1111/jbi.12808</t>
+  </si>
+  <si>
+    <t>realized climatic niche (the set env and climate condiions a spiece occupies in nature); herpetofauna (Invasive) realized climatic nich is conserved along max temp;</t>
+  </si>
+  <si>
+    <t>WOS:000399848100008</t>
+  </si>
+  <si>
+    <t>Combined effects of climate and land management on watershed vegetation dynamics in an arid environment</t>
+  </si>
+  <si>
+    <t>Leaf area index (LAI) is a key parameter to characterize vegetation dynamics and ecosystem structure that determines the ecosystem functions and services such as clean water supply and carbon sequestration in a watershed. However, linking LAI dynamics and environmental controls (i.e., coupling biosphere, atmosphere, and anthroposphere) remains challenging and such type of studies have rarely been done at a watershed scale due to data availability. The present study examined the spatial and temporal variations of LAI for five ecosystem types within a watershed with a complex topography in the Upper Heihe River Basin, a major inland river in the arid and semi-arid western China. We integrated remote sensing-based GLASS (Global Land Surface Satellite) LAI products, interpolated climate data, watershed characteristics, and land management records for the period of 2001-2012. We determined the relationships among LAI, topography, air temperature and precipitation, and grazing history by five ecosystem types using several advanced statistical methods. We show that long-term mean LAI distribution had an obvious vertical pattern as controlled by precipitation and temperature in a hilly watershed. Overall, watershed-wide mean LAI had an increasing trend overtime for all ecosystem types during 2001-2012, presumably as a result of global warming and a wetting climate. However, the fluctuations of observed LAI at a pixel scale (1 km) varied greatly across the watershed. We classified the vegetation changes within the watershed as 'Improved', 'Stabilized', and 'Degraded' according their respective LAI changes. We found that climate was not the only driver for temporal vegetation changes for all land cover types. Grazing partially contributed to the decline of LAI in some areas and masked the positive climate warming effects in other areas. Extreme weathers such as cold spells and droughts could substantially affect inter-annual variability of LAI dynamics. We concluded that temporal and spatial LAI dynamics were rather complex and were affected by both climate variations and human disturbances in the study basin. Future monitoring studies should focus on the functional interactions among vegetation dynamics, climate variations, land management, and human disturbances. Published by Elsevier B.V.</t>
+  </si>
+  <si>
+    <t>10.1016/j.scitotenv.2017.02.210</t>
+  </si>
+  <si>
+    <t xml:space="preserve">vegetation dynamics linked to effects from cc and land mgt </t>
+  </si>
+  <si>
+    <t>WOS:000401719600004</t>
+  </si>
+  <si>
+    <t>Identifying and quantifying environmental thresholds for ecological shifts in a large semi-regulated river</t>
+  </si>
+  <si>
+    <t>Ecological shifts, between a clear macrophyte-dominated state and a turbid state dominated by phytoplankton and high inorganic suspended solids, have been well described in shallow lake ecosystems. While few documented examples exist in rivers, models predict regime shifts, especially in regulated rivers with high water retention time. Here I quantified ecological shifts in a large, semi-regulated floodplain river during a transition from a turbid-to a clear-water state using water quality, aquatic vegetation and fisheries data from a rigorous, standardized long-term data set. My findings indicate that significant changes occurred in total suspended solids concentration, aquatic macrophyte abundance, native and non-native fish biomass, fish functional feeding guild patterns, fish habitat guild assemblages and fish spawning guild assemblage patterns over a nearly 20-year period in Navigation Pool 8 of the Upper Mississippi River. Transitions in physical and biological indicators were examined to identify mechanisms underlying the ecological shifts. Environmental variables driving fish assemblage changes were identified (total suspended solids and aquatic vegetation) and management-relevant thresholds are presented. Awareness of management thresholds is critical for resource managers to implement measures to prevent the river from moving to a degraded state characterized by high non-native fish abundance and low predatory fish species abundance.</t>
+  </si>
+  <si>
+    <t>10.1080/02705060.2017.1319431</t>
+  </si>
+  <si>
+    <t>river regulation (anthro source) as driver of aquatic biodiv change</t>
+  </si>
+  <si>
+    <t>WOS:000414755500014</t>
+  </si>
+  <si>
+    <t>Inter-decadal changes in fish communities of a tropical bay in southeastern Brazil</t>
+  </si>
+  <si>
+    <t>Long-term evaluations of coastal fish communities worldwide have in many cases showed a decrease in the species richness and abundance as a result of anthropogenic impacts. Fish communities in two zones (inner and outer) of a tropical bay in southeastern Brazil were sampled monthly during six years over two decades (1983-1985, 1993-1995, 1999-2001) using identical sampling methods. Over time, an increase in temperature and a decrease in water transparency were detected, while salinity remained stable. Fish assemblage was dominated by benthivorous species both migrant and resident species. The fish assemblage structure differed significantly between the two bay zones. Significant decreases in the fish richness, abundance and biomass were detected over time. The highest decreases in the species richness was recorded between 1983-1985 and 1993-1995 for the marine migrants in both bay zones and for the resident and marine straggler species in the outer zone. Dominant species such as the clupeoids Anchoa januaria, Anchoa tricolor, Harengula clupeola, the gerreid Eucinostomos argenteus, the sciaenid Micropogonias furnieri, the atherinopsid Atherinella brasiliensis and the ariid Genidens barbus decreased over time, whereas the mugilid Mugil liza increased. Persistent differences in the fish assemblage structure between the two bay zones over the three periods can be attributed at least in part to differences in environmental variables between the zones and seem to be a key ecological element to maintenance of biodiversity. This is the first study to examine long-term changes in the fish community of a tropical bay in Brazil. (C) 2015 Elsevier B.V. All rights reserved.</t>
+  </si>
+  <si>
+    <t>10.1016/j.rsma.2015.06.001</t>
+  </si>
+  <si>
+    <t>decrease in richness of fish communities from anthro impacts</t>
+  </si>
+  <si>
+    <t>WOS:000418334200001</t>
+  </si>
+  <si>
+    <t>Long-term carbon sink in Borneo's forests halted by drought and vulnerable to edge effects</t>
+  </si>
+  <si>
+    <t>Less than half of anthropogenic carbon dioxide emissions remain in the atmosphere. While carbon balance models imply large carbon uptake in tropical forests, direct on-the-ground observations are still lacking in Southeast Asia. Here, using long-term plot monitoring records of up to half a century, we find that intact forests in Borneo gained 0.43 Mg C ha(-1) per year (95% CI 0.14-0.72, mean period 1988-2010) above-ground live biomass. These results closely match those from African and Amazonian plot networks, suggesting that the world's remaining intact tropical forests are now en masse out-of-equilibrium. Although both pantropical and long-term, the sink in remaining intact forests appears vulnerable to climate and land use changes. Across Borneo the 1997-1998 El Nino drought temporarily halted the carbon sink by increasing tree mortality, while fragmentation persistently offset the sink and turned many edge-affected forests into a carbon source to the atmosphere.</t>
+  </si>
+  <si>
+    <t>10.1038/s41467-017-01997-0</t>
+  </si>
+  <si>
+    <t>Forest loss (anthro driver) affecting forest biomas and biodiv. , i.e. long term carbon sink in borneo forests vulnerable to effects from deforestation</t>
+  </si>
+  <si>
+    <t>WOS:000428400500003</t>
+  </si>
+  <si>
+    <t>Productivity and recovery of forage fish under climate change and fishing: North Sea sandeel as a case study</t>
+  </si>
+  <si>
+    <t>Forage fish occupy a central position in marine food-webs worldwide by mediating the transfer of energy and organic matter from lower to higher trophic levels. The lesser sandeel (Ammodytes marinus) is one of the ecologically and economically most important forage fish species in the North-east Atlantic, acting as a key prey for predatory fish and sea birds, as well as supporting a large commercial fishery. In this case study, we investigate the underlying factors affecting recruitment and how these in turn affect productivity of the North Sea sandeel using long-term data and modelling. Our results demonstrate how sandeel productivity in the central North Sea (Dogger Bank) depends on a combination of external and internal regulatory factors, including fishing and climate effects, as well as density dependence and food availability of the preferred zooplankton prey (Calanus finmarchicus and Temora longicornis). Furthermore, our model scenarios suggest that while fishing largely contributed to the abrupt stock decline during the late 1990s and the following period of low biomass, a complete recovery of the stock to the highly productive levels of the early 1980s would only be possible through changes in the surrounding ecosystem, involving lower temperatures and improved feeding conditions. To that end, we stress the need for ecosystem-based management accounting for multiple internal and external factors occurring within the broader context of the ecosystem in which forage fish species, such as sandeel, play an important and integral part.</t>
+  </si>
+  <si>
+    <t>10.1111/fog.12246</t>
+  </si>
+  <si>
+    <t>fishing and climate (anthro drivers) affecting forage fish biodiv</t>
+  </si>
+  <si>
+    <t>WOS:000432992100019</t>
+  </si>
+  <si>
+    <t>Genetic diversity through time and space: diversity and demographic history from natural history specimens and serially sampled contemporary populations of the threatened Gouldian finch (Erythrura gouldiae)</t>
+  </si>
+  <si>
+    <t>Declines in population size can compromise the viability of populations by reducing the effective population size (N-e), which may result in loss of genetic diversity and inbreeding. Temporal population genetic data can be a powerful tool for testing the presence and severity of reductions in N-e. The Gouldian finch (Erythrura gouldiae) is a flagship for conservation of Australian monsoonal savanna species. This species underwent severe population declines in the twentieth century due to land use changes associated with European colonization. Microsatellite and mitochondrial genetic data from Gouldian finch samples sourced from natural history collections prior to land use changes were compared with contemporary samples to estimate the severity of decline in effective population size and to detect changes in gene flow. These data show that Gouldian finch decline was not as severe as some sources suggest, and that population genetic connectivity has not changed following land use changes in the twentieth century. Multiple estimators of current N-e using genetic data from consecutive years suggest the Gouldian finch N-e is likely between a few hundred and a few thousand individuals, with some estimates within the range considered of conservation concern. This work has identified the need to genetically characterize populations in Queensland, and to understand critical demographic parameters (e.g. lifespan) in the Gouldian finch. Understanding these factors is vital to further improve genetic estimates of population size, key to the formation of appropriate conservation management of this species.</t>
+  </si>
+  <si>
+    <t>10.1007/s10592-018-1051-1</t>
+  </si>
+  <si>
+    <t>Gouldian finch population decline due to land use change and fire</t>
+  </si>
+  <si>
+    <t>WOS:000435480900008</t>
+  </si>
+  <si>
+    <t>Demographic and Density Response of Northern Bobwhites to Pyric Herbivory of Non-Native Grasslands</t>
+  </si>
+  <si>
+    <t>Usable space for northern bobwhites (Colinus virginianus) has declined significantly over the past 3 decades in Texas because non-native grasses have replaced native vegetation. We hypothesized that burning patches in pastures dominated by buffelgrass (Pennisetum ciliare) and OldWorld bluestems (Bothriochloa spp. and Dichanthium spp.) followed by livestock grazing would increase limiting habitat attributes, thereby increasing usable space and bobwhite demographic parameters and population densities. Our study was conducted during 2009-2011 in LaSalle County, Texas on a ranch dominated by non-native grasses. Our experimental design was composed of 2 blocks with two 240-ha pastures, one control (graze only), and one treatment (patch-burn and graze) in each. We estimated grass standing crop in grazing exclosures (June-September) and habitat attributes along transects (October) 2009-2011. Bobwhites were captured and monitored via radiotelemetry 2-3 times/wk during March-November. Means of vegetation metrics important to bobwhites such as bare ground, traversibility, and forb and subshrub cover were similar between control and treatment units in post-treatment years. However, grass standing crop tended to be lower in treatment (June and August 2010 and September 2011-110.5 +/- 26.2 g/m(2)) compared with control units (June and August 2010 and September 2011-145.5 +/- 58.6 g/m(2)). Plant species richness was also greater (21%) in treatment (4.6 +/- 0.4/0.1 m(2)) compared with control units (3.8 +/- 0.4/0.1 m(2)) during the last year of the study (P = 0.057). Patch heterogeneity was increased in treatment units. There was an increase in bobwhite densities in treatment units, although demographicmetrics remained similar between treatment and controls. Patch burning and grazing is a viable tool for managing monotypic non-native grasslands for bobwhites in semiarid environments. (C) 2018 Published by Elsevier Inc. on behalf of The Society for Range Management.</t>
+  </si>
+  <si>
+    <t>10.1016/j.rama.2018.02.008</t>
+  </si>
+  <si>
+    <t>Ias and habitat modification affecting Northern Bobwhites</t>
+  </si>
+  <si>
+    <t>WOS:000438220000023</t>
+  </si>
+  <si>
+    <t>Recovery of mammal diversity in tropical forests: a functional approach to measuring restoration</t>
+  </si>
+  <si>
+    <t>Ecological restoration is increasingly applied in tropical forests to mitigate biodiversity loss and recover ecosystem functions. In restoration ecology, functional richness, rather than species richness, often determines community assembly, and measures of functional diversity provide a mechanistic link between diversity and ecological functioning of restored habitat. Vertebrate animals are important for ecosystem functioning. Here, we examine the functional diversity of small-to-medium sized mammals to evaluate the diversity and functional recovery of tropical rainforest. We assess how mammal species diversity and composition and functional diversity and composition, vary along a restoration chronosequence from degraded pasture to old-growth tropical rainforest in the Wet Tropics of Australia. Species richness, diversity, evenness, and abundance did not vary, but total mammal biomass and mean species body mass increased with restoration age. Species composition in restoration forests converged on the composition of old-growth rainforest and diverged from pasture with increasing restoration age. Functional metrics provided a clearer pattern of recovery than traditional species metrics, with most functional metrics significantly increasing with restoration age when taxonomic-based metrics did not. Functional evenness and dispersion increased significantly with restoration age, suggesting that niche complementarity enhances species' abundances in restored sites. The change in community composition represented a functional shift from invasive, herbivorous, terrestrial habitat generalists and open environment specialists in pasture and young restoration sites, to predominantly endemic, folivorous, arboreal, and fossorial forest species in older restoration sites. This shift has positive implications for conservation and demonstrates the potential of tropical forest restoration to recover rainforest-like, diverse faunal communities.</t>
+  </si>
+  <si>
+    <t>10.1111/rec.12582</t>
+  </si>
+  <si>
+    <t>recovery of mamal functional diversity in tropical forests; 
+" a functional shift from invasive, herbivorous, terrestrial habitat generalists and open environment specialists in pasture and young restoration sites"</t>
+  </si>
+  <si>
+    <t>WOS:000443567600013</t>
+  </si>
+  <si>
+    <t>World's Largest Mass Bathing Event Influences the Bacterial Communities of Godavari, a Holy River of India</t>
+  </si>
+  <si>
+    <t>Kumbh Mela is one of the largest religious mass gathering events (MGE) involving bathing in rivers. The exponential rise in the number of devotees, from around 0.4 million in 1903 to 120 million in 2013, bathing in small specified sites can have a dramatic impact on the river ecosystem. Here, we present the spatiotemporal profiling of bacterial communities in Godavari River, Nashik, India, comprising five sites during the Kumbh Mela, held in 2015. Assessment of environmental parameters indicated deterioration of water quality. Targeted amplicon sequencing demonstrates approximately 37.5% loss in microbial diversity because of anthropogenic activity during MGE. A significant decrease in phyla viz. Actinobacteria, Chloroflexi, Proteobacteria, and Bacteroidetes was observed, while we noted substantial increase in prevalence of the phylum Firmicutes (94.6%) during MGE. qPCR estimations suggested nearly 130-fold increase in bacterial load during the event. Bayesian mixing model accounted the source of enormous incorporation of bacterial load of human origin. Further, metagenomic imputations depicted increase in virulence and antibiotic resistance genes during the MGE. These observations suggest the striking impact of the mass bathing on river ecosystem. The subsequent increase in infectious diseases and drug-resistant microbes pose a critical public health concern.</t>
+  </si>
+  <si>
+    <t>10.1007/s00248-018-1169-1</t>
+  </si>
+  <si>
+    <t>mass bathing (anthro source) and impact of river bacterial communities</t>
+  </si>
+  <si>
+    <t>WOS:000534700300001</t>
+  </si>
+  <si>
+    <t>Urbanization alters the composition, but not the diversity and structure, of Neotropical savanna woody plant communities</t>
+  </si>
+  <si>
+    <t>Urbanization is one of the main drivers of environmental change and can result in drastic changes to the biodiversity and composition of plant communities. The objective of the present work was to investigate whether the structure, diversity and composition of Neotropical savanna woody plant communities differ among fragments immersed in urban, peri-urban and rural environments. The study was carried out in nine Neotropical savannas with distinct levels of urbanization in the municipality of Montes Claros, state of Minas Gerais, Brazil. A total of 469 woody individuals belonging to 76 species and 30 families of plants were sampled. The most specious families were the Fabaceae with seventeen species and the Vochysiaceae with eight. The most abundant species were Myracrodruon urundeuva in urban areas, Byrsonima pachyphyla in peri-urban areas and Hymenaea stigonocarpa in rural areas. The diversity (species richness, estimated species richness and Simpson diversity index) and structure (abundance, cover and height) of the plant communities under study did not vary in response to urbanization, although species composition experienced notable changes. The urban plant communities were very distinct from the rural plant communities. Furthermore, the dominant species were very different among the urban, peri-urban and rural areas. These findings demonstrate that urbanization affects Neotropical savanna species that are susceptible to anthropization. Furthermore, among the anthropogenic pressures related to urbanization, fragmentation and isolation seem to be the most influential determinants of the composition of Neotropical savanna communities.</t>
+  </si>
+  <si>
+    <t>10.1007/s12224-020-09366-4</t>
+  </si>
+  <si>
+    <t>Effect on urbanization on composition of woody plant communities</t>
+  </si>
+  <si>
+    <t>WOS:000608979000001</t>
+  </si>
+  <si>
+    <t>Sea-ice microbial communities in the Central Arctic Ocean: Limited responses to short-term pCO2 perturbations</t>
+  </si>
+  <si>
+    <t>The Arctic Ocean is more susceptible to ocean acidification than other marine environments due to its weaker buffering capacity, while its cold surface water with relatively low salinity promotes atmospheric CO2 uptake. We studied how sea-ice microbial communities in the central Arctic Ocean may be affected by changes in the carbonate system expected as a consequence of ocean acidification. In a series of four experiments during late summer 2018 aboard the icebreaker Oden, we addressed microbial growth, production of dissolved organic carbon (DOC) and extracellular polymeric substances (EPS), photosynthetic activity, and bacterial assemblage structure as sea-ice microbial communities were exposed to elevated partial pressures of CO2 (pCO(2)). We incubated intact, bottom ice-core sections and dislodged, under-ice algal aggregates (dominated by Melosira arctica) in separate experiments under approximately 400, 650, 1000, and 2000 mu atm pCO(2) for 10 d under different nutrient regimes. The results indicate that the growth of sea-ice algae and bacteria was unaffected by these higher pCO(2) levels, and concentrations of DOC and EPS were unaffected by a shifted inorganic C/N balance, resulting from the CO2 enrichment. These central Arctic sea-ice microbial communities thus appear to be largely insensitive to short-term pCO(2) perturbations. Given the natural, seasonally driven fluctuations in the carbonate system of sea ice, its resident microorganisms may be sufficiently tolerant of large variations in pCO(2) and thus less vulnerable than pelagic communities to the impacts of ocean acidification, increasing the ecological importance of sea-ice microorganisms even as the loss of Arctic sea ice continues.</t>
+  </si>
+  <si>
+    <t>10.1002/lno.11690</t>
+  </si>
+  <si>
+    <t>pCO2 perturbations (sustained changes in pressure of CO2 in surface oceans);  microbial community changes due to pCO2 pertub.</t>
+  </si>
+  <si>
+    <t>WOS:000646507600009</t>
+  </si>
+  <si>
+    <t>Land use land cover dynamics and fragmentation-induced changes in woody plant community structure in a mining landscape, Ghana</t>
+  </si>
+  <si>
+    <t>The study assessed the dynamics of mining land use land cover changes and consequent fragmentation impacts on woody plant community structure in the Ahafo Region, Ghana. Landsat images were utilised to determine land use and cover changes using a supervised classification method. Plant community structure was determined within 60 (20 x 20 m) plots that were randomly laid in equal numbers in fragmented and intact forests. Our findings showed that the mining landscape experienced a substantial land use/cover change between 2003 and 2018, with considerable forest cover loss at the expense of increasing cover of plantation, settlement/bare surface, mine site, and waterbody. Woody plant species diversity was significantly lower in the fragmented forest around the mine. Likewise, fragmentation caused a shift in plant species composition in the fragmented forest, whose composition was less homogenised compared to the intact forest. Plant abundance did not differ significantly between the two forests, but it was invasive and cultivated tree species that increased the total abundance of woody plants in the fragmented forests. The mining landscape was dominated by an invasive alien species, Broussonetia papyrifera which poses an ecological threat to native species. In conclusion, our findings suggest that mining contributed to intense land use/cover dynamics and fragmentation that impaired woody plant community structure around the mine. There is the need to accord priority to management intervention that would seek to manage and conserve the remaining forest fragments and its biodiversity in the mining landscape.</t>
+  </si>
+  <si>
+    <t>10.1016/j.tfp.2021.100070</t>
+  </si>
+  <si>
+    <t>impact of land use change and fragmentation on woodly plants community structure</t>
+  </si>
+  <si>
+    <t>WOS:000668739900006</t>
+  </si>
+  <si>
+    <t>Human encroachment into wildlife gut microbiomes</t>
+  </si>
+  <si>
+    <t>In the Anthropocene, humans, domesticated animals, wildlife, and their environments are interconnected, especially as humans advance further into wildlife habitats. Wildlife gut microbiomes play a vital role in host health. Changes to wildlife gut microbiomes due to anthropogenic disturbances, such as habitat fragmentation, can disrupt natural gut microbiota homeostasis and make animals vulnerable to infections that may become zoonotic. However, it remains unclear whether the disruption to wildlife gut microbiomes is caused by habitat fragmentation per se or the combination of habitat fragmentation with additional anthropogenic disturbances, such as contact with humans, domesticated animals, invasive species, and their pathogens. Here, we show that habitat fragmentation per se does not impact the gut microbiome of a generalist rodent species native to Central America, Tome's spiny rat Proechimys semispinosus, but additional anthropogenic disturbances do. Indeed, compared to protected continuous and fragmented forest landscapes that are largely untouched by other human activities, the gut microbiomes of spiny rats inhabiting human-disturbed fragmented landscapes revealed a reduced alpha diversity and a shifted and more dispersed beta diversity. Their microbiomes contained more taxa associated with domesticated animals and their potential pathogens, suggesting a shift in potential metagenome functions. On the one hand, the compositional shift could indicate a degree of gut microbial adaption known as metagenomic plasticity. On the other hand, the greater variation in community structure and reduced alpha diversity may signal a decline in beneficial microbial functions and illustrate that gut adaption may not catch up with anthropogenic disturbances, even in a generalist species with large phenotypic plasticity, with potentially harmful consequences to both wildlife and human health. Fackelmann et al. study the gut microbial composition of spiny rats across tropical forests in Panama with varying levels of protection and fragmentation in order to disentangle the relative influences of habitat fragmentation and anthropogenic disturbance on wildlife gut microbiomes. They find that habitat fragmentation on its own did not affect the gut microbiome, but the microbiomes of individuals inhabiting forest fragments affected by anthropogenic disturbance displayed a shift in community composition and structure, and were more likely to have microbiota associated with domesticated animals and their pathogens.</t>
+  </si>
+  <si>
+    <t>10.1038/s42003-021-02315-7</t>
+  </si>
+  <si>
+    <t>human encroachment via habitat fragmentation into wildlife gut microbiomes</t>
+  </si>
+  <si>
+    <t>WOS:000701772800007</t>
+  </si>
+  <si>
+    <t>A survey of benthic invertebrate communities in native and non-native seagrass beds in St. John, USVI</t>
+  </si>
+  <si>
+    <t>Halophila stipulacea, a seagrass native to the Indian Ocean, spread to the Caribbean in 2002. Few studies have explored the spatiotemporal distribution of H. stipulacea throughout the Caribbean and whether native invertebrates utilize this non-native seagrass as habitat. We surveyed the shallow, nearshore subtidal zones of four bays in St. John, US Virgin Islands over a two-year period to assess the abundance of both H. stipulacea and native seagrass species. We then surveyed macroinvertebrate communities in one bay with large areas of H. stipulacea, native seagrasses, and bare substrate to assess how macroinvertebrate species composition varied in these habitats. Our survey of the benthic macroinvertebrates revealed that: (1) native invertebrate species utilize H. stipulacea beds and (2) the density and richness of invertebrates was significantly higher in H. stipulacea beds compared to both native seagrass beds and bare substrate. Our results show that H. stipulacea is a common component of nearshore communities in St. John, USVI and that native invertebrates use H. stipulacea beds as habitat - results that agree with findings from other recent studies. While these findings indicate that native macroinvertebrate species can be abundant in non-native seagrass, further investigation, including experimental manipulations, preference tests, and surveys across broad spatial scales, are required to develop a robust understanding of the ecological impacts of this non-native grass.</t>
+  </si>
+  <si>
+    <t>10.1016/j.aquabot.2021.103448</t>
+  </si>
+  <si>
+    <t>non-native seagrass invastion and its effect on benthic invertebrate communities</t>
+  </si>
+  <si>
+    <t>WOS:000704969600011</t>
+  </si>
+  <si>
+    <t>Diuron environmental levels effects on marine nematodes: Assessment of ecological indices, taxonomic diversity, and functional traits</t>
+  </si>
+  <si>
+    <t>Coastal marine systems are the most sensitive zones to emerging pollutants. The present study aims to investigate the effect of Diuron on the meiofaunal assemblages, collected from the Bizerte channel (Tunisia). Microcosm experiments were set up using four increasing Diuron concentrations [D1 (10 ng g-1 dry weight (DW)), D2 (50 ng g-1 DW), D3 (250 ng g-1 DW) and (1250 ng g-1 DW)] compared to non-contaminated sediments (controls) and all plots were incubated for 30 days. Our results show that Diuron-supplemented sediments provoked the significant decrease of meiofaunal abundance as well as a change in nematodes' diversity and structure composition. All univariate indices, as well as the cumulative k-dominance, were lower in the Diuron than the control plot. Additionally, the ordination of treatments according to the two-dimensional nMDS plots analysis showed a clear structural separation of the Diuron treated replicates from the controls based on the functional groups lists. These current data emphasize the utility of the use of biological traits in the detection of disturbances in the aquatic biotope.</t>
+  </si>
+  <si>
+    <t>10.1016/j.chemosphere.2021.132262</t>
+  </si>
+  <si>
+    <t>diuron (herbicide pollutant) effects on marine nematode communities</t>
+  </si>
+  <si>
+    <t>Scientific Foundations for an IUCN Red List of Ecosystems</t>
+  </si>
+  <si>
+    <t>An understanding of risks to biodiversity is needed for planning action to slow current rates of decline and secure ecosystem services for future human use. Although the IUCN Red List criteria provide an effective assessment protocol for species, a standard global assessment of risks to higher levels of biodiversity is currently limited. In 2008, IUCN initiated development of risk assessment criteria to support a global Red List of ecosystems. We present a new conceptual model for ecosystem risk assessment founded on a synthesis of relevant ecological theories. To support the model, we review key elements of ecosystem definition and introduce the concept of ecosystem collapse, an analogue of species extinction. The model identifies four distributional and functional symptoms of ecosystem risk as a basis for assessment criteria: A) rates of decline in ecosystem distribution; B) restricted distributions with continuing declines or threats; C) rates of environmental (abiotic) degradation; and D) rates of disruption to biotic processes. A fifth criterion, E) quantitative estimates of the risk of ecosystem collapse, enables integrated assessment of multiple processes and provides a conceptual anchor for the other criteria. We present the theoretical rationale for the construction and interpretation of each criterion. The assessment protocol and threat categories mirror those of the IUCN Red List of species. A trial of the protocol on terrestrial, subterranean, freshwater and marine ecosystems from around the world shows that its concepts are workable and its outcomes are robust, that required data are available, and that results are consistent with assessments carried out by local experts and authorities. The new protocol provides a consistent, practical and theoretically grounded framework for establishing a systematic Red List of the world’s ecosystems. This will complement the Red List of species and strengthen global capacity to report on and monitor the status of biodiversity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">not related to any specific biodiversity change but a conceptual paper </t>
+  </si>
+  <si>
+    <t>["NOT_ELIGIBLE"]</t>
+  </si>
+  <si>
+    <t>A review of spatial patterns across species ranges to aid the targeting of conservation interventions</t>
+  </si>
+  <si>
+    <t>Conservation resources are limited and need to be used where they can be most effective. Deciding where within a species range to implement conservation interventions requires knowledge of where threats operate and consideration of multiple spatial issues concerning patterns in abundance across species' ranges, and geographical and environmental gradients in these and other traits across species' ranges. Although these biogeographical patterns have been of great interest to ecologists for many years, the implications of these patterns for conservation are often unclear. Here we review these patterns in the context of targeting spatial conservation. We find that an inconsistent use of terminology, a lack of consistent rules and the use of imperfect datasets, hampers us drawing firm conclusions on the nature of these patterns. Evidence that abundance and ecological traits change systematically towards range edges is inconclusive. Abundance variation is influenced by many factors independent of position within a species range, including habitat type, habitat quality, environment, interspecific competition, dispersal ecology and metapopulation dynamics. This results in complex textured abundance patterns compared to a simple theoretical core-edge gradient. We conclude that any conservation practitioner looking to target the location of interventions will need to examine these patterns and processes for the species of interest. Current knowledge does not adequately inform spatial conservation prioritization for single-species conservation programmes and incorporating the complexities of spatial processes is challenging. The development of tools to inform spatial targeting of resources for single- or multiple-species conservation is required urgently to enable better use of conservation resources.</t>
+  </si>
+  <si>
+    <t>Text is a review of spatial patterns for conservation targetting; there's no biodiversity change aspect present</t>
+  </si>
+  <si>
+    <t>WOS:000171279300012</t>
+  </si>
+  <si>
+    <t>Using restriction fragment length polymorphisms to assess temporal variation and estimate the number of ascospores that initiate epidemics in field populations of Mycosphaerella graminicola</t>
+  </si>
+  <si>
+    <t>Restriction fragment length polymorphisms (RFLPs) and DNA fingerprints were used to assess temporal variation and estimate the effective population size of the wheat pathogen Mycosphaerella graminicola over a 6-year period. In each year, the fungal population was founded by ascospores originating from outside the sampled fields. A total of 605 fungal isolates were included in this study. Our results indicate that the genetic structure of these M. graminicola populations were stable over the 6-year period. The common alleles at each RFLP locus were present at similar frequencies each year. More than 99% of gene diversity was distributed within populations sampled from the same year and less than 1% was attributed to differences among years. The lack of population differentiation among collections taken in different years indicated that the effective size of the source population was sufficiently large that genetic drift was insignificant in this location. It also suggests that the initial colonists from ascospore founder populations were a fair reflection of the source population. We estimate that the effective sizes of these field populations ranged from 3,400 to 700,000 individuals, depending on the size of the field sampled and assumptions about mutation rates. Estimates of the number of ascospores initiating epidemics of leaf blotch disease in each field plot and factors that contribute to the large effective population size of M. graminicola are discussed.</t>
+  </si>
+  <si>
+    <t>10.1094/PHYTO.2001.91.10.1011</t>
+  </si>
+  <si>
+    <t>unclear what is  biodiversity change here</t>
+  </si>
+  <si>
+    <t>WOS:000179492800006</t>
+  </si>
+  <si>
+    <t>Metapopulation structure of the specialized herbivore Macrosiphoniella tanacetaria (Homoptera, Aphididae)</t>
+  </si>
+  <si>
+    <t>We investigated population dynamics, genetic diversity and spatial structure in the aphid species Macrosiphoniella tanacetaria, a specialist herbivore feeding on tansy, Tanacetum vulgare. Tansy plants (genets) consist of many shoots (ramets), and genets are grouped in sites. Thus, aphids feeding on tansy can cluster at the level of ramets, genets and sites. We studied aphid population dynamics in 1997 and 2001 and found that within sites: (i) at any time, aphids used only a fraction of the available ramets and genets; (ii) at the level of ramets, most aphid colonies survived only one week; (iii) at the level of genets, mean survival time was less than 4 weeks; and (iv) colonization and extinction events occurred throughout the season. We sampled aphids in seven sites in the Alsace region, France (4-45 km apart) and two sites in Germany in 1999 to study genetic structure within and between populations. Genetic analyses using nine microsatellite loci showed that: (i) genotypic variability was high, (ii) none of the populations was in Hardy-Weinberg equilibrium, (iii) heterozygote deficits and linkage disequilibria were frequent, and (iv) all populations were genetically differentiated, even at a small geographical scale. Renewed sampling of the Alsace sites in 2001 showed that three populations had become extinct and significant genetic changes had occurred in the remaining four populations. The frequencies of extinction and colonization events at several spatial scales suggest a hierarchical metapopulation structure for M. tanacetaria. Frequent population turnover and drift are likely causes for the genetic differentiation of M. tanacetaria populations.</t>
+  </si>
+  <si>
+    <t>10.1046/j.1365-294X.2002.01633.x</t>
+  </si>
+  <si>
+    <t>can't infer what is anthropogenic driver here</t>
+  </si>
+  <si>
+    <t>WOS:000236141500018</t>
+  </si>
+  <si>
+    <t>Population genetic structure of the Japanese eel Anguilla japonica in the northwest Pacific Ocean:: evidence of non-panmictic populations</t>
+  </si>
+  <si>
+    <t>The catadromous Japanese eel has an unusual life history. Controversy remains, however, as to whether its population structure is characterized by panmixia or genetic differentiation. Migration patterns are considered an important factor in determining a species' population structure. Eight polymorphic microsatellite loci were used as genetic markers through which we were able to reject the null hypothesis of panmixia. Slight genetic differentiation between these populations was determined by Wright's and Slatkin's fixation indices, F-ST and R-ST statistics adjusted using Bonferroni's correction. Although isolation-by-distance is often observed in marine species, the present result is thought to follow the member-vagrant migratory hypothesis. The metapopulation model fits the elver recruitment strategy according to results of the high probability of assignment test. The UPGMA tree showed the Japanese eel populations as being divided into 2 groups: a low-latitude group (Shantou in South China, and Tanshui and Fangliao in Taiwan) and a high-latitude group (Mikawa Bay in Japan, Daecheon-myon in Korea, and the Yalu River and Hangzhou in Northeast China). Temporal genetic variations indicate that most progeny return to similar habitats where their ancestors formerly resided. There was a high correlation (AMOVA; p &lt; 0.05) when the Japanese eel was divided into the 2 management units (high- and low-latitude groups), These units will be useful when applied to fisheries conservation and management in the northwestern Pacific Ocean.</t>
+  </si>
+  <si>
+    <t>10.3354/meps308221</t>
+  </si>
+  <si>
+    <t>WOS:000281181500007</t>
+  </si>
+  <si>
+    <t>Population genetic structure of dolphinfish (Coryphaena hippurus) in the Gulf of California, using microsatellite loci</t>
+  </si>
+  <si>
+    <t>We assayed genetic variations at five microsatellite loci of dolphinfish captured at five sites in 2005 and eight sites in 2006 to detect genetic population structure of dolphinfish Coryphaena hippurus in the Gulf of California and surrounding waters. Results show high genetic variation, similar to other pelagic fishes with large populations. Pairwise F-ST values and hierarchical AMOVA detected subtle but significant spatial and temporal heterogeneity, mainly in samples of 2005 and some of 2006. However, Bayesian assignment analysis failed to detect genetic differentiation, which was also supported by the Mantel test and gene flow estimates among the sampled sites. This suggests that, despite the slight heterogeneity detected in this region, the dolphinfish forms a single panmictic population with high genetic variation and gene flow. (C) 2010 Elsevier B.V. All rights reserved.</t>
+  </si>
+  <si>
+    <t>10.1016/j.fishres.2010.03.023</t>
+  </si>
+  <si>
+    <t>WOS:000303476600020</t>
+  </si>
+  <si>
+    <t>Inferring the ancestry of African wild dogs that returned to the Serengeti-Mara</t>
+  </si>
+  <si>
+    <t>An endangered population of African wild dogs (Lycaon pictus) disappeared from the Serengeti-Mara area in 1991. The reasons for the extinction are not well understood, but disease was implicated in the disappearance. In 2001, wild dogs naturally re-established themselves in the region. We conducted genetic profiling on samples collected prior and subsequent to this event, as well as samples from three geographically close populations, to determine the potential source of colonisers. Contrary to expectations, we found no evidence of re-colonisation from these nearby wild dog populations. Rather, our analyses suggest that the re-established animals are primarily derived from the same genetic population as the pre-extinction animals, indicating that wild dogs are likely to have persisted in the Serengeti-Mara after 1991. We also detected some migrants that could be derived from genetically distinct populations outside the recovery area. Overall, we did not detect a decline in genetic diversity at either neutral microsatellites or major histocompatibility complex loci, indicating that the supposed disappearance of wild dogs in the Serengeti-Mara did not substantially impact genetic variation of the population.</t>
+  </si>
+  <si>
+    <t>10.1007/s10592-011-0304-z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">unclear about the anthropogenic driver here. Here was the disease natural or human-associated? </t>
+  </si>
+  <si>
+    <t>WOS:000305154000001</t>
+  </si>
+  <si>
+    <t>Attributing carbon changes in conterminous U.S. forests to disturbance and non-disturbance factors from 1901 to 2010</t>
+  </si>
+  <si>
+    <t>Recent climate variability (increasing temperature, droughts) and atmospheric composition changes (nitrogen deposition, rising CO2 concentration) along with harvesting, wildfires, and insect infestations have had significant effects on U. S. forest carbon (C) uptake. In this study, we attribute C changes in the conterminous U. S. forests to disturbance and non-disturbance factors with the help of forest inventory data, a continental stand age map, and an updated Integrated Terrestrial Ecosystem Carbon Cycle model (InTEC). We grouped factors into disturbances (harvesting, fire, insect infestation) and non-disturbances (CO2 concentration, N deposition, and climate variability) and estimated their subsequent impacts on forest regrowth patterns. Results showed that on average, the C sink in the conterminous U. S. forests from 1950 to 2010 was 206 Tg C yr(-1) with 87% (180 Tg C yr(-1)) of the sink in living biomass. Compared with the simulation of all factors combined, the estimated C sink would be reduced by 95 Tg C yr(-1) if disturbance factors were omitted, and reduced by 50 Tg C yr(-1) if non-disturbance factors were omitted. Our study also showed diverse regional patterns of C sinks related to the importance of driving factors. During 1980-2010, disturbance effects dominated the C changes in the South and Rocky Mountain regions, were almost equal to non-disturbance effects in the North region, and had minor effects compared with non-disturbance effects in the West Coast region.</t>
+  </si>
+  <si>
+    <t>10.1029/2011JG001930</t>
+  </si>
+  <si>
+    <t>Text is not about biodiversity change but carbon changes</t>
+  </si>
+  <si>
+    <t>WOS:000315414700007</t>
+  </si>
+  <si>
+    <t>Landscape genetics of an early successional specialist in a disturbance-prone environment</t>
+  </si>
+  <si>
+    <t>Species that specialize in disturbed habitats may have considerably different dispersal strategies than those adapted to more stable environments. However, little is known of the dispersal patterns and population structure of such species. This information is important for conservation because many postfire specialists are at risk from anthropogenic changes to natural disturbance regimes. We used microsatellite markers to assess the effect of landscape variation and recent disturbance history on dispersal by a small mammal species that occupies the early seral stage of vegetation regeneration in burnt environments. We predicted that a postfire specialist would be able to disperse over multiple habitat types (generalist) and not exhibit sex-biased dispersal, as such strategies should enable effective colonization of spatially and temporally variable habitat. We found significant differentiation between sites that fitted an isolation-by-distance pattern and spatial autocorrelation of multilocus genotypes to a distance of 23km. There was no consistent genetic evidence for sex-biased dispersal. We tested the influence of different habitat- and fire-specific landscape resistance scenarios on genetic distance between individuals and found a significant effect of fire. Our genetic data supported recently burned vegetation having greater conductance for gene flow than unburnt habitat, but variation in habitat quality between vegetation types and occupied patches had no effect on gene flow. Postfire specialists must evolve an effective dispersal ability to move over distances that would ensure access to early successional stage vegetation. Natural disturbance and natural heterogeneity may therefore not influence population genetic structure as negatively as expected.</t>
+  </si>
+  <si>
+    <t>10.1111/mec.12172</t>
+  </si>
+  <si>
+    <t>WOS:000323115800128</t>
+  </si>
+  <si>
+    <t>Genetic Network and Breeding Patterns of a Sicklefin Lemon Shark (Negaprion acutidens) Population in the Society Islands, French Polynesia</t>
+  </si>
+  <si>
+    <t>Human pressures have put many top predator populations at risk of extinction. Recent years have seen alarming declines in sharks worldwide, while their resilience remains poorly understood. Studying the ecology of small populations of marine predators is a priority to better understand their ability to withstand anthropogenic and environmental stressors. In the present study, we monitored a naturally small island population of 40 adult sicklefin lemon sharks in Moorea, French Polynesia over 5 years. We reconstructed the genetic relationships among individuals and determined the population's mating system. The genetic network illustrates that all individuals, except one, are interconnected at least through one first order genetic relationship. While this species developed a clear inbreeding avoidance strategy involving dispersal and migration, the small population size, low number of breeders, and the fragmented environment characterizing these tropical islands, limits its complete effectiveness.</t>
+  </si>
+  <si>
+    <t>10.1371/journal.pone.0073899</t>
+  </si>
+  <si>
+    <t>text is describing population with limited genetic diversity and high vulner. I can not infer any positive or negative biodiversity change here</t>
+  </si>
+  <si>
+    <t>WOS:000350025600019</t>
+  </si>
+  <si>
+    <t>Temporal Population Genetic Structure of Yellow Perch Spawning Groups in the Lower Great Lakes</t>
+  </si>
+  <si>
+    <t>This study tested the hypothesis that the genetic composition of Yellow Perch Perca flavescens spawning groups at specific sites remained consistent among years or age-cohorts; this likely would influence spatial population structure and be important for delineating management units. Previous studies identified that spawning groups genetically differed among locations across fine geographic scales, but it was unknown whether these patterns persisted from year to year. We analyzed 15 nuclear DNA microsatellite loci from Yellow Perch spawning at six Lake Erie locations in 2009 in reference to two out-groups spawning in Lakes St. Clair and Ontario. Results were compared with a prior study of samples from the same locations that had been collected in various years, ranging from 2001 to 2005. We evaluated consistency for two of the spawning groups across multiple birth-year-cohorts. Results indicated that the levels of genetic diversity were similar across all spawning groups and years. All eight spawning groups genetically differed from one other, with their allelic compositions varying between the two sampling periods. Some variation occurred among individual sampling years and birth-cohorts, with the 2003 cohort being the most distinctive. Sampling groups contained relatively high proportions of full siblings (mean = 18.5%, ranging to 75% for the 2001 birth-cohort spawning at the eastern Lake Erie site), yet inbreeding appeared relatively low. Differences at sampling sites over time did not appear to reflect genetic drift but may instead suggest that spawning groups reproduce in slightly different locations from year to year or perhaps within a given season; this merits examination. Spatial and temporal patterns may reflect kin-group structuring and differential reproductive success, in which strong year-classes dominate spawning groups and impact genetic structure.</t>
+  </si>
+  <si>
+    <t>10.1080/00028487.2014.982260</t>
+  </si>
+  <si>
+    <t>WOS:000376022300013</t>
+  </si>
+  <si>
+    <t>Still here after all these years: the persistence of the Uncompahgre fritillary butterfly</t>
+  </si>
+  <si>
+    <t>The US federally endangered Uncompahgre fritillary butterfly (Boloria acrocnema) lives in isolated alpine habitats of the San Juan Mountains of Colorado, USA. Its apparent extirpation from the type locality and its low genetic diversity raised concern in the late 1980s, thus monitoring for this species has continued and genetic samples were collected in 2008 and 2009 from all but one known site, each on a separate peak. Data for five new microsatellite markers were collected from 316 total specimens, including 26 from wings preserved from 1987 and 1988 seasons. Only three main colonies had high enough sample sizes for adequate analyses. We estimated levels of genetic variability and structure, and effective population size. Despite low demographic numbers at these sites, the species has maintained relatively high heterozygosity ranging from 0.41 to 0.46 at three sites. Allelic richness corrected by sample size ranged from 5.3 to 5.9. Genetic structure assessed with non-spatially explicit methods indicated that despite separation on high mountain peaks, colonies were fairly well mixed, which is surprising for these weak fliers with very short growing and adult flight seasons. Estimates of effective population sizes were low, reflecting the life history and limited habitat range for the species. Comparisons at the site with historic and modern specimens revealed a consistent pattern in genetic indices. Our data suggest that the three focal butterfly colonies exist as a metapopulation that persists due to low-level migration between sites and temporal leakage via flexibility in development time in this biennial species.</t>
+  </si>
+  <si>
+    <t>10.1007/s10841-016-9867-9</t>
+  </si>
+  <si>
+    <t>WOS:000391939700003</t>
+  </si>
+  <si>
+    <t>Temporal genetic stability in natural populations of the waterflea Daphnia magna in response to strong selection pressure</t>
+  </si>
+  <si>
+    <t>Studies monitoring changes in genetic diversity and composition through time allow a unique understanding of evolutionary dynamics and persistence of natural populations. However, such studies are often limited to species with short generation times that can be propagated in the laboratory or few exceptional cases in the wild. Species that produce dormant stages provide powerful models for the reconstruction of evolutionary dynamics in the natural environment. A remaining open question is to what extent dormant egg banks are an unbiased representation of populations and hence of the species' evolutionary potential, especially in the presence of strong environmental selection. We address this key question using the water flea Daphnia magna, which produces dormant stages that accumulate in biological archives over time. We assess temporal genetic stability in three biological archives, previously used in resurrection ecology studies showing adaptive evolutionary responses to rapid environmental change. We show that neutral genetic diversity does not decline with the age of the population and it is maintained in the presence of strong selection. In addition, by comparing temporal genetic stability in hatched and unhatched populations from the same biological archive, we show that dormant egg banks can be consulted to obtain a reliable measure of genetic diversity over time, at least in the multidecadal time frame studied here. The stability of neutral genetic diversity through time is likely mediated by the buffering effect of the resting egg bank.</t>
+  </si>
+  <si>
+    <t>10.1111/mec.13907</t>
   </si>
   <si>
     <t>WOS:000401104900001</t>
@@ -1377,22 +1544,16 @@
     <t>No biodiveristy change aspect present here</t>
   </si>
   <si>
-    <t>["NOT_ELIGIBLE"]</t>
-  </si>
-  <si>
-    <t>WOS:000305154000001</t>
-  </si>
-  <si>
-    <t>Attributing carbon changes in conterminous U.S. forests to disturbance and non-disturbance factors from 1901 to 2010</t>
-  </si>
-  <si>
-    <t>Recent climate variability (increasing temperature, droughts) and atmospheric composition changes (nitrogen deposition, rising CO2 concentration) along with harvesting, wildfires, and insect infestations have had significant effects on U. S. forest carbon (C) uptake. In this study, we attribute C changes in the conterminous U. S. forests to disturbance and non-disturbance factors with the help of forest inventory data, a continental stand age map, and an updated Integrated Terrestrial Ecosystem Carbon Cycle model (InTEC). We grouped factors into disturbances (harvesting, fire, insect infestation) and non-disturbances (CO2 concentration, N deposition, and climate variability) and estimated their subsequent impacts on forest regrowth patterns. Results showed that on average, the C sink in the conterminous U. S. forests from 1950 to 2010 was 206 Tg C yr(-1) with 87% (180 Tg C yr(-1)) of the sink in living biomass. Compared with the simulation of all factors combined, the estimated C sink would be reduced by 95 Tg C yr(-1) if disturbance factors were omitted, and reduced by 50 Tg C yr(-1) if non-disturbance factors were omitted. Our study also showed diverse regional patterns of C sinks related to the importance of driving factors. During 1980-2010, disturbance effects dominated the C changes in the South and Rocky Mountain regions, were almost equal to non-disturbance effects in the North region, and had minor effects compared with non-disturbance effects in the West Coast region.</t>
-  </si>
-  <si>
-    <t>10.1029/2011JG001930</t>
-  </si>
-  <si>
-    <t>Text is not about biodiversity change but carbon changes</t>
+    <t>WOS:000406912400011</t>
+  </si>
+  <si>
+    <t>Genetic composition and origin of juvenile green turtles foraging at Culebra, Puerto Rico, as revealed by mtDNA</t>
+  </si>
+  <si>
+    <t>Marine migratory species encounter a range of threats as they move through coastal and oceanic zones. Understanding the connectivity and dispersal patterns of such species is critical to their effective conservation. Here we analyzed the temporal genetic composition and the most likely origin of juvenile green turtles foraging at Puerto Manglar and Tortuga Bay, Culebra, Puerto Rico, using mitochondrial DNA control region sequences. We identified 17 haplotypes, of which CM-A3 (51.5%), CM-A5 (19.4%) and CM-A1 (13.6%) were the most common. Haplotype (h) and nucleotide (pi) diversities were 0.680 and 0.008, respectively. There was no evidence of significant variation in the genetic composition of these aggregations throughout seven years (2000-2006), suggesting that relative contributions from source populations did not significantly change during this period. Mixed Stock Analysis (MSA), incorporating 14 Atlantic nesting populations as possible sources, indicated four main contributing stocks to the Culebra foraging grounds: Costa Rica (34.9%), Mexico (29.2%), East Central Florida (13.2%), and Suriname (12.0%). The regional pattern of connectivity among Wider Caribbean rookeries and Culebra was further evidenced by a second MSA using Atlantic Regional Management Units (RMUs) as sources, with 94.1% of the mixed stock attributed to this area. This study addresses the information gap on the connectivity of the green turtle in the North Atlantic, and establishes an important baseline that can be used to determine future changes in stock composition.</t>
+  </si>
+  <si>
+    <t>10.3856/vol45-issue3-fulltext-2</t>
   </si>
   <si>
     <t>WOS:000431791200005</t>
@@ -1410,51 +1571,6 @@
     <t xml:space="preserve">there is no clear indication of any biodiversity change and anthro drivers </t>
   </si>
   <si>
-    <t>Scientific Foundations for an IUCN Red List of Ecosystems</t>
-  </si>
-  <si>
-    <t>An understanding of risks to biodiversity is needed for planning action to slow current rates of decline and secure ecosystem services for future human use. Although the IUCN Red List criteria provide an effective assessment protocol for species, a standard global assessment of risks to higher levels of biodiversity is currently limited. In 2008, IUCN initiated development of risk assessment criteria to support a global Red List of ecosystems. We present a new conceptual model for ecosystem risk assessment founded on a synthesis of relevant ecological theories. To support the model, we review key elements of ecosystem definition and introduce the concept of ecosystem collapse, an analogue of species extinction. The model identifies four distributional and functional symptoms of ecosystem risk as a basis for assessment criteria: A) rates of decline in ecosystem distribution; B) restricted distributions with continuing declines or threats; C) rates of environmental (abiotic) degradation; and D) rates of disruption to biotic processes. A fifth criterion, E) quantitative estimates of the risk of ecosystem collapse, enables integrated assessment of multiple processes and provides a conceptual anchor for the other criteria. We present the theoretical rationale for the construction and interpretation of each criterion. The assessment protocol and threat categories mirror those of the IUCN Red List of species. A trial of the protocol on terrestrial, subterranean, freshwater and marine ecosystems from around the world shows that its concepts are workable and its outcomes are robust, that required data are available, and that results are consistent with assessments carried out by local experts and authorities. The new protocol provides a consistent, practical and theoretically grounded framework for establishing a systematic Red List of the world’s ecosystems. This will complement the Red List of species and strengthen global capacity to report on and monitor the status of biodiversity</t>
-  </si>
-  <si>
-    <t xml:space="preserve">not related to any specific biodiversity change but a conceptual paper </t>
-  </si>
-  <si>
-    <t>A review of spatial patterns across species ranges to aid the targeting of conservation interventions</t>
-  </si>
-  <si>
-    <t>Conservation resources are limited and need to be used where they can be most effective. Deciding where within a species range to implement conservation interventions requires knowledge of where threats operate and consideration of multiple spatial issues concerning patterns in abundance across species' ranges, and geographical and environmental gradients in these and other traits across species' ranges. Although these biogeographical patterns have been of great interest to ecologists for many years, the implications of these patterns for conservation are often unclear. Here we review these patterns in the context of targeting spatial conservation. We find that an inconsistent use of terminology, a lack of consistent rules and the use of imperfect datasets, hampers us drawing firm conclusions on the nature of these patterns. Evidence that abundance and ecological traits change systematically towards range edges is inconclusive. Abundance variation is influenced by many factors independent of position within a species range, including habitat type, habitat quality, environment, interspecific competition, dispersal ecology and metapopulation dynamics. This results in complex textured abundance patterns compared to a simple theoretical core-edge gradient. We conclude that any conservation practitioner looking to target the location of interventions will need to examine these patterns and processes for the species of interest. Current knowledge does not adequately inform spatial conservation prioritization for single-species conservation programmes and incorporating the complexities of spatial processes is challenging. The development of tools to inform spatial targeting of resources for single- or multiple-species conservation is required urgently to enable better use of conservation resources.</t>
-  </si>
-  <si>
-    <t>Text is a review of spatial patterns for conservation targetting; there's no biodiversity change aspect present</t>
-  </si>
-  <si>
-    <t>WOS:000315414700007</t>
-  </si>
-  <si>
-    <t>Landscape genetics of an early successional specialist in a disturbance-prone environment</t>
-  </si>
-  <si>
-    <t>Species that specialize in disturbed habitats may have considerably different dispersal strategies than those adapted to more stable environments. However, little is known of the dispersal patterns and population structure of such species. This information is important for conservation because many postfire specialists are at risk from anthropogenic changes to natural disturbance regimes. We used microsatellite markers to assess the effect of landscape variation and recent disturbance history on dispersal by a small mammal species that occupies the early seral stage of vegetation regeneration in burnt environments. We predicted that a postfire specialist would be able to disperse over multiple habitat types (generalist) and not exhibit sex-biased dispersal, as such strategies should enable effective colonization of spatially and temporally variable habitat. We found significant differentiation between sites that fitted an isolation-by-distance pattern and spatial autocorrelation of multilocus genotypes to a distance of 23km. There was no consistent genetic evidence for sex-biased dispersal. We tested the influence of different habitat- and fire-specific landscape resistance scenarios on genetic distance between individuals and found a significant effect of fire. Our genetic data supported recently burned vegetation having greater conductance for gene flow than unburnt habitat, but variation in habitat quality between vegetation types and occupied patches had no effect on gene flow. Postfire specialists must evolve an effective dispersal ability to move over distances that would ensure access to early successional stage vegetation. Natural disturbance and natural heterogeneity may therefore not influence population genetic structure as negatively as expected.</t>
-  </si>
-  <si>
-    <t>10.1111/mec.12172</t>
-  </si>
-  <si>
-    <t>unclear what is  biodiversity change here</t>
-  </si>
-  <si>
-    <t>WOS:000171279300012</t>
-  </si>
-  <si>
-    <t>Using restriction fragment length polymorphisms to assess temporal variation and estimate the number of ascospores that initiate epidemics in field populations of Mycosphaerella graminicola</t>
-  </si>
-  <si>
-    <t>Restriction fragment length polymorphisms (RFLPs) and DNA fingerprints were used to assess temporal variation and estimate the effective population size of the wheat pathogen Mycosphaerella graminicola over a 6-year period. In each year, the fungal population was founded by ascospores originating from outside the sampled fields. A total of 605 fungal isolates were included in this study. Our results indicate that the genetic structure of these M. graminicola populations were stable over the 6-year period. The common alleles at each RFLP locus were present at similar frequencies each year. More than 99% of gene diversity was distributed within populations sampled from the same year and less than 1% was attributed to differences among years. The lack of population differentiation among collections taken in different years indicated that the effective size of the source population was sufficiently large that genetic drift was insignificant in this location. It also suggests that the initial colonists from ascospore founder populations were a fair reflection of the source population. We estimate that the effective sizes of these field populations ranged from 3,400 to 700,000 individuals, depending on the size of the field sampled and assumptions about mutation rates. Estimates of the number of ascospores initiating epidemics of leaf blotch disease in each field plot and factors that contribute to the large effective population size of M. graminicola are discussed.</t>
-  </si>
-  <si>
-    <t>10.1094/PHYTO.2001.91.10.1011</t>
-  </si>
-  <si>
     <t>WOS:000439769400019</t>
   </si>
   <si>
@@ -1465,123 +1581,6 @@
   </si>
   <si>
     <t>10.1002/ece3.4143</t>
-  </si>
-  <si>
-    <t>can't infer what is anthropogenic driver here</t>
-  </si>
-  <si>
-    <t>WOS:000303476600020</t>
-  </si>
-  <si>
-    <t>Inferring the ancestry of African wild dogs that returned to the Serengeti-Mara</t>
-  </si>
-  <si>
-    <t>An endangered population of African wild dogs (Lycaon pictus) disappeared from the Serengeti-Mara area in 1991. The reasons for the extinction are not well understood, but disease was implicated in the disappearance. In 2001, wild dogs naturally re-established themselves in the region. We conducted genetic profiling on samples collected prior and subsequent to this event, as well as samples from three geographically close populations, to determine the potential source of colonisers. Contrary to expectations, we found no evidence of re-colonisation from these nearby wild dog populations. Rather, our analyses suggest that the re-established animals are primarily derived from the same genetic population as the pre-extinction animals, indicating that wild dogs are likely to have persisted in the Serengeti-Mara after 1991. We also detected some migrants that could be derived from genetically distinct populations outside the recovery area. Overall, we did not detect a decline in genetic diversity at either neutral microsatellites or major histocompatibility complex loci, indicating that the supposed disappearance of wild dogs in the Serengeti-Mara did not substantially impact genetic variation of the population.</t>
-  </si>
-  <si>
-    <t>10.1007/s10592-011-0304-z</t>
-  </si>
-  <si>
-    <t xml:space="preserve">unclear about the anthropogenic driver here. Here was the disease natural or human-associated? </t>
-  </si>
-  <si>
-    <t>WOS:000406912400011</t>
-  </si>
-  <si>
-    <t>Genetic composition and origin of juvenile green turtles foraging at Culebra, Puerto Rico, as revealed by mtDNA</t>
-  </si>
-  <si>
-    <t>Marine migratory species encounter a range of threats as they move through coastal and oceanic zones. Understanding the connectivity and dispersal patterns of such species is critical to their effective conservation. Here we analyzed the temporal genetic composition and the most likely origin of juvenile green turtles foraging at Puerto Manglar and Tortuga Bay, Culebra, Puerto Rico, using mitochondrial DNA control region sequences. We identified 17 haplotypes, of which CM-A3 (51.5%), CM-A5 (19.4%) and CM-A1 (13.6%) were the most common. Haplotype (h) and nucleotide (pi) diversities were 0.680 and 0.008, respectively. There was no evidence of significant variation in the genetic composition of these aggregations throughout seven years (2000-2006), suggesting that relative contributions from source populations did not significantly change during this period. Mixed Stock Analysis (MSA), incorporating 14 Atlantic nesting populations as possible sources, indicated four main contributing stocks to the Culebra foraging grounds: Costa Rica (34.9%), Mexico (29.2%), East Central Florida (13.2%), and Suriname (12.0%). The regional pattern of connectivity among Wider Caribbean rookeries and Culebra was further evidenced by a second MSA using Atlantic Regional Management Units (RMUs) as sources, with 94.1% of the mixed stock attributed to this area. This study addresses the information gap on the connectivity of the green turtle in the North Atlantic, and establishes an important baseline that can be used to determine future changes in stock composition.</t>
-  </si>
-  <si>
-    <t>10.3856/vol45-issue3-fulltext-2</t>
-  </si>
-  <si>
-    <t>WOS:000236141500018</t>
-  </si>
-  <si>
-    <t>Population genetic structure of the Japanese eel Anguilla japonica in the northwest Pacific Ocean:: evidence of non-panmictic populations</t>
-  </si>
-  <si>
-    <t>The catadromous Japanese eel has an unusual life history. Controversy remains, however, as to whether its population structure is characterized by panmixia or genetic differentiation. Migration patterns are considered an important factor in determining a species' population structure. Eight polymorphic microsatellite loci were used as genetic markers through which we were able to reject the null hypothesis of panmixia. Slight genetic differentiation between these populations was determined by Wright's and Slatkin's fixation indices, F-ST and R-ST statistics adjusted using Bonferroni's correction. Although isolation-by-distance is often observed in marine species, the present result is thought to follow the member-vagrant migratory hypothesis. The metapopulation model fits the elver recruitment strategy according to results of the high probability of assignment test. The UPGMA tree showed the Japanese eel populations as being divided into 2 groups: a low-latitude group (Shantou in South China, and Tanshui and Fangliao in Taiwan) and a high-latitude group (Mikawa Bay in Japan, Daecheon-myon in Korea, and the Yalu River and Hangzhou in Northeast China). Temporal genetic variations indicate that most progeny return to similar habitats where their ancestors formerly resided. There was a high correlation (AMOVA; p &lt; 0.05) when the Japanese eel was divided into the 2 management units (high- and low-latitude groups), These units will be useful when applied to fisheries conservation and management in the northwestern Pacific Ocean.</t>
-  </si>
-  <si>
-    <t>10.3354/meps308221</t>
-  </si>
-  <si>
-    <t>WOS:000350025600019</t>
-  </si>
-  <si>
-    <t>Temporal Population Genetic Structure of Yellow Perch Spawning Groups in the Lower Great Lakes</t>
-  </si>
-  <si>
-    <t>This study tested the hypothesis that the genetic composition of Yellow Perch Perca flavescens spawning groups at specific sites remained consistent among years or age-cohorts; this likely would influence spatial population structure and be important for delineating management units. Previous studies identified that spawning groups genetically differed among locations across fine geographic scales, but it was unknown whether these patterns persisted from year to year. We analyzed 15 nuclear DNA microsatellite loci from Yellow Perch spawning at six Lake Erie locations in 2009 in reference to two out-groups spawning in Lakes St. Clair and Ontario. Results were compared with a prior study of samples from the same locations that had been collected in various years, ranging from 2001 to 2005. We evaluated consistency for two of the spawning groups across multiple birth-year-cohorts. Results indicated that the levels of genetic diversity were similar across all spawning groups and years. All eight spawning groups genetically differed from one other, with their allelic compositions varying between the two sampling periods. Some variation occurred among individual sampling years and birth-cohorts, with the 2003 cohort being the most distinctive. Sampling groups contained relatively high proportions of full siblings (mean = 18.5%, ranging to 75% for the 2001 birth-cohort spawning at the eastern Lake Erie site), yet inbreeding appeared relatively low. Differences at sampling sites over time did not appear to reflect genetic drift but may instead suggest that spawning groups reproduce in slightly different locations from year to year or perhaps within a given season; this merits examination. Spatial and temporal patterns may reflect kin-group structuring and differential reproductive success, in which strong year-classes dominate spawning groups and impact genetic structure.</t>
-  </si>
-  <si>
-    <t>10.1080/00028487.2014.982260</t>
-  </si>
-  <si>
-    <t>WOS:000376022300013</t>
-  </si>
-  <si>
-    <t>Still here after all these years: the persistence of the Uncompahgre fritillary butterfly</t>
-  </si>
-  <si>
-    <t>The US federally endangered Uncompahgre fritillary butterfly (Boloria acrocnema) lives in isolated alpine habitats of the San Juan Mountains of Colorado, USA. Its apparent extirpation from the type locality and its low genetic diversity raised concern in the late 1980s, thus monitoring for this species has continued and genetic samples were collected in 2008 and 2009 from all but one known site, each on a separate peak. Data for five new microsatellite markers were collected from 316 total specimens, including 26 from wings preserved from 1987 and 1988 seasons. Only three main colonies had high enough sample sizes for adequate analyses. We estimated levels of genetic variability and structure, and effective population size. Despite low demographic numbers at these sites, the species has maintained relatively high heterozygosity ranging from 0.41 to 0.46 at three sites. Allelic richness corrected by sample size ranged from 5.3 to 5.9. Genetic structure assessed with non-spatially explicit methods indicated that despite separation on high mountain peaks, colonies were fairly well mixed, which is surprising for these weak fliers with very short growing and adult flight seasons. Estimates of effective population sizes were low, reflecting the life history and limited habitat range for the species. Comparisons at the site with historic and modern specimens revealed a consistent pattern in genetic indices. Our data suggest that the three focal butterfly colonies exist as a metapopulation that persists due to low-level migration between sites and temporal leakage via flexibility in development time in this biennial species.</t>
-  </si>
-  <si>
-    <t>10.1007/s10841-016-9867-9</t>
-  </si>
-  <si>
-    <t>WOS:000179492800006</t>
-  </si>
-  <si>
-    <t>Metapopulation structure of the specialized herbivore Macrosiphoniella tanacetaria (Homoptera, Aphididae)</t>
-  </si>
-  <si>
-    <t>We investigated population dynamics, genetic diversity and spatial structure in the aphid species Macrosiphoniella tanacetaria, a specialist herbivore feeding on tansy, Tanacetum vulgare. Tansy plants (genets) consist of many shoots (ramets), and genets are grouped in sites. Thus, aphids feeding on tansy can cluster at the level of ramets, genets and sites. We studied aphid population dynamics in 1997 and 2001 and found that within sites: (i) at any time, aphids used only a fraction of the available ramets and genets; (ii) at the level of ramets, most aphid colonies survived only one week; (iii) at the level of genets, mean survival time was less than 4 weeks; and (iv) colonization and extinction events occurred throughout the season. We sampled aphids in seven sites in the Alsace region, France (4-45 km apart) and two sites in Germany in 1999 to study genetic structure within and between populations. Genetic analyses using nine microsatellite loci showed that: (i) genotypic variability was high, (ii) none of the populations was in Hardy-Weinberg equilibrium, (iii) heterozygote deficits and linkage disequilibria were frequent, and (iv) all populations were genetically differentiated, even at a small geographical scale. Renewed sampling of the Alsace sites in 2001 showed that three populations had become extinct and significant genetic changes had occurred in the remaining four populations. The frequencies of extinction and colonization events at several spatial scales suggest a hierarchical metapopulation structure for M. tanacetaria. Frequent population turnover and drift are likely causes for the genetic differentiation of M. tanacetaria populations.</t>
-  </si>
-  <si>
-    <t>10.1046/j.1365-294X.2002.01633.x</t>
-  </si>
-  <si>
-    <t>WOS:000391939700003</t>
-  </si>
-  <si>
-    <t>Temporal genetic stability in natural populations of the waterflea Daphnia magna in response to strong selection pressure</t>
-  </si>
-  <si>
-    <t>Studies monitoring changes in genetic diversity and composition through time allow a unique understanding of evolutionary dynamics and persistence of natural populations. However, such studies are often limited to species with short generation times that can be propagated in the laboratory or few exceptional cases in the wild. Species that produce dormant stages provide powerful models for the reconstruction of evolutionary dynamics in the natural environment. A remaining open question is to what extent dormant egg banks are an unbiased representation of populations and hence of the species' evolutionary potential, especially in the presence of strong environmental selection. We address this key question using the water flea Daphnia magna, which produces dormant stages that accumulate in biological archives over time. We assess temporal genetic stability in three biological archives, previously used in resurrection ecology studies showing adaptive evolutionary responses to rapid environmental change. We show that neutral genetic diversity does not decline with the age of the population and it is maintained in the presence of strong selection. In addition, by comparing temporal genetic stability in hatched and unhatched populations from the same biological archive, we show that dormant egg banks can be consulted to obtain a reliable measure of genetic diversity over time, at least in the multidecadal time frame studied here. The stability of neutral genetic diversity through time is likely mediated by the buffering effect of the resting egg bank.</t>
-  </si>
-  <si>
-    <t>10.1111/mec.13907</t>
-  </si>
-  <si>
-    <t>WOS:000281181500007</t>
-  </si>
-  <si>
-    <t>Population genetic structure of dolphinfish (Coryphaena hippurus) in the Gulf of California, using microsatellite loci</t>
-  </si>
-  <si>
-    <t>We assayed genetic variations at five microsatellite loci of dolphinfish captured at five sites in 2005 and eight sites in 2006 to detect genetic population structure of dolphinfish Coryphaena hippurus in the Gulf of California and surrounding waters. Results show high genetic variation, similar to other pelagic fishes with large populations. Pairwise F-ST values and hierarchical AMOVA detected subtle but significant spatial and temporal heterogeneity, mainly in samples of 2005 and some of 2006. However, Bayesian assignment analysis failed to detect genetic differentiation, which was also supported by the Mantel test and gene flow estimates among the sampled sites. This suggests that, despite the slight heterogeneity detected in this region, the dolphinfish forms a single panmictic population with high genetic variation and gene flow. (C) 2010 Elsevier B.V. All rights reserved.</t>
-  </si>
-  <si>
-    <t>10.1016/j.fishres.2010.03.023</t>
-  </si>
-  <si>
-    <t>WOS:000323115800128</t>
-  </si>
-  <si>
-    <t>Genetic Network and Breeding Patterns of a Sicklefin Lemon Shark (Negaprion acutidens) Population in the Society Islands, French Polynesia</t>
-  </si>
-  <si>
-    <t>Human pressures have put many top predator populations at risk of extinction. Recent years have seen alarming declines in sharks worldwide, while their resilience remains poorly understood. Studying the ecology of small populations of marine predators is a priority to better understand their ability to withstand anthropogenic and environmental stressors. In the present study, we monitored a naturally small island population of 40 adult sicklefin lemon sharks in Moorea, French Polynesia over 5 years. We reconstructed the genetic relationships among individuals and determined the population's mating system. The genetic network illustrates that all individuals, except one, are interconnected at least through one first order genetic relationship. While this species developed a clear inbreeding avoidance strategy involving dispersal and migration, the small population size, low number of breeders, and the fragmented environment characterizing these tropical islands, limits its complete effectiveness.</t>
-  </si>
-  <si>
-    <t>10.1371/journal.pone.0073899</t>
-  </si>
-  <si>
-    <t>text is describing population with limited genetic diversity and high vulner. I can not infer any positive or negative biodiversity change here</t>
   </si>
   <si>
     <t>WOS:000487568900003</t>
@@ -7743,1953 +7742,1951 @@
       <c r="I1" s="17"/>
     </row>
     <row r="2">
-      <c r="A2" s="18" t="s">
+      <c r="A2" s="18">
+        <v>1.0</v>
+      </c>
+      <c r="B2" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="C2" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="C2" s="18" t="s">
+      <c r="D2" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="D2" s="18" t="s">
+      <c r="E2" s="19" t="s">
         <v>25</v>
-      </c>
-      <c r="E2" s="19" t="s">
-        <v>26</v>
       </c>
       <c r="F2" s="20"/>
       <c r="G2" s="21" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="H2" s="22" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" s="18">
+        <v>3.0</v>
+      </c>
+      <c r="B3" s="18" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="18" t="s">
+      <c r="C3" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="B3" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C3" s="18" t="s">
-        <v>31</v>
-      </c>
       <c r="D3" s="18" t="s">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="E3" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F3" s="20"/>
       <c r="G3" s="21" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="H3" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="18" t="s">
-        <v>34</v>
+      <c r="A4" s="18">
+        <v>4.0</v>
       </c>
       <c r="B4" s="18" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D4" s="18" t="s">
-        <v>37</v>
+        <v>24</v>
       </c>
       <c r="E4" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="20"/>
       <c r="G4" s="21" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
       <c r="H4" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="18" t="s">
-        <v>39</v>
+      <c r="A5" s="18">
+        <v>5.0</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="D5" s="18" t="s">
-        <v>42</v>
+        <v>24</v>
       </c>
       <c r="E5" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F5" s="20"/>
       <c r="G5" s="21" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="H5" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="18" t="s">
-        <v>44</v>
+      <c r="A6" s="18">
+        <v>6.0</v>
       </c>
       <c r="B6" s="18" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="C6" s="18" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D6" s="18" t="s">
-        <v>47</v>
+        <v>24</v>
       </c>
       <c r="E6" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F6" s="20"/>
       <c r="G6" s="21" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="H6" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="18" t="s">
-        <v>49</v>
+      <c r="A7" s="18">
+        <v>9.0</v>
       </c>
       <c r="B7" s="18" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C7" s="18" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="D7" s="18" t="s">
-        <v>52</v>
+        <v>24</v>
       </c>
       <c r="E7" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F7" s="20"/>
       <c r="G7" s="21" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="H7" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="18" t="s">
-        <v>54</v>
+      <c r="A8" s="18">
+        <v>12.0</v>
       </c>
       <c r="B8" s="18" t="s">
-        <v>55</v>
+        <v>43</v>
       </c>
       <c r="C8" s="18" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="D8" s="18" t="s">
-        <v>57</v>
+        <v>24</v>
       </c>
       <c r="E8" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F8" s="20"/>
       <c r="G8" s="21" t="s">
-        <v>58</v>
+        <v>45</v>
       </c>
       <c r="H8" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="18" t="s">
-        <v>59</v>
+      <c r="A9" s="18">
+        <v>14.0</v>
       </c>
       <c r="B9" s="18" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="D9" s="18" t="s">
-        <v>62</v>
+        <v>24</v>
       </c>
       <c r="E9" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="20"/>
+        <v>25</v>
+      </c>
+      <c r="F9" s="21"/>
       <c r="G9" s="21" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="H9" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="18" t="s">
-        <v>64</v>
+      <c r="A10" s="18">
+        <v>15.0</v>
       </c>
       <c r="B10" s="18" t="s">
-        <v>65</v>
+        <v>49</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>66</v>
+        <v>50</v>
       </c>
       <c r="D10" s="18" t="s">
-        <v>67</v>
+        <v>24</v>
       </c>
       <c r="E10" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F10" s="20"/>
       <c r="G10" s="21" t="s">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="H10" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="18" t="s">
-        <v>69</v>
+      <c r="A11" s="18">
+        <v>16.0</v>
       </c>
       <c r="B11" s="18" t="s">
-        <v>70</v>
+        <v>52</v>
       </c>
       <c r="C11" s="18" t="s">
-        <v>71</v>
+        <v>53</v>
       </c>
       <c r="D11" s="18" t="s">
-        <v>72</v>
+        <v>24</v>
       </c>
       <c r="E11" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F11" s="20"/>
       <c r="G11" s="21" t="s">
-        <v>73</v>
+        <v>54</v>
       </c>
       <c r="H11" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="18" t="s">
-        <v>74</v>
+      <c r="A12" s="18">
+        <v>19.0</v>
       </c>
       <c r="B12" s="18" t="s">
-        <v>75</v>
+        <v>55</v>
       </c>
       <c r="C12" s="18" t="s">
-        <v>76</v>
+        <v>56</v>
       </c>
       <c r="D12" s="18" t="s">
-        <v>77</v>
+        <v>24</v>
       </c>
       <c r="E12" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F12" s="20"/>
       <c r="G12" s="21" t="s">
-        <v>78</v>
+        <v>57</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="18" t="s">
-        <v>79</v>
+      <c r="A13" s="18">
+        <v>20.0</v>
       </c>
       <c r="B13" s="18" t="s">
-        <v>80</v>
+        <v>58</v>
       </c>
       <c r="C13" s="18" t="s">
-        <v>81</v>
+        <v>59</v>
       </c>
       <c r="D13" s="18" t="s">
-        <v>82</v>
+        <v>24</v>
       </c>
       <c r="E13" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F13" s="20"/>
       <c r="G13" s="21" t="s">
-        <v>83</v>
+        <v>60</v>
       </c>
       <c r="H13" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="18" t="s">
-        <v>84</v>
+      <c r="A14" s="18">
+        <v>21.0</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>85</v>
+        <v>61</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>86</v>
+        <v>62</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>87</v>
+        <v>24</v>
       </c>
       <c r="E14" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F14" s="20"/>
       <c r="G14" s="21" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="H14" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="18" t="s">
-        <v>89</v>
+      <c r="A15" s="18">
+        <v>22.0</v>
       </c>
       <c r="B15" s="18" t="s">
-        <v>90</v>
+        <v>64</v>
       </c>
       <c r="C15" s="18" t="s">
-        <v>91</v>
+        <v>65</v>
       </c>
       <c r="D15" s="18" t="s">
-        <v>92</v>
+        <v>24</v>
       </c>
       <c r="E15" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F15" s="20"/>
       <c r="G15" s="21" t="s">
-        <v>93</v>
+        <v>66</v>
       </c>
       <c r="H15" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="18" t="s">
-        <v>94</v>
+      <c r="A16" s="18">
+        <v>23.0</v>
       </c>
       <c r="B16" s="18" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="C16" s="18" t="s">
-        <v>96</v>
+        <v>68</v>
       </c>
       <c r="D16" s="18" t="s">
-        <v>97</v>
+        <v>24</v>
       </c>
       <c r="E16" s="19" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F16" s="20"/>
       <c r="G16" s="21" t="s">
-        <v>98</v>
+        <v>69</v>
       </c>
       <c r="H16" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="18" t="s">
-        <v>99</v>
+      <c r="A17" s="18">
+        <v>25.0</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="C17" s="18" t="s">
-        <v>101</v>
+        <v>71</v>
       </c>
       <c r="D17" s="18" t="s">
-        <v>102</v>
+        <v>24</v>
       </c>
       <c r="E17" s="19" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="F17" s="20"/>
       <c r="G17" s="21" t="s">
-        <v>104</v>
+        <v>72</v>
       </c>
       <c r="H17" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="18" t="s">
-        <v>105</v>
+      <c r="A18" s="18">
+        <v>27.0</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="E18" s="19" t="s">
-        <v>103</v>
+        <v>25</v>
       </c>
       <c r="F18" s="20"/>
       <c r="G18" s="21" t="s">
-        <v>109</v>
+        <v>75</v>
       </c>
       <c r="H18" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="18" t="s">
-        <v>110</v>
+        <v>76</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>111</v>
+        <v>77</v>
       </c>
       <c r="C19" s="18" t="s">
-        <v>112</v>
+        <v>78</v>
       </c>
       <c r="D19" s="18" t="s">
-        <v>113</v>
+        <v>79</v>
       </c>
       <c r="E19" s="19" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F19" s="20"/>
       <c r="G19" s="21" t="s">
-        <v>114</v>
+        <v>81</v>
       </c>
       <c r="H19" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="18" t="s">
-        <v>115</v>
+        <v>82</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>116</v>
+        <v>83</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>117</v>
+        <v>84</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>118</v>
+        <v>85</v>
       </c>
       <c r="E20" s="19" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="F20" s="20"/>
       <c r="G20" s="21" t="s">
-        <v>119</v>
+        <v>87</v>
       </c>
       <c r="H20" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="18" t="s">
-        <v>120</v>
+        <v>88</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>121</v>
+        <v>89</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>122</v>
+        <v>90</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>123</v>
+        <v>91</v>
       </c>
       <c r="E21" s="19" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F21" s="20"/>
       <c r="G21" s="21" t="s">
-        <v>124</v>
+        <v>93</v>
       </c>
       <c r="H21" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="18" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="B22" s="18" t="s">
-        <v>126</v>
+        <v>95</v>
       </c>
       <c r="C22" s="18" t="s">
-        <v>127</v>
+        <v>96</v>
       </c>
       <c r="D22" s="18" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="E22" s="19" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="F22" s="20"/>
       <c r="G22" s="21" t="s">
-        <v>129</v>
+        <v>98</v>
       </c>
       <c r="H22" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I22" s="23"/>
+        <v>27</v>
+      </c>
       <c r="J22" s="23"/>
       <c r="K22" s="23"/>
     </row>
     <row r="23">
       <c r="A23" s="18" t="s">
-        <v>130</v>
+        <v>99</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>131</v>
+        <v>100</v>
       </c>
       <c r="C23" s="18" t="s">
-        <v>132</v>
+        <v>101</v>
       </c>
       <c r="D23" s="18" t="s">
-        <v>133</v>
+        <v>102</v>
       </c>
       <c r="E23" s="19" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="F23" s="20"/>
       <c r="G23" s="21" t="s">
-        <v>134</v>
+        <v>103</v>
       </c>
       <c r="H23" s="22" t="s">
-        <v>28</v>
-      </c>
-      <c r="I23" s="23"/>
+        <v>27</v>
+      </c>
       <c r="J23" s="23"/>
       <c r="K23" s="23"/>
     </row>
     <row r="24">
       <c r="A24" s="18" t="s">
-        <v>135</v>
+        <v>104</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>136</v>
+        <v>105</v>
       </c>
       <c r="C24" s="18" t="s">
-        <v>137</v>
+        <v>106</v>
       </c>
       <c r="D24" s="18" t="s">
-        <v>138</v>
+        <v>107</v>
       </c>
       <c r="E24" s="19" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F24" s="20"/>
       <c r="G24" s="21" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="H24" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="18" t="s">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="E25" s="19" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F25" s="20"/>
       <c r="G25" s="21" t="s">
-        <v>144</v>
+        <v>114</v>
       </c>
       <c r="H25" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="18" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="B26" s="18" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="C26" s="18" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="D26" s="18" t="s">
-        <v>148</v>
+        <v>118</v>
       </c>
       <c r="E26" s="19" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="F26" s="20"/>
       <c r="G26" s="21" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="H26" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="18" t="s">
-        <v>150</v>
+        <v>120</v>
       </c>
       <c r="B27" s="18" t="s">
-        <v>151</v>
+        <v>121</v>
       </c>
       <c r="C27" s="18" t="s">
-        <v>152</v>
+        <v>122</v>
       </c>
       <c r="D27" s="18" t="s">
-        <v>153</v>
+        <v>123</v>
       </c>
       <c r="E27" s="19" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="F27" s="20"/>
       <c r="G27" s="21" t="s">
-        <v>154</v>
+        <v>124</v>
       </c>
       <c r="H27" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="18" t="s">
-        <v>155</v>
+        <v>125</v>
       </c>
       <c r="B28" s="18" t="s">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="C28" s="18" t="s">
-        <v>157</v>
+        <v>127</v>
       </c>
       <c r="D28" s="18" t="s">
-        <v>158</v>
+        <v>128</v>
       </c>
       <c r="E28" s="19" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F28" s="20"/>
       <c r="G28" s="21" t="s">
-        <v>159</v>
+        <v>129</v>
       </c>
       <c r="H28" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="18" t="s">
-        <v>160</v>
+        <v>130</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>161</v>
+        <v>131</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>162</v>
+        <v>132</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="E29" s="19" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="F29" s="20"/>
       <c r="G29" s="21" t="s">
-        <v>164</v>
+        <v>134</v>
       </c>
       <c r="H29" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="18" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>166</v>
+        <v>136</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>167</v>
+        <v>137</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>168</v>
+        <v>138</v>
       </c>
       <c r="E30" s="19" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="F30" s="20"/>
       <c r="G30" s="21" t="s">
-        <v>169</v>
+        <v>139</v>
       </c>
       <c r="H30" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="18" t="s">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>171</v>
+        <v>141</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>172</v>
+        <v>142</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>173</v>
+        <v>143</v>
       </c>
       <c r="E31" s="19" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F31" s="20"/>
       <c r="G31" s="21" t="s">
-        <v>174</v>
+        <v>144</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="18" t="s">
-        <v>175</v>
+        <v>145</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>176</v>
+        <v>146</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>177</v>
+        <v>147</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>178</v>
+        <v>148</v>
       </c>
       <c r="E32" s="19" t="s">
-        <v>103</v>
+        <v>80</v>
       </c>
       <c r="F32" s="20"/>
       <c r="G32" s="21" t="s">
-        <v>179</v>
+        <v>149</v>
       </c>
       <c r="H32" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="18" t="s">
-        <v>180</v>
+        <v>150</v>
       </c>
       <c r="B33" s="18" t="s">
-        <v>181</v>
+        <v>151</v>
       </c>
       <c r="C33" s="18" t="s">
-        <v>182</v>
+        <v>152</v>
       </c>
       <c r="D33" s="18" t="s">
-        <v>183</v>
+        <v>153</v>
       </c>
       <c r="E33" s="19" t="s">
-        <v>103</v>
+        <v>86</v>
       </c>
       <c r="F33" s="20"/>
       <c r="G33" s="21" t="s">
-        <v>184</v>
+        <v>154</v>
       </c>
       <c r="H33" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="18" t="s">
-        <v>185</v>
+        <v>155</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>186</v>
+        <v>156</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>187</v>
+        <v>157</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>188</v>
+        <v>158</v>
       </c>
       <c r="E34" s="19" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F34" s="20"/>
       <c r="G34" s="21" t="s">
-        <v>189</v>
+        <v>159</v>
       </c>
       <c r="H34" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="18" t="s">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="B35" s="18" t="s">
-        <v>191</v>
+        <v>161</v>
       </c>
       <c r="C35" s="18" t="s">
-        <v>192</v>
+        <v>162</v>
       </c>
       <c r="D35" s="18" t="s">
-        <v>193</v>
+        <v>163</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="F35" s="20"/>
       <c r="G35" s="21" t="s">
-        <v>195</v>
+        <v>164</v>
       </c>
       <c r="H35" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="18" t="s">
-        <v>196</v>
+        <v>165</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>197</v>
+        <v>166</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>198</v>
+        <v>167</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>199</v>
+        <v>168</v>
       </c>
       <c r="E36" s="19" t="s">
-        <v>194</v>
+        <v>86</v>
       </c>
       <c r="F36" s="20"/>
       <c r="G36" s="21" t="s">
-        <v>200</v>
+        <v>169</v>
       </c>
       <c r="H36" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="18" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>203</v>
+        <v>172</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>204</v>
+        <v>173</v>
       </c>
       <c r="E37" s="19" t="s">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="F37" s="20"/>
       <c r="G37" s="21" t="s">
-        <v>205</v>
+        <v>174</v>
       </c>
       <c r="H37" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="18" t="s">
-        <v>206</v>
+        <v>175</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>207</v>
+        <v>176</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>208</v>
+        <v>177</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>209</v>
+        <v>178</v>
       </c>
       <c r="E38" s="19" t="s">
-        <v>194</v>
+        <v>86</v>
       </c>
       <c r="F38" s="20"/>
       <c r="G38" s="21" t="s">
-        <v>210</v>
+        <v>179</v>
       </c>
       <c r="H38" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="18" t="s">
-        <v>211</v>
+        <v>180</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>212</v>
+        <v>181</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>213</v>
+        <v>182</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>214</v>
+        <v>183</v>
       </c>
       <c r="E39" s="19" t="s">
-        <v>194</v>
+        <v>86</v>
       </c>
       <c r="F39" s="20"/>
       <c r="G39" s="21" t="s">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="H39" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="18" t="s">
-        <v>216</v>
+        <v>185</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>217</v>
+        <v>186</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>218</v>
+        <v>187</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>219</v>
+        <v>188</v>
       </c>
       <c r="E40" s="19" t="s">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="F40" s="20"/>
       <c r="G40" s="21" t="s">
-        <v>220</v>
+        <v>189</v>
       </c>
       <c r="H40" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="18" t="s">
-        <v>221</v>
+        <v>190</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>222</v>
+        <v>191</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>223</v>
+        <v>192</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>224</v>
+        <v>193</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="F41" s="20"/>
       <c r="G41" s="21" t="s">
-        <v>225</v>
+        <v>194</v>
       </c>
       <c r="H41" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="18" t="s">
-        <v>226</v>
+        <v>195</v>
       </c>
       <c r="B42" s="18" t="s">
-        <v>227</v>
+        <v>196</v>
       </c>
       <c r="C42" s="18" t="s">
-        <v>228</v>
+        <v>197</v>
       </c>
       <c r="D42" s="18" t="s">
-        <v>229</v>
+        <v>198</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>194</v>
+        <v>86</v>
       </c>
       <c r="F42" s="20"/>
       <c r="G42" s="21" t="s">
-        <v>230</v>
+        <v>199</v>
       </c>
       <c r="H42" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="18" t="s">
-        <v>231</v>
+        <v>200</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>232</v>
+        <v>201</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>233</v>
+        <v>202</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>234</v>
+        <v>203</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>194</v>
+        <v>86</v>
       </c>
       <c r="F43" s="20"/>
       <c r="G43" s="21" t="s">
-        <v>235</v>
+        <v>204</v>
       </c>
       <c r="H43" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="18" t="s">
-        <v>236</v>
+        <v>205</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>237</v>
+        <v>206</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>238</v>
+        <v>207</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>239</v>
+        <v>208</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>194</v>
+        <v>86</v>
       </c>
       <c r="F44" s="20"/>
       <c r="G44" s="21" t="s">
-        <v>240</v>
+        <v>209</v>
       </c>
       <c r="H44" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="18" t="s">
-        <v>241</v>
+        <v>210</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>242</v>
+        <v>211</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>243</v>
+        <v>212</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>244</v>
+        <v>213</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>194</v>
+        <v>86</v>
       </c>
       <c r="F45" s="20"/>
       <c r="G45" s="21" t="s">
-        <v>245</v>
+        <v>214</v>
       </c>
       <c r="H45" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="18" t="s">
-        <v>246</v>
+        <v>215</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>247</v>
+        <v>216</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>248</v>
+        <v>217</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>249</v>
+        <v>218</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>194</v>
+        <v>86</v>
       </c>
       <c r="F46" s="20"/>
       <c r="G46" s="21" t="s">
-        <v>250</v>
+        <v>219</v>
       </c>
       <c r="H46" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="18" t="s">
-        <v>251</v>
+        <v>220</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>252</v>
+        <v>221</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>253</v>
+        <v>222</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>254</v>
+        <v>223</v>
       </c>
       <c r="E47" s="19" t="s">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="F47" s="20"/>
       <c r="G47" s="21" t="s">
-        <v>255</v>
+        <v>224</v>
       </c>
       <c r="H47" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="18" t="s">
-        <v>256</v>
+        <v>225</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>257</v>
+        <v>226</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>258</v>
+        <v>227</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>259</v>
+        <v>228</v>
       </c>
       <c r="E48" s="19" t="s">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="F48" s="20"/>
       <c r="G48" s="21" t="s">
-        <v>260</v>
+        <v>229</v>
       </c>
       <c r="H48" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="18" t="s">
-        <v>261</v>
+        <v>230</v>
       </c>
       <c r="B49" s="18" t="s">
-        <v>262</v>
+        <v>231</v>
       </c>
       <c r="C49" s="18" t="s">
-        <v>263</v>
+        <v>232</v>
       </c>
       <c r="D49" s="18" t="s">
-        <v>264</v>
+        <v>233</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>194</v>
+        <v>86</v>
       </c>
       <c r="F49" s="20"/>
       <c r="G49" s="21" t="s">
-        <v>265</v>
+        <v>234</v>
       </c>
       <c r="H49" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="18" t="s">
-        <v>266</v>
+        <v>235</v>
       </c>
       <c r="B50" s="18" t="s">
-        <v>267</v>
+        <v>236</v>
       </c>
       <c r="C50" s="18" t="s">
-        <v>268</v>
+        <v>237</v>
       </c>
       <c r="D50" s="18" t="s">
-        <v>269</v>
+        <v>238</v>
       </c>
       <c r="E50" s="19" t="s">
-        <v>194</v>
+        <v>86</v>
       </c>
       <c r="F50" s="20"/>
       <c r="G50" s="21" t="s">
-        <v>270</v>
+        <v>239</v>
       </c>
       <c r="H50" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="18" t="s">
-        <v>271</v>
+        <v>240</v>
       </c>
       <c r="B51" s="18" t="s">
-        <v>272</v>
+        <v>241</v>
       </c>
       <c r="C51" s="18" t="s">
-        <v>273</v>
+        <v>242</v>
       </c>
       <c r="D51" s="18" t="s">
-        <v>274</v>
+        <v>243</v>
       </c>
       <c r="E51" s="19" t="s">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="F51" s="20"/>
       <c r="G51" s="21" t="s">
-        <v>275</v>
+        <v>244</v>
       </c>
       <c r="H51" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="18" t="s">
-        <v>276</v>
+        <v>245</v>
       </c>
       <c r="B52" s="18" t="s">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="C52" s="18" t="s">
-        <v>278</v>
+        <v>247</v>
       </c>
       <c r="D52" s="18" t="s">
-        <v>279</v>
+        <v>248</v>
       </c>
       <c r="E52" s="19" t="s">
-        <v>194</v>
+        <v>108</v>
       </c>
       <c r="F52" s="20"/>
       <c r="G52" s="21" t="s">
-        <v>280</v>
+        <v>249</v>
       </c>
       <c r="H52" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="18">
-        <v>6.0</v>
+      <c r="A53" s="18" t="s">
+        <v>250</v>
       </c>
       <c r="B53" s="18" t="s">
-        <v>281</v>
+        <v>251</v>
       </c>
       <c r="C53" s="18" t="s">
-        <v>282</v>
+        <v>252</v>
       </c>
       <c r="D53" s="18" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="E53" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="F53" s="20"/>
+        <v>86</v>
+      </c>
+      <c r="F53" s="21"/>
       <c r="G53" s="21" t="s">
-        <v>285</v>
+        <v>254</v>
       </c>
       <c r="H53" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="18">
-        <v>4.0</v>
+      <c r="A54" s="18" t="s">
+        <v>255</v>
       </c>
       <c r="B54" s="18" t="s">
-        <v>286</v>
+        <v>256</v>
       </c>
       <c r="C54" s="18" t="s">
-        <v>287</v>
+        <v>257</v>
       </c>
       <c r="D54" s="18" t="s">
-        <v>283</v>
+        <v>258</v>
       </c>
       <c r="E54" s="19" t="s">
-        <v>284</v>
+        <v>86</v>
       </c>
       <c r="F54" s="20"/>
       <c r="G54" s="21" t="s">
-        <v>288</v>
+        <v>259</v>
       </c>
       <c r="H54" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="18">
-        <v>22.0</v>
+      <c r="A55" s="18" t="s">
+        <v>260</v>
       </c>
       <c r="B55" s="18" t="s">
-        <v>289</v>
+        <v>261</v>
       </c>
       <c r="C55" s="18" t="s">
-        <v>290</v>
+        <v>262</v>
       </c>
       <c r="D55" s="18" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="E55" s="19" t="s">
-        <v>284</v>
+        <v>80</v>
       </c>
       <c r="F55" s="20"/>
       <c r="G55" s="21" t="s">
-        <v>291</v>
+        <v>264</v>
       </c>
       <c r="H55" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="18">
-        <v>12.0</v>
+      <c r="A56" s="18" t="s">
+        <v>265</v>
       </c>
       <c r="B56" s="18" t="s">
-        <v>292</v>
+        <v>266</v>
       </c>
       <c r="C56" s="18" t="s">
-        <v>293</v>
+        <v>267</v>
       </c>
       <c r="D56" s="18" t="s">
-        <v>283</v>
+        <v>268</v>
       </c>
       <c r="E56" s="19" t="s">
-        <v>284</v>
+        <v>108</v>
       </c>
       <c r="F56" s="20"/>
       <c r="G56" s="21" t="s">
-        <v>294</v>
+        <v>269</v>
       </c>
       <c r="H56" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="18">
-        <v>20.0</v>
+      <c r="A57" s="18" t="s">
+        <v>270</v>
       </c>
       <c r="B57" s="18" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="C57" s="18" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="D57" s="18" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="E57" s="19" t="s">
-        <v>284</v>
+        <v>108</v>
       </c>
       <c r="F57" s="20"/>
       <c r="G57" s="21" t="s">
-        <v>297</v>
+        <v>274</v>
       </c>
       <c r="H57" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="18">
-        <v>5.0</v>
+      <c r="A58" s="18" t="s">
+        <v>275</v>
       </c>
       <c r="B58" s="18" t="s">
-        <v>298</v>
+        <v>276</v>
       </c>
       <c r="C58" s="18" t="s">
-        <v>299</v>
+        <v>277</v>
       </c>
       <c r="D58" s="18" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="E58" s="19" t="s">
-        <v>284</v>
+        <v>108</v>
       </c>
       <c r="F58" s="20"/>
       <c r="G58" s="21" t="s">
-        <v>300</v>
+        <v>279</v>
       </c>
       <c r="H58" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="18">
-        <v>16.0</v>
+      <c r="A59" s="18" t="s">
+        <v>280</v>
       </c>
       <c r="B59" s="18" t="s">
-        <v>301</v>
+        <v>281</v>
       </c>
       <c r="C59" s="18" t="s">
-        <v>302</v>
+        <v>282</v>
       </c>
       <c r="D59" s="18" t="s">
         <v>283</v>
       </c>
       <c r="E59" s="19" t="s">
-        <v>284</v>
+        <v>108</v>
       </c>
       <c r="F59" s="20"/>
       <c r="G59" s="21" t="s">
-        <v>303</v>
+        <v>284</v>
       </c>
       <c r="H59" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="18">
-        <v>21.0</v>
+      <c r="A60" s="18" t="s">
+        <v>285</v>
       </c>
       <c r="B60" s="18" t="s">
-        <v>304</v>
+        <v>286</v>
       </c>
       <c r="C60" s="18" t="s">
-        <v>305</v>
+        <v>287</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="E60" s="19" t="s">
-        <v>284</v>
+        <v>80</v>
       </c>
       <c r="F60" s="20"/>
       <c r="G60" s="21" t="s">
-        <v>306</v>
+        <v>289</v>
       </c>
       <c r="H60" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="18">
-        <v>25.0</v>
+      <c r="A61" s="18" t="s">
+        <v>290</v>
       </c>
       <c r="B61" s="18" t="s">
-        <v>307</v>
+        <v>291</v>
       </c>
       <c r="C61" s="18" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="E61" s="19" t="s">
-        <v>284</v>
+        <v>92</v>
       </c>
       <c r="F61" s="20"/>
       <c r="G61" s="21" t="s">
-        <v>309</v>
+        <v>294</v>
       </c>
       <c r="H61" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="18">
-        <v>3.0</v>
+      <c r="A62" s="18" t="s">
+        <v>295</v>
       </c>
       <c r="B62" s="18" t="s">
-        <v>310</v>
+        <v>296</v>
       </c>
       <c r="C62" s="18" t="s">
-        <v>311</v>
+        <v>297</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>283</v>
+        <v>298</v>
       </c>
       <c r="E62" s="19" t="s">
-        <v>284</v>
+        <v>92</v>
       </c>
       <c r="F62" s="20"/>
       <c r="G62" s="21" t="s">
-        <v>312</v>
+        <v>299</v>
       </c>
       <c r="H62" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="18">
-        <v>9.0</v>
+      <c r="A63" s="18" t="s">
+        <v>300</v>
       </c>
       <c r="B63" s="18" t="s">
-        <v>313</v>
+        <v>301</v>
       </c>
       <c r="C63" s="18" t="s">
-        <v>314</v>
+        <v>302</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>283</v>
+        <v>303</v>
       </c>
       <c r="E63" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="F63" s="20"/>
+        <v>92</v>
+      </c>
+      <c r="F63" s="21"/>
       <c r="G63" s="21" t="s">
-        <v>315</v>
+        <v>304</v>
       </c>
       <c r="H63" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="18">
-        <v>19.0</v>
+      <c r="A64" s="18" t="s">
+        <v>305</v>
       </c>
       <c r="B64" s="18" t="s">
-        <v>316</v>
+        <v>306</v>
       </c>
       <c r="C64" s="18" t="s">
-        <v>317</v>
+        <v>307</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>283</v>
+        <v>308</v>
       </c>
       <c r="E64" s="19" t="s">
-        <v>284</v>
+        <v>108</v>
       </c>
       <c r="F64" s="20"/>
       <c r="G64" s="21" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="H64" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="18">
-        <v>1.0</v>
+      <c r="A65" s="18" t="s">
+        <v>310</v>
       </c>
       <c r="B65" s="18" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="C65" s="18" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>283</v>
+        <v>313</v>
       </c>
       <c r="E65" s="19" t="s">
-        <v>284</v>
+        <v>92</v>
       </c>
       <c r="F65" s="20"/>
       <c r="G65" s="21" t="s">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="H65" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="18">
-        <v>15.0</v>
+      <c r="A66" s="18" t="s">
+        <v>315</v>
       </c>
       <c r="B66" s="18" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="C66" s="18" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>283</v>
+        <v>318</v>
       </c>
       <c r="E66" s="19" t="s">
-        <v>284</v>
+        <v>80</v>
       </c>
       <c r="F66" s="20"/>
       <c r="G66" s="21" t="s">
+        <v>319</v>
+      </c>
+      <c r="H66" s="22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="18" t="s">
+        <v>320</v>
+      </c>
+      <c r="B67" s="18" t="s">
+        <v>321</v>
+      </c>
+      <c r="C67" s="18" t="s">
+        <v>322</v>
+      </c>
+      <c r="D67" s="18" t="s">
+        <v>323</v>
+      </c>
+      <c r="E67" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F67" s="21"/>
+      <c r="G67" s="21" t="s">
         <v>324</v>
       </c>
-      <c r="H66" s="22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="18">
-        <v>27.0</v>
-      </c>
-      <c r="B67" s="18" t="s">
+      <c r="H67" s="22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="18" t="s">
         <v>325</v>
       </c>
-      <c r="C67" s="18" t="s">
+      <c r="B68" s="18" t="s">
         <v>326</v>
       </c>
-      <c r="D67" s="18" t="s">
-        <v>283</v>
-      </c>
-      <c r="E67" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="F67" s="20"/>
-      <c r="G67" s="21" t="s">
+      <c r="C68" s="18" t="s">
         <v>327</v>
       </c>
-      <c r="H67" s="22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="18">
-        <v>23.0</v>
-      </c>
-      <c r="B68" s="18" t="s">
+      <c r="D68" s="18" t="s">
         <v>328</v>
       </c>
-      <c r="C68" s="18" t="s">
-        <v>329</v>
-      </c>
-      <c r="D68" s="18" t="s">
-        <v>283</v>
-      </c>
       <c r="E68" s="19" t="s">
-        <v>284</v>
+        <v>80</v>
       </c>
       <c r="F68" s="20"/>
       <c r="G68" s="21" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H68" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="18" t="s">
+        <v>330</v>
+      </c>
+      <c r="B69" s="18" t="s">
         <v>331</v>
       </c>
-      <c r="B69" s="18" t="s">
+      <c r="C69" s="18" t="s">
         <v>332</v>
       </c>
-      <c r="C69" s="18" t="s">
+      <c r="D69" s="18" t="s">
         <v>333</v>
       </c>
-      <c r="D69" s="18" t="s">
-        <v>334</v>
-      </c>
       <c r="E69" s="19" t="s">
-        <v>335</v>
+        <v>108</v>
       </c>
       <c r="F69" s="20"/>
       <c r="G69" s="21" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H69" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="18" t="s">
+        <v>335</v>
+      </c>
+      <c r="B70" s="18" t="s">
+        <v>336</v>
+      </c>
+      <c r="C70" s="18" t="s">
         <v>337</v>
       </c>
-      <c r="B70" s="18" t="s">
+      <c r="D70" s="18" t="s">
         <v>338</v>
       </c>
-      <c r="C70" s="18" t="s">
-        <v>339</v>
-      </c>
-      <c r="D70" s="18" t="s">
-        <v>340</v>
-      </c>
       <c r="E70" s="19" t="s">
-        <v>335</v>
+        <v>108</v>
       </c>
       <c r="F70" s="20"/>
       <c r="G70" s="21" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H70" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="18" t="s">
+        <v>340</v>
+      </c>
+      <c r="B71" s="18" t="s">
+        <v>341</v>
+      </c>
+      <c r="C71" s="18" t="s">
         <v>342</v>
       </c>
-      <c r="B71" s="18" t="s">
+      <c r="D71" s="18" t="s">
         <v>343</v>
       </c>
-      <c r="C71" s="18" t="s">
-        <v>344</v>
-      </c>
-      <c r="D71" s="18" t="s">
-        <v>345</v>
-      </c>
       <c r="E71" s="19" t="s">
-        <v>335</v>
+        <v>108</v>
       </c>
       <c r="F71" s="20"/>
       <c r="G71" s="21" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="H71" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="18" t="s">
+        <v>345</v>
+      </c>
+      <c r="B72" s="18" t="s">
+        <v>346</v>
+      </c>
+      <c r="C72" s="18" t="s">
         <v>347</v>
       </c>
-      <c r="B72" s="18" t="s">
+      <c r="D72" s="18" t="s">
         <v>348</v>
       </c>
-      <c r="C72" s="18" t="s">
-        <v>349</v>
-      </c>
-      <c r="D72" s="18" t="s">
-        <v>350</v>
-      </c>
       <c r="E72" s="19" t="s">
-        <v>335</v>
+        <v>108</v>
       </c>
       <c r="F72" s="20"/>
       <c r="G72" s="21" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="H72" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="18" t="s">
+        <v>350</v>
+      </c>
+      <c r="B73" s="18" t="s">
+        <v>351</v>
+      </c>
+      <c r="C73" s="18" t="s">
         <v>352</v>
       </c>
-      <c r="B73" s="18" t="s">
+      <c r="D73" s="18" t="s">
         <v>353</v>
       </c>
-      <c r="C73" s="18" t="s">
-        <v>354</v>
-      </c>
-      <c r="D73" s="18" t="s">
-        <v>355</v>
-      </c>
       <c r="E73" s="19" t="s">
-        <v>335</v>
+        <v>108</v>
       </c>
       <c r="F73" s="20"/>
       <c r="G73" s="21" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="H73" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="18" t="s">
+        <v>355</v>
+      </c>
+      <c r="B74" s="18" t="s">
+        <v>356</v>
+      </c>
+      <c r="C74" s="18" t="s">
         <v>357</v>
       </c>
-      <c r="B74" s="18" t="s">
+      <c r="D74" s="18" t="s">
         <v>358</v>
       </c>
-      <c r="C74" s="18" t="s">
-        <v>359</v>
-      </c>
-      <c r="D74" s="18" t="s">
-        <v>360</v>
-      </c>
       <c r="E74" s="19" t="s">
-        <v>335</v>
+        <v>108</v>
       </c>
       <c r="F74" s="20"/>
       <c r="G74" s="21" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="H74" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="18" t="s">
+        <v>360</v>
+      </c>
+      <c r="B75" s="18" t="s">
+        <v>361</v>
+      </c>
+      <c r="C75" s="18" t="s">
         <v>362</v>
       </c>
-      <c r="B75" s="18" t="s">
+      <c r="D75" s="18" t="s">
         <v>363</v>
       </c>
-      <c r="C75" s="18" t="s">
-        <v>364</v>
-      </c>
-      <c r="D75" s="18" t="s">
-        <v>365</v>
-      </c>
       <c r="E75" s="19" t="s">
-        <v>26</v>
+        <v>92</v>
       </c>
       <c r="F75" s="20"/>
       <c r="G75" s="21" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="H75" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="18" t="s">
+        <v>365</v>
+      </c>
+      <c r="B76" s="18" t="s">
+        <v>366</v>
+      </c>
+      <c r="C76" s="18" t="s">
         <v>367</v>
       </c>
-      <c r="B76" s="18" t="s">
+      <c r="D76" s="18" t="s">
         <v>368</v>
       </c>
-      <c r="C76" s="18" t="s">
+      <c r="E76" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F76" s="21" t="s">
         <v>369</v>
       </c>
-      <c r="D76" s="18" t="s">
-        <v>370</v>
-      </c>
-      <c r="E76" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F76" s="20"/>
-      <c r="G76" s="21" t="s">
-        <v>371</v>
-      </c>
+      <c r="G76" s="20"/>
       <c r="H76" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="18" t="s">
+        <v>370</v>
+      </c>
+      <c r="B77" s="18" t="s">
+        <v>371</v>
+      </c>
+      <c r="C77" s="18" t="s">
         <v>372</v>
       </c>
-      <c r="B77" s="18" t="s">
+      <c r="D77" s="18" t="s">
         <v>373</v>
       </c>
-      <c r="C77" s="18" t="s">
-        <v>374</v>
-      </c>
-      <c r="D77" s="18" t="s">
-        <v>375</v>
-      </c>
       <c r="E77" s="19" t="s">
-        <v>26</v>
+        <v>80</v>
       </c>
       <c r="F77" s="20"/>
       <c r="G77" s="21" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="H77" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="18" t="s">
+        <v>375</v>
+      </c>
+      <c r="B78" s="18" t="s">
+        <v>376</v>
+      </c>
+      <c r="C78" s="18" t="s">
         <v>377</v>
       </c>
-      <c r="B78" s="18" t="s">
+      <c r="D78" s="18" t="s">
         <v>378</v>
       </c>
-      <c r="C78" s="18" t="s">
+      <c r="E78" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F78" s="20"/>
+      <c r="G78" s="21" t="s">
         <v>379</v>
       </c>
-      <c r="D78" s="18" t="s">
-        <v>380</v>
-      </c>
-      <c r="E78" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="F78" s="21"/>
-      <c r="G78" s="21" t="s">
-        <v>381</v>
-      </c>
       <c r="H78" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="18" t="s">
+        <v>380</v>
+      </c>
+      <c r="B79" s="18" t="s">
+        <v>381</v>
+      </c>
+      <c r="C79" s="18" t="s">
         <v>382</v>
       </c>
-      <c r="B79" s="18" t="s">
+      <c r="D79" s="18" t="s">
         <v>383</v>
       </c>
-      <c r="C79" s="18" t="s">
-        <v>384</v>
-      </c>
-      <c r="D79" s="18" t="s">
-        <v>385</v>
-      </c>
       <c r="E79" s="19" t="s">
-        <v>194</v>
+        <v>80</v>
       </c>
       <c r="F79" s="20"/>
       <c r="G79" s="21" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="H79" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="18" t="s">
+        <v>385</v>
+      </c>
+      <c r="B80" s="18" t="s">
+        <v>386</v>
+      </c>
+      <c r="C80" s="18" t="s">
         <v>387</v>
       </c>
-      <c r="B80" s="18" t="s">
+      <c r="D80" s="18" t="s">
         <v>388</v>
       </c>
-      <c r="C80" s="18" t="s">
+      <c r="E80" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F80" s="21"/>
+      <c r="G80" s="21" t="s">
         <v>389</v>
       </c>
-      <c r="D80" s="18" t="s">
-        <v>390</v>
-      </c>
-      <c r="E80" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F80" s="21" t="s">
-        <v>391</v>
-      </c>
-      <c r="G80" s="20"/>
       <c r="H80" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="18" t="s">
+        <v>390</v>
+      </c>
+      <c r="B81" s="18" t="s">
+        <v>391</v>
+      </c>
+      <c r="C81" s="18" t="s">
         <v>392</v>
       </c>
-      <c r="B81" s="18" t="s">
+      <c r="D81" s="18" t="s">
         <v>393</v>
       </c>
-      <c r="C81" s="18" t="s">
+      <c r="E81" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F81" s="20"/>
+      <c r="G81" s="21" t="s">
         <v>394</v>
       </c>
-      <c r="D81" s="18" t="s">
+      <c r="H81" s="22" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="18" t="s">
         <v>395</v>
       </c>
-      <c r="E81" s="19" t="s">
-        <v>194</v>
-      </c>
-      <c r="F81" s="21"/>
-      <c r="G81" s="21" t="s">
+      <c r="B82" s="18" t="s">
         <v>396</v>
       </c>
-      <c r="H81" s="22" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="18">
-        <v>14.0</v>
-      </c>
-      <c r="B82" s="18" t="s">
+      <c r="C82" s="18" t="s">
         <v>397</v>
       </c>
-      <c r="C82" s="18" t="s">
+      <c r="D82" s="18" t="s">
         <v>398</v>
       </c>
-      <c r="D82" s="18" t="s">
-        <v>283</v>
-      </c>
       <c r="E82" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="F82" s="21"/>
+        <v>80</v>
+      </c>
+      <c r="F82" s="20"/>
       <c r="G82" s="21" t="s">
         <v>399</v>
       </c>
       <c r="H82" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83">
@@ -9706,14 +9703,14 @@
         <v>403</v>
       </c>
       <c r="E83" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="F83" s="21"/>
+        <v>80</v>
+      </c>
+      <c r="F83" s="20"/>
       <c r="G83" s="21" t="s">
         <v>404</v>
       </c>
       <c r="H83" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84">
@@ -9730,350 +9727,350 @@
         <v>408</v>
       </c>
       <c r="E84" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="F84" s="21"/>
+        <v>80</v>
+      </c>
+      <c r="F84" s="20"/>
       <c r="G84" s="21" t="s">
         <v>409</v>
       </c>
       <c r="H84" s="22" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="18" t="s">
+      <c r="A85" s="18">
+        <v>8.0</v>
+      </c>
+      <c r="B85" s="18" t="s">
         <v>410</v>
       </c>
-      <c r="B85" s="18" t="s">
+      <c r="C85" s="18" t="s">
         <v>411</v>
       </c>
-      <c r="C85" s="18" t="s">
+      <c r="D85" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E85" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F85" s="21" t="s">
         <v>412</v>
       </c>
-      <c r="D85" s="18" t="s">
-        <v>413</v>
-      </c>
-      <c r="E85" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F85" s="21" t="s">
+      <c r="G85" s="20"/>
+      <c r="H85" s="22" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="18">
+        <v>24.0</v>
+      </c>
+      <c r="B86" s="18" t="s">
         <v>414</v>
       </c>
-      <c r="G85" s="21"/>
-      <c r="H85" s="22" t="s">
+      <c r="C86" s="18" t="s">
         <v>415</v>
       </c>
-    </row>
-    <row r="86">
-      <c r="A86" s="18" t="s">
+      <c r="D86" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="E86" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="F86" s="21" t="s">
         <v>416</v>
       </c>
-      <c r="B86" s="18" t="s">
-        <v>417</v>
-      </c>
-      <c r="C86" s="18" t="s">
-        <v>418</v>
-      </c>
-      <c r="D86" s="18" t="s">
-        <v>419</v>
-      </c>
-      <c r="E86" s="19" t="s">
-        <v>26</v>
-      </c>
-      <c r="F86" s="21" t="s">
-        <v>420</v>
-      </c>
-      <c r="G86" s="21"/>
+      <c r="G86" s="20"/>
       <c r="H86" s="22" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="18" t="s">
+        <v>417</v>
+      </c>
+      <c r="B87" s="18" t="s">
+        <v>418</v>
+      </c>
+      <c r="C87" s="18" t="s">
+        <v>419</v>
+      </c>
+      <c r="D87" s="18" t="s">
+        <v>420</v>
+      </c>
+      <c r="E87" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F87" s="21" t="s">
         <v>421</v>
       </c>
-      <c r="B87" s="18" t="s">
+      <c r="G87" s="20"/>
+      <c r="H87" s="22" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="18" t="s">
         <v>422</v>
       </c>
-      <c r="C87" s="18" t="s">
+      <c r="B88" s="18" t="s">
         <v>423</v>
       </c>
-      <c r="D87" s="18" t="s">
+      <c r="C88" s="18" t="s">
         <v>424</v>
       </c>
-      <c r="E87" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="F87" s="21" t="s">
+      <c r="D88" s="18" t="s">
         <v>425</v>
       </c>
-      <c r="G87" s="21"/>
-      <c r="H87" s="22" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="18">
-        <v>8.0</v>
-      </c>
-      <c r="B88" s="18" t="s">
+      <c r="E88" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F88" s="21" t="s">
         <v>426</v>
-      </c>
-      <c r="C88" s="18" t="s">
-        <v>427</v>
-      </c>
-      <c r="D88" s="18" t="s">
-        <v>283</v>
-      </c>
-      <c r="E88" s="19" t="s">
-        <v>284</v>
-      </c>
-      <c r="F88" s="21" t="s">
-        <v>428</v>
       </c>
       <c r="G88" s="20"/>
       <c r="H88" s="22" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="18">
-        <v>24.0</v>
+      <c r="A89" s="18" t="s">
+        <v>427</v>
       </c>
       <c r="B89" s="18" t="s">
+        <v>428</v>
+      </c>
+      <c r="C89" s="18" t="s">
         <v>429</v>
       </c>
-      <c r="C89" s="18" t="s">
+      <c r="D89" s="18" t="s">
         <v>430</v>
       </c>
-      <c r="D89" s="18" t="s">
-        <v>283</v>
-      </c>
       <c r="E89" s="19" t="s">
-        <v>284</v>
+        <v>92</v>
       </c>
       <c r="F89" s="21" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
       <c r="G89" s="20"/>
       <c r="H89" s="22" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="18" t="s">
+        <v>431</v>
+      </c>
+      <c r="B90" s="18" t="s">
         <v>432</v>
       </c>
-      <c r="B90" s="18" t="s">
+      <c r="C90" s="18" t="s">
         <v>433</v>
       </c>
-      <c r="C90" s="18" t="s">
+      <c r="D90" s="18" t="s">
         <v>434</v>
       </c>
-      <c r="D90" s="18" t="s">
-        <v>435</v>
-      </c>
       <c r="E90" s="19" t="s">
-        <v>335</v>
+        <v>92</v>
       </c>
       <c r="F90" s="21" t="s">
-        <v>436</v>
+        <v>426</v>
       </c>
       <c r="G90" s="20"/>
       <c r="H90" s="22" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="18" t="s">
+        <v>435</v>
+      </c>
+      <c r="B91" s="18" t="s">
+        <v>436</v>
+      </c>
+      <c r="C91" s="18" t="s">
         <v>437</v>
       </c>
-      <c r="B91" s="18" t="s">
+      <c r="D91" s="18" t="s">
         <v>438</v>
       </c>
-      <c r="C91" s="18" t="s">
+      <c r="E91" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F91" s="21" t="s">
         <v>439</v>
-      </c>
-      <c r="D91" s="18" t="s">
-        <v>440</v>
-      </c>
-      <c r="E91" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="F91" s="21" t="s">
-        <v>436</v>
       </c>
       <c r="G91" s="20"/>
       <c r="H91" s="22" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="18" t="s">
+        <v>440</v>
+      </c>
+      <c r="B92" s="18" t="s">
         <v>441</v>
       </c>
-      <c r="B92" s="18" t="s">
+      <c r="C92" s="18" t="s">
         <v>442</v>
       </c>
-      <c r="C92" s="18" t="s">
+      <c r="D92" s="18" t="s">
         <v>443</v>
       </c>
-      <c r="D92" s="18" t="s">
+      <c r="E92" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F92" s="21" t="s">
         <v>444</v>
       </c>
-      <c r="E92" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="F92" s="21" t="s">
-        <v>445</v>
-      </c>
-      <c r="G92" s="20"/>
+      <c r="G92" s="21"/>
       <c r="H92" s="22" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="18" t="s">
+        <v>445</v>
+      </c>
+      <c r="B93" s="18" t="s">
         <v>446</v>
       </c>
-      <c r="B93" s="18" t="s">
+      <c r="C93" s="18" t="s">
         <v>447</v>
       </c>
-      <c r="C93" s="18" t="s">
+      <c r="D93" s="18" t="s">
         <v>448</v>
       </c>
-      <c r="D93" s="18" t="s">
-        <v>449</v>
-      </c>
       <c r="E93" s="19" t="s">
-        <v>335</v>
+        <v>92</v>
       </c>
       <c r="F93" s="21" t="s">
-        <v>450</v>
+        <v>421</v>
       </c>
       <c r="G93" s="20"/>
       <c r="H93" s="22" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="18" t="s">
+        <v>449</v>
+      </c>
+      <c r="B94" s="18" t="s">
+        <v>450</v>
+      </c>
+      <c r="C94" s="18" t="s">
         <v>451</v>
       </c>
-      <c r="B94" s="18" t="s">
+      <c r="D94" s="18" t="s">
         <v>452</v>
       </c>
-      <c r="C94" s="18" t="s">
+      <c r="E94" s="19" t="s">
+        <v>92</v>
+      </c>
+      <c r="F94" s="21" t="s">
         <v>453</v>
-      </c>
-      <c r="D94" s="18" t="s">
-        <v>454</v>
-      </c>
-      <c r="E94" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="F94" s="21" t="s">
-        <v>445</v>
       </c>
       <c r="G94" s="20"/>
       <c r="H94" s="22" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="18" t="s">
+        <v>454</v>
+      </c>
+      <c r="B95" s="18" t="s">
         <v>455</v>
       </c>
-      <c r="B95" s="18" t="s">
+      <c r="C95" s="18" t="s">
         <v>456</v>
       </c>
-      <c r="C95" s="18" t="s">
+      <c r="D95" s="18" t="s">
         <v>457</v>
       </c>
-      <c r="D95" s="18" t="s">
-        <v>458</v>
-      </c>
       <c r="E95" s="19" t="s">
-        <v>335</v>
+        <v>92</v>
       </c>
       <c r="F95" s="21" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="G95" s="20"/>
       <c r="H95" s="22" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="18" t="s">
+        <v>458</v>
+      </c>
+      <c r="B96" s="18" t="s">
         <v>459</v>
       </c>
-      <c r="B96" s="18" t="s">
+      <c r="C96" s="18" t="s">
         <v>460</v>
       </c>
-      <c r="C96" s="18" t="s">
+      <c r="D96" s="18" t="s">
         <v>461</v>
       </c>
-      <c r="D96" s="18" t="s">
-        <v>462</v>
-      </c>
       <c r="E96" s="19" t="s">
-        <v>335</v>
+        <v>92</v>
       </c>
       <c r="F96" s="21" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="G96" s="20"/>
       <c r="H96" s="22" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="18" t="s">
+        <v>462</v>
+      </c>
+      <c r="B97" s="18" t="s">
         <v>463</v>
       </c>
-      <c r="B97" s="18" t="s">
+      <c r="C97" s="18" t="s">
         <v>464</v>
       </c>
-      <c r="C97" s="18" t="s">
+      <c r="D97" s="18" t="s">
         <v>465</v>
       </c>
-      <c r="D97" s="18" t="s">
-        <v>466</v>
-      </c>
       <c r="E97" s="19" t="s">
-        <v>335</v>
+        <v>92</v>
       </c>
       <c r="F97" s="21" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="G97" s="20"/>
       <c r="H97" s="22" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="18" t="s">
+        <v>466</v>
+      </c>
+      <c r="B98" s="18" t="s">
         <v>467</v>
       </c>
-      <c r="B98" s="18" t="s">
+      <c r="C98" s="18" t="s">
         <v>468</v>
       </c>
-      <c r="C98" s="18" t="s">
+      <c r="D98" s="18" t="s">
         <v>469</v>
       </c>
-      <c r="D98" s="18" t="s">
+      <c r="E98" s="19" t="s">
+        <v>108</v>
+      </c>
+      <c r="F98" s="21" t="s">
         <v>470</v>
       </c>
-      <c r="E98" s="19" t="s">
-        <v>335</v>
-      </c>
-      <c r="F98" s="21" t="s">
-        <v>445</v>
-      </c>
-      <c r="G98" s="20"/>
+      <c r="G98" s="21"/>
       <c r="H98" s="22" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="99">
@@ -10090,14 +10087,14 @@
         <v>474</v>
       </c>
       <c r="E99" s="19" t="s">
-        <v>335</v>
+        <v>92</v>
       </c>
       <c r="F99" s="21" t="s">
-        <v>445</v>
+        <v>426</v>
       </c>
       <c r="G99" s="20"/>
       <c r="H99" s="22" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="100">
@@ -10114,38 +10111,38 @@
         <v>478</v>
       </c>
       <c r="E100" s="19" t="s">
-        <v>335</v>
+        <v>80</v>
       </c>
       <c r="F100" s="21" t="s">
-        <v>445</v>
-      </c>
-      <c r="G100" s="20"/>
+        <v>479</v>
+      </c>
+      <c r="G100" s="21"/>
       <c r="H100" s="22" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="18" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="B101" s="18" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="C101" s="18" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="D101" s="18" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="E101" s="19" t="s">
-        <v>335</v>
+        <v>92</v>
       </c>
       <c r="F101" s="21" t="s">
-        <v>483</v>
+        <v>426</v>
       </c>
       <c r="G101" s="20"/>
       <c r="H101" s="22" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="102">
@@ -14649,10 +14646,10 @@
       <c r="G1001" s="25"/>
     </row>
   </sheetData>
-  <autoFilter ref="$A$1:$H$101">
-    <sortState ref="A1:H101">
+  <autoFilter ref="$A$1:$I$101">
+    <sortState ref="A1:I101">
       <sortCondition ref="H1:H101"/>
-      <sortCondition ref="E1:E101"/>
+      <sortCondition ref="I1:I101"/>
     </sortState>
   </autoFilter>
   <drawing r:id="rId1"/>
@@ -14714,7 +14711,7 @@
         <v>488</v>
       </c>
       <c r="G2" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3">
@@ -14735,7 +14732,7 @@
         <v>492</v>
       </c>
       <c r="G3" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -14756,7 +14753,7 @@
         <v>496</v>
       </c>
       <c r="G4" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="5">
@@ -14777,7 +14774,7 @@
         <v>500</v>
       </c>
       <c r="G5" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="6">
@@ -14798,7 +14795,7 @@
         <v>504</v>
       </c>
       <c r="G6" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="7">
@@ -14819,7 +14816,7 @@
         <v>508</v>
       </c>
       <c r="G7" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="8">
@@ -14840,7 +14837,7 @@
         <v>512</v>
       </c>
       <c r="G8" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
@@ -14861,7 +14858,7 @@
         <v>516</v>
       </c>
       <c r="G9" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="10">
@@ -14882,7 +14879,7 @@
         <v>520</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
@@ -14903,7 +14900,7 @@
         <v>524</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="12">
@@ -14924,7 +14921,7 @@
         <v>528</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="13">
@@ -14945,7 +14942,7 @@
         <v>532</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="14">
@@ -14966,7 +14963,7 @@
         <v>536</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="15">
@@ -14987,7 +14984,7 @@
         <v>540</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="16">
@@ -15008,7 +15005,7 @@
         <v>544</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="17">
@@ -15029,7 +15026,7 @@
         <v>548</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -15050,7 +15047,7 @@
         <v>552</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19">
@@ -15071,7 +15068,7 @@
         <v>556</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="20">
@@ -15092,7 +15089,7 @@
         <v>560</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="21">
@@ -15113,7 +15110,7 @@
         <v>564</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="22">
@@ -15134,7 +15131,7 @@
         <v>568</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="23">
@@ -15155,7 +15152,7 @@
         <v>572</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -15176,7 +15173,7 @@
         <v>576</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="25">
@@ -15197,7 +15194,7 @@
         <v>580</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="26">
@@ -15218,7 +15215,7 @@
         <v>584</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="27">
@@ -15239,7 +15236,7 @@
         <v>588</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="28">
@@ -15260,7 +15257,7 @@
         <v>592</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="29">
@@ -15281,7 +15278,7 @@
         <v>596</v>
       </c>
       <c r="G29" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
@@ -15302,7 +15299,7 @@
         <v>600</v>
       </c>
       <c r="G30" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="31">
@@ -15323,7 +15320,7 @@
         <v>604</v>
       </c>
       <c r="G31" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="32">
@@ -15344,7 +15341,7 @@
         <v>608</v>
       </c>
       <c r="G32" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="33">
@@ -15365,7 +15362,7 @@
         <v>612</v>
       </c>
       <c r="G33" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="34">
@@ -15386,7 +15383,7 @@
         <v>616</v>
       </c>
       <c r="G34" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="35">
@@ -15407,7 +15404,7 @@
         <v>620</v>
       </c>
       <c r="G35" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="36">
@@ -15428,7 +15425,7 @@
         <v>624</v>
       </c>
       <c r="G36" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="37">
@@ -15449,7 +15446,7 @@
         <v>628</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="38">
@@ -15470,7 +15467,7 @@
         <v>632</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="39">
@@ -15491,7 +15488,7 @@
         <v>636</v>
       </c>
       <c r="G39" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="40">
@@ -15512,7 +15509,7 @@
         <v>640</v>
       </c>
       <c r="G40" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="41">
@@ -15533,7 +15530,7 @@
         <v>644</v>
       </c>
       <c r="G41" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="42">
@@ -15554,7 +15551,7 @@
         <v>648</v>
       </c>
       <c r="G42" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="43">
@@ -15575,7 +15572,7 @@
         <v>652</v>
       </c>
       <c r="G43" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="44">
@@ -15596,7 +15593,7 @@
         <v>656</v>
       </c>
       <c r="G44" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="45">
@@ -15617,7 +15614,7 @@
         <v>660</v>
       </c>
       <c r="G45" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="46">
@@ -15638,7 +15635,7 @@
         <v>664</v>
       </c>
       <c r="G46" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="47">
@@ -15659,7 +15656,7 @@
         <v>668</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="48">
@@ -15680,7 +15677,7 @@
         <v>672</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="49">
@@ -15701,7 +15698,7 @@
         <v>676</v>
       </c>
       <c r="G49" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="50">
@@ -15722,7 +15719,7 @@
         <v>680</v>
       </c>
       <c r="G50" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="51">
@@ -15743,7 +15740,7 @@
         <v>684</v>
       </c>
       <c r="G51" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="52">
@@ -15764,7 +15761,7 @@
         <v>688</v>
       </c>
       <c r="G52" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="53">
@@ -15785,7 +15782,7 @@
         <v>692</v>
       </c>
       <c r="G53" s="18" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="54">
@@ -15806,7 +15803,7 @@
         <v>696</v>
       </c>
       <c r="G54" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="55">
@@ -15827,7 +15824,7 @@
         <v>700</v>
       </c>
       <c r="G55" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="56">
@@ -15848,7 +15845,7 @@
         <v>704</v>
       </c>
       <c r="G56" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="57">
@@ -15869,7 +15866,7 @@
         <v>708</v>
       </c>
       <c r="G57" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="58">
@@ -15890,7 +15887,7 @@
         <v>712</v>
       </c>
       <c r="G58" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="59">
@@ -15911,7 +15908,7 @@
         <v>716</v>
       </c>
       <c r="G59" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="60">
@@ -15932,7 +15929,7 @@
         <v>720</v>
       </c>
       <c r="G60" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="61">
@@ -15953,7 +15950,7 @@
         <v>724</v>
       </c>
       <c r="G61" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="62">
@@ -15974,7 +15971,7 @@
         <v>728</v>
       </c>
       <c r="G62" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="63">
@@ -15995,7 +15992,7 @@
         <v>732</v>
       </c>
       <c r="G63" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="64">
@@ -16016,7 +16013,7 @@
         <v>736</v>
       </c>
       <c r="G64" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="65">
@@ -16037,7 +16034,7 @@
         <v>740</v>
       </c>
       <c r="G65" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="66">
@@ -16058,7 +16055,7 @@
         <v>744</v>
       </c>
       <c r="G66" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="67">
@@ -16079,7 +16076,7 @@
         <v>748</v>
       </c>
       <c r="G67" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="68">
@@ -16100,7 +16097,7 @@
         <v>752</v>
       </c>
       <c r="G68" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="69">
@@ -16121,7 +16118,7 @@
         <v>756</v>
       </c>
       <c r="G69" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="70">
@@ -16142,7 +16139,7 @@
         <v>760</v>
       </c>
       <c r="G70" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="I70" s="12" t="s">
         <v>761</v>
@@ -16166,7 +16163,7 @@
         <v>765</v>
       </c>
       <c r="G71" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="72">
@@ -16187,7 +16184,7 @@
         <v>769</v>
       </c>
       <c r="G72" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="73">
@@ -16208,7 +16205,7 @@
         <v>773</v>
       </c>
       <c r="G73" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="74">
@@ -16229,7 +16226,7 @@
         <v>777</v>
       </c>
       <c r="G74" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="75">
@@ -16250,7 +16247,7 @@
         <v>781</v>
       </c>
       <c r="G75" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="76">
@@ -16271,7 +16268,7 @@
         <v>785</v>
       </c>
       <c r="G76" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="77">
@@ -16292,7 +16289,7 @@
         <v>789</v>
       </c>
       <c r="G77" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="78">
@@ -16313,7 +16310,7 @@
         <v>793</v>
       </c>
       <c r="G78" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="79">
@@ -16334,7 +16331,7 @@
         <v>797</v>
       </c>
       <c r="G79" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="80">
@@ -16355,7 +16352,7 @@
         <v>801</v>
       </c>
       <c r="G80" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="81">
@@ -16376,7 +16373,7 @@
         <v>805</v>
       </c>
       <c r="G81" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="82">
@@ -16397,7 +16394,7 @@
         <v>809</v>
       </c>
       <c r="G82" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="83">
@@ -16418,7 +16415,7 @@
         <v>813</v>
       </c>
       <c r="G83" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="84">
@@ -16439,7 +16436,7 @@
         <v>817</v>
       </c>
       <c r="G84" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="85">
@@ -16460,7 +16457,7 @@
         <v>821</v>
       </c>
       <c r="G85" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="86">
@@ -16481,7 +16478,7 @@
         <v>825</v>
       </c>
       <c r="G86" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="87">
@@ -16502,7 +16499,7 @@
         <v>829</v>
       </c>
       <c r="G87" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88">
@@ -16523,7 +16520,7 @@
         <v>833</v>
       </c>
       <c r="G88" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="89">
@@ -16544,7 +16541,7 @@
         <v>837</v>
       </c>
       <c r="G89" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="90">
@@ -16565,7 +16562,7 @@
         <v>841</v>
       </c>
       <c r="G90" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="91">
@@ -16586,7 +16583,7 @@
         <v>845</v>
       </c>
       <c r="G91" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="92">
@@ -16607,7 +16604,7 @@
         <v>849</v>
       </c>
       <c r="G92" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="93">
@@ -16628,7 +16625,7 @@
         <v>853</v>
       </c>
       <c r="G93" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="94">
@@ -16649,7 +16646,7 @@
         <v>857</v>
       </c>
       <c r="G94" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="95">
@@ -16670,7 +16667,7 @@
         <v>861</v>
       </c>
       <c r="G95" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="96">
@@ -16691,7 +16688,7 @@
         <v>865</v>
       </c>
       <c r="G96" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="97">
@@ -16712,7 +16709,7 @@
         <v>869</v>
       </c>
       <c r="G97" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="98">
@@ -16733,7 +16730,7 @@
         <v>873</v>
       </c>
       <c r="G98" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="99">
@@ -16754,7 +16751,7 @@
         <v>877</v>
       </c>
       <c r="G99" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="100">
@@ -16775,7 +16772,7 @@
         <v>881</v>
       </c>
       <c r="G100" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="101">
@@ -16796,7 +16793,7 @@
         <v>885</v>
       </c>
       <c r="G101" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="102">
@@ -16817,7 +16814,7 @@
         <v>889</v>
       </c>
       <c r="G102" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="103">
@@ -16838,7 +16835,7 @@
         <v>893</v>
       </c>
       <c r="G103" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="104">
@@ -16859,7 +16856,7 @@
         <v>897</v>
       </c>
       <c r="G104" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="105">
@@ -16880,7 +16877,7 @@
         <v>901</v>
       </c>
       <c r="G105" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="106">
@@ -16901,7 +16898,7 @@
         <v>905</v>
       </c>
       <c r="G106" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="107">
@@ -16922,7 +16919,7 @@
         <v>909</v>
       </c>
       <c r="G107" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="108">
@@ -16943,7 +16940,7 @@
         <v>913</v>
       </c>
       <c r="G108" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="109">
@@ -16964,7 +16961,7 @@
         <v>917</v>
       </c>
       <c r="G109" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="110">
@@ -16985,7 +16982,7 @@
         <v>921</v>
       </c>
       <c r="G110" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="111">
@@ -17006,7 +17003,7 @@
         <v>925</v>
       </c>
       <c r="G111" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="112">
@@ -17027,7 +17024,7 @@
         <v>929</v>
       </c>
       <c r="G112" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="113">
@@ -17048,7 +17045,7 @@
         <v>933</v>
       </c>
       <c r="G113" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="114">
@@ -17069,7 +17066,7 @@
         <v>937</v>
       </c>
       <c r="G114" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="115">
@@ -17090,7 +17087,7 @@
         <v>941</v>
       </c>
       <c r="G115" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="116">
@@ -17111,7 +17108,7 @@
         <v>945</v>
       </c>
       <c r="G116" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="117">
@@ -17132,7 +17129,7 @@
         <v>949</v>
       </c>
       <c r="G117" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="118">
@@ -17153,7 +17150,7 @@
         <v>953</v>
       </c>
       <c r="G118" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="119">
@@ -17174,7 +17171,7 @@
         <v>957</v>
       </c>
       <c r="G119" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="120">
@@ -17195,7 +17192,7 @@
         <v>961</v>
       </c>
       <c r="G120" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="121">
@@ -17216,7 +17213,7 @@
         <v>965</v>
       </c>
       <c r="G121" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="122">
@@ -17237,7 +17234,7 @@
         <v>969</v>
       </c>
       <c r="G122" s="21" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="123">
@@ -17258,7 +17255,7 @@
       </c>
       <c r="F123" s="21"/>
       <c r="G123" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="124">
@@ -17279,7 +17276,7 @@
       </c>
       <c r="F124" s="20"/>
       <c r="G124" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="125">
@@ -17300,7 +17297,7 @@
       </c>
       <c r="F125" s="21"/>
       <c r="G125" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="126">
@@ -17321,7 +17318,7 @@
       </c>
       <c r="F126" s="21"/>
       <c r="G126" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="127">
@@ -17342,7 +17339,7 @@
       </c>
       <c r="F127" s="21"/>
       <c r="G127" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="128">
@@ -17363,7 +17360,7 @@
       </c>
       <c r="F128" s="20"/>
       <c r="G128" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="129">
@@ -17384,7 +17381,7 @@
       </c>
       <c r="F129" s="20"/>
       <c r="G129" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="130">
@@ -17405,7 +17402,7 @@
       </c>
       <c r="F130" s="21"/>
       <c r="G130" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="131">
@@ -17426,7 +17423,7 @@
       </c>
       <c r="F131" s="21"/>
       <c r="G131" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="132">
@@ -17447,7 +17444,7 @@
       </c>
       <c r="F132" s="21"/>
       <c r="G132" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="133">
@@ -17468,7 +17465,7 @@
       </c>
       <c r="F133" s="21"/>
       <c r="G133" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="134">
@@ -17489,7 +17486,7 @@
       </c>
       <c r="F134" s="21"/>
       <c r="G134" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="135">
@@ -17510,7 +17507,7 @@
       </c>
       <c r="F135" s="20"/>
       <c r="G135" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="136">
@@ -17531,7 +17528,7 @@
       </c>
       <c r="F136" s="21"/>
       <c r="G136" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="137">
@@ -17552,7 +17549,7 @@
       </c>
       <c r="F137" s="21"/>
       <c r="G137" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="138">
@@ -17573,7 +17570,7 @@
       </c>
       <c r="F138" s="21"/>
       <c r="G138" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="139">
@@ -17594,7 +17591,7 @@
       </c>
       <c r="F139" s="21"/>
       <c r="G139" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="140">
@@ -17615,7 +17612,7 @@
       </c>
       <c r="F140" s="21"/>
       <c r="G140" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="141">
@@ -17636,7 +17633,7 @@
       </c>
       <c r="F141" s="21"/>
       <c r="G141" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="142">
@@ -17657,7 +17654,7 @@
       </c>
       <c r="F142" s="21"/>
       <c r="G142" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="143">
@@ -17678,7 +17675,7 @@
       </c>
       <c r="F143" s="21"/>
       <c r="G143" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="144">
@@ -17699,7 +17696,7 @@
       </c>
       <c r="F144" s="21"/>
       <c r="G144" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="145">
@@ -17720,7 +17717,7 @@
       </c>
       <c r="F145" s="21"/>
       <c r="G145" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="146">
@@ -17741,7 +17738,7 @@
       </c>
       <c r="F146" s="21"/>
       <c r="G146" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="147">
@@ -17762,7 +17759,7 @@
       </c>
       <c r="F147" s="21"/>
       <c r="G147" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="148">
@@ -17783,7 +17780,7 @@
       </c>
       <c r="F148" s="21"/>
       <c r="G148" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="149">
@@ -17804,7 +17801,7 @@
       </c>
       <c r="F149" s="21"/>
       <c r="G149" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="150">
@@ -17825,7 +17822,7 @@
       </c>
       <c r="F150" s="21"/>
       <c r="G150" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="151">
@@ -17846,7 +17843,7 @@
       </c>
       <c r="F151" s="21"/>
       <c r="G151" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="152">
@@ -17867,7 +17864,7 @@
       </c>
       <c r="F152" s="21"/>
       <c r="G152" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="153">
@@ -17888,7 +17885,7 @@
       </c>
       <c r="F153" s="21"/>
       <c r="G153" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="154">
@@ -17909,7 +17906,7 @@
       </c>
       <c r="F154" s="21"/>
       <c r="G154" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="155">
@@ -17930,7 +17927,7 @@
       </c>
       <c r="F155" s="21"/>
       <c r="G155" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="156">
@@ -17951,7 +17948,7 @@
       </c>
       <c r="F156" s="21"/>
       <c r="G156" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="157">
@@ -17972,7 +17969,7 @@
       </c>
       <c r="F157" s="21"/>
       <c r="G157" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="158">
@@ -17993,7 +17990,7 @@
       </c>
       <c r="F158" s="21"/>
       <c r="G158" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="159">
@@ -18014,7 +18011,7 @@
       </c>
       <c r="F159" s="21"/>
       <c r="G159" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="160">
@@ -18035,7 +18032,7 @@
       </c>
       <c r="F160" s="21"/>
       <c r="G160" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="161">
@@ -18056,7 +18053,7 @@
       </c>
       <c r="F161" s="21"/>
       <c r="G161" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="162">
@@ -18077,7 +18074,7 @@
       </c>
       <c r="F162" s="21"/>
       <c r="G162" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="163">
@@ -18098,7 +18095,7 @@
       </c>
       <c r="F163" s="21"/>
       <c r="G163" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="164">
@@ -18119,7 +18116,7 @@
       </c>
       <c r="F164" s="21"/>
       <c r="G164" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="165">
@@ -18140,7 +18137,7 @@
       </c>
       <c r="F165" s="21"/>
       <c r="G165" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="166">
@@ -18161,7 +18158,7 @@
       </c>
       <c r="F166" s="21"/>
       <c r="G166" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="167">
@@ -18182,7 +18179,7 @@
       </c>
       <c r="F167" s="21"/>
       <c r="G167" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="168">
@@ -18203,7 +18200,7 @@
       </c>
       <c r="F168" s="21"/>
       <c r="G168" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="169">
@@ -18224,7 +18221,7 @@
       </c>
       <c r="F169" s="21"/>
       <c r="G169" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="170">
@@ -18245,7 +18242,7 @@
       </c>
       <c r="F170" s="21"/>
       <c r="G170" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="171">
@@ -18266,7 +18263,7 @@
       </c>
       <c r="F171" s="21"/>
       <c r="G171" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="172">
@@ -18287,7 +18284,7 @@
       </c>
       <c r="F172" s="21"/>
       <c r="G172" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="173">
@@ -18308,7 +18305,7 @@
       </c>
       <c r="F173" s="21"/>
       <c r="G173" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="174">
@@ -18329,7 +18326,7 @@
       </c>
       <c r="F174" s="21"/>
       <c r="G174" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="175">
@@ -18350,7 +18347,7 @@
       </c>
       <c r="F175" s="21"/>
       <c r="G175" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="176">
@@ -18371,7 +18368,7 @@
       </c>
       <c r="F176" s="21"/>
       <c r="G176" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="177">
@@ -18392,7 +18389,7 @@
       </c>
       <c r="F177" s="21"/>
       <c r="G177" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="178">
@@ -18413,7 +18410,7 @@
       </c>
       <c r="F178" s="21"/>
       <c r="G178" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="179">
@@ -18434,7 +18431,7 @@
       </c>
       <c r="F179" s="21"/>
       <c r="G179" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="180">
@@ -18455,7 +18452,7 @@
       </c>
       <c r="F180" s="21"/>
       <c r="G180" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="181">
@@ -18476,7 +18473,7 @@
       </c>
       <c r="F181" s="21"/>
       <c r="G181" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="182">
@@ -18497,7 +18494,7 @@
       </c>
       <c r="F182" s="21"/>
       <c r="G182" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="183">
@@ -18518,7 +18515,7 @@
       </c>
       <c r="F183" s="21"/>
       <c r="G183" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="184">
@@ -18539,7 +18536,7 @@
       </c>
       <c r="F184" s="21"/>
       <c r="G184" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="185">
@@ -18560,7 +18557,7 @@
       </c>
       <c r="F185" s="21"/>
       <c r="G185" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="186">
@@ -18581,7 +18578,7 @@
       </c>
       <c r="F186" s="21"/>
       <c r="G186" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="187">
@@ -18602,7 +18599,7 @@
       </c>
       <c r="F187" s="21"/>
       <c r="G187" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="188">
@@ -18623,7 +18620,7 @@
       </c>
       <c r="F188" s="21"/>
       <c r="G188" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="189">
@@ -18644,7 +18641,7 @@
       </c>
       <c r="F189" s="21"/>
       <c r="G189" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="190">
@@ -18665,7 +18662,7 @@
       </c>
       <c r="F190" s="21"/>
       <c r="G190" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="191">
@@ -18686,7 +18683,7 @@
       </c>
       <c r="F191" s="21"/>
       <c r="G191" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="192">
@@ -18707,7 +18704,7 @@
       </c>
       <c r="F192" s="21"/>
       <c r="G192" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="193">
@@ -18728,7 +18725,7 @@
       </c>
       <c r="F193" s="21"/>
       <c r="G193" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="194">
@@ -18749,7 +18746,7 @@
       </c>
       <c r="F194" s="21"/>
       <c r="G194" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="195">
@@ -18770,7 +18767,7 @@
       </c>
       <c r="F195" s="21"/>
       <c r="G195" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="196">
@@ -18791,7 +18788,7 @@
       </c>
       <c r="F196" s="21"/>
       <c r="G196" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="197">
@@ -18812,7 +18809,7 @@
       </c>
       <c r="F197" s="21"/>
       <c r="G197" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="198">
@@ -18833,7 +18830,7 @@
       </c>
       <c r="F198" s="21"/>
       <c r="G198" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="199">
@@ -18854,7 +18851,7 @@
       </c>
       <c r="F199" s="21"/>
       <c r="G199" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="200">
@@ -18875,7 +18872,7 @@
       </c>
       <c r="F200" s="21"/>
       <c r="G200" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="201">
@@ -18896,7 +18893,7 @@
       </c>
       <c r="F201" s="21"/>
       <c r="G201" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="202">
@@ -18917,7 +18914,7 @@
       </c>
       <c r="F202" s="21"/>
       <c r="G202" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="203">
@@ -18938,7 +18935,7 @@
       </c>
       <c r="F203" s="21"/>
       <c r="G203" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="204">
@@ -18959,7 +18956,7 @@
       </c>
       <c r="F204" s="21"/>
       <c r="G204" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="205">
@@ -18980,7 +18977,7 @@
       </c>
       <c r="F205" s="21"/>
       <c r="G205" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="206">
@@ -19001,7 +18998,7 @@
       </c>
       <c r="F206" s="21"/>
       <c r="G206" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="207">
@@ -19022,7 +19019,7 @@
       </c>
       <c r="F207" s="21"/>
       <c r="G207" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="208">
@@ -19043,7 +19040,7 @@
       </c>
       <c r="F208" s="21"/>
       <c r="G208" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="209">
@@ -19064,7 +19061,7 @@
       </c>
       <c r="F209" s="21"/>
       <c r="G209" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="210">
@@ -19085,7 +19082,7 @@
       </c>
       <c r="F210" s="21"/>
       <c r="G210" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="211">
@@ -19106,7 +19103,7 @@
       </c>
       <c r="F211" s="21"/>
       <c r="G211" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="212">
@@ -19127,7 +19124,7 @@
       </c>
       <c r="F212" s="21"/>
       <c r="G212" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="213">
@@ -19148,7 +19145,7 @@
       </c>
       <c r="F213" s="21"/>
       <c r="G213" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="214">
@@ -19169,7 +19166,7 @@
       </c>
       <c r="F214" s="21"/>
       <c r="G214" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="215">
@@ -19190,7 +19187,7 @@
       </c>
       <c r="F215" s="21"/>
       <c r="G215" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="216">
@@ -19211,7 +19208,7 @@
       </c>
       <c r="F216" s="21"/>
       <c r="G216" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="217">
@@ -19232,7 +19229,7 @@
       </c>
       <c r="F217" s="21"/>
       <c r="G217" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="218">
@@ -19253,7 +19250,7 @@
       </c>
       <c r="F218" s="21"/>
       <c r="G218" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="219">
@@ -19274,7 +19271,7 @@
       </c>
       <c r="F219" s="21"/>
       <c r="G219" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="220">
@@ -19295,7 +19292,7 @@
       </c>
       <c r="F220" s="21"/>
       <c r="G220" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="221">
@@ -19316,7 +19313,7 @@
       </c>
       <c r="F221" s="21"/>
       <c r="G221" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="222">
@@ -19337,7 +19334,7 @@
       </c>
       <c r="F222" s="21"/>
       <c r="G222" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="223">
@@ -19358,7 +19355,7 @@
       </c>
       <c r="F223" s="21"/>
       <c r="G223" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="224">
@@ -19379,7 +19376,7 @@
       </c>
       <c r="F224" s="21"/>
       <c r="G224" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="225">
@@ -19400,7 +19397,7 @@
       </c>
       <c r="F225" s="21"/>
       <c r="G225" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="226">
@@ -19421,7 +19418,7 @@
       </c>
       <c r="F226" s="21"/>
       <c r="G226" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="227">
@@ -19442,7 +19439,7 @@
       </c>
       <c r="F227" s="21"/>
       <c r="G227" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="228">
@@ -19463,7 +19460,7 @@
       </c>
       <c r="F228" s="21"/>
       <c r="G228" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="229">
@@ -19484,7 +19481,7 @@
       </c>
       <c r="F229" s="21"/>
       <c r="G229" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="230">
@@ -19505,7 +19502,7 @@
       </c>
       <c r="F230" s="21"/>
       <c r="G230" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="231">
@@ -19526,7 +19523,7 @@
       </c>
       <c r="F231" s="21"/>
       <c r="G231" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="232">
@@ -19547,7 +19544,7 @@
       </c>
       <c r="F232" s="21"/>
       <c r="G232" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="233">
@@ -19568,7 +19565,7 @@
       </c>
       <c r="F233" s="21"/>
       <c r="G233" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="234">
@@ -19589,7 +19586,7 @@
       </c>
       <c r="F234" s="21"/>
       <c r="G234" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="235">
@@ -19610,7 +19607,7 @@
       </c>
       <c r="F235" s="21"/>
       <c r="G235" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="236">
@@ -19631,7 +19628,7 @@
       </c>
       <c r="F236" s="21"/>
       <c r="G236" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="237">
@@ -19652,7 +19649,7 @@
       </c>
       <c r="F237" s="21"/>
       <c r="G237" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="238">
@@ -19673,7 +19670,7 @@
       </c>
       <c r="F238" s="21"/>
       <c r="G238" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="239">
@@ -19694,7 +19691,7 @@
       </c>
       <c r="F239" s="21"/>
       <c r="G239" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="240">
@@ -19715,7 +19712,7 @@
       </c>
       <c r="F240" s="21"/>
       <c r="G240" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="241">
@@ -19736,7 +19733,7 @@
       </c>
       <c r="F241" s="21"/>
       <c r="G241" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="242">
@@ -19757,7 +19754,7 @@
       </c>
       <c r="F242" s="21"/>
       <c r="G242" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="243">
@@ -19778,7 +19775,7 @@
       </c>
       <c r="F243" s="21"/>
       <c r="G243" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="244">
@@ -19799,7 +19796,7 @@
       </c>
       <c r="F244" s="21"/>
       <c r="G244" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="245">
@@ -19820,7 +19817,7 @@
       </c>
       <c r="F245" s="21"/>
       <c r="G245" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="246">
@@ -19841,7 +19838,7 @@
       </c>
       <c r="F246" s="21"/>
       <c r="G246" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="247">
@@ -19862,7 +19859,7 @@
       </c>
       <c r="F247" s="21"/>
       <c r="G247" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="248">
@@ -19883,7 +19880,7 @@
       </c>
       <c r="F248" s="21"/>
       <c r="G248" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="249">
@@ -19904,7 +19901,7 @@
       </c>
       <c r="F249" s="21"/>
       <c r="G249" s="18" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="250">
@@ -19925,7 +19922,7 @@
       </c>
       <c r="F250" s="21"/>
       <c r="G250" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="251">
@@ -19946,7 +19943,7 @@
       </c>
       <c r="F251" s="21"/>
       <c r="G251" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="252">
@@ -19967,7 +19964,7 @@
       </c>
       <c r="F252" s="21"/>
       <c r="G252" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="253">
@@ -19988,7 +19985,7 @@
       </c>
       <c r="F253" s="21"/>
       <c r="G253" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="254">
@@ -20009,7 +20006,7 @@
       </c>
       <c r="F254" s="21"/>
       <c r="G254" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="255">
@@ -20030,7 +20027,7 @@
       </c>
       <c r="F255" s="21"/>
       <c r="G255" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="256">
@@ -20051,7 +20048,7 @@
       </c>
       <c r="F256" s="21"/>
       <c r="G256" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="257">
@@ -20072,7 +20069,7 @@
       </c>
       <c r="F257" s="21"/>
       <c r="G257" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="258">
@@ -20093,7 +20090,7 @@
       </c>
       <c r="F258" s="21"/>
       <c r="G258" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="259">
@@ -20114,7 +20111,7 @@
       </c>
       <c r="F259" s="21"/>
       <c r="G259" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="260">
@@ -20135,7 +20132,7 @@
       </c>
       <c r="F260" s="21"/>
       <c r="G260" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="261">
@@ -20156,7 +20153,7 @@
       </c>
       <c r="F261" s="21"/>
       <c r="G261" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="262">
@@ -20177,7 +20174,7 @@
       </c>
       <c r="F262" s="21"/>
       <c r="G262" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="263">
@@ -20198,7 +20195,7 @@
       </c>
       <c r="F263" s="21"/>
       <c r="G263" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="264">
@@ -20219,7 +20216,7 @@
       </c>
       <c r="F264" s="21"/>
       <c r="G264" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="265">
@@ -20240,7 +20237,7 @@
       </c>
       <c r="F265" s="21"/>
       <c r="G265" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="266">
@@ -20261,7 +20258,7 @@
       </c>
       <c r="F266" s="21"/>
       <c r="G266" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="267">
@@ -20282,7 +20279,7 @@
       </c>
       <c r="F267" s="21"/>
       <c r="G267" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="268">
@@ -20303,7 +20300,7 @@
       </c>
       <c r="F268" s="21"/>
       <c r="G268" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="269">
@@ -20324,7 +20321,7 @@
       </c>
       <c r="F269" s="21"/>
       <c r="G269" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="270">
@@ -20345,7 +20342,7 @@
       </c>
       <c r="F270" s="21"/>
       <c r="G270" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="271">
@@ -20366,7 +20363,7 @@
       </c>
       <c r="F271" s="21"/>
       <c r="G271" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="272">
@@ -20387,7 +20384,7 @@
       </c>
       <c r="F272" s="21"/>
       <c r="G272" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="273">
@@ -20408,7 +20405,7 @@
       </c>
       <c r="F273" s="21"/>
       <c r="G273" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="274">
@@ -20429,7 +20426,7 @@
       </c>
       <c r="F274" s="21"/>
       <c r="G274" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="275">
@@ -20450,7 +20447,7 @@
       </c>
       <c r="F275" s="21"/>
       <c r="G275" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="276">
@@ -20471,7 +20468,7 @@
       </c>
       <c r="F276" s="21"/>
       <c r="G276" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="277">
@@ -20492,7 +20489,7 @@
       </c>
       <c r="F277" s="21"/>
       <c r="G277" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="278">
@@ -20513,7 +20510,7 @@
       </c>
       <c r="F278" s="21"/>
       <c r="G278" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="279">
@@ -20534,7 +20531,7 @@
       </c>
       <c r="F279" s="21"/>
       <c r="G279" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="280">
@@ -20555,7 +20552,7 @@
       </c>
       <c r="F280" s="21"/>
       <c r="G280" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="281">
@@ -20576,7 +20573,7 @@
       </c>
       <c r="F281" s="21"/>
       <c r="G281" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="282">
@@ -20597,7 +20594,7 @@
       </c>
       <c r="F282" s="21"/>
       <c r="G282" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="283">
@@ -20618,7 +20615,7 @@
       </c>
       <c r="F283" s="21"/>
       <c r="G283" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="284">
@@ -20639,7 +20636,7 @@
       </c>
       <c r="F284" s="21"/>
       <c r="G284" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="285">
@@ -20660,7 +20657,7 @@
       </c>
       <c r="F285" s="21"/>
       <c r="G285" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="286">
@@ -20681,7 +20678,7 @@
       </c>
       <c r="F286" s="21"/>
       <c r="G286" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="287">
@@ -20702,7 +20699,7 @@
       </c>
       <c r="F287" s="21"/>
       <c r="G287" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="288">
@@ -20723,7 +20720,7 @@
       </c>
       <c r="F288" s="21"/>
       <c r="G288" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="289">
@@ -20744,7 +20741,7 @@
       </c>
       <c r="F289" s="21"/>
       <c r="G289" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="290">
@@ -20765,7 +20762,7 @@
       </c>
       <c r="F290" s="21"/>
       <c r="G290" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="291">
@@ -20786,7 +20783,7 @@
       </c>
       <c r="F291" s="21"/>
       <c r="G291" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="292">
@@ -20807,7 +20804,7 @@
       </c>
       <c r="F292" s="21"/>
       <c r="G292" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="293">
@@ -20828,7 +20825,7 @@
       </c>
       <c r="F293" s="21"/>
       <c r="G293" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="294">
@@ -20849,7 +20846,7 @@
       </c>
       <c r="F294" s="21"/>
       <c r="G294" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="295">
@@ -20870,7 +20867,7 @@
       </c>
       <c r="F295" s="21"/>
       <c r="G295" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="296">
@@ -20891,7 +20888,7 @@
       </c>
       <c r="F296" s="21"/>
       <c r="G296" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="297">
@@ -20912,7 +20909,7 @@
       </c>
       <c r="F297" s="21"/>
       <c r="G297" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="298">
@@ -20933,7 +20930,7 @@
       </c>
       <c r="F298" s="21"/>
       <c r="G298" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="299">
@@ -20954,7 +20951,7 @@
       </c>
       <c r="F299" s="21"/>
       <c r="G299" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="300">
@@ -20975,7 +20972,7 @@
       </c>
       <c r="F300" s="21"/>
       <c r="G300" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="301">
@@ -20996,7 +20993,7 @@
       </c>
       <c r="F301" s="21"/>
       <c r="G301" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="302">
@@ -21017,7 +21014,7 @@
       </c>
       <c r="F302" s="21"/>
       <c r="G302" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="303">
@@ -21038,7 +21035,7 @@
       </c>
       <c r="F303" s="21"/>
       <c r="G303" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="304">
@@ -21059,7 +21056,7 @@
       </c>
       <c r="F304" s="21"/>
       <c r="G304" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="305">
@@ -21080,7 +21077,7 @@
       </c>
       <c r="F305" s="21"/>
       <c r="G305" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="306">
@@ -21101,7 +21098,7 @@
       </c>
       <c r="F306" s="21"/>
       <c r="G306" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="307">
@@ -21122,7 +21119,7 @@
       </c>
       <c r="F307" s="21"/>
       <c r="G307" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="308">
@@ -21143,7 +21140,7 @@
       </c>
       <c r="F308" s="21"/>
       <c r="G308" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="309">
@@ -21164,7 +21161,7 @@
       </c>
       <c r="F309" s="21"/>
       <c r="G309" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="310">
@@ -21185,7 +21182,7 @@
       </c>
       <c r="F310" s="21"/>
       <c r="G310" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="311">
@@ -21206,7 +21203,7 @@
       </c>
       <c r="F311" s="21"/>
       <c r="G311" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="312">
@@ -21227,7 +21224,7 @@
       </c>
       <c r="F312" s="21"/>
       <c r="G312" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="313">
@@ -21248,7 +21245,7 @@
       </c>
       <c r="F313" s="21"/>
       <c r="G313" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="314">
@@ -21269,7 +21266,7 @@
       </c>
       <c r="F314" s="21"/>
       <c r="G314" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="315">
@@ -21290,7 +21287,7 @@
       </c>
       <c r="F315" s="21"/>
       <c r="G315" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="316">
@@ -21311,7 +21308,7 @@
       </c>
       <c r="F316" s="21"/>
       <c r="G316" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="317">
@@ -21332,7 +21329,7 @@
       </c>
       <c r="F317" s="21"/>
       <c r="G317" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="318">
@@ -21353,7 +21350,7 @@
       </c>
       <c r="F318" s="21"/>
       <c r="G318" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="319">
@@ -21374,7 +21371,7 @@
       </c>
       <c r="F319" s="21"/>
       <c r="G319" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="320">
@@ -21395,7 +21392,7 @@
       </c>
       <c r="F320" s="21"/>
       <c r="G320" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="321">
@@ -21416,7 +21413,7 @@
       </c>
       <c r="F321" s="21"/>
       <c r="G321" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="322">
@@ -21437,7 +21434,7 @@
       </c>
       <c r="F322" s="21"/>
       <c r="G322" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="323">
@@ -21458,7 +21455,7 @@
       </c>
       <c r="F323" s="21"/>
       <c r="G323" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="324">
@@ -21479,7 +21476,7 @@
       </c>
       <c r="F324" s="21"/>
       <c r="G324" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="325">
@@ -21500,7 +21497,7 @@
       </c>
       <c r="F325" s="21"/>
       <c r="G325" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="326">
@@ -21521,7 +21518,7 @@
       </c>
       <c r="F326" s="21"/>
       <c r="G326" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="327">
@@ -21542,7 +21539,7 @@
       </c>
       <c r="F327" s="21"/>
       <c r="G327" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="328">
@@ -21563,7 +21560,7 @@
       </c>
       <c r="F328" s="21"/>
       <c r="G328" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="329">
@@ -21584,7 +21581,7 @@
       </c>
       <c r="F329" s="21"/>
       <c r="G329" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="330">
@@ -21605,7 +21602,7 @@
       </c>
       <c r="F330" s="21"/>
       <c r="G330" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="331">
@@ -21626,7 +21623,7 @@
       </c>
       <c r="F331" s="21"/>
       <c r="G331" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="332">
@@ -21647,7 +21644,7 @@
       </c>
       <c r="F332" s="21"/>
       <c r="G332" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="333">
@@ -21668,7 +21665,7 @@
       </c>
       <c r="F333" s="21"/>
       <c r="G333" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="334">
@@ -21689,7 +21686,7 @@
       </c>
       <c r="F334" s="21"/>
       <c r="G334" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="335">
@@ -21710,7 +21707,7 @@
       </c>
       <c r="F335" s="21"/>
       <c r="G335" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="336">
@@ -21731,7 +21728,7 @@
       </c>
       <c r="F336" s="21"/>
       <c r="G336" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="337">
@@ -21752,7 +21749,7 @@
       </c>
       <c r="F337" s="21"/>
       <c r="G337" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="338">
@@ -21773,7 +21770,7 @@
       </c>
       <c r="F338" s="21"/>
       <c r="G338" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="339">
@@ -21794,7 +21791,7 @@
       </c>
       <c r="F339" s="21"/>
       <c r="G339" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="340">
@@ -21815,7 +21812,7 @@
       </c>
       <c r="F340" s="21"/>
       <c r="G340" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="341">
@@ -21836,7 +21833,7 @@
       </c>
       <c r="F341" s="21"/>
       <c r="G341" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="342">
@@ -21857,7 +21854,7 @@
       </c>
       <c r="F342" s="21"/>
       <c r="G342" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="343">
@@ -21878,7 +21875,7 @@
       </c>
       <c r="F343" s="21"/>
       <c r="G343" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="344">
@@ -21899,7 +21896,7 @@
       </c>
       <c r="F344" s="21"/>
       <c r="G344" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="345">
@@ -21920,7 +21917,7 @@
       </c>
       <c r="F345" s="21"/>
       <c r="G345" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="346">
@@ -21941,7 +21938,7 @@
       </c>
       <c r="F346" s="21"/>
       <c r="G346" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="347">
@@ -21962,7 +21959,7 @@
       </c>
       <c r="F347" s="21"/>
       <c r="G347" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="348">
@@ -21983,7 +21980,7 @@
       </c>
       <c r="F348" s="21"/>
       <c r="G348" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="349">
@@ -22004,7 +22001,7 @@
       </c>
       <c r="F349" s="21"/>
       <c r="G349" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="350">
@@ -22025,7 +22022,7 @@
       </c>
       <c r="F350" s="21"/>
       <c r="G350" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="351">
@@ -22046,7 +22043,7 @@
       </c>
       <c r="F351" s="21"/>
       <c r="G351" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="352">
@@ -22067,7 +22064,7 @@
       </c>
       <c r="F352" s="21"/>
       <c r="G352" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="353">
@@ -22088,7 +22085,7 @@
       </c>
       <c r="F353" s="21"/>
       <c r="G353" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="354">
@@ -22109,7 +22106,7 @@
       </c>
       <c r="F354" s="21"/>
       <c r="G354" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="355">
@@ -22130,7 +22127,7 @@
       </c>
       <c r="F355" s="21"/>
       <c r="G355" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="356">
@@ -22151,7 +22148,7 @@
       </c>
       <c r="F356" s="21"/>
       <c r="G356" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="357">
@@ -22172,7 +22169,7 @@
       </c>
       <c r="F357" s="21"/>
       <c r="G357" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="358">
@@ -22193,7 +22190,7 @@
       </c>
       <c r="F358" s="21"/>
       <c r="G358" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="359">
@@ -22214,7 +22211,7 @@
       </c>
       <c r="F359" s="21"/>
       <c r="G359" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="360">
@@ -22235,7 +22232,7 @@
       </c>
       <c r="F360" s="21"/>
       <c r="G360" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="361">
@@ -22256,7 +22253,7 @@
       </c>
       <c r="F361" s="21"/>
       <c r="G361" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="362">
@@ -22277,7 +22274,7 @@
       </c>
       <c r="F362" s="21"/>
       <c r="G362" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="363">
@@ -22298,7 +22295,7 @@
       </c>
       <c r="F363" s="21"/>
       <c r="G363" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="364">
@@ -22319,7 +22316,7 @@
       </c>
       <c r="F364" s="21"/>
       <c r="G364" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="365">
@@ -22340,7 +22337,7 @@
       </c>
       <c r="F365" s="21"/>
       <c r="G365" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="366">
@@ -22361,7 +22358,7 @@
       </c>
       <c r="F366" s="21"/>
       <c r="G366" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="367">
@@ -22382,7 +22379,7 @@
       </c>
       <c r="F367" s="21"/>
       <c r="G367" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="368">
@@ -22403,7 +22400,7 @@
       </c>
       <c r="F368" s="21"/>
       <c r="G368" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="369">
@@ -22424,7 +22421,7 @@
       </c>
       <c r="F369" s="21"/>
       <c r="G369" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="370">
@@ -22445,7 +22442,7 @@
       </c>
       <c r="F370" s="21"/>
       <c r="G370" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="371">
@@ -22466,7 +22463,7 @@
       </c>
       <c r="F371" s="21"/>
       <c r="G371" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="372">
@@ -22487,7 +22484,7 @@
       </c>
       <c r="F372" s="21"/>
       <c r="G372" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="373">
@@ -22508,7 +22505,7 @@
       </c>
       <c r="F373" s="21"/>
       <c r="G373" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="374">
@@ -22529,7 +22526,7 @@
       </c>
       <c r="F374" s="21"/>
       <c r="G374" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="375">
@@ -22550,7 +22547,7 @@
       </c>
       <c r="F375" s="21"/>
       <c r="G375" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="376">
@@ -22571,7 +22568,7 @@
       </c>
       <c r="F376" s="21"/>
       <c r="G376" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="377">
@@ -22592,7 +22589,7 @@
       </c>
       <c r="F377" s="21"/>
       <c r="G377" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="378">
@@ -22613,7 +22610,7 @@
       </c>
       <c r="F378" s="21"/>
       <c r="G378" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="379">
@@ -22634,7 +22631,7 @@
       </c>
       <c r="F379" s="21"/>
       <c r="G379" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="380">
@@ -22655,7 +22652,7 @@
       </c>
       <c r="F380" s="21"/>
       <c r="G380" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="381">
@@ -22676,7 +22673,7 @@
       </c>
       <c r="F381" s="21"/>
       <c r="G381" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="382">
@@ -22697,7 +22694,7 @@
       </c>
       <c r="F382" s="21"/>
       <c r="G382" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="383">
@@ -22718,7 +22715,7 @@
       </c>
       <c r="F383" s="21"/>
       <c r="G383" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="384">
@@ -22739,7 +22736,7 @@
       </c>
       <c r="F384" s="21"/>
       <c r="G384" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="385">
@@ -22760,7 +22757,7 @@
       </c>
       <c r="F385" s="21"/>
       <c r="G385" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="386">
@@ -22781,7 +22778,7 @@
       </c>
       <c r="F386" s="21"/>
       <c r="G386" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="387">
@@ -22802,7 +22799,7 @@
       </c>
       <c r="F387" s="21"/>
       <c r="G387" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="388">
@@ -22823,7 +22820,7 @@
       </c>
       <c r="F388" s="21"/>
       <c r="G388" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="389">
@@ -22844,7 +22841,7 @@
       </c>
       <c r="F389" s="21"/>
       <c r="G389" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="390">
@@ -22865,7 +22862,7 @@
       </c>
       <c r="F390" s="21"/>
       <c r="G390" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="391">
@@ -22886,7 +22883,7 @@
       </c>
       <c r="F391" s="21"/>
       <c r="G391" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="392">
@@ -22907,7 +22904,7 @@
       </c>
       <c r="F392" s="21"/>
       <c r="G392" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="393">
@@ -22928,7 +22925,7 @@
       </c>
       <c r="F393" s="21"/>
       <c r="G393" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="394">
@@ -22949,7 +22946,7 @@
       </c>
       <c r="F394" s="21"/>
       <c r="G394" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="395">
@@ -22970,7 +22967,7 @@
       </c>
       <c r="F395" s="21"/>
       <c r="G395" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="396">
@@ -22991,7 +22988,7 @@
       </c>
       <c r="F396" s="21"/>
       <c r="G396" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="397">
@@ -23012,7 +23009,7 @@
       </c>
       <c r="F397" s="21"/>
       <c r="G397" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="398">
@@ -23033,7 +23030,7 @@
       </c>
       <c r="F398" s="21"/>
       <c r="G398" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="399">
@@ -23054,7 +23051,7 @@
       </c>
       <c r="F399" s="21"/>
       <c r="G399" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="400">
@@ -23075,7 +23072,7 @@
       </c>
       <c r="F400" s="21"/>
       <c r="G400" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="401">
@@ -23096,7 +23093,7 @@
       </c>
       <c r="F401" s="21"/>
       <c r="G401" s="21" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="402">

--- a/data/consistency-check-datasets/screening/annotated_screening_dataset.xlsx
+++ b/data/consistency-check-datasets/screening/annotated_screening_dataset.xlsx
@@ -4,11 +4,11 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Readme" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="train-sample" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="l0-sample" sheetId="2" r:id="rId6"/>
     <sheet state="visible" name="search-sample" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'train-sample'!$A$1:$I$101</definedName>
+    <definedName hidden="1" localSheetId="1" name="_xlnm._FilterDatabase">'l0-sample'!$A$1:$I$101</definedName>
     <definedName hidden="1" localSheetId="2" name="_xlnm._FilterDatabase">'search-sample'!$A$1:$G$401</definedName>
   </definedNames>
   <calcPr/>
@@ -79,7 +79,7 @@
     <t>Purpose in consistency checking</t>
   </si>
   <si>
-    <t>train-sample</t>
+    <t>l0-sample</t>
   </si>
   <si>
     <r>
@@ -110,14 +110,14 @@
         <b/>
         <color theme="1"/>
       </rPr>
-      <t>from the train split</t>
+      <t>from the screening dataset</t>
     </r>
     <r>
       <rPr>
         <rFont val="Arial"/>
         <color theme="1"/>
       </rPr>
-      <t xml:space="preserve"> of the screening dataset was drawn and manually coded after reading titles and abstracts. 
+      <t xml:space="preserve"> was drawn and manually coded after reading titles and abstracts. 
 In their original source, each of these records was adopted from a previously published review, where it had been read in full and marked "Eligible" by the review authors. Here, we re-read the titles and abstracts of these records in line with our eligibility criteria and relabelled them to measure consistency.
 </t>
     </r>
@@ -7695,7 +7695,7 @@
     <mergeCell ref="H11:K11"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink display="train-sample" location="'train-sample'!A1" ref="B10"/>
+    <hyperlink display="l0-sample" location="'l0-sample'!A1" ref="B10"/>
     <hyperlink display="search-sample" location="'search-sample'!A1" ref="B11"/>
   </hyperlinks>
   <drawing r:id="rId1"/>
